--- a/docs/test_plan/I3C_Testplan.xlsx
+++ b/docs/test_plan/I3C_Testplan.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="817">
   <si>
     <t xml:space="preserve">Category</t>
   </si>
@@ -59,7 +59,7 @@
 Stimulus / Actions: Read `HC_CONTROL`, `HC_STATUS`, all timing registers, `QUEUE_STATUS`, and DAT[0..15].</t>
   </si>
   <si>
-    <t xml:space="preserve">Enable is 0; FSM idle/status reflects idle; queue flags show empty; DAT entries are 0; timing defaults match RTL.</t>
+    <t xml:space="preserve">Enable is 0; FSM idle/status reflects idle; queue flags show empty; DAT entries are 0; timing defaults match the CSR/module specification.</t>
   </si>
   <si>
     <t xml:space="preserve">High</t>
@@ -380,7 +380,7 @@
 Stimulus / Actions: Instantiate `sync_fifo` with non-power-of-two depth in a negative compile test.</t>
   </si>
   <si>
-    <t xml:space="preserve">Elaboration fatal/assertion occurs as implemented.</t>
+    <t xml:space="preserve">Elaboration fails with the documented parameter-check fatal/assertion required by the FIFO contract.</t>
   </si>
   <si>
     <t xml:space="preserve">Low</t>
@@ -600,7 +600,7 @@
 Stimulus / Actions: Observe `sel_od_pp_o` through address, ACK, data, T-bit, START/STOP.</t>
   </si>
   <si>
-    <t xml:space="preserve">OD is used for START/address/ACK/STOP and ENTDAA; PP is used only for implemented I3C SDR data phases.</t>
+    <t xml:space="preserve">OD is used for START/address/ACK/STOP and ENTDAA; PP is used only for in-scope MIPI I3C SDR data phases.</t>
   </si>
   <si>
     <t xml:space="preserve">`controller_active`, `flow_active`, `i3c_phy`</t>
@@ -612,23 +612,23 @@
     <t xml:space="preserve">BUS_011</t>
   </si>
   <si>
-    <t xml:space="preserve">Document current pad model limitation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`tb_pad_model_limit_check`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Top-level UVM TB.
-Stimulus / Actions: Observe bus while `sel_od_pp_o` is active.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test records that `tb_i3c_top` models DUT pins as open-drain and leaves `sel_od_pp_o` unconnected; true pad-level PP verification needs TB enhancement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`tb_i3c_top`, `i3c_phy`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_tb_limitation`</t>
+    <t xml:space="preserve">Verify enhanced TB pad-model wiring for SDA drive/release and OD/PP visibility.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`tb_pad_model_odpp_wiring`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: Top-level UVM TB with `sda_oe_o` and `sel_od_pp_o` connected.
+Stimulus / Actions: Observe `sda_oe_o`, `sda_o`, `sel_od_pp_o`, and `sda_bus` during existing I3C write/read traffic; later extend with a dedicated OD/PP pad vseq.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`tb_i3c_top` drives SDA only when `sda_oe_o=1`, releases SDA when `sda_oe_o=0`, and exposes DUT pad signals through `i3c_if`; existing smoke/write/read regressions show no SDA contention. Dedicated phase-level PP checks remain future work.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`tb_i3c_top`, `i3c_if`, `i3c_phy`, `i3c_controller_top`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_pad_model`, `cp_sda_oe`, `cp_tb_odpp_visibility`</t>
   </si>
   <si>
     <t xml:space="preserve">I3C SDR Private Write</t>
@@ -637,7 +637,7 @@
     <t xml:space="preserve">SDRW_001</t>
   </si>
   <si>
-    <t xml:space="preserve">Preserve existing write regression.</t>
+    <t xml:space="preserve">Verify baseline 4-byte SDR private write.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_regular_write_4b_existing`</t>
@@ -647,7 +647,7 @@
 Stimulus / Actions: Run `i3c_write_vseq` with TX word `DEAD_BEEF`.</t>
   </si>
   <si>
-    <t xml:space="preserve">Bus write uses dynamic address+W; data byte order is little-endian from TX word; RESP success length 4.</t>
+    <t xml:space="preserve">Bus write uses dynamic address+W; data byte order follows the project TX FIFO packing contract; RESP success length 4.</t>
   </si>
   <si>
     <t xml:space="preserve">Full DUT, UVM scoreboard</t>
@@ -713,7 +713,7 @@
 Stimulus / Actions: Send data bytes with even and odd parity.</t>
   </si>
   <si>
-    <t xml:space="preserve">T-bit equals odd parity generation used by RTL (`~^data_byte`) for every write byte.</t>
+    <t xml:space="preserve">T-bit makes the 8-bit data byte plus T-bit odd parity, equivalent to `~^data_byte`, for every write byte.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `bus_tx_flow`</t>
@@ -769,20 +769,20 @@
     <t xml:space="preserve">SDRW_007</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify no STOP when `toc=0`.</t>
+    <t xml:space="preserve">Verify SDR regular write continuation when `toc=0`.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_write_toc_zero`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: Device ACKs; next command is queued as applicable.
-Stimulus / Actions: Issue write with `toc=0`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESP is produced without STOP only if current RTL/spec defines continuation; otherwise behavior is recorded as a spec gap.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_toc`</t>
+    <t xml:space="preserve">Preconditions: I3C device ACKs; a second SDR regular I3C command is already queued.
+Stimulus / Actions: Queue first write with `toc=0` and second write with `toc=1`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First write completes data/T-bit then emits `Sr` instead of STOP; second command starts after `Sr`; final STOP occurs only after the `toc=1` command; both RESPs report success with matching TID/length.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_toc`, `cp_rstart_continuation`</t>
   </si>
   <si>
     <t xml:space="preserve">SDRW_008</t>
@@ -813,7 +813,7 @@
     <t xml:space="preserve">SDRR_001</t>
   </si>
   <si>
-    <t xml:space="preserve">Preserve existing read regression.</t>
+    <t xml:space="preserve">Verify baseline 4-byte SDR private read.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_regular_read_4b_existing`</t>
@@ -823,7 +823,7 @@
 Stimulus / Actions: Run `i3c_read_vseq`.</t>
   </si>
   <si>
-    <t xml:space="preserve">RX FIFO word is `32'hBEBA_FECA`; RESP success length 4.</t>
+    <t xml:space="preserve">RX FIFO word matches the target bytes packed by the project RX FIFO contract, e.g. `32'hBEBA_FECA` for the existing stimulus; RESP success length 4.</t>
   </si>
   <si>
     <t xml:space="preserve">SDRR_002</t>
@@ -956,7 +956,7 @@
 Stimulus / Actions: Run read where final T-bit is 0.</t>
   </si>
   <si>
-    <t xml:space="preserve">Controller treats T-bit=0 as end/short-read indicator, not as parity error. `Parity` response is not expected in current RTL.</t>
+    <t xml:space="preserve">Per I3C SDR read semantics, T-bit=0 is an end-of-data indicator, not a parity error; response is Success if the requested length is met, otherwise `I3cShortReadErr`.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`</t>
@@ -965,13 +965,35 @@
     <t xml:space="preserve">`cp_read_tbit`, `cp_resp_err`</t>
   </si>
   <si>
+    <t xml:space="preserve">SDRR_009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify SDR regular read continuation when `toc=0`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_read_toc_zero`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: I3C device returns requested read data; a second SDR regular I3C command is already queued.
+Stimulus / Actions: Queue first read with `toc=0` and second write with `toc=1`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First read completes requested data/T-bit then emits `Sr` instead of STOP; second command starts after `Sr`; final STOP occurs only after the `toc=1` command; RX data and both RESPs match expected length/TID.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `scl_generator`, `bus_rx_flow`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_toc`, `cp_rstart_continuation`, `cp_dir_read_to_write`</t>
+  </si>
+  <si>
     <t xml:space="preserve">Immediate Data Transfer</t>
   </si>
   <si>
     <t xml:space="preserve">IMM_001</t>
   </si>
   <si>
-    <t xml:space="preserve">Preserve existing immediate smoke.</t>
+    <t xml:space="preserve">Verify baseline immediate write descriptor flow.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_immediate_write_smoke_existing`</t>
@@ -981,7 +1003,7 @@
 Stimulus / Actions: Run `i3c_smoke_vseq`.</t>
   </si>
   <si>
-    <t xml:space="preserve">Two inline data bytes are transmitted; RESP success.</t>
+    <t xml:space="preserve">Two inline data bytes are transmitted according to descriptor `dtt` and project packing rules; RESP success.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `bus_tx_flow`, UVM</t>
@@ -1015,20 +1037,20 @@
     <t xml:space="preserve">IMM_003</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify immediate STOP control.</t>
+    <t xml:space="preserve">Verify immediate `toc` policy.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_immediate_write_toc`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: Target ACKs.
+    <t xml:space="preserve">Preconditions: Target ACKs; immediate `toc=0` continuation policy is not specified for the current project descriptor set.
 Stimulus / Actions: Repeat immediate command with `toc=1` and `toc=0`.</t>
   </si>
   <si>
-    <t xml:space="preserve">`toc=1` generates STOP; `toc=0` behavior matches RTL/spec or is documented as a gap.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_toc`, `cp_imm`</t>
+    <t xml:space="preserve">`toc=1` generates STOP and success. `toc=0` is a clarification/negative case until the project spec defines immediate continuation; acceptable sign-off behavior must be one specified policy such as reject/abort with error or forced STOP, and the bus must not hang without STOP or `Sr`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_toc`, `cp_imm`, `cp_unsupported_policy`</t>
   </si>
   <si>
     <t xml:space="preserve">IMM_004</t>
@@ -1059,11 +1081,11 @@
     <t xml:space="preserve">`immediate_addr_nack`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: Target NACKs address.
+    <t xml:space="preserve">Preconditions: Target NACKs the address ACK/NACK slot.
 Stimulus / Actions: Issue I3C and I2C immediate writes.</t>
   </si>
   <si>
-    <t xml:space="preserve">No data phase after NACK; RESP error is `AddrHeader`; controller returns idle.</t>
+    <t xml:space="preserve">Controller generates STOP immediately after address NACK; no inline data byte is transmitted; RESP error is `AddrHeader` with length 0.</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_resp_err`, `cross_imm_x_device_type`</t>
@@ -1082,7 +1104,7 @@
 Stimulus / Actions: Issue multi-byte I2C immediate write.</t>
   </si>
   <si>
-    <t xml:space="preserve">RESP error is `Nack`; transfer stops/recover behavior follows RTL/spec.</t>
+    <t xml:space="preserve">Controller generates STOP after data NACK; no later inline data byte is transmitted; RESP error is `Nack`.</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_data_ack`, `cp_resp_err`</t>
@@ -1100,11 +1122,11 @@
     <t xml:space="preserve">`ccc_entdaa_opening_frame`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: AddressAssignment CMD queued; device ACKs broadcast header and CCC.
+    <t xml:space="preserve">Preconditions: AddressAssignment CMD queued; targets ACK the broadcast header.
 Stimulus / Actions: Issue `AddressAssignment` with `cmd=0x07`.</t>
   </si>
   <si>
-    <t xml:space="preserve">Bus shows START, `7'h7E+W`, ACK, `8'h07`, ACK before ENTDAA rounds.</t>
+    <t xml:space="preserve">Bus shows START, `7'h7E+W`, broadcast-header ACK, ENTDAA opcode `8'h07` with T-bit odd parity, then the ENTDAA `7'h7E+R` round sequence.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `bus_tx_flow`, `bus_rx_flow`</t>
@@ -1116,41 +1138,44 @@
     <t xml:space="preserve">CCC_002</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify broadcast ENEC frame generation as implemented.</t>
+    <t xml:space="preserve">Verify broadcast ENEC frame generation.</t>
   </si>
   <si>
     <t xml:space="preserve">`ccc_broadcast_enec_frame`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: Immediate CMD with `cp=1`, `cmd=8'h00`; target ACKs.
-Stimulus / Actions: Send event byte/defining data according to descriptor convention.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bus frame matches current ENEC implementation; any missing defining-byte behavior is recorded as implementation gap.</t>
+    <t xml:space="preserve">Preconditions: Immediate CMD with `cp=1`, `cmd=8'h00`; target ACKs only the broadcast header.
+Stimulus / Actions: Send Target Events byte in `def_or_data_byte1` according to the immediate descriptor convention.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bus shows START, `7'h7E+W` in open-drain, broadcast-header ACK in open-drain, ENEC opcode `8'h00` in push-pull, opcode T-bit `~^8'h00`, Target Events byte in push-pull, event-byte T-bit `~^event_byte`, and STOP. No target ACK is expected after the CCC opcode or event byte.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `i3c_monitor`</t>
   </si>
   <si>
+    <t xml:space="preserve">`cp_ccc_opcode`, `cp_ccc_broadcast`, `cp_odpp_phase`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCC_003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify broadcast DISEC frame generation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`ccc_broadcast_disec_frame`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: Immediate CMD with `cp=1`, `cmd=8'h01`; target ACKs the broadcast header.
+Stimulus / Actions: Send Target Events byte according to the project descriptor convention.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bus frame follows the MIPI broadcast DISEC format: START, `7'h7E+W`, broadcast-header ACK, DISEC opcode `8'h01` with T-bit, Target Events byte with T-bit, then STOP; ENTDAA controller is not activated.</t>
+  </si>
+  <si>
     <t xml:space="preserve">`cp_ccc_opcode`, `cp_ccc_broadcast`</t>
   </si>
   <si>
-    <t xml:space="preserve">CCC_003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify broadcast DISEC frame generation as implemented.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`ccc_broadcast_disec_frame`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Immediate CMD with `cp=1`, `cmd=8'h01`; target ACKs.
-Stimulus / Actions: Send event byte/defining data according to descriptor convention.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bus frame matches current DISEC implementation; no ENTDAA controller activation.</t>
-  </si>
-  <si>
     <t xml:space="preserve">CCC_004</t>
   </si>
   <si>
@@ -1160,11 +1185,11 @@
     <t xml:space="preserve">`ccc_direct_enec_frame`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: DAT dynamic address valid; target ACKs broadcast and direct address.
+    <t xml:space="preserve">Preconditions: DAT dynamic address valid; target ACKs broadcast header and direct address.
 Stimulus / Actions: Immediate CMD with `cp=1`, `cmd=8'h80`, one data byte.</t>
   </si>
   <si>
-    <t xml:space="preserve">Bus shows broadcast header, CCC, Sr, target dynamic address+W, data/T-bit, STOP.</t>
+    <t xml:space="preserve">Bus shows broadcast header, CCC opcode/T-bit, Sr, target dynamic address+W, address ACK, data/T-bit, STOP.</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_ccc_direct`, `cp_rstart`</t>
@@ -1179,11 +1204,11 @@
     <t xml:space="preserve">`ccc_direct_disec_frame`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: DAT dynamic address valid; target ACKs.
+    <t xml:space="preserve">Preconditions: DAT dynamic address valid; target ACKs broadcast header and direct address.
 Stimulus / Actions: Immediate CMD with `cp=1`, `cmd=8'h81`.</t>
   </si>
   <si>
-    <t xml:space="preserve">Direct DISEC frame is emitted; RESP success if all ACKs are received.</t>
+    <t xml:space="preserve">Direct DISEC frame is emitted with CCC opcode/T-bit, Sr, direct address ACK, optional data/T-bit as specified; RESP success if all required address ACKs are received.</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_ccc_opcode`, `cp_ccc_direct`</t>
@@ -1198,11 +1223,11 @@
     <t xml:space="preserve">`ccc_broadcast_header_nack`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: Device NACKs `7'h7E+W` or CCC byte ACK slot.
+    <t xml:space="preserve">Preconditions: Device NACKs `7'h7E+W`.
 Stimulus / Actions: Issue ENEC/DISEC/ENTDAA command.</t>
   </si>
   <si>
-    <t xml:space="preserve">Controller reports an implemented error status or the gap is documented; no hang is allowed for sign-off.</t>
+    <t xml:space="preserve">Controller reports the specified address/header error, generates legal bus recovery, and does not send CCC payload after broadcast-header NACK.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, RESP FIFO</t>
@@ -1220,11 +1245,11 @@
     <t xml:space="preserve">`ccc_direct_target_nack`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: Target ACKs broadcast header and CCC, NACKs direct address.
+    <t xml:space="preserve">Preconditions: Target ACKs broadcast header, observes the direct CCC opcode/T-bit, and NACKs direct address.
 Stimulus / Actions: Issue direct ENEC/DISEC.</t>
   </si>
   <si>
-    <t xml:space="preserve">No direct data byte is sent after address NACK; RESP and bus recovery match RTL/spec.</t>
+    <t xml:space="preserve">No direct data byte is sent after address NACK; RESP and bus recovery match the address/header NACK policy in the project spec.</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_ccc_direct`, `cp_addr_ack`</t>
@@ -1243,7 +1268,7 @@
 Stimulus / Actions: Issue representative unsupported broadcast and direct opcodes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Current RTL lacks explicit opcode validation; expected result is documented behavior or a required `NotSupported` enhancement.</t>
+    <t xml:space="preserve">This is a clarification/negative test until the project spec defines unsupported CCC handling. Required sign-off behavior should be a specified `NotSupported`/error response or software restriction; the controller must not emit an undefined successful CCC frame, corrupt queues, or lock up.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `i3c_pkg`</t>
@@ -1268,7 +1293,7 @@
 Stimulus / Actions: Issue AddressAssignment with `dev_idx=0`, `dev_count=1`.</t>
   </si>
   <si>
-    <t xml:space="preserve">ENTDAA frame completes; assigned address byte uses correct parity; RESP success; RX visibility follows implemented policy.</t>
+    <t xml:space="preserve">ENTDAA frame completes per MIPI sequence; assigned address byte uses correct parity; target ACKs the assignment; RESP success; any software-visible DAA result follows the documented project format.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `entdaa_controller`, `entdaa_fsm`</t>
@@ -1397,7 +1422,7 @@
 Stimulus / Actions: Run successful ENTDAA.</t>
   </si>
   <si>
-    <t xml:space="preserve">Internal captured PID/BCR/DCR match target; software-visible RX data format is verified against RTL or documented as spec gap.</t>
+    <t xml:space="preserve">Captured PID/BCR/DCR match the bits driven by the target in the MIPI ENTDAA order; software-visible RX data is checked only after its project format is specified.</t>
   </si>
   <si>
     <t xml:space="preserve">`entdaa_fsm`, `flow_active`, RX FIFO</t>
@@ -1419,7 +1444,7 @@
 Stimulus / Actions: Run `dev_idx=15`, `dev_count=1`, then `dev_idx=15`, `dev_count&gt;1`.</t>
   </si>
   <si>
-    <t xml:space="preserve">Single entry works; out-of-range case follows current saturation behavior or is documented as SW responsibility.</t>
+    <t xml:space="preserve">Single entry works; out-of-range `dev_idx+dev_count` is a clarification/negative case that must either produce a specified error or be forbidden by a documented software precondition.</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_dat_boundary`</t>
@@ -1438,7 +1463,7 @@
 Stimulus / Actions: Interrupt during PID/BCR/DCR reception.</t>
   </si>
   <si>
-    <t xml:space="preserve">ENTDAA terminates to Done/NoDev path and controller returns idle or gap is documented.</t>
+    <t xml:space="preserve">ENTDAA exits through a specified abort/recovery policy and controller returns to a legal idle/recoverable state; if no policy exists, this is a spec gap and not positive sign-off coverage.</t>
   </si>
   <si>
     <t xml:space="preserve">`entdaa_fsm`, `entdaa_controller`, `bus_monitor`</t>
@@ -1567,7 +1592,7 @@
 Stimulus / Actions: Issue multi-byte write.</t>
   </si>
   <si>
-    <t xml:space="preserve">Transfer stops or recovers according to RTL/spec; RESP error is `Nack`; next legal transfer passes.</t>
+    <t xml:space="preserve">Transfer stops after the NACKed byte per I2C/project error policy; RESP error is `Nack`; next legal transfer passes.</t>
   </si>
   <si>
     <t xml:space="preserve">I2C_006</t>
@@ -1649,7 +1674,7 @@
 Stimulus / Actions: Run I3C write/read, I2C write/read, and direct CCC address phases.</t>
   </si>
   <si>
-    <t xml:space="preserve">RESP error is `AddrHeader` where current RTL supports it; no data phase after address NACK.</t>
+    <t xml:space="preserve">RESP error is `AddrHeader` for every supported command class with an address/header NACK; no data phase occurs after address NACK.</t>
   </si>
   <si>
     <t xml:space="preserve">ERR_003</t>
@@ -1697,7 +1722,7 @@
 Stimulus / Actions: Attempt CRC, Frame, Ovl, HcAborted, NotSupported, Parity scenarios.</t>
   </si>
   <si>
-    <t xml:space="preserve">Current RTL has no production paths for these codes; results are N/A or enhancement requests, not expected positive coverage.</t>
+    <t xml:space="preserve">Error codes outside the specified controller scope are N/A or enhancement requests, not positive coverage; any in-scope error code must have a spec-derived stimulus and expected response.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_pkg`, `flow_active`</t>
@@ -1779,7 +1804,7 @@
 Stimulus / Actions: Assert `HC_CONTROL[1]` while not idle.</t>
   </si>
   <si>
-    <t xml:space="preserve">Current spec says this is undefined; test documents behavior and recommends SW only reset when `FSM_IDLE=1`.</t>
+    <t xml:space="preserve">If the spec leaves this undefined, the test records a spec gap and recommends SW only reset when `FSM_IDLE=1`; it is not positive sign-off coverage until a busy-reset policy is specified.</t>
   </si>
   <si>
     <t xml:space="preserve">`csr_registers`, `hci_queues`, `flow_active`</t>
@@ -1801,7 +1826,7 @@
 Stimulus / Actions: Hold SCL low during transfer.</t>
   </si>
   <si>
-    <t xml:space="preserve">Current design has no complete bus recovery/timeout; test should fail by timeout or document gap.</t>
+    <t xml:space="preserve">If no timeout/recovery requirement is specified in the project scope, this is a documented N/A/gap; it must not be treated as a functional pass merely because the controller waits forever.</t>
   </si>
   <si>
     <t xml:space="preserve">`scl_generator`, `bus_monitor`</t>
@@ -1889,7 +1914,7 @@
 Stimulus / Actions: Inject STOP-like SDA rise while SCL high during DAA or data phase.</t>
   </si>
   <si>
-    <t xml:space="preserve">Implemented modules terminate or test records missing recovery behavior.</t>
+    <t xml:space="preserve">Controller follows a specified abort/recovery policy; if none exists, the test records a spec gap and is not positive sign-off coverage.</t>
   </si>
   <si>
     <t xml:space="preserve">`bus_monitor`, `flow_active`, `entdaa_controller`</t>
@@ -1911,7 +1936,7 @@
 Stimulus / Actions: Queue command while SCL/SDA not both high.</t>
   </si>
   <si>
-    <t xml:space="preserve">Current RTL behavior is documented; if unsupported, SW precondition must require idle bus before command.</t>
+    <t xml:space="preserve">Controller must either wait for the specified Bus Available/Idle condition or reject the command with a specified error/software precondition; observed RTL behavior alone is not a pass criterion.</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_bus_busy_start`</t>
@@ -2364,6 +2389,9 @@
   </si>
   <si>
     <t xml:space="preserve">zero, all-one, alternating A/5, walking-one, random</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_toc`</t>
   </si>
   <si>
     <t xml:space="preserve">0, 1</t>
@@ -3485,7 +3513,7 @@
         <v>194</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>118</v>
+        <v>52</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>195</v>
@@ -4008,39 +4036,39 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="B45" t="s" s="2">
+      <c r="C45" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="C45" t="s" s="2">
+      <c r="D45" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="D45" t="s" s="2">
+      <c r="E45" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="F45" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="E45" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="F45" t="s" s="2">
+      <c r="G45" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="G45" t="s" s="2">
+      <c r="H45" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="I45" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="H45" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I45" t="s" s="2">
+      <c r="J45" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>310</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>19</v>
+        <v>310</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>311</v>
@@ -4093,13 +4121,13 @@
         <v>322</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>160</v>
+        <v>323</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="48">
@@ -4107,31 +4135,31 @@
         <v>19</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D48" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="E48" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="E48" t="s" s="2">
-        <v>325</v>
-      </c>
       <c r="F48" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="49">
@@ -4139,31 +4167,31 @@
         <v>19</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D49" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="E49" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="E49" t="s" s="2">
-        <v>331</v>
-      </c>
       <c r="F49" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>283</v>
+        <v>224</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="50">
@@ -4171,36 +4199,36 @@
         <v>19</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D50" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="E50" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="E50" t="s" s="2">
-        <v>337</v>
-      </c>
       <c r="F50" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>342</v>
+        <v>19</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>343</v>
@@ -4224,15 +4252,15 @@
         <v>16</v>
       </c>
       <c r="I51" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="J51" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>349</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>19</v>
+        <v>349</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>350</v>
@@ -4288,10 +4316,10 @@
         <v>16</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>301</v>
+        <v>362</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
     </row>
     <row r="54">
@@ -4299,31 +4327,31 @@
         <v>19</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F54" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>160</v>
+        <v>301</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="55">
@@ -4331,31 +4359,31 @@
         <v>19</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F55" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>301</v>
+        <v>160</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="56">
@@ -4363,31 +4391,31 @@
         <v>19</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F56" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>379</v>
+        <v>301</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="57">
@@ -4395,31 +4423,31 @@
         <v>19</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D57" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="E57" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="E57" t="s" s="2">
-        <v>382</v>
-      </c>
       <c r="F57" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>301</v>
+        <v>387</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="58">
@@ -4427,36 +4455,36 @@
         <v>19</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F58" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>392</v>
+        <v>301</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>394</v>
+        <v>19</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>395</v>
@@ -4477,7 +4505,7 @@
         <v>399</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>400</v>
@@ -4488,34 +4516,34 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>19</v>
+        <v>402</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D60" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="E60" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="E60" t="s" s="2">
-        <v>403</v>
-      </c>
       <c r="F60" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="61">
@@ -4523,31 +4551,31 @@
         <v>19</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D61" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="E61" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="E61" t="s" s="2">
-        <v>410</v>
-      </c>
       <c r="F61" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="62">
@@ -4555,31 +4583,31 @@
         <v>19</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D62" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="E62" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="E62" t="s" s="2">
-        <v>417</v>
-      </c>
       <c r="F62" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="63">
@@ -4587,31 +4615,31 @@
         <v>19</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D63" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="E63" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="E63" t="s" s="2">
-        <v>424</v>
-      </c>
       <c r="F63" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="64">
@@ -4619,31 +4647,31 @@
         <v>19</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D64" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="E64" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="E64" t="s" s="2">
-        <v>431</v>
-      </c>
       <c r="F64" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>407</v>
+        <v>436</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="65">
@@ -4651,31 +4679,31 @@
         <v>19</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F65" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>441</v>
+        <v>415</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="66">
@@ -4683,31 +4711,31 @@
         <v>19</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D66" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="E66" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="E66" t="s" s="2">
-        <v>444</v>
-      </c>
       <c r="F66" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>421</v>
+        <v>449</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="67">
@@ -4715,31 +4743,31 @@
         <v>19</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F67" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>52</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>454</v>
+        <v>429</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="68">
@@ -4747,25 +4775,25 @@
         <v>19</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D68" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="E68" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="E68" t="s" s="2">
-        <v>457</v>
-      </c>
       <c r="F68" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>461</v>
+        <v>52</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>462</v>
@@ -4776,28 +4804,28 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="B69" t="s" s="2">
+      <c r="C69" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="C69" t="s" s="2">
+      <c r="D69" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="D69" t="s" s="2">
+      <c r="E69" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="F69" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="E69" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="F69" t="s" s="2">
+      <c r="G69" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="G69" t="s" s="2">
+      <c r="H69" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>16</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>470</v>
@@ -4808,34 +4836,34 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>19</v>
+        <v>472</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D70" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="E70" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="E70" t="s" s="2">
-        <v>473</v>
-      </c>
       <c r="F70" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="71">
@@ -4843,31 +4871,31 @@
         <v>19</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D71" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="E71" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="E71" t="s" s="2">
-        <v>480</v>
-      </c>
       <c r="F71" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>264</v>
+        <v>485</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>265</v>
+        <v>486</v>
       </c>
     </row>
     <row r="72">
@@ -4875,31 +4903,31 @@
         <v>19</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F72" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>489</v>
+        <v>265</v>
       </c>
     </row>
     <row r="73">
@@ -4907,31 +4935,31 @@
         <v>19</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F73" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>341</v>
+        <v>497</v>
       </c>
     </row>
     <row r="74">
@@ -4939,31 +4967,31 @@
         <v>19</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="F74" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>500</v>
+        <v>301</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>501</v>
+        <v>348</v>
       </c>
     </row>
     <row r="75">
@@ -4971,36 +4999,36 @@
         <v>19</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D75" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="E75" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="E75" t="s" s="2">
-        <v>503</v>
-      </c>
       <c r="F75" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>509</v>
+        <v>19</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>510</v>
@@ -5021,45 +5049,45 @@
         <v>514</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>379</v>
+        <v>515</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>19</v>
+        <v>517</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E77" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F77" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>301</v>
+        <v>387</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>232</v>
+        <v>523</v>
       </c>
     </row>
     <row r="78">
@@ -5067,22 +5095,22 @@
         <v>19</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="F78" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>16</v>
@@ -5091,7 +5119,7 @@
         <v>301</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>341</v>
+        <v>232</v>
       </c>
     </row>
     <row r="79">
@@ -5099,22 +5127,22 @@
         <v>19</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E79" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F79" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>16</v>
@@ -5123,7 +5151,7 @@
         <v>301</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>271</v>
+        <v>348</v>
       </c>
     </row>
     <row r="80">
@@ -5131,31 +5159,31 @@
         <v>19</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F80" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>118</v>
+        <v>16</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>536</v>
+        <v>301</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>537</v>
+        <v>271</v>
       </c>
     </row>
     <row r="81">
@@ -5163,31 +5191,31 @@
         <v>19</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D81" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="E81" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="E81" t="s" s="2">
-        <v>539</v>
-      </c>
       <c r="F81" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>264</v>
+        <v>544</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="82">
@@ -5195,31 +5223,31 @@
         <v>19</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="F82" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>549</v>
+        <v>264</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="83">
@@ -5227,31 +5255,31 @@
         <v>19</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D83" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="E83" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="E83" t="s" s="2">
-        <v>552</v>
-      </c>
       <c r="F83" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="84">
@@ -5259,31 +5287,31 @@
         <v>19</v>
       </c>
       <c r="B84" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="C84" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="D84" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="E84" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="F84" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I84" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="C84" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="D84" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="E84" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="F84" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>562</v>
-      </c>
       <c r="J84" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="85">
@@ -5291,31 +5319,31 @@
         <v>19</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D85" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="E85" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="E85" t="s" s="2">
-        <v>565</v>
-      </c>
       <c r="F85" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>52</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="86">
@@ -5323,36 +5351,36 @@
         <v>19</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D86" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="E86" t="s" s="2">
         <v>573</v>
       </c>
-      <c r="E86" t="s" s="2">
-        <v>572</v>
-      </c>
       <c r="F86" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>52</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>578</v>
+        <v>19</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>579</v>
@@ -5373,7 +5401,7 @@
         <v>583</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>584</v>
@@ -5384,34 +5412,34 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>19</v>
+        <v>586</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D88" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="E88" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="E88" t="s" s="2">
-        <v>587</v>
-      </c>
       <c r="F88" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>461</v>
+        <v>16</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>463</v>
+        <v>593</v>
       </c>
     </row>
     <row r="89">
@@ -5419,31 +5447,31 @@
         <v>19</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="E89" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="F89" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>52</v>
+        <v>469</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>598</v>
+        <v>471</v>
       </c>
     </row>
     <row r="90">
@@ -5451,60 +5479,60 @@
         <v>19</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D90" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="E90" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="E90" t="s" s="2">
-        <v>600</v>
-      </c>
       <c r="F90" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>52</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>569</v>
+        <v>605</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>605</v>
+        <v>19</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D91" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="E91" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="E91" t="s" s="2">
-        <v>607</v>
-      </c>
       <c r="F91" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>611</v>
+        <v>577</v>
       </c>
       <c r="J91" t="s" s="2">
         <v>612</v>
@@ -5512,34 +5540,34 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>19</v>
+        <v>613</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D92" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="E92" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="E92" t="s" s="2">
-        <v>614</v>
-      </c>
       <c r="F92" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="93">
@@ -5547,31 +5575,31 @@
         <v>19</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D93" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="E93" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="E93" t="s" s="2">
-        <v>621</v>
-      </c>
       <c r="F93" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>619</v>
+        <v>627</v>
       </c>
     </row>
     <row r="94">
@@ -5579,31 +5607,31 @@
         <v>19</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C94" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="D94" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="E94" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="F94" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="J94" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="D94" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="E94" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="F94" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="G94" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>632</v>
       </c>
     </row>
     <row r="95">
@@ -5611,31 +5639,31 @@
         <v>19</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D95" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="E95" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="E95" t="s" s="2">
-        <v>634</v>
-      </c>
       <c r="F95" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="96">
@@ -5643,31 +5671,31 @@
         <v>19</v>
       </c>
       <c r="B96" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="D96" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="E96" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="F96" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="I96" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="C96" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="D96" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="E96" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="F96" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>644</v>
-      </c>
       <c r="J96" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="97">
@@ -5675,31 +5703,31 @@
         <v>19</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D97" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="E97" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="E97" t="s" s="2">
-        <v>647</v>
-      </c>
       <c r="F97" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="98">
@@ -5707,36 +5735,36 @@
         <v>19</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="D98" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="E98" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="E98" t="s" s="2">
-        <v>654</v>
-      </c>
       <c r="F98" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>660</v>
+        <v>19</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>661</v>
@@ -5757,7 +5785,7 @@
         <v>665</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>666</v>
@@ -5768,34 +5796,34 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>19</v>
+        <v>668</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D100" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="E100" t="s" s="2">
         <v>670</v>
       </c>
-      <c r="E100" t="s" s="2">
-        <v>669</v>
-      </c>
       <c r="F100" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="101">
@@ -5803,31 +5831,31 @@
         <v>19</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D101" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="E101" t="s" s="2">
         <v>677</v>
       </c>
-      <c r="E101" t="s" s="2">
-        <v>676</v>
-      </c>
       <c r="F101" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>666</v>
+        <v>681</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="102">
@@ -5835,31 +5863,31 @@
         <v>19</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D102" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E102" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="F102" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>686</v>
+        <v>674</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="103">
@@ -5867,31 +5895,31 @@
         <v>19</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D103" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="E103" t="s" s="2">
         <v>690</v>
       </c>
-      <c r="E103" t="s" s="2">
-        <v>689</v>
-      </c>
       <c r="F103" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I103" t="s" s="2">
-        <v>666</v>
+        <v>694</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="104">
@@ -5899,31 +5927,31 @@
         <v>19</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="D104" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="F104" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>118</v>
+        <v>52</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="105">
@@ -5931,31 +5959,31 @@
         <v>19</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D105" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="E105" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="F105" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>118</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>699</v>
+        <v>707</v>
       </c>
     </row>
     <row r="106">
@@ -5963,60 +5991,60 @@
         <v>19</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="D106" t="s" s="2">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="E106" t="s" s="2">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="F106" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>118</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>160</v>
+        <v>674</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>710</v>
+        <v>707</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>711</v>
+        <v>19</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D107" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="E107" t="s" s="2">
         <v>714</v>
       </c>
-      <c r="E107" t="s" s="2">
-        <v>713</v>
-      </c>
       <c r="F107" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>118</v>
       </c>
       <c r="I107" t="s" s="2">
-        <v>717</v>
+        <v>160</v>
       </c>
       <c r="J107" t="s" s="2">
         <v>718</v>
@@ -6024,34 +6052,34 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>19</v>
+        <v>719</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D108" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="E108" t="s" s="2">
         <v>721</v>
       </c>
-      <c r="E108" t="s" s="2">
-        <v>720</v>
-      </c>
       <c r="F108" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>118</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>718</v>
+        <v>726</v>
       </c>
     </row>
     <row r="109">
@@ -6059,31 +6087,31 @@
         <v>19</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="D109" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="E109" t="s" s="2">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="F109" t="s" s="2">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>118</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>718</v>
+        <v>726</v>
       </c>
     </row>
     <row r="110">
@@ -6091,31 +6119,63 @@
         <v>19</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="D110" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="E110" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="F110" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>118</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>536</v>
+        <v>737</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>718</v>
+        <v>726</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="D111" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="E111" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="F111" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>742</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>726</v>
       </c>
     </row>
   </sheetData>
@@ -6127,18 +6187,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>737</v>
+        <v>745</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>19</v>
@@ -6152,10 +6212,10 @@
         <v>19</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>740</v>
+        <v>748</v>
       </c>
     </row>
     <row r="4">
@@ -6163,10 +6223,10 @@
         <v>19</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>742</v>
+        <v>750</v>
       </c>
     </row>
     <row r="5">
@@ -6174,10 +6234,10 @@
         <v>19</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>744</v>
+        <v>752</v>
       </c>
     </row>
     <row r="6">
@@ -6185,10 +6245,10 @@
         <v>19</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>746</v>
+        <v>754</v>
       </c>
     </row>
     <row r="7">
@@ -6199,7 +6259,7 @@
         <v>218</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>747</v>
+        <v>755</v>
       </c>
     </row>
     <row r="8">
@@ -6207,10 +6267,10 @@
         <v>19</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>245</v>
+        <v>756</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>748</v>
+        <v>757</v>
       </c>
     </row>
     <row r="9">
@@ -6218,10 +6278,10 @@
         <v>19</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>749</v>
+        <v>758</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>750</v>
+        <v>759</v>
       </c>
     </row>
     <row r="10">
@@ -6229,10 +6289,10 @@
         <v>19</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>751</v>
+        <v>760</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>752</v>
+        <v>761</v>
       </c>
     </row>
     <row r="11">
@@ -6240,10 +6300,10 @@
         <v>19</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>753</v>
+        <v>762</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>754</v>
+        <v>763</v>
       </c>
     </row>
     <row r="12">
@@ -6251,10 +6311,10 @@
         <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>755</v>
+        <v>764</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>756</v>
+        <v>765</v>
       </c>
     </row>
     <row r="13">
@@ -6265,7 +6325,7 @@
         <v>225</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>757</v>
+        <v>766</v>
       </c>
     </row>
     <row r="14">
@@ -6273,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>759</v>
+        <v>768</v>
       </c>
     </row>
     <row r="15">
@@ -6284,10 +6344,10 @@
         <v>19</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>761</v>
+        <v>770</v>
       </c>
     </row>
     <row r="16">
@@ -6295,10 +6355,10 @@
         <v>19</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>762</v>
+        <v>771</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>763</v>
+        <v>772</v>
       </c>
     </row>
     <row r="17">
@@ -6306,10 +6366,10 @@
         <v>19</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>764</v>
+        <v>773</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>765</v>
+        <v>774</v>
       </c>
     </row>
     <row r="18">
@@ -6320,7 +6380,7 @@
         <v>134</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>766</v>
+        <v>775</v>
       </c>
     </row>
     <row r="19">
@@ -6331,7 +6391,7 @@
         <v>189</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>767</v>
+        <v>776</v>
       </c>
     </row>
     <row r="20">
@@ -6339,10 +6399,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>768</v>
+        <v>777</v>
       </c>
     </row>
     <row r="21">
@@ -6353,7 +6413,7 @@
         <v>161</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>769</v>
+        <v>778</v>
       </c>
     </row>
     <row r="22">
@@ -6361,10 +6421,10 @@
         <v>19</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>770</v>
+        <v>779</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>771</v>
+        <v>780</v>
       </c>
     </row>
     <row r="23">
@@ -6372,10 +6432,10 @@
         <v>19</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>772</v>
+        <v>781</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>773</v>
+        <v>782</v>
       </c>
     </row>
     <row r="24">
@@ -6383,10 +6443,10 @@
         <v>19</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>774</v>
+        <v>783</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>775</v>
+        <v>784</v>
       </c>
     </row>
     <row r="25">
@@ -6394,10 +6454,10 @@
         <v>19</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>776</v>
+        <v>785</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>777</v>
+        <v>786</v>
       </c>
     </row>
     <row r="26">
@@ -6405,10 +6465,10 @@
         <v>19</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>778</v>
+        <v>787</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>779</v>
+        <v>788</v>
       </c>
     </row>
     <row r="27">
@@ -6416,10 +6476,10 @@
         <v>19</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>780</v>
+        <v>789</v>
       </c>
     </row>
     <row r="28">
@@ -6435,7 +6495,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>781</v>
+        <v>790</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>19</v>
@@ -6449,10 +6509,10 @@
         <v>19</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>782</v>
+        <v>791</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>783</v>
+        <v>792</v>
       </c>
     </row>
     <row r="31">
@@ -6460,10 +6520,10 @@
         <v>19</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>784</v>
+        <v>793</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>785</v>
+        <v>794</v>
       </c>
     </row>
     <row r="32">
@@ -6471,10 +6531,10 @@
         <v>19</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>786</v>
+        <v>795</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>787</v>
+        <v>796</v>
       </c>
     </row>
     <row r="33">
@@ -6482,10 +6542,10 @@
         <v>19</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>788</v>
+        <v>797</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>789</v>
+        <v>798</v>
       </c>
     </row>
     <row r="34">
@@ -6493,10 +6553,10 @@
         <v>19</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>790</v>
+        <v>799</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>791</v>
+        <v>800</v>
       </c>
     </row>
     <row r="35">
@@ -6504,10 +6564,10 @@
         <v>19</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>792</v>
+        <v>801</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>793</v>
+        <v>802</v>
       </c>
     </row>
     <row r="36">
@@ -6515,10 +6575,10 @@
         <v>19</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>794</v>
+        <v>803</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>795</v>
+        <v>804</v>
       </c>
     </row>
     <row r="37">
@@ -6526,10 +6586,10 @@
         <v>19</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>796</v>
+        <v>805</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>797</v>
+        <v>806</v>
       </c>
     </row>
     <row r="38">
@@ -6537,10 +6597,10 @@
         <v>19</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>798</v>
+        <v>807</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>799</v>
+        <v>808</v>
       </c>
     </row>
     <row r="39">
@@ -6548,10 +6608,10 @@
         <v>19</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>800</v>
+        <v>809</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>801</v>
+        <v>810</v>
       </c>
     </row>
   </sheetData>
@@ -6566,43 +6626,43 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>802</v>
+        <v>811</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>803</v>
+        <v>812</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>804</v>
+        <v>813</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>698</v>
+        <v>706</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>805</v>
+        <v>814</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>704</v>
+        <v>712</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>806</v>
+        <v>815</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>709</v>
+        <v>717</v>
       </c>
     </row>
   </sheetData>
@@ -6626,58 +6686,58 @@
         <v>4</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>807</v>
+        <v>816</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>699</v>
+        <v>707</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>699</v>
+        <v>707</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>710</v>
+        <v>718</v>
       </c>
     </row>
   </sheetData>

--- a/docs/test_plan/I3C_Testplan.xlsx
+++ b/docs/test_plan/I3C_Testplan.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="817">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="854">
   <si>
     <t xml:space="preserve">Category</t>
   </si>
@@ -99,6 +99,28 @@
     <t xml:space="preserve">CSR_003</t>
   </si>
   <si>
+    <t xml:space="preserve">Verify broadcast-header control bit read/write behavior and both private-transfer bus-framing modes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`csr_broadcast_header_control`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: Controller idle and CMD FIFO empty; DAT[0] is I3C dynamic address `0x08`; device ACKs target address and, when enabled, broadcast header.
+Stimulus / Actions: Read `HC_CONTROL[BROADCAST_ADDR_ENABLE]` after reset; set and clear the bit through `HC_CONTROL`; set only this bit without `HC_CONTROL[0]`; then issue one 4-byte SDR private write with `BROADCAST_ADDR_ENABLE=0` and one with `BROADCAST_ADDR_ENABLE=1`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reset value is 0; writable set/clear behavior is correct; setting `BROADCAST_ADDR_ENABLE` alone does not enable the controller and does not start a bus transaction; disabled write starts directly with `START + 0x08/W`; enabled write emits `START + 0x7e/W + ACK + Sr + 0x08/W + ACK + data/T-bit + STOP`; both RESPs report success with matching lengths.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`csr_registers`, `flow_active`, `scl_generator`, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_broadcast_addr_enable`, `cp_enable`, `cp_private_start_prefix`, `cp_first_address`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSR_004</t>
+  </si>
+  <si>
     <t xml:space="preserve">Verify timing register read/write behavior.</t>
   </si>
   <si>
@@ -106,16 +128,16 @@
   </si>
   <si>
     <t xml:space="preserve">Preconditions: Controller idle.
-Stimulus / Actions: Write/read `T_R` through `T_HD_DAT` using default, minimum nonzero, and random legal values.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Readback matches written `[19:0]` values; reserved upper bits read 0.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_timing_reg`, `cp_timing_value`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSR_004</t>
+Stimulus / Actions: Write/read all I3C timing CSRs `T_R` through `T_BUS_FREE` and all I2C timing CSRs `I2C_T_R` through `I2C_T_BUF` using default, zero, minimum nonzero, maximum 20-bit, random legal, and reserved-upper-bit values.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Readback matches written `[19:0]` values; reserved upper bits read 0; writes to one timing CSR do not alter other timing CSRs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_timing_reg`, `cp_timing_value`, `cr_timing_reg_value`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSR_005</t>
   </si>
   <si>
     <t xml:space="preserve">Verify all DAT entries and field packing.</t>
@@ -137,7 +159,7 @@
     <t xml:space="preserve">`cp_dat_idx`, `cp_device_type`</t>
   </si>
   <si>
-    <t xml:space="preserve">CSR_005</t>
+    <t xml:space="preserve">CSR_006</t>
   </si>
   <si>
     <t xml:space="preserve">Verify 64-bit CMD staging from two 32-bit writes.</t>
@@ -159,7 +181,7 @@
     <t xml:space="preserve">`cp_cmd_staging`</t>
   </si>
   <si>
-    <t xml:space="preserve">CSR_006</t>
+    <t xml:space="preserve">CSR_007</t>
   </si>
   <si>
     <t xml:space="preserve">Verify partial CMD staging is not disturbed by unrelated CSR writes.</t>
@@ -184,7 +206,7 @@
     <t xml:space="preserve">`cp_cmd_staging`, `cp_csr_interleave`</t>
   </si>
   <si>
-    <t xml:space="preserve">CSR_007</t>
+    <t xml:space="preserve">CSR_008</t>
   </si>
   <si>
     <t xml:space="preserve">Verify software reset flushes queues.</t>
@@ -203,7 +225,7 @@
     <t xml:space="preserve">`cp_sw_reset`, `cp_fifo_state`</t>
   </si>
   <si>
-    <t xml:space="preserve">CSR_008</t>
+    <t xml:space="preserve">CSR_009</t>
   </si>
   <si>
     <t xml:space="preserve">Verify stale DWORD0 cannot corrupt a later command.</t>
@@ -222,7 +244,7 @@
     <t xml:space="preserve">`cp_sw_reset`, `cp_cmd_staging`</t>
   </si>
   <si>
-    <t xml:space="preserve">CSR_009</t>
+    <t xml:space="preserve">CSR_010</t>
   </si>
   <si>
     <t xml:space="preserve">Verify full/empty status bits.</t>
@@ -244,7 +266,7 @@
     <t xml:space="preserve">`cp_fifo_kind`, `cp_fifo_state`</t>
   </si>
   <si>
-    <t xml:space="preserve">CSR_010</t>
+    <t xml:space="preserve">CSR_011</t>
   </si>
   <si>
     <t xml:space="preserve">Verify RX/RESP port pop behavior.</t>
@@ -263,7 +285,7 @@
     <t xml:space="preserve">`cp_port_pop`, `cp_empty_read`</t>
   </si>
   <si>
-    <t xml:space="preserve">CSR_011</t>
+    <t xml:space="preserve">CSR_012</t>
   </si>
   <si>
     <t xml:space="preserve">Verify unmapped address behavior.</t>
@@ -502,23 +524,23 @@
     <t xml:space="preserve">BUS_006</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify clock stall behavior.</t>
+    <t xml:space="preserve">Verify clock stall behavior while waiting for commands or legal backpressure conditions.</t>
   </si>
   <si>
     <t xml:space="preserve">`scl_waitcmd_stall_resume`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: TX FIFO or RX FIFO backpressure condition available.
-Stimulus / Actions: Force `StallWrite` or `StallRead`; later remove the stall.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCL is held low during wait and resumes without extra START/STOP or data corruption.</t>
+    <t xml:space="preserve">Preconditions: Controller is idle or in a supported wait condition.
+Stimulus / Actions: Hold the relevant wait condition, then release it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCL behavior remains legal and traffic resumes or terminates without data corruption.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `scl_generator`</t>
   </si>
   <si>
-    <t xml:space="preserve">`cp_stall_type`</t>
+    <t xml:space="preserve">`cp_wait_state`</t>
   </si>
   <si>
     <t xml:space="preserve">BUS_007</t>
@@ -637,45 +659,45 @@
     <t xml:space="preserve">SDRW_001</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify baseline 4-byte SDR private write.</t>
+    <t xml:space="preserve">Verify baseline 4-byte SDR private write without broadcast-header preamble.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_regular_write_4b_existing`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; device ACKs.
+    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; `HC_CONTROL[BROADCAST_ADDR_ENABLE]=0`; device ACKs.
 Stimulus / Actions: Run `i3c_write_vseq` with TX word `DEAD_BEEF`.</t>
   </si>
   <si>
-    <t xml:space="preserve">Bus write uses dynamic address+W; data byte order follows the project TX FIFO packing contract; RESP success length 4.</t>
+    <t xml:space="preserve">Bus write starts with `START + 0x08/W + ACK`; no `0x7e` preamble is emitted; data byte order follows the project TX FIFO packing contract; RESP success length 4.</t>
   </si>
   <si>
     <t xml:space="preserve">Full DUT, UVM scoreboard</t>
   </si>
   <si>
-    <t xml:space="preserve">`cp_cmd_attr`, `cp_dir`, `cp_len_4`</t>
+    <t xml:space="preserve">`cp_cmd_attr`, `cp_dir`, `cp_len_4`, `cp_private_start_prefix`</t>
   </si>
   <si>
     <t xml:space="preserve">SDRW_002</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify write lengths and TX packing.</t>
+    <t xml:space="preserve">Verify write lengths, TX packing, and broadcast-header private-write framing.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_regular_write_len_sweep`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: Device ACKs address and write data.
-Stimulus / Actions: Write lengths 1,2,3,4,5,7,8,16 using patterned TX words.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exact byte count transmitted; correct byte order; RESP length equals bytes transferred.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `hci_queues`, `bus_tx_flow`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_data_len`, `cp_tx_word_boundary`</t>
+    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; device ACKs address and write data; run once with `HC_CONTROL[BROADCAST_ADDR_ENABLE]=0` and once with it set.
+Stimulus / Actions: Write lengths 1,2,3,4,5,7,8,16 using patterned TX words in both private-address modes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exact byte count transmitted; correct byte order; RESP length equals bytes transferred; disabled mode starts directly with `START + 0x08/W`; enabled mode emits `START + 0x7e/W + ACK + Sr + 0x08/W` before data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `hci_queues`, `bus_tx_flow`, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_data_len`, `cp_tx_word_boundary`, `cp_private_start_prefix`</t>
   </si>
   <si>
     <t xml:space="preserve">SDRW_003</t>
@@ -747,42 +769,45 @@
     <t xml:space="preserve">SDRW_006</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify TX underflow stall/recovery.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_write_tx_fifo_empty_stall`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Write length exceeds initially available TX data.
-Stimulus / Actions: Issue write, delay additional TX data, then provide it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Controller stalls without corrupting bus data and resumes when TX data is available.</t>
+    <t xml:space="preserve">Verify TX underflow error handling.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_write_tx_fifo_underflow_ovl`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: Write length exceeds available TX FIFO data.
+Stimulus / Actions: Issue an 8-byte write with only one TX DWORD available.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controller transfers the available 4 bytes, does not enter old `StallWrite`, generates STOP, and writes RESP `Ovl` with response length 4.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `hci_queues`, `scl_generator`</t>
   </si>
   <si>
-    <t xml:space="preserve">`cp_stall_type`, `cp_tx_empty`</t>
+    <t xml:space="preserve">`cp_resp_err_ovl`, `cp_tx_empty`</t>
   </si>
   <si>
     <t xml:space="preserve">SDRW_007</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify SDR regular write continuation when `toc=0`.</t>
+    <t xml:space="preserve">Verify SDR regular write continuation when `toc=0`, including broadcast-header-enabled private continuation framing.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_write_toc_zero`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: I3C device ACKs; a second SDR regular I3C command is already queued.
+    <t xml:space="preserve">Preconditions: I3C device ACKs; a second SDR regular I3C command is already queued; run once with `HC_CONTROL[BROADCAST_ADDR_ENABLE]=0` and once with it set.
 Stimulus / Actions: Queue first write with `toc=0` and second write with `toc=1`.</t>
   </si>
   <si>
-    <t xml:space="preserve">First write completes data/T-bit then emits `Sr` instead of STOP; second command starts after `Sr`; final STOP occurs only after the `toc=1` command; both RESPs report success with matching TID/length.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_toc`, `cp_rstart_continuation`</t>
+    <t xml:space="preserve">First write completes data/T-bit then emits `Sr` instead of STOP; second command starts after `Sr`; final STOP occurs only after the `toc=1` command; both RESPs report success with matching TID/length. With broadcast-header enabled, the first private transfer emits `START + 0x7e/W + ACK + Sr + dynamic address`, and the continuation does not emit a second `0x7e` preamble.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `scl_generator`, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_broadcast_addr_enable`, `cp_toc`, `cp_rstart_continuation`, `cp_private_start_prefix`</t>
   </si>
   <si>
     <t xml:space="preserve">SDRW_008</t>
@@ -813,20 +838,42 @@
     <t xml:space="preserve">SDRR_001</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify baseline 4-byte SDR private read.</t>
+    <t xml:space="preserve">Verify baseline 4-byte SDR private read without broadcast-header preamble.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_regular_read_4b_existing`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; target returns four bytes.
+    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; `HC_CONTROL[BROADCAST_ADDR_ENABLE]=0`; target returns four bytes.
 Stimulus / Actions: Run `i3c_read_vseq`.</t>
   </si>
   <si>
-    <t xml:space="preserve">RX FIFO word matches the target bytes packed by the project RX FIFO contract, e.g. `32'hBEBA_FECA` for the existing stimulus; RESP success length 4.</t>
+    <t xml:space="preserve">Bus read starts with `START + 0x08/R + ACK`; no `0x7e` preamble is emitted; RX FIFO word matches the target bytes packed by the project RX FIFO contract, e.g. `32'hBEBA_FECA` for the existing stimulus; RESP success length 4.</t>
   </si>
   <si>
     <t xml:space="preserve">SDRR_002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify SDR private read with broadcast-header preamble enabled.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_read_broadcast_header_enabled`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; `HC_CONTROL[BROADCAST_ADDR_ENABLE]=1`; target ACKs broadcast header and returns read data.
+Stimulus / Actions: Issue a 4-byte regular read.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bus frame is `START + 0x7e/W + ACK + Sr + 0x08/R + ACK + read data/T-bit + STOP`; monitor/scoreboard treat the preamble and target phase as one complete transaction; RX data and RESP length match expected bytes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `scl_generator`, `bus_rx_flow`, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_broadcast_addr_enable`, `cp_private_start_prefix`, `cp_first_address`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDRR_003</t>
   </si>
   <si>
     <t xml:space="preserve">Verify read lengths and RX packing.</t>
@@ -848,7 +895,7 @@
     <t xml:space="preserve">`cp_data_len`, `cp_rx_partial_dword`</t>
   </si>
   <si>
-    <t xml:space="preserve">SDRR_003</t>
+    <t xml:space="preserve">SDRR_004</t>
   </si>
   <si>
     <t xml:space="preserve">Verify target early end handling.</t>
@@ -867,7 +914,7 @@
     <t xml:space="preserve">`cp_short_read`, `cp_resp_err`</t>
   </si>
   <si>
-    <t xml:space="preserve">SDRR_004</t>
+    <t xml:space="preserve">SDRR_005</t>
   </si>
   <si>
     <t xml:space="preserve">Verify controller termination at requested length.</t>
@@ -886,7 +933,7 @@
     <t xml:space="preserve">`cp_read_end_policy`</t>
   </si>
   <si>
-    <t xml:space="preserve">SDRR_005</t>
+    <t xml:space="preserve">SDRR_006</t>
   </si>
   <si>
     <t xml:space="preserve">Verify address NACK response on read.</t>
@@ -905,7 +952,7 @@
     <t xml:space="preserve">`flow_active`, `bus_rx_flow`</t>
   </si>
   <si>
-    <t xml:space="preserve">SDRR_006</t>
+    <t xml:space="preserve">SDRR_007</t>
   </si>
   <si>
     <t xml:space="preserve">Verify RX backpressure.</t>
@@ -924,7 +971,7 @@
     <t xml:space="preserve">`cp_rx_full`, `cp_stall_type`</t>
   </si>
   <si>
-    <t xml:space="preserve">SDRR_007</t>
+    <t xml:space="preserve">SDRR_008</t>
   </si>
   <si>
     <t xml:space="preserve">Verify read data integrity.</t>
@@ -943,7 +990,7 @@
     <t xml:space="preserve">`i3c_driver`, `bus_rx_flow`, scoreboard</t>
   </si>
   <si>
-    <t xml:space="preserve">SDRR_008</t>
+    <t xml:space="preserve">SDRR_009</t>
   </si>
   <si>
     <t xml:space="preserve">Verify read T-bit semantics.</t>
@@ -965,7 +1012,7 @@
     <t xml:space="preserve">`cp_read_tbit`, `cp_resp_err`</t>
   </si>
   <si>
-    <t xml:space="preserve">SDRR_009</t>
+    <t xml:space="preserve">SDRR_010</t>
   </si>
   <si>
     <t xml:space="preserve">Verify SDR regular read continuation when `toc=0`.</t>
@@ -987,6 +1034,25 @@
     <t xml:space="preserve">`cp_toc`, `cp_rstart_continuation`, `cp_dir_read_to_write`</t>
   </si>
   <si>
+    <t xml:space="preserve">SDRR_011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify broadcast-header preamble is not repeated across a private read continuation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_read_toc_zero_broadcast_header_once`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: `HC_CONTROL[BROADCAST_ADDR_ENABLE]=1`; I3C device returns requested read data; a second SDR regular I3C command is already queued.
+Stimulus / Actions: Queue first read with `toc=0` and second command with `toc=1`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First command emits `START + 0x7e/W + ACK + Sr + dynamic address`; continuation after the repeated START does not emit a second `0x7e` preamble before the final STOP; RX data and RESPs remain correct.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_broadcast_addr_enable`, `cp_toc`, `cp_private_start_prefix`</t>
+  </si>
+  <si>
     <t xml:space="preserve">Immediate Data Transfer</t>
   </si>
   <si>
@@ -1547,6 +1613,28 @@
     <t xml:space="preserve">I2C_003</t>
   </si>
   <si>
+    <t xml:space="preserve">Verify legacy I2C transfers ignore private-transfer broadcast-header control.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i2c_broadcast_addr_enable_ignored`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: `HC_CONTROL[BROADCAST_ADDR_ENABLE]=1`; DAT[0].`device=1` with static address programmed; target ACKs.
+Stimulus / Actions: Run representative I2C read and write commands.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First address remains the DAT static address for both directions; no `0x7e` preamble is emitted; OD-only behavior and I2C ACK/NACK sequencing are unchanged.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `scl_generator`, `bus_tx_flow`, `bus_rx_flow`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_broadcast_addr_enable`, `cp_first_address`, `cp_i2c_dir`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I2C_004</t>
+  </si>
+  <si>
     <t xml:space="preserve">Verify I2C read/write length behavior.</t>
   </si>
   <si>
@@ -1560,7 +1648,7 @@
     <t xml:space="preserve">Correct TX/RX packing; partial RX DWORD preserved; RESP length correct.</t>
   </si>
   <si>
-    <t xml:space="preserve">I2C_004</t>
+    <t xml:space="preserve">I2C_005</t>
   </si>
   <si>
     <t xml:space="preserve">Verify I2C address NACK.</t>
@@ -1579,7 +1667,7 @@
     <t xml:space="preserve">`cp_resp_err`, `cp_i2c_addr_ack`</t>
   </si>
   <si>
-    <t xml:space="preserve">I2C_005</t>
+    <t xml:space="preserve">I2C_006</t>
   </si>
   <si>
     <t xml:space="preserve">Verify I2C data-byte NACK.</t>
@@ -1595,7 +1683,7 @@
     <t xml:space="preserve">Transfer stops after the NACKed byte per I2C/project error policy; RESP error is `Nack`; next legal transfer passes.</t>
   </si>
   <si>
-    <t xml:space="preserve">I2C_006</t>
+    <t xml:space="preserve">I2C_007</t>
   </si>
   <si>
     <t xml:space="preserve">Verify legacy transfers remain open-drain.</t>
@@ -1617,7 +1705,7 @@
     <t xml:space="preserve">`cp_odpp_phase`, `cp_i2c`</t>
   </si>
   <si>
-    <t xml:space="preserve">I2C_007</t>
+    <t xml:space="preserve">I2C_008</t>
   </si>
   <si>
     <t xml:space="preserve">Verify configured I2C timing path.</t>
@@ -2382,6 +2470,24 @@
     <t xml:space="preserve">Write, Read</t>
   </si>
   <si>
+    <t xml:space="preserve">`cp_broadcast_addr_enable`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">disabled, enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_private_start_prefix`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dynamic-address-first, broadcast-header-then-dynamic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_first_address`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`0x7e`, dynamic address, static address</t>
+  </si>
+  <si>
     <t xml:space="preserve">`cp_data_len`</t>
   </si>
   <si>
@@ -2457,6 +2563,9 @@
     <t xml:space="preserve">I3C SDR timing, I2C legacy timing, custom timing</t>
   </si>
   <si>
+    <t xml:space="preserve">`cp_stall_type`</t>
+  </si>
+  <si>
     <t xml:space="preserve">TX empty, RX full, RESP full, none</t>
   </si>
   <si>
@@ -2548,6 +2657,12 @@
   </si>
   <si>
     <t xml:space="preserve">Verify timing for START/STOP/Sr under I3C and I2C settings.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`broadcast_addr_enable x transaction_type x first_address`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ensure the control bit changes only private I3C first-address behavior while I2C, CCC, and ENTDAA retain their protocol-required address flows.</t>
   </si>
   <si>
     <t xml:space="preserve">`prev_cmd_attr x next_cmd_attr`</t>
@@ -2748,10 +2863,10 @@
         <v>16</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -2759,28 +2874,28 @@
         <v>19</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="E5" t="s" s="2">
-        <v>34</v>
-      </c>
       <c r="F5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="J5" t="s" s="2">
         <v>39</v>
@@ -2841,13 +2956,13 @@
         <v>51</v>
       </c>
       <c r="H7" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I7" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="I7" t="s" s="2">
+      <c r="J7" t="s" s="2">
         <v>53</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>54</v>
       </c>
     </row>
     <row r="8">
@@ -2855,31 +2970,31 @@
         <v>19</v>
       </c>
       <c r="B8" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="C8" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="C8" t="s" s="2">
+      <c r="D8" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="D8" t="s" s="2">
+      <c r="E8" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="F8" t="s" s="2">
         <v>57</v>
       </c>
-      <c r="E8" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="F8" t="s" s="2">
+      <c r="G8" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="G8" t="s" s="2">
+      <c r="H8" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="H8" t="s" s="2">
-        <v>16</v>
-      </c>
       <c r="I8" t="s" s="2">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9">
@@ -2887,31 +3002,31 @@
         <v>19</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="E9" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="E9" t="s" s="2">
-        <v>62</v>
-      </c>
       <c r="F9" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
@@ -2919,28 +3034,28 @@
         <v>19</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="E10" t="s" s="2">
         <v>69</v>
       </c>
-      <c r="E10" t="s" s="2">
-        <v>68</v>
-      </c>
       <c r="F10" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>73</v>
@@ -2972,10 +3087,10 @@
         <v>16</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12">
@@ -2983,36 +3098,36 @@
         <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E12" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="E12" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="F12" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H12" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I12" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="I12" t="s" s="2">
-        <v>17</v>
-      </c>
       <c r="J12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>87</v>
@@ -3033,18 +3148,18 @@
         <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I13" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J13" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="J13" t="s" s="2">
-        <v>93</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>19</v>
+        <v>93</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>94</v>
@@ -3097,13 +3212,13 @@
         <v>105</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16">
@@ -3111,31 +3226,31 @@
         <v>19</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D16" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E16" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="E16" t="s" s="2">
-        <v>108</v>
-      </c>
       <c r="F16" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>99</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17">
@@ -3143,28 +3258,28 @@
         <v>19</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D17" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="E17" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="E17" t="s" s="2">
-        <v>114</v>
-      </c>
       <c r="F17" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>118</v>
+        <v>16</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>119</v>
@@ -3172,39 +3287,39 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="B18" t="s" s="2">
+      <c r="C18" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="C18" t="s" s="2">
+      <c r="D18" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="D18" t="s" s="2">
+      <c r="E18" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="F18" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="E18" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="F18" t="s" s="2">
+      <c r="G18" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="G18" t="s" s="2">
+      <c r="H18" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="H18" t="s" s="2">
-        <v>52</v>
-      </c>
       <c r="I18" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="J18" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>127</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>19</v>
+        <v>127</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>128</v>
@@ -3225,7 +3340,7 @@
         <v>132</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>133</v>
@@ -3263,7 +3378,7 @@
         <v>140</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21">
@@ -3271,31 +3386,31 @@
         <v>19</v>
       </c>
       <c r="B21" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="D21" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="E21" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="F21" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="G21" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="H21" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>147</v>
       </c>
     </row>
     <row r="22">
@@ -3513,7 +3628,7 @@
         <v>194</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>195</v>
@@ -3524,39 +3639,39 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="B29" t="s" s="2">
+      <c r="C29" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="C29" t="s" s="2">
+      <c r="D29" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="D29" t="s" s="2">
+      <c r="E29" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="F29" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="E29" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="F29" t="s" s="2">
+      <c r="G29" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="G29" t="s" s="2">
+      <c r="H29" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I29" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="H29" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I29" t="s" s="2">
+      <c r="J29" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>204</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>19</v>
+        <v>204</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>205</v>
@@ -3609,7 +3724,7 @@
         <v>216</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>217</v>
@@ -3641,7 +3756,7 @@
         <v>223</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>224</v>
@@ -3737,13 +3852,13 @@
         <v>244</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>160</v>
+        <v>245</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="36">
@@ -3751,36 +3866,36 @@
         <v>19</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D36" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="E36" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="E36" t="s" s="2">
-        <v>247</v>
-      </c>
       <c r="F36" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>253</v>
+        <v>19</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>254</v>
@@ -3804,42 +3919,42 @@
         <v>16</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>203</v>
+        <v>259</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>204</v>
+        <v>260</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>19</v>
+        <v>261</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>264</v>
+        <v>210</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>265</v>
+        <v>211</v>
       </c>
     </row>
     <row r="39">
@@ -3847,31 +3962,31 @@
         <v>19</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D39" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="E39" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="E39" t="s" s="2">
-        <v>267</v>
-      </c>
       <c r="F39" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="40">
@@ -3879,31 +3994,31 @@
         <v>19</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F40" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>160</v>
+        <v>279</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="41">
@@ -3911,31 +4026,31 @@
         <v>19</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E41" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F41" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>283</v>
+        <v>238</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>232</v>
+        <v>286</v>
       </c>
     </row>
     <row r="42">
@@ -3943,31 +4058,31 @@
         <v>19</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F42" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>238</v>
+        <v>167</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="43">
@@ -3975,31 +4090,31 @@
         <v>19</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F43" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>218</v>
+        <v>239</v>
       </c>
     </row>
     <row r="44">
@@ -4007,31 +4122,31 @@
         <v>19</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F44" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>301</v>
+        <v>245</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45">
@@ -4039,36 +4154,36 @@
         <v>19</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>309</v>
+        <v>225</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>310</v>
+        <v>19</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>311</v>
@@ -4121,7 +4236,7 @@
         <v>322</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>323</v>
@@ -4153,10 +4268,10 @@
         <v>329</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>160</v>
+        <v>272</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>330</v>
@@ -4164,34 +4279,34 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>19</v>
+        <v>331</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D49" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="E49" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="E49" t="s" s="2">
-        <v>332</v>
-      </c>
       <c r="F49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>224</v>
+        <v>337</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="50">
@@ -4199,31 +4314,31 @@
         <v>19</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F50" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>283</v>
+        <v>344</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="51">
@@ -4231,63 +4346,63 @@
         <v>19</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F51" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>301</v>
+        <v>167</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>349</v>
+        <v>19</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F52" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>355</v>
+        <v>231</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="53">
@@ -4295,28 +4410,28 @@
         <v>19</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D53" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="E53" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="E53" t="s" s="2">
-        <v>358</v>
-      </c>
       <c r="F53" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>362</v>
+        <v>298</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>363</v>
@@ -4348,7 +4463,7 @@
         <v>16</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>369</v>
@@ -4356,34 +4471,34 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>19</v>
+        <v>370</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D55" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="E55" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="E55" t="s" s="2">
-        <v>371</v>
-      </c>
       <c r="F55" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>160</v>
+        <v>376</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="56">
@@ -4391,31 +4506,31 @@
         <v>19</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F56" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>301</v>
+        <v>383</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="57">
@@ -4423,31 +4538,31 @@
         <v>19</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="F57" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>387</v>
+        <v>316</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="58">
@@ -4455,31 +4570,31 @@
         <v>19</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F58" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>301</v>
+        <v>167</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="59">
@@ -4487,36 +4602,36 @@
         <v>19</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F59" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>400</v>
+        <v>316</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>402</v>
+        <v>19</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>403</v>
@@ -4572,10 +4687,10 @@
         <v>16</v>
       </c>
       <c r="I61" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="J61" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>416</v>
       </c>
     </row>
     <row r="62">
@@ -4583,36 +4698,36 @@
         <v>19</v>
       </c>
       <c r="B62" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="C62" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="C62" t="s" s="2">
+      <c r="D62" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="D62" t="s" s="2">
+      <c r="E62" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="F62" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="E62" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="F62" t="s" s="2">
+      <c r="G62" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="G62" t="s" s="2">
+      <c r="H62" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I62" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="H62" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I62" t="s" s="2">
+      <c r="J62" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>423</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>19</v>
+        <v>423</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>424</v>
@@ -4700,10 +4815,10 @@
         <v>16</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>415</v>
+        <v>443</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="66">
@@ -4711,31 +4826,31 @@
         <v>19</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D66" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="E66" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="E66" t="s" s="2">
-        <v>445</v>
-      </c>
       <c r="F66" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="67">
@@ -4743,31 +4858,31 @@
         <v>19</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D67" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="E67" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="E67" t="s" s="2">
-        <v>452</v>
-      </c>
       <c r="F67" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>429</v>
+        <v>457</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="68">
@@ -4775,31 +4890,31 @@
         <v>19</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="69">
@@ -4807,25 +4922,25 @@
         <v>19</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D69" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="E69" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="E69" t="s" s="2">
-        <v>465</v>
-      </c>
       <c r="F69" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>469</v>
+        <v>16</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>470</v>
@@ -4836,34 +4951,34 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="B70" t="s" s="2">
+      <c r="C70" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="C70" t="s" s="2">
+      <c r="D70" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="D70" t="s" s="2">
+      <c r="E70" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="F70" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="E70" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="F70" t="s" s="2">
+      <c r="G70" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="G70" t="s" s="2">
+      <c r="H70" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="J70" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>479</v>
       </c>
     </row>
     <row r="71">
@@ -4871,31 +4986,31 @@
         <v>19</v>
       </c>
       <c r="B71" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="D71" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="C71" t="s" s="2">
+      <c r="E71" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="F71" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="D71" t="s" s="2">
+      <c r="G71" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="E71" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="F71" t="s" s="2">
+      <c r="H71" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I71" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="G71" t="s" s="2">
+      <c r="J71" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>486</v>
       </c>
     </row>
     <row r="72">
@@ -4903,63 +5018,63 @@
         <v>19</v>
       </c>
       <c r="B72" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C72" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="D72" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="C72" t="s" s="2">
+      <c r="E72" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="F72" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="D72" t="s" s="2">
+      <c r="G72" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="E72" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="F72" t="s" s="2">
+      <c r="H72" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="G72" t="s" s="2">
+      <c r="I72" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="H72" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>264</v>
-      </c>
       <c r="J72" t="s" s="2">
-        <v>265</v>
+        <v>492</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>19</v>
+        <v>493</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F73" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>283</v>
+        <v>499</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="74">
@@ -4967,31 +5082,31 @@
         <v>19</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="F74" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>301</v>
+        <v>506</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>348</v>
+        <v>507</v>
       </c>
     </row>
     <row r="75">
@@ -4999,31 +5114,31 @@
         <v>19</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="F75" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="76">
@@ -5031,63 +5146,63 @@
         <v>19</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="F76" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>515</v>
+        <v>279</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>516</v>
+        <v>280</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>517</v>
+        <v>19</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E77" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F77" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>387</v>
+        <v>298</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="78">
@@ -5095,31 +5210,31 @@
         <v>19</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="F78" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>232</v>
+        <v>369</v>
       </c>
     </row>
     <row r="79">
@@ -5127,31 +5242,31 @@
         <v>19</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E79" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F79" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>301</v>
+        <v>536</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>348</v>
+        <v>537</v>
       </c>
     </row>
     <row r="80">
@@ -5159,63 +5274,63 @@
         <v>19</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="F80" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>301</v>
+        <v>543</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>271</v>
+        <v>544</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>19</v>
+        <v>545</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="F81" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>118</v>
+        <v>16</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>544</v>
+        <v>408</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>545</v>
+        <v>551</v>
       </c>
     </row>
     <row r="82">
@@ -5223,31 +5338,31 @@
         <v>19</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="F82" t="s" s="2">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>264</v>
+        <v>316</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>551</v>
+        <v>239</v>
       </c>
     </row>
     <row r="83">
@@ -5255,31 +5370,31 @@
         <v>19</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="F83" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>557</v>
+        <v>316</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>558</v>
+        <v>369</v>
       </c>
     </row>
     <row r="84">
@@ -5287,31 +5402,31 @@
         <v>19</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="E84" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F84" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>557</v>
+        <v>316</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>564</v>
+        <v>286</v>
       </c>
     </row>
     <row r="85">
@@ -5319,31 +5434,31 @@
         <v>19</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="F85" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>52</v>
+        <v>125</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="86">
@@ -5351,31 +5466,31 @@
         <v>19</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E86" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F86" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>577</v>
+        <v>279</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="87">
@@ -5383,36 +5498,36 @@
         <v>19</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D87" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="E87" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="E87" t="s" s="2">
-        <v>580</v>
-      </c>
       <c r="F87" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>586</v>
+        <v>19</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>587</v>
@@ -5436,10 +5551,10 @@
         <v>16</v>
       </c>
       <c r="I88" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="J88" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>593</v>
       </c>
     </row>
     <row r="89">
@@ -5447,31 +5562,31 @@
         <v>19</v>
       </c>
       <c r="B89" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="C89" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="C89" t="s" s="2">
+      <c r="D89" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="D89" t="s" s="2">
+      <c r="E89" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="F89" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="E89" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="F89" t="s" s="2">
+      <c r="G89" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="G89" t="s" s="2">
+      <c r="H89" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I89" t="s" s="2">
         <v>598</v>
       </c>
-      <c r="H89" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="I89" t="s" s="2">
+      <c r="J89" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>471</v>
       </c>
     </row>
     <row r="90">
@@ -5497,7 +5612,7 @@
         <v>604</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>605</v>
@@ -5529,45 +5644,45 @@
         <v>611</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>577</v>
+        <v>612</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D92" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="E92" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="E92" t="s" s="2">
-        <v>615</v>
-      </c>
       <c r="F92" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="93">
@@ -5575,31 +5690,31 @@
         <v>19</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D93" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="E93" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="E93" t="s" s="2">
-        <v>622</v>
-      </c>
       <c r="F93" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>16</v>
+        <v>490</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>627</v>
+        <v>492</v>
       </c>
     </row>
     <row r="94">
@@ -5625,13 +5740,13 @@
         <v>632</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>633</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>627</v>
+        <v>634</v>
       </c>
     </row>
     <row r="95">
@@ -5639,28 +5754,28 @@
         <v>19</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D95" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="E95" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="E95" t="s" s="2">
-        <v>635</v>
-      </c>
       <c r="F95" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>639</v>
+        <v>605</v>
       </c>
       <c r="J95" t="s" s="2">
         <v>640</v>
@@ -5668,34 +5783,34 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>19</v>
+        <v>641</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D96" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="E96" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="E96" t="s" s="2">
-        <v>642</v>
-      </c>
       <c r="F96" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="97">
@@ -5703,31 +5818,31 @@
         <v>19</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="F97" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="98">
@@ -5735,31 +5850,31 @@
         <v>19</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C98" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="D98" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="E98" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="F98" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="J98" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="D98" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="E98" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="F98" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>660</v>
       </c>
     </row>
     <row r="99">
@@ -5767,36 +5882,36 @@
         <v>19</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D99" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="E99" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="E99" t="s" s="2">
-        <v>662</v>
-      </c>
       <c r="F99" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>668</v>
+        <v>19</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>669</v>
@@ -5817,13 +5932,13 @@
         <v>673</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I100" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="J100" t="s" s="2">
         <v>674</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>675</v>
       </c>
     </row>
     <row r="101">
@@ -5831,31 +5946,31 @@
         <v>19</v>
       </c>
       <c r="B101" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="C101" t="s" s="2">
         <v>676</v>
       </c>
-      <c r="C101" t="s" s="2">
+      <c r="D101" t="s" s="2">
         <v>677</v>
       </c>
-      <c r="D101" t="s" s="2">
+      <c r="E101" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="F101" t="s" s="2">
         <v>678</v>
       </c>
-      <c r="E101" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="F101" t="s" s="2">
+      <c r="G101" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="G101" t="s" s="2">
+      <c r="H101" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I101" t="s" s="2">
         <v>680</v>
       </c>
-      <c r="H101" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I101" t="s" s="2">
+      <c r="J101" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>682</v>
       </c>
     </row>
     <row r="102">
@@ -5863,28 +5978,28 @@
         <v>19</v>
       </c>
       <c r="B102" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="C102" t="s" s="2">
         <v>683</v>
       </c>
-      <c r="C102" t="s" s="2">
+      <c r="D102" t="s" s="2">
         <v>684</v>
       </c>
-      <c r="D102" t="s" s="2">
+      <c r="E102" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="F102" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="E102" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="F102" t="s" s="2">
+      <c r="G102" t="s" s="2">
         <v>686</v>
       </c>
-      <c r="G102" t="s" s="2">
+      <c r="H102" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I102" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>674</v>
       </c>
       <c r="J102" t="s" s="2">
         <v>688</v>
@@ -5913,7 +6028,7 @@
         <v>693</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>694</v>
@@ -5924,34 +6039,34 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>19</v>
+        <v>696</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D104" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="E104" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="E104" t="s" s="2">
-        <v>697</v>
-      </c>
       <c r="F104" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>674</v>
+        <v>702</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="105">
@@ -5959,31 +6074,31 @@
         <v>19</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D105" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="E105" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="F105" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>118</v>
+        <v>16</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>674</v>
+        <v>709</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>707</v>
+        <v>710</v>
       </c>
     </row>
     <row r="106">
@@ -5991,31 +6106,31 @@
         <v>19</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="D106" t="s" s="2">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="E106" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="F106" t="s" s="2">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>118</v>
+        <v>16</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>674</v>
+        <v>702</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="107">
@@ -6023,63 +6138,63 @@
         <v>19</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="D107" t="s" s="2">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="E107" t="s" s="2">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="F107" t="s" s="2">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>118</v>
+        <v>16</v>
       </c>
       <c r="I107" t="s" s="2">
-        <v>160</v>
+        <v>722</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>718</v>
+        <v>723</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>719</v>
+        <v>19</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="D108" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="E108" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="F108" t="s" s="2">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>118</v>
+        <v>59</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>725</v>
+        <v>702</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
     </row>
     <row r="109">
@@ -6087,31 +6202,31 @@
         <v>19</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="D109" t="s" s="2">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="E109" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="F109" t="s" s="2">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>725</v>
+        <v>702</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>726</v>
+        <v>735</v>
       </c>
     </row>
     <row r="110">
@@ -6119,31 +6234,31 @@
         <v>19</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="D110" t="s" s="2">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="E110" t="s" s="2">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="F110" t="s" s="2">
+        <v>739</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="J110" t="s" s="2">
         <v>735</v>
-      </c>
-      <c r="G110" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="H110" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="I110" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>726</v>
       </c>
     </row>
     <row r="111">
@@ -6151,31 +6266,159 @@
         <v>19</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="D111" t="s" s="2">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="E111" t="s" s="2">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="F111" t="s" s="2">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>544</v>
+        <v>167</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>726</v>
+        <v>746</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="C112" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="D112" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="E112" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="F112" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="C113" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="D113" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="E113" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="F113" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="C114" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="D114" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="E114" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="F114" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="C115" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="D115" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="E115" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="F115" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>754</v>
       </c>
     </row>
   </sheetData>
@@ -6187,18 +6430,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>743</v>
+        <v>771</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>744</v>
+        <v>772</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>745</v>
+        <v>773</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>746</v>
+        <v>774</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>19</v>
@@ -6212,10 +6455,10 @@
         <v>19</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>747</v>
+        <v>775</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>748</v>
+        <v>776</v>
       </c>
     </row>
     <row r="4">
@@ -6223,10 +6466,10 @@
         <v>19</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>749</v>
+        <v>777</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>750</v>
+        <v>778</v>
       </c>
     </row>
     <row r="5">
@@ -6234,10 +6477,10 @@
         <v>19</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>751</v>
+        <v>779</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>752</v>
+        <v>780</v>
       </c>
     </row>
     <row r="6">
@@ -6245,10 +6488,10 @@
         <v>19</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>753</v>
+        <v>781</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>754</v>
+        <v>782</v>
       </c>
     </row>
     <row r="7">
@@ -6256,10 +6499,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>218</v>
+        <v>783</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>755</v>
+        <v>784</v>
       </c>
     </row>
     <row r="8">
@@ -6267,10 +6510,10 @@
         <v>19</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>756</v>
+        <v>785</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>757</v>
+        <v>786</v>
       </c>
     </row>
     <row r="9">
@@ -6278,10 +6521,10 @@
         <v>19</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>758</v>
+        <v>787</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>759</v>
+        <v>788</v>
       </c>
     </row>
     <row r="10">
@@ -6289,10 +6532,10 @@
         <v>19</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>760</v>
+        <v>225</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>761</v>
+        <v>789</v>
       </c>
     </row>
     <row r="11">
@@ -6300,10 +6543,10 @@
         <v>19</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>762</v>
+        <v>790</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>763</v>
+        <v>791</v>
       </c>
     </row>
     <row r="12">
@@ -6311,10 +6554,10 @@
         <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>764</v>
+        <v>792</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>765</v>
+        <v>793</v>
       </c>
     </row>
     <row r="13">
@@ -6322,10 +6565,10 @@
         <v>19</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>225</v>
+        <v>794</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>766</v>
+        <v>795</v>
       </c>
     </row>
     <row r="14">
@@ -6333,10 +6576,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>767</v>
+        <v>796</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>768</v>
+        <v>797</v>
       </c>
     </row>
     <row r="15">
@@ -6344,10 +6587,10 @@
         <v>19</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>769</v>
+        <v>798</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>770</v>
+        <v>799</v>
       </c>
     </row>
     <row r="16">
@@ -6355,10 +6598,10 @@
         <v>19</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>771</v>
+        <v>232</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>772</v>
+        <v>800</v>
       </c>
     </row>
     <row r="17">
@@ -6366,10 +6609,10 @@
         <v>19</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>773</v>
+        <v>801</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>774</v>
+        <v>802</v>
       </c>
     </row>
     <row r="18">
@@ -6377,10 +6620,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>803</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>775</v>
+        <v>804</v>
       </c>
     </row>
     <row r="19">
@@ -6388,10 +6631,10 @@
         <v>19</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>189</v>
+        <v>805</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>776</v>
+        <v>806</v>
       </c>
     </row>
     <row r="20">
@@ -6399,10 +6642,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>516</v>
+        <v>807</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>777</v>
+        <v>808</v>
       </c>
     </row>
     <row r="21">
@@ -6410,10 +6653,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>778</v>
+        <v>809</v>
       </c>
     </row>
     <row r="22">
@@ -6421,10 +6664,10 @@
         <v>19</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>779</v>
+        <v>196</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>780</v>
+        <v>810</v>
       </c>
     </row>
     <row r="23">
@@ -6432,10 +6675,10 @@
         <v>19</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>781</v>
+        <v>544</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>782</v>
+        <v>811</v>
       </c>
     </row>
     <row r="24">
@@ -6443,10 +6686,10 @@
         <v>19</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>783</v>
+        <v>812</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>784</v>
+        <v>813</v>
       </c>
     </row>
     <row r="25">
@@ -6454,10 +6697,10 @@
         <v>19</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>785</v>
+        <v>814</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>786</v>
+        <v>815</v>
       </c>
     </row>
     <row r="26">
@@ -6465,10 +6708,10 @@
         <v>19</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>787</v>
+        <v>816</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>788</v>
+        <v>817</v>
       </c>
     </row>
     <row r="27">
@@ -6476,10 +6719,10 @@
         <v>19</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>558</v>
+        <v>818</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>789</v>
+        <v>819</v>
       </c>
     </row>
     <row r="28">
@@ -6487,21 +6730,21 @@
         <v>19</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>19</v>
+        <v>820</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>19</v>
+        <v>821</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>790</v>
+        <v>19</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>19</v>
+        <v>822</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>19</v>
+        <v>823</v>
       </c>
     </row>
     <row r="30">
@@ -6509,10 +6752,10 @@
         <v>19</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>791</v>
+        <v>586</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>792</v>
+        <v>824</v>
       </c>
     </row>
     <row r="31">
@@ -6520,21 +6763,21 @@
         <v>19</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>793</v>
+        <v>19</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>794</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>19</v>
+        <v>825</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>795</v>
+        <v>19</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>796</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
@@ -6542,10 +6785,10 @@
         <v>19</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>797</v>
+        <v>826</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>798</v>
+        <v>827</v>
       </c>
     </row>
     <row r="34">
@@ -6553,10 +6796,10 @@
         <v>19</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>799</v>
+        <v>828</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>800</v>
+        <v>829</v>
       </c>
     </row>
     <row r="35">
@@ -6564,10 +6807,10 @@
         <v>19</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>801</v>
+        <v>830</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>802</v>
+        <v>831</v>
       </c>
     </row>
     <row r="36">
@@ -6575,10 +6818,10 @@
         <v>19</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>803</v>
+        <v>832</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>804</v>
+        <v>833</v>
       </c>
     </row>
     <row r="37">
@@ -6586,10 +6829,10 @@
         <v>19</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>805</v>
+        <v>834</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>806</v>
+        <v>835</v>
       </c>
     </row>
     <row r="38">
@@ -6597,10 +6840,10 @@
         <v>19</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>807</v>
+        <v>836</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>808</v>
+        <v>837</v>
       </c>
     </row>
     <row r="39">
@@ -6608,10 +6851,54 @@
         <v>19</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>809</v>
+        <v>838</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>810</v>
+        <v>839</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>840</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>842</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>844</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>846</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>847</v>
       </c>
     </row>
   </sheetData>
@@ -6626,43 +6913,43 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>811</v>
+        <v>848</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>812</v>
+        <v>849</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>813</v>
+        <v>850</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>703</v>
+        <v>731</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>706</v>
+        <v>734</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>814</v>
+        <v>851</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>709</v>
+        <v>737</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>712</v>
+        <v>740</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>815</v>
+        <v>852</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>714</v>
+        <v>742</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>717</v>
+        <v>745</v>
       </c>
     </row>
   </sheetData>
@@ -6686,58 +6973,58 @@
         <v>4</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>816</v>
+        <v>853</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>702</v>
+        <v>730</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>668</v>
+        <v>696</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>704</v>
+        <v>732</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>703</v>
+        <v>731</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>707</v>
+        <v>735</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>708</v>
+        <v>736</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>668</v>
+        <v>696</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>710</v>
+        <v>738</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>709</v>
+        <v>737</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>707</v>
+        <v>735</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>713</v>
+        <v>741</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>668</v>
+        <v>696</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>715</v>
+        <v>743</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>714</v>
+        <v>742</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>718</v>
+        <v>746</v>
       </c>
     </row>
   </sheetData>

--- a/docs/test_plan/I3C_Testplan.xlsx
+++ b/docs/test_plan/I3C_Testplan.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="876">
   <si>
     <t xml:space="preserve">Category</t>
   </si>
@@ -304,6 +304,25 @@
     <t xml:space="preserve">`cp_invalid_reg_addr`</t>
   </si>
   <si>
+    <t xml:space="preserve">CSR_013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify `HC_CONTROL[3]` (HC abort) read/write and level-bit persistence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`csr_hc_abort_control`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: Controller idle and CMD FIFO empty.
+Stimulus / Actions: Read `HC_CONTROL[3]` after reset; set and clear the bit through `HC_CONTROL`; set only this bit without `HC_CONTROL[0]`; hold it set across several read cycles and a queued command.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reset value is 0; writable set/clear behavior is correct; the bit is never auto-cleared by hardware and holds its written value until software clears it; setting it alone does not enable the controller. The abort effect on an active transfer and its response encoding are covered by `SDRW_009`, `SDRR_009`, and `ERR_012`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_hc_abort`, `cp_csr_addr`</t>
+  </si>
+  <si>
     <t xml:space="preserve">FIFO and Queue Behavior</t>
   </si>
   <si>
@@ -681,23 +700,23 @@
     <t xml:space="preserve">SDRW_002</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify write lengths, TX packing, and broadcast-header private-write framing.</t>
+    <t xml:space="preserve">Verify write lengths, TX packing, zero-length behavior, large payloads, and broadcast-header private-write framing.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_regular_write_len_sweep`</t>
   </si>
   <si>
     <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; device ACKs address and write data; run once with `HC_CONTROL[BROADCAST_ADDR_ENABLE]=0` and once with it set.
-Stimulus / Actions: Write lengths 1,2,3,4,5,7,8,16 using patterned TX words in both private-address modes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exact byte count transmitted; correct byte order; RESP length equals bytes transferred; disabled mode starts directly with `START + 0x08/W`; enabled mode emits `START + 0x7e/W + ACK + Sr + 0x08/W` before data.</t>
+Stimulus / Actions: Write lengths 0,1,2,3,4,5,7,8,16,64,256 using patterned TX words in both private-address modes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exact byte count transmitted; correct byte order and T-bit parity; RESP length equals bytes transferred. Length 0 ACKs address then STOPs with no data/T-bit and success length 0. Length 256 consumes 64 TX DWORDs in order and leaves queues empty. Disabled mode starts directly with `START + 0x08/W`; enabled mode emits `START + 0x7e/W + ACK + Sr + 0x08/W` before data.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `hci_queues`, `bus_tx_flow`, UVM scoreboard</t>
   </si>
   <si>
-    <t xml:space="preserve">`cp_data_len`, `cp_tx_word_boundary`, `cp_private_start_prefix`</t>
+    <t xml:space="preserve">`cp_data_len`, `cp_len_zero`, `cp_len_large`, `cp_tx_word_boundary`, `cp_private_start_prefix`</t>
   </si>
   <si>
     <t xml:space="preserve">SDRW_003</t>
@@ -747,70 +766,48 @@
     <t xml:space="preserve">SDRW_005</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify address NACK response.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_write_addr_nack`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Device configured to NACK dynamic address.
-Stimulus / Actions: Issue regular write.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No data bytes are transmitted; STOP/recovery occurs; RESP error is `AddrHeader`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `bus_rx_flow`, RESP FIFO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_resp_err`, `cp_addr_ack`</t>
+    <t xml:space="preserve">Verify TX underflow flow handling.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_write_tx_fifo_underflow_ovl`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: Write length exceeds available TX FIFO data or TX FIFO is empty at transfer start.
+Stimulus / Actions: Issue an 8-byte write with only one TX DWORD available; issue 4-byte and 8-byte writes with no TX data; run both `toc=1` and `toc=0` in both private-address modes. Also write a late TX DWORD after an aborted underflow.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controller transfers only available bytes, never transmits garbage, does not enter old `StallWrite`, and generates STOP. For `toc=0`, underflow still terminates with STOP and must not create a Repeated START/continuation. Late refill remains in TX FIFO until SW reset flushes queues. Response descriptor encoding is checked by `ERR_005`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `hci_queues`, `scl_generator`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_tx_empty`, `cp_tx_late_refill`</t>
   </si>
   <si>
     <t xml:space="preserve">SDRW_006</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify TX underflow error handling.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_write_tx_fifo_underflow_ovl`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Write length exceeds available TX FIFO data.
-Stimulus / Actions: Issue an 8-byte write with only one TX DWORD available.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Controller transfers the available 4 bytes, does not enter old `StallWrite`, generates STOP, and writes RESP `Ovl` with response length 4.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `hci_queues`, `scl_generator`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_resp_err_ovl`, `cp_tx_empty`</t>
+    <t xml:space="preserve">Verify SDR regular write continuation when `toc=0`, including broadcast-header-enabled private continuation framing and missing-continuation policy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_write_toc_zero`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: I3C device ACKs; valid-continuation subcase has a second SDR regular I3C command already queued; run once with `HC_CONTROL[BROADCAST_ADDR_ENABLE]=0` and once with it set.
+Stimulus / Actions: Queue first write with `toc=0` and second write with `toc=1`; separately issue a `toc=0` write with no next supported command.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valid case: first write completes data/T-bit then emits `Sr` instead of STOP; second command starts after `Sr`; final STOP occurs only after the `toc=1` command; both RESPs report success with matching TID/length. With broadcast-header enabled, only the first private transfer emits the `0x7e` preamble. Negative case: the first write data is transmitted, controller emits STOP instead of RSTART, and RESP is `NotSupported` with actual length transmitted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `scl_generator`, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_broadcast_addr_enable`, `cp_toc`, `cp_rstart_continuation`, `cp_private_start_prefix`, `cp_unsupported_policy`</t>
   </si>
   <si>
     <t xml:space="preserve">SDRW_007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify SDR regular write continuation when `toc=0`, including broadcast-header-enabled private continuation framing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_write_toc_zero`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: I3C device ACKs; a second SDR regular I3C command is already queued; run once with `HC_CONTROL[BROADCAST_ADDR_ENABLE]=0` and once with it set.
-Stimulus / Actions: Queue first write with `toc=0` and second write with `toc=1`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First write completes data/T-bit then emits `Sr` instead of STOP; second command starts after `Sr`; final STOP occurs only after the `toc=1` command; both RESPs report success with matching TID/length. With broadcast-header enabled, the first private transfer emits `START + 0x7e/W + ACK + Sr + dynamic address`, and the continuation does not emit a second `0x7e` preamble.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `scl_generator`, UVM scoreboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_broadcast_addr_enable`, `cp_toc`, `cp_rstart_continuation`, `cp_private_start_prefix`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDRW_008</t>
   </si>
   <si>
     <t xml:space="preserve">Verify write-to-write sequencing.</t>
@@ -832,225 +829,234 @@
     <t xml:space="preserve">`cp_sequence_type`, `cross_tid_x_order`</t>
   </si>
   <si>
+    <t xml:space="preserve">SDRW_008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify SDR private write DAT index selection.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_write_multi_dat_idx`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; DAT[1] is I3C dynamic address `0x12`; both targets ACK; `HC_CONTROL[BROADCAST_ADDR_ENABLE]=0`.
+Stimulus / Actions: Queue a write to `dev_idx=0` and a write to `dev_idx=1` with distinct TIDs and payloads.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bus addresses are observed in order as `0x08/W` then `0x12/W`; each payload and generated T-bit sequence matches its TX FIFO data; RESP success TID/length fields match each command; queues empty afterward. Broadcast-header DAT[1] coverage is left as a future extension; broadcast-header framing is covered elsewhere with DAT[0].</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`csr_registers`, `flow_active`, `hci_queues`, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_dat_idx`, `cross_dat_idx_x_tid`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDRW_009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify HC abort during the SDR private write data phase.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_write_abort`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; device ACKs address and data; a multi-byte write is in progress in the data phase (`abort_stop_required` true); run once with `HC_CONTROL[BROADCAST_ADDR_ENABLE]=0` and once with it set.
+Stimulus / Actions: Assert `HC_CONTROL[3]` (HC abort) while the FSM is in the write data phase.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every byte already committed up to the abort point is transmitted on the bus with the correct T-bit and no garbage or extra byte; the in-flight byte plus its T-bit boundary completes, then STOP is generated and the FSM advances to `WriteResp`. This case checks only byte completeness and STOP-at-correct-state; response status/length correctness and all non-data-phase abort entry states are covered by `ERR_012`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `scl_generator`, `bus_tx_flow`, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_hc_abort`, `cp_abort_stop_state`, `cp_private_start_prefix`</t>
+  </si>
+  <si>
     <t xml:space="preserve">I3C SDR Private Read</t>
   </si>
   <si>
     <t xml:space="preserve">SDRR_001</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify baseline 4-byte SDR private read without broadcast-header preamble.</t>
+    <t xml:space="preserve">Verify baseline 4-byte SDR private read in both private-address modes.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_regular_read_4b_existing`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; `HC_CONTROL[BROADCAST_ADDR_ENABLE]=0`; target returns four bytes.
+    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; target returns four bytes; run once with `HC_CONTROL[BROADCAST_ADDR_ENABLE]=0` and once with it set.
 Stimulus / Actions: Run `i3c_read_vseq`.</t>
   </si>
   <si>
-    <t xml:space="preserve">Bus read starts with `START + 0x08/R + ACK`; no `0x7e` preamble is emitted; RX FIFO word matches the target bytes packed by the project RX FIFO contract, e.g. `32'hBEBA_FECA` for the existing stimulus; RESP success length 4.</t>
+    <t xml:space="preserve">Disabled mode starts with `START + 0x08/R + ACK` and emits no `0x7e` preamble. Enabled mode emits `START + 0x7e/W + ACK + Sr + 0x08/R + ACK` before read data. In both modes, RX FIFO word matches the target bytes packed by the project RX FIFO contract, e.g. `32'hBEBA_FECA` for the existing stimulus; RESP success length 4.</t>
   </si>
   <si>
     <t xml:space="preserve">SDRR_002</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify SDR private read with broadcast-header preamble enabled.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_read_broadcast_header_enabled`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; `HC_CONTROL[BROADCAST_ADDR_ENABLE]=1`; target ACKs broadcast header and returns read data.
-Stimulus / Actions: Issue a 4-byte regular read.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bus frame is `START + 0x7e/W + ACK + Sr + 0x08/R + ACK + read data/T-bit + STOP`; monitor/scoreboard treat the preamble and target phase as one complete transaction; RX data and RESP length match expected bytes.</t>
+    <t xml:space="preserve">Verify read lengths and RX packing in both private-address modes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_regular_read_len_sweep`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; device returns enough bytes.
+Stimulus / Actions: Run `i3c_read_len_sweep_vseq` with lengths 1,2,3,4,5,7,8,16.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each mode uses the expected private-address prefix; RX FIFO contains all bytes in little-endian DWORD packing; partial final DWORD is preserved; RESP success length matches the requested length.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `hci_queues`, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_data_len`, `cp_rx_partial_dword`, `cp_private_start_prefix`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDRR_003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify target early end handling in both private-address modes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_read_short_target_end`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; target returns T-bit end before requested length.
+Stimulus / Actions: Run `i3c_read_short_target_end_vseq` with requested length N and actual target length M&lt;N.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each mode uses the expected private-address prefix; controller does not read fake data after target early end; RX FIFO contains only transferred bytes; queues are cleaned up after the response is drained. Response descriptor encoding is checked by `ERR_004`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `bus_rx_flow`, RESP FIFO, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_short_read`, `cp_private_start_prefix`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDRR_004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify controller termination at requested length in both private-address modes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_read_target_more_than_requested`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; target can provide more bytes than requested.
+Stimulus / Actions: Run `i3c_read_target_more_than_requested_vseq` with target data longer than the command length.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each mode uses the expected private-address prefix; controller takes over after the requested byte count, stores no extra RX bytes, and reports RESP success with the requested length.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_read_end_policy`, `cp_private_start_prefix`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDRR_005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify RX FIFO full overflow flow handling in both private-address modes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_read_rx_fifo_full_overflow`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; RX FIFO is prefilled full before read data flush.
+Stimulus / Actions: Run `i3c_read_rx_fifo_full_overflow_vseq`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each mode uses the expected private-address prefix; controller takes over the read before forced STOP, preserves prefilled RX FIFO words, and leaves queues empty after drain. Response descriptor encoding is checked by `ERR_005`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `hci_queues`, `scl_generator`, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_rx_full`, `cp_stall_type`, `cp_private_start_prefix`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDRR_006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify read data integrity in both private-address modes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_read_data_patterns`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; device sequence can drive arbitrary data.
+Stimulus / Actions: Run `i3c_read_data_patterns_vseq` with all-zero, all-one, walking-one, alternating, and fixed-random patterns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each mode uses the expected private-address prefix; RX FIFO contents match target data exactly; RESP success length matches pattern length.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_driver`, `bus_rx_flow`, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_data_pattern`, `cp_private_start_prefix`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDRR_007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify read T-bit end semantics in both private-address modes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_read_no_parity_error_on_end_tbit`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; target ends transfer with T-bit=0 at the requested length.
+Stimulus / Actions: Run `i3c_read_no_parity_error_on_end_tbit_vseq`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each mode uses the expected private-address prefix; T-bit=0 is treated as end-of-data, no extra RX byte is consumed, and queues drain cleanly. Detailed RESP field classification for this same legal end condition is covered by `ERR_013`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `bus_rx_flow`, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_read_tbit`, `cp_private_start_prefix`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDRR_008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify SDR regular read continuation when `toc=0` in both private-address modes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_read_toc_zero`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; I3C device returns requested read data; a second SDR regular I3C write command is already queued.
+Stimulus / Actions: Run `i3c_read_toc_zero_vseq`: queue first read with `toc=0` and second write with `toc=1`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disabled mode starts the first read directly with dynamic address; enabled mode emits the broadcast-header preamble only before the first private read. In both modes, the first read ends with `Sr`, the continuation does not repeat the preamble, final STOP occurs only after the second command, and RX data plus both RESPs match expected length/TID.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `scl_generator`, `bus_rx_flow`, UVM scoreboard</t>
   </si>
   <si>
-    <t xml:space="preserve">`cp_broadcast_addr_enable`, `cp_private_start_prefix`, `cp_first_address`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDRR_003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify read lengths and RX packing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_regular_read_len_sweep`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Device returns enough bytes.
-Stimulus / Actions: Read lengths 1,2,3,4,5,7,8,16.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RX FIFO contains all bytes in little-endian DWORD packing; partial final DWORD is preserved.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `hci_queues`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_data_len`, `cp_rx_partial_dword`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDRR_004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify target early end handling.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_read_short_target_end`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Device returns T-bit end before requested length.
-Stimulus / Actions: Request N bytes; target ends after M&lt;N bytes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESP error is `I3cShortReadErr`; RX FIFO contains only transferred bytes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_short_read`, `cp_resp_err`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDRR_005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify controller termination at requested length.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_read_target_more_than_requested`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Device can provide more bytes.
-Stimulus / Actions: Request N bytes while target indicates continuation beyond N.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Controller terminates after N bytes with STOP when `toc=1`; no extra RX bytes are stored.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_read_end_policy`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDRR_006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify address NACK response on read.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_read_addr_nack`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Device NACKs dynamic address+R.
-Stimulus / Actions: Issue regular read.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No RX data is written; RESP error is `AddrHeader`; controller recovers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `bus_rx_flow`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDRR_007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify RX backpressure.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_read_rx_fifo_full_stall`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: RX FIFO is full before final data flush.
-Stimulus / Actions: Issue read, hold RX full, then drain RX.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Controller stalls safely and resumes; no data loss.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_rx_full`, `cp_stall_type`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDRR_008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify read data integrity.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_read_data_patterns`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Device sequence can drive arbitrary data.
-Stimulus / Actions: Return zero, one, alternating, walking, and random byte patterns.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RX FIFO contents match target data exactly.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_driver`, `bus_rx_flow`, scoreboard</t>
+    <t xml:space="preserve">`cp_broadcast_addr_enable`, `cp_toc`, `cp_rstart_continuation`, `cp_dir_read_to_write`, `cp_private_start_prefix`</t>
   </si>
   <si>
     <t xml:space="preserve">SDRR_009</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify read T-bit semantics.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_read_no_parity_error_on_end_tbit`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Target ends transfer with T-bit=0.
-Stimulus / Actions: Run read where final T-bit is 0.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per I3C SDR read semantics, T-bit=0 is an end-of-data indicator, not a parity error; response is Success if the requested length is met, otherwise `I3cShortReadErr`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_read_tbit`, `cp_resp_err`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDRR_010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify SDR regular read continuation when `toc=0`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_read_toc_zero`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: I3C device returns requested read data; a second SDR regular I3C command is already queued.
-Stimulus / Actions: Queue first read with `toc=0` and second write with `toc=1`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First read completes requested data/T-bit then emits `Sr` instead of STOP; second command starts after `Sr`; final STOP occurs only after the `toc=1` command; RX data and both RESPs match expected length/TID.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `scl_generator`, `bus_rx_flow`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_toc`, `cp_rstart_continuation`, `cp_dir_read_to_write`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDRR_011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify broadcast-header preamble is not repeated across a private read continuation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_read_toc_zero_broadcast_header_once`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: `HC_CONTROL[BROADCAST_ADDR_ENABLE]=1`; I3C device returns requested read data; a second SDR regular I3C command is already queued.
-Stimulus / Actions: Queue first read with `toc=0` and second command with `toc=1`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First command emits `START + 0x7e/W + ACK + Sr + dynamic address`; continuation after the repeated START does not emit a second `0x7e` preamble before the final STOP; RX data and RESPs remain correct.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_broadcast_addr_enable`, `cp_toc`, `cp_private_start_prefix`</t>
+    <t xml:space="preserve">Verify HC abort during the SDR private read data phase.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_read_abort`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; target returns read data; a multi-byte read is in progress in the data phase (`abort_stop_required` true); run once with `HC_CONTROL[BROADCAST_ADDR_ENABLE]=0` and once with it set.
+Stimulus / Actions: Assert `HC_CONTROL[3]` (HC abort) while the FSM is in the read data phase.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bytes already received up to the abort point are stored in the RX FIFO with correct packing and no fake bytes are read after abort; the controller completes the current byte boundary, then STOP is generated and the FSM advances to `WriteResp`. This case checks only byte completeness and STOP-at-correct-state; response status/length correctness and all non-data-phase abort entry states are covered by `ERR_012`.</t>
   </si>
   <si>
     <t xml:space="preserve">Immediate Data Transfer</t>
@@ -1066,7 +1072,7 @@
   </si>
   <si>
     <t xml:space="preserve">Preconditions: DAT[0] I3C device; target ACKs.
-Stimulus / Actions: Run `i3c_smoke_vseq`.</t>
+Stimulus / Actions: Run `i3c_imm_vseq`.</t>
   </si>
   <si>
     <t xml:space="preserve">Two inline data bytes are transmitted according to descriptor `dtt` and project packing rules; RESP success.</t>
@@ -1154,6 +1160,9 @@
     <t xml:space="preserve">Controller generates STOP immediately after address NACK; no inline data byte is transmitted; RESP error is `AddrHeader` with length 0.</t>
   </si>
   <si>
+    <t xml:space="preserve">`flow_active`, `bus_rx_flow`</t>
+  </si>
+  <si>
     <t xml:space="preserve">`cp_resp_err`, `cross_imm_x_device_type`</t>
   </si>
   <si>
@@ -1173,6 +1182,9 @@
     <t xml:space="preserve">Controller generates STOP after data NACK; no later inline data byte is transmitted; RESP error is `Nack`.</t>
   </si>
   <si>
+    <t xml:space="preserve">`flow_active`</t>
+  </si>
+  <si>
     <t xml:space="preserve">`cp_data_ack`, `cp_resp_err`</t>
   </si>
   <si>
@@ -1648,6 +1660,12 @@
     <t xml:space="preserve">Correct TX/RX packing; partial RX DWORD preserved; RESP length correct.</t>
   </si>
   <si>
+    <t xml:space="preserve">`flow_active`, `hci_queues`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_data_len`, `cp_rx_partial_dword`</t>
+  </si>
+  <si>
     <t xml:space="preserve">I2C_005</t>
   </si>
   <si>
@@ -1752,17 +1770,20 @@
     <t xml:space="preserve">ERR_002</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify address NACK error.</t>
+    <t xml:space="preserve">Verify address/header NACK response encoding.</t>
   </si>
   <si>
     <t xml:space="preserve">`resp_addr_header_error`</t>
   </si>
   <si>
     <t xml:space="preserve">Preconditions: Device NACKs address.
-Stimulus / Actions: Run I3C write/read, I2C write/read, and direct CCC address phases.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESP error is `AddrHeader` for every supported command class with an address/header NACK; no data phase occurs after address NACK.</t>
+Stimulus / Actions: Run `i3c_addr_header_nack_resp_vseq` for I3C write/read address NACK; extend to I2C write/read and direct CCC address phases as those directed tests are added.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESP status is `AddrHeader`, TID matches the command, reserved bits are zero, and length is 0 for every supported command class with address/header NACK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_resp_err`, `cp_addr_ack`, `cp_tid`, `cp_resp_len`</t>
   </si>
   <si>
     <t xml:space="preserve">ERR_003</t>
@@ -1784,39 +1805,39 @@
     <t xml:space="preserve">ERR_004</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify short read response.</t>
+    <t xml:space="preserve">Verify short read response encoding.</t>
   </si>
   <si>
     <t xml:space="preserve">`resp_short_read_error`</t>
   </si>
   <si>
     <t xml:space="preserve">Preconditions: Target ends I3C read early.
-Stimulus / Actions: Request N bytes, target ends after M&lt;N.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESP error is `I3cShortReadErr`; length reflects actual received bytes.</t>
+Stimulus / Actions: Run `i3c_short_read_resp_vseq`: request N bytes, target ends after M&lt;N.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESP status is `I3cShortReadErr`, TID matches the command, reserved bits are zero, and length reflects actual received bytes M.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_short_read`, `cp_resp_err`, `cp_tid`, `cp_resp_len`</t>
   </si>
   <si>
     <t xml:space="preserve">ERR_005</t>
   </si>
   <si>
-    <t xml:space="preserve">Document defined but unused error codes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`resp_unreachable_error_codes`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Code review plus directed unsupported stimuli.
-Stimulus / Actions: Attempt CRC, Frame, Ovl, HcAborted, NotSupported, Parity scenarios.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error codes outside the specified controller scope are N/A or enhancement requests, not positive coverage; any in-scope error code must have a spec-derived stimulus and expected response.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_pkg`, `flow_active`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_error_code_reachability`</t>
+    <t xml:space="preserve">Verify overflow response encoding.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`resp_ovl_error`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: TX FIFO underflow or RX FIFO full overflow condition.
+Stimulus / Actions: Run `i3c_ovl_resp_vseq` for TX underflow with partial/empty TX FIFO and RX FIFO full during read.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESP status is `Ovl`, TID matches the command, reserved bits are zero, and length equals the number of bytes actually processed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_resp_err_ovl`, `cp_tid`, `cp_resp_len`</t>
   </si>
   <si>
     <t xml:space="preserve">ERR_006</t>
@@ -1945,6 +1966,50 @@
     <t xml:space="preserve">`cp_invalid_cmd`</t>
   </si>
   <si>
+    <t xml:space="preserve">ERR_012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify HC abort response encoding, status priority, and non-data-phase abort entry states.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`resp_hc_abort_error`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: Controller can be aborted from selectable FSM states via `HC_CONTROL[3]`; bus-error injection available; `HC_CONTROL[3]` is a level bit that is never auto-cleared by hardware.
+Stimulus / Actions: Assert HC abort (a) during a data-phase transfer that terminates via STOP, (b) in a pre-bus state (`FetchDAT`, or `WaitDAT` with no pending continuation), (c) while idle (`Idle`/`WaitForCmd`), (d) after a bus error has already latched, and (e) leave the bit asserted across a following queued command.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(a) RESP status is `HcAborted`, TID matches the command, reserved bits zero, and length equals the bytes processed before abort. (b) No STOP and no bus activity occur; the FSM advances directly to `WriteResp` with `HcAborted`. (c) Abort is a no-op; the active/next command proceeds normally. (d) The previously latched bus error wins over `HcAborted` per the response-status priority. (e) Because the bit is not auto-cleared, the next command is also aborted until software clears `HC_CONTROL[3]`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `csr_registers`, RESP FIFO, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_hc_abort`, `cp_resp_err`, `cp_abort_entry_state`, `cp_resp_err_priority`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERR_013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify response classification for a legal SDR read final T-bit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_read_tbit_no_parity_resp`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; target ends transfer with T-bit=0 at the requested length.
+Stimulus / Actions: Run `i3c_read_tbit_no_parity_resp_vseq`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final T-bit=0 at the requested length is not classified as `Parity`; RESP is `Success`, TID matches the command, reserved bits are zero, and length matches the requested length.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, RESP FIFO, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_read_tbit`, `cp_resp_err`, `cp_tid`, `cp_resp_len`</t>
+  </si>
+  <si>
     <t xml:space="preserve">Arbitration and Bus Behavior</t>
   </si>
   <si>
@@ -2440,6 +2505,9 @@
     <t xml:space="preserve">No HDR positive tests are required until HDR datapath is implemented.</t>
   </si>
   <si>
+    <t xml:space="preserve">`i3c_pkg`, `flow_active`</t>
+  </si>
+  <si>
     <t xml:space="preserve">Section</t>
   </si>
   <si>
@@ -2506,7 +2574,7 @@
     <t xml:space="preserve">`cp_resp_err`</t>
   </si>
   <si>
-    <t xml:space="preserve">Success, AddrHeader, Nack, I3cShortReadErr, unreachable-defined-codes</t>
+    <t xml:space="preserve">Success, AddrHeader, Nack, Ovl, I3cShortReadErr, unreachable-defined-codes</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_addr_ack`</t>
@@ -3159,66 +3227,66 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="B14" t="s" s="2">
+      <c r="C14" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="C14" t="s" s="2">
+      <c r="D14" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="D14" t="s" s="2">
+      <c r="E14" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="F14" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="E14" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="F14" t="s" s="2">
+      <c r="G14" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="G14" t="s" s="2">
+      <c r="H14" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="J14" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="H14" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="B15" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="C15" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="C15" t="s" s="2">
+      <c r="D15" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="D15" t="s" s="2">
+      <c r="E15" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F15" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="E15" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="F15" t="s" s="2">
+      <c r="G15" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="G15" t="s" s="2">
+      <c r="H15" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I15" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="H15" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I15" t="s" s="2">
+      <c r="J15" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>107</v>
       </c>
     </row>
     <row r="16">
@@ -3226,28 +3294,28 @@
         <v>19</v>
       </c>
       <c r="B16" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="C16" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="C16" t="s" s="2">
+      <c r="D16" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="D16" t="s" s="2">
+      <c r="E16" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="F16" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="E16" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="F16" t="s" s="2">
+      <c r="G16" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="G16" t="s" s="2">
+      <c r="H16" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I16" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>113</v>
@@ -3276,10 +3344,10 @@
         <v>118</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>119</v>
@@ -3308,77 +3376,77 @@
         <v>124</v>
       </c>
       <c r="H18" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="J18" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>126</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="C19" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="B19" t="s" s="2">
+      <c r="D19" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="C19" t="s" s="2">
+      <c r="E19" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F19" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="D19" t="s" s="2">
+      <c r="G19" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="E19" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="F19" t="s" s="2">
+      <c r="H19" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="G19" t="s" s="2">
+      <c r="I19" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="J19" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="H19" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>134</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>19</v>
+        <v>133</v>
       </c>
       <c r="B20" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="C20" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="C20" t="s" s="2">
+      <c r="D20" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="D20" t="s" s="2">
+      <c r="E20" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="F20" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="E20" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="F20" t="s" s="2">
+      <c r="G20" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="G20" t="s" s="2">
+      <c r="H20" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I20" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="H20" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I20" t="s" s="2">
+      <c r="J20" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>141</v>
       </c>
     </row>
     <row r="21">
@@ -3386,31 +3454,31 @@
         <v>19</v>
       </c>
       <c r="B21" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="C21" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="C21" t="s" s="2">
+      <c r="D21" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="D21" t="s" s="2">
+      <c r="E21" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="F21" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="E21" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="F21" t="s" s="2">
+      <c r="G21" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="G21" t="s" s="2">
+      <c r="H21" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I21" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="H21" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I21" t="s" s="2">
+      <c r="J21" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>141</v>
       </c>
     </row>
     <row r="22">
@@ -3442,7 +3510,7 @@
         <v>153</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23">
@@ -3450,31 +3518,31 @@
         <v>19</v>
       </c>
       <c r="B23" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="C23" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="C23" t="s" s="2">
+      <c r="D23" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="D23" t="s" s="2">
+      <c r="E23" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="F23" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="E23" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="F23" t="s" s="2">
+      <c r="G23" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="G23" t="s" s="2">
+      <c r="H23" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I23" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="H23" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I23" t="s" s="2">
+      <c r="J23" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>161</v>
       </c>
     </row>
     <row r="24">
@@ -3482,31 +3550,31 @@
         <v>19</v>
       </c>
       <c r="B24" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="C24" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="C24" t="s" s="2">
+      <c r="D24" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="D24" t="s" s="2">
+      <c r="E24" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="F24" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="E24" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="F24" t="s" s="2">
+      <c r="G24" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="G24" t="s" s="2">
+      <c r="H24" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I24" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I24" t="s" s="2">
+      <c r="J24" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>168</v>
       </c>
     </row>
     <row r="25">
@@ -3514,31 +3582,31 @@
         <v>19</v>
       </c>
       <c r="B25" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="C25" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="C25" t="s" s="2">
+      <c r="D25" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="D25" t="s" s="2">
+      <c r="E25" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="F25" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="E25" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="F25" t="s" s="2">
+      <c r="G25" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="G25" t="s" s="2">
+      <c r="H25" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I25" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="H25" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I25" t="s" s="2">
+      <c r="J25" t="s" s="2">
         <v>174</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>175</v>
       </c>
     </row>
     <row r="26">
@@ -3546,31 +3614,31 @@
         <v>19</v>
       </c>
       <c r="B26" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="C26" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="C26" t="s" s="2">
+      <c r="D26" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="D26" t="s" s="2">
+      <c r="E26" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="F26" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="E26" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="F26" t="s" s="2">
+      <c r="G26" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="G26" t="s" s="2">
+      <c r="H26" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I26" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="H26" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I26" t="s" s="2">
+      <c r="J26" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>182</v>
       </c>
     </row>
     <row r="27">
@@ -3578,31 +3646,31 @@
         <v>19</v>
       </c>
       <c r="B27" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="C27" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="C27" t="s" s="2">
+      <c r="D27" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="D27" t="s" s="2">
+      <c r="E27" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="F27" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="E27" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="F27" t="s" s="2">
+      <c r="G27" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="G27" t="s" s="2">
+      <c r="H27" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I27" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="H27" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I27" t="s" s="2">
+      <c r="J27" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>189</v>
       </c>
     </row>
     <row r="28">
@@ -3610,31 +3678,31 @@
         <v>19</v>
       </c>
       <c r="B28" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="C28" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="C28" t="s" s="2">
+      <c r="D28" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="D28" t="s" s="2">
+      <c r="E28" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="F28" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="E28" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="F28" t="s" s="2">
+      <c r="G28" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="G28" t="s" s="2">
+      <c r="H28" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I28" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="H28" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I28" t="s" s="2">
+      <c r="J28" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>196</v>
       </c>
     </row>
     <row r="29">
@@ -3642,95 +3710,95 @@
         <v>19</v>
       </c>
       <c r="B29" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="C29" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="C29" t="s" s="2">
+      <c r="D29" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="D29" t="s" s="2">
+      <c r="E29" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="F29" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="E29" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="F29" t="s" s="2">
+      <c r="G29" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="G29" t="s" s="2">
+      <c r="H29" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I29" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="H29" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="I29" t="s" s="2">
+      <c r="J29" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>203</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="C30" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="B30" t="s" s="2">
+      <c r="D30" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="C30" t="s" s="2">
+      <c r="E30" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="F30" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="D30" t="s" s="2">
+      <c r="G30" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="E30" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="F30" t="s" s="2">
+      <c r="H30" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I30" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="G30" t="s" s="2">
+      <c r="J30" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>211</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>19</v>
+        <v>210</v>
       </c>
       <c r="B31" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="C31" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="C31" t="s" s="2">
+      <c r="D31" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="D31" t="s" s="2">
+      <c r="E31" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="F31" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="E31" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="F31" t="s" s="2">
+      <c r="G31" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="G31" t="s" s="2">
+      <c r="H31" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I31" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="H31" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I31" t="s" s="2">
+      <c r="J31" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>218</v>
       </c>
     </row>
     <row r="32">
@@ -3738,31 +3806,31 @@
         <v>19</v>
       </c>
       <c r="B32" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C32" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="C32" t="s" s="2">
+      <c r="D32" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="D32" t="s" s="2">
+      <c r="E32" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="F32" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="E32" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="F32" t="s" s="2">
+      <c r="G32" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="G32" t="s" s="2">
+      <c r="H32" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I32" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="H32" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="I32" t="s" s="2">
+      <c r="J32" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>225</v>
       </c>
     </row>
     <row r="33">
@@ -3770,31 +3838,31 @@
         <v>19</v>
       </c>
       <c r="B33" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="C33" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="C33" t="s" s="2">
+      <c r="D33" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="D33" t="s" s="2">
+      <c r="E33" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="F33" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="E33" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="F33" t="s" s="2">
+      <c r="G33" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="G33" t="s" s="2">
+      <c r="H33" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I33" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="H33" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I33" t="s" s="2">
+      <c r="J33" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>232</v>
       </c>
     </row>
     <row r="34">
@@ -3802,31 +3870,31 @@
         <v>19</v>
       </c>
       <c r="B34" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="C34" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="C34" t="s" s="2">
+      <c r="D34" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="D34" t="s" s="2">
+      <c r="E34" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="F34" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="E34" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="F34" t="s" s="2">
+      <c r="G34" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="G34" t="s" s="2">
+      <c r="H34" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I34" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="H34" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I34" t="s" s="2">
+      <c r="J34" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>239</v>
       </c>
     </row>
     <row r="35">
@@ -3834,31 +3902,31 @@
         <v>19</v>
       </c>
       <c r="B35" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="C35" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="C35" t="s" s="2">
+      <c r="D35" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="D35" t="s" s="2">
+      <c r="E35" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="F35" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="E35" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="F35" t="s" s="2">
+      <c r="G35" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="G35" t="s" s="2">
+      <c r="H35" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I35" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="H35" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I35" t="s" s="2">
+      <c r="J35" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>246</v>
       </c>
     </row>
     <row r="36">
@@ -3866,31 +3934,31 @@
         <v>19</v>
       </c>
       <c r="B36" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="C36" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="C36" t="s" s="2">
+      <c r="D36" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="D36" t="s" s="2">
+      <c r="E36" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="F36" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="E36" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="F36" t="s" s="2">
+      <c r="G36" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="G36" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>59</v>
       </c>
       <c r="I36" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="J36" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>253</v>
       </c>
     </row>
     <row r="37">
@@ -3898,63 +3966,63 @@
         <v>19</v>
       </c>
       <c r="B37" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="C37" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="C37" t="s" s="2">
+      <c r="D37" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="D37" t="s" s="2">
+      <c r="E37" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="F37" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="E37" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="F37" t="s" s="2">
+      <c r="G37" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="G37" t="s" s="2">
+      <c r="H37" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I37" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="H37" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I37" t="s" s="2">
+      <c r="J37" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>260</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="C38" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="B38" t="s" s="2">
+      <c r="D38" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="C38" t="s" s="2">
+      <c r="E38" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="F38" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="D38" t="s" s="2">
+      <c r="G38" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="E38" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="F38" t="s" s="2">
+      <c r="H38" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I38" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="G38" t="s" s="2">
+      <c r="J38" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>211</v>
       </c>
     </row>
     <row r="39">
@@ -3991,34 +4059,34 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>19</v>
+        <v>274</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D40" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="E40" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="E40" t="s" s="2">
-        <v>275</v>
-      </c>
       <c r="F40" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>279</v>
+        <v>216</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>280</v>
+        <v>217</v>
       </c>
     </row>
     <row r="41">
@@ -4026,28 +4094,28 @@
         <v>19</v>
       </c>
       <c r="B41" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="C41" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="C41" t="s" s="2">
+      <c r="D41" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="D41" t="s" s="2">
+      <c r="E41" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="F41" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="E41" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="F41" t="s" s="2">
+      <c r="G41" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="G41" t="s" s="2">
+      <c r="H41" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I41" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="J41" t="s" s="2">
         <v>286</v>
@@ -4079,10 +4147,10 @@
         <v>16</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>167</v>
+        <v>292</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="43">
@@ -4090,31 +4158,31 @@
         <v>19</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D43" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="E43" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="E43" t="s" s="2">
-        <v>294</v>
-      </c>
       <c r="F43" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>298</v>
+        <v>251</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>239</v>
+        <v>299</v>
       </c>
     </row>
     <row r="44">
@@ -4122,31 +4190,31 @@
         <v>19</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D44" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="E44" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="E44" t="s" s="2">
-        <v>300</v>
-      </c>
       <c r="F44" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>245</v>
+        <v>305</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45">
@@ -4154,31 +4222,31 @@
         <v>19</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>59</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>225</v>
+        <v>313</v>
       </c>
     </row>
     <row r="46">
@@ -4186,31 +4254,31 @@
         <v>19</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F46" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="47">
@@ -4218,31 +4286,31 @@
         <v>19</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F47" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>59</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="48">
@@ -4250,63 +4318,63 @@
         <v>19</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C48" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="D48" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="E48" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="F48" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I48" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="D48" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="E48" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="F48" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="G48" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>272</v>
-      </c>
       <c r="J48" t="s" s="2">
-        <v>330</v>
+        <v>273</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F49" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="50">
@@ -4314,31 +4382,31 @@
         <v>19</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F50" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="51">
@@ -4346,31 +4414,31 @@
         <v>19</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F51" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>59</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="52">
@@ -4378,31 +4446,31 @@
         <v>19</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F52" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="53">
@@ -4410,31 +4478,31 @@
         <v>19</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F53" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>298</v>
+        <v>365</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="54">
@@ -4442,63 +4510,63 @@
         <v>19</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F54" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>316</v>
+        <v>372</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F55" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="56">
@@ -4506,31 +4574,31 @@
         <v>19</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="F56" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="57">
@@ -4538,31 +4606,31 @@
         <v>19</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="F57" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>316</v>
+        <v>372</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="58">
@@ -4570,31 +4638,31 @@
         <v>19</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F58" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="59">
@@ -4602,31 +4670,31 @@
         <v>19</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F59" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>316</v>
+        <v>372</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="60">
@@ -4634,31 +4702,31 @@
         <v>19</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F60" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="61">
@@ -4666,31 +4734,31 @@
         <v>19</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F61" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>316</v>
+        <v>372</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="62">
@@ -4698,63 +4766,63 @@
         <v>19</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F62" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>59</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="F63" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="64">
@@ -4762,31 +4830,31 @@
         <v>19</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="F64" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="65">
@@ -4794,31 +4862,31 @@
         <v>19</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F65" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="66">
@@ -4826,31 +4894,31 @@
         <v>19</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="F66" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="67">
@@ -4858,31 +4926,31 @@
         <v>19</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="F67" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="68">
@@ -4890,31 +4958,31 @@
         <v>19</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="69">
@@ -4922,31 +4990,31 @@
         <v>19</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="F69" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="70">
@@ -4954,31 +5022,31 @@
         <v>19</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="E70" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F70" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>59</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="71">
@@ -4986,31 +5054,31 @@
         <v>19</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="F71" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>59</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="72">
@@ -5018,63 +5086,63 @@
         <v>19</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F72" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F73" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="74">
@@ -5082,31 +5150,31 @@
         <v>19</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F74" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="75">
@@ -5114,31 +5182,31 @@
         <v>19</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="F75" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="76">
@@ -5146,31 +5214,31 @@
         <v>19</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F76" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>279</v>
+        <v>524</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>280</v>
+        <v>525</v>
       </c>
     </row>
     <row r="77">
@@ -5178,31 +5246,31 @@
         <v>19</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="E77" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="F77" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>298</v>
+        <v>365</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>525</v>
+        <v>531</v>
       </c>
     </row>
     <row r="78">
@@ -5210,31 +5278,31 @@
         <v>19</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="F78" t="s" s="2">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>316</v>
+        <v>372</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="79">
@@ -5242,31 +5310,31 @@
         <v>19</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="E79" t="s" s="2">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="F79" t="s" s="2">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>537</v>
+        <v>543</v>
       </c>
     </row>
     <row r="80">
@@ -5274,63 +5342,63 @@
         <v>19</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="F80" t="s" s="2">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>59</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>544</v>
+        <v>550</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="F81" t="s" s="2">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>551</v>
+        <v>557</v>
       </c>
     </row>
     <row r="82">
@@ -5338,31 +5406,31 @@
         <v>19</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="F82" t="s" s="2">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>316</v>
+        <v>412</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>239</v>
+        <v>563</v>
       </c>
     </row>
     <row r="83">
@@ -5370,31 +5438,31 @@
         <v>19</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="F83" t="s" s="2">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>316</v>
+        <v>372</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="84">
@@ -5402,31 +5470,31 @@
         <v>19</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="E84" t="s" s="2">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="F84" t="s" s="2">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>316</v>
+        <v>412</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>286</v>
+        <v>574</v>
       </c>
     </row>
     <row r="85">
@@ -5434,31 +5502,31 @@
         <v>19</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="F85" t="s" s="2">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>125</v>
+        <v>16</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>572</v>
+        <v>412</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>573</v>
+        <v>580</v>
       </c>
     </row>
     <row r="86">
@@ -5466,31 +5534,31 @@
         <v>19</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="E86" t="s" s="2">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="F86" t="s" s="2">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>279</v>
+        <v>524</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>579</v>
+        <v>586</v>
       </c>
     </row>
     <row r="87">
@@ -5498,31 +5566,31 @@
         <v>19</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="E87" t="s" s="2">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="F87" t="s" s="2">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>586</v>
+        <v>593</v>
       </c>
     </row>
     <row r="88">
@@ -5530,31 +5598,31 @@
         <v>19</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="F88" t="s" s="2">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>592</v>
+        <v>599</v>
       </c>
     </row>
     <row r="89">
@@ -5562,31 +5630,31 @@
         <v>19</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="E89" t="s" s="2">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="F89" t="s" s="2">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>59</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>599</v>
+        <v>606</v>
       </c>
     </row>
     <row r="90">
@@ -5594,31 +5662,31 @@
         <v>19</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="E90" t="s" s="2">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="F90" t="s" s="2">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>59</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>606</v>
+        <v>613</v>
       </c>
     </row>
     <row r="91">
@@ -5626,63 +5694,63 @@
         <v>19</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="F91" t="s" s="2">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>59</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>613</v>
+        <v>620</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>614</v>
+        <v>19</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="E92" t="s" s="2">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="F92" t="s" s="2">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>621</v>
+        <v>627</v>
       </c>
     </row>
     <row r="93">
@@ -5690,63 +5758,63 @@
         <v>19</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="F93" t="s" s="2">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>490</v>
+        <v>16</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>492</v>
+        <v>634</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>19</v>
+        <v>635</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="D94" t="s" s="2">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="E94" t="s" s="2">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="F94" t="s" s="2">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>634</v>
+        <v>642</v>
       </c>
     </row>
     <row r="95">
@@ -5754,63 +5822,63 @@
         <v>19</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="D95" t="s" s="2">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="E95" t="s" s="2">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="F95" t="s" s="2">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>59</v>
+        <v>494</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>605</v>
+        <v>648</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>640</v>
+        <v>496</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>641</v>
+        <v>19</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="E96" t="s" s="2">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="F96" t="s" s="2">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>648</v>
+        <v>655</v>
       </c>
     </row>
     <row r="97">
@@ -5818,63 +5886,63 @@
         <v>19</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="F97" t="s" s="2">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>654</v>
+        <v>612</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>655</v>
+        <v>661</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>19</v>
+        <v>662</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="D98" t="s" s="2">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="E98" t="s" s="2">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="F98" t="s" s="2">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>655</v>
+        <v>669</v>
       </c>
     </row>
     <row r="99">
@@ -5882,31 +5950,31 @@
         <v>19</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="D99" t="s" s="2">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="E99" t="s" s="2">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="F99" t="s" s="2">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>668</v>
+        <v>676</v>
       </c>
     </row>
     <row r="100">
@@ -5914,31 +5982,31 @@
         <v>19</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="D100" t="s" s="2">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="E100" t="s" s="2">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="F100" t="s" s="2">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>667</v>
+        <v>682</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="101">
@@ -5946,31 +6014,31 @@
         <v>19</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="D101" t="s" s="2">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="F101" t="s" s="2">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>681</v>
+        <v>689</v>
       </c>
     </row>
     <row r="102">
@@ -5978,31 +6046,31 @@
         <v>19</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="D102" t="s" s="2">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="E102" t="s" s="2">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="F102" t="s" s="2">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>688</v>
+        <v>695</v>
       </c>
     </row>
     <row r="103">
@@ -6010,63 +6078,63 @@
         <v>19</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="D103" t="s" s="2">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="F103" t="s" s="2">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="I103" t="s" s="2">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>695</v>
+        <v>702</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>696</v>
+        <v>19</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="D104" t="s" s="2">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="F104" t="s" s="2">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>703</v>
+        <v>709</v>
       </c>
     </row>
     <row r="105">
@@ -6074,63 +6142,63 @@
         <v>19</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="D105" t="s" s="2">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="E105" t="s" s="2">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="F105" t="s" s="2">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>710</v>
+        <v>716</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>19</v>
+        <v>717</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="D106" t="s" s="2">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="E106" t="s" s="2">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="F106" t="s" s="2">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>702</v>
+        <v>723</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>716</v>
+        <v>724</v>
       </c>
     </row>
     <row r="107">
@@ -6138,31 +6206,31 @@
         <v>19</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="D107" t="s" s="2">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="E107" t="s" s="2">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="F107" t="s" s="2">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I107" t="s" s="2">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>723</v>
+        <v>731</v>
       </c>
     </row>
     <row r="108">
@@ -6170,31 +6238,31 @@
         <v>19</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="D108" t="s" s="2">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="E108" t="s" s="2">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="F108" t="s" s="2">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>702</v>
+        <v>723</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>729</v>
+        <v>737</v>
       </c>
     </row>
     <row r="109">
@@ -6202,31 +6270,31 @@
         <v>19</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="D109" t="s" s="2">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="E109" t="s" s="2">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="F109" t="s" s="2">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>125</v>
+        <v>16</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>702</v>
+        <v>743</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>735</v>
+        <v>744</v>
       </c>
     </row>
     <row r="110">
@@ -6234,31 +6302,31 @@
         <v>19</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>736</v>
+        <v>745</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>737</v>
+        <v>746</v>
       </c>
       <c r="D110" t="s" s="2">
-        <v>738</v>
+        <v>747</v>
       </c>
       <c r="E110" t="s" s="2">
-        <v>737</v>
+        <v>746</v>
       </c>
       <c r="F110" t="s" s="2">
-        <v>739</v>
+        <v>748</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>740</v>
+        <v>749</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>125</v>
+        <v>59</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>702</v>
+        <v>723</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>735</v>
+        <v>750</v>
       </c>
     </row>
     <row r="111">
@@ -6266,63 +6334,63 @@
         <v>19</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>741</v>
+        <v>751</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>742</v>
+        <v>752</v>
       </c>
       <c r="D111" t="s" s="2">
-        <v>743</v>
+        <v>753</v>
       </c>
       <c r="E111" t="s" s="2">
-        <v>742</v>
+        <v>752</v>
       </c>
       <c r="F111" t="s" s="2">
-        <v>744</v>
+        <v>754</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>745</v>
+        <v>755</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>167</v>
+        <v>723</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>746</v>
+        <v>756</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>747</v>
+        <v>19</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>748</v>
+        <v>757</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>749</v>
+        <v>758</v>
       </c>
       <c r="D112" t="s" s="2">
-        <v>750</v>
+        <v>759</v>
       </c>
       <c r="E112" t="s" s="2">
-        <v>749</v>
+        <v>758</v>
       </c>
       <c r="F112" t="s" s="2">
-        <v>751</v>
+        <v>760</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>752</v>
+        <v>761</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>753</v>
+        <v>723</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="113">
@@ -6330,63 +6398,63 @@
         <v>19</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="D113" t="s" s="2">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="E113" t="s" s="2">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="F113" t="s" s="2">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>753</v>
+        <v>173</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>754</v>
+        <v>767</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>19</v>
+        <v>768</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>761</v>
+        <v>770</v>
       </c>
       <c r="D114" t="s" s="2">
-        <v>762</v>
+        <v>771</v>
       </c>
       <c r="E114" t="s" s="2">
-        <v>761</v>
+        <v>770</v>
       </c>
       <c r="F114" t="s" s="2">
-        <v>763</v>
+        <v>772</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>764</v>
+        <v>773</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>765</v>
+        <v>774</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>754</v>
+        <v>775</v>
       </c>
     </row>
     <row r="115">
@@ -6394,31 +6462,95 @@
         <v>19</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>766</v>
+        <v>776</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>767</v>
+        <v>777</v>
       </c>
       <c r="D115" t="s" s="2">
-        <v>768</v>
+        <v>778</v>
       </c>
       <c r="E115" t="s" s="2">
-        <v>767</v>
+        <v>777</v>
       </c>
       <c r="F115" t="s" s="2">
-        <v>769</v>
+        <v>779</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>770</v>
+        <v>780</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="I115" t="s" s="2">
-        <v>572</v>
+        <v>774</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>754</v>
+        <v>775</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="D116" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="E116" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="F116" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="D117" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="E117" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="F117" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>775</v>
       </c>
     </row>
   </sheetData>
@@ -6430,18 +6562,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>771</v>
+        <v>793</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>772</v>
+        <v>794</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>773</v>
+        <v>795</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>774</v>
+        <v>796</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>19</v>
@@ -6455,10 +6587,10 @@
         <v>19</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>775</v>
+        <v>797</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>776</v>
+        <v>798</v>
       </c>
     </row>
     <row r="4">
@@ -6466,10 +6598,10 @@
         <v>19</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>777</v>
+        <v>799</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>778</v>
+        <v>800</v>
       </c>
     </row>
     <row r="5">
@@ -6477,10 +6609,10 @@
         <v>19</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>779</v>
+        <v>801</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>780</v>
+        <v>802</v>
       </c>
     </row>
     <row r="6">
@@ -6488,10 +6620,10 @@
         <v>19</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>781</v>
+        <v>803</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>782</v>
+        <v>804</v>
       </c>
     </row>
     <row r="7">
@@ -6499,10 +6631,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>783</v>
+        <v>805</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>784</v>
+        <v>806</v>
       </c>
     </row>
     <row r="8">
@@ -6510,10 +6642,10 @@
         <v>19</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>785</v>
+        <v>807</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>786</v>
+        <v>808</v>
       </c>
     </row>
     <row r="9">
@@ -6521,10 +6653,10 @@
         <v>19</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>787</v>
+        <v>809</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>788</v>
+        <v>810</v>
       </c>
     </row>
     <row r="10">
@@ -6532,10 +6664,10 @@
         <v>19</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>789</v>
+        <v>811</v>
       </c>
     </row>
     <row r="11">
@@ -6543,10 +6675,10 @@
         <v>19</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>790</v>
+        <v>812</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>791</v>
+        <v>813</v>
       </c>
     </row>
     <row r="12">
@@ -6554,10 +6686,10 @@
         <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>792</v>
+        <v>814</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>793</v>
+        <v>815</v>
       </c>
     </row>
     <row r="13">
@@ -6565,10 +6697,10 @@
         <v>19</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>794</v>
+        <v>816</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>795</v>
+        <v>817</v>
       </c>
     </row>
     <row r="14">
@@ -6576,10 +6708,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>796</v>
+        <v>818</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>797</v>
+        <v>819</v>
       </c>
     </row>
     <row r="15">
@@ -6587,10 +6719,10 @@
         <v>19</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>798</v>
+        <v>820</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>799</v>
+        <v>821</v>
       </c>
     </row>
     <row r="16">
@@ -6598,10 +6730,10 @@
         <v>19</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>800</v>
+        <v>822</v>
       </c>
     </row>
     <row r="17">
@@ -6609,10 +6741,10 @@
         <v>19</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>801</v>
+        <v>823</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>802</v>
+        <v>824</v>
       </c>
     </row>
     <row r="18">
@@ -6620,10 +6752,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>803</v>
+        <v>825</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>804</v>
+        <v>826</v>
       </c>
     </row>
     <row r="19">
@@ -6631,10 +6763,10 @@
         <v>19</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>805</v>
+        <v>827</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>806</v>
+        <v>828</v>
       </c>
     </row>
     <row r="20">
@@ -6642,10 +6774,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>807</v>
+        <v>829</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>808</v>
+        <v>830</v>
       </c>
     </row>
     <row r="21">
@@ -6653,10 +6785,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>809</v>
+        <v>831</v>
       </c>
     </row>
     <row r="22">
@@ -6664,10 +6796,10 @@
         <v>19</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>810</v>
+        <v>832</v>
       </c>
     </row>
     <row r="23">
@@ -6675,10 +6807,10 @@
         <v>19</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>811</v>
+        <v>833</v>
       </c>
     </row>
     <row r="24">
@@ -6686,10 +6818,10 @@
         <v>19</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>812</v>
+        <v>834</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>813</v>
+        <v>835</v>
       </c>
     </row>
     <row r="25">
@@ -6697,10 +6829,10 @@
         <v>19</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>814</v>
+        <v>836</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>815</v>
+        <v>837</v>
       </c>
     </row>
     <row r="26">
@@ -6708,10 +6840,10 @@
         <v>19</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>816</v>
+        <v>838</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>817</v>
+        <v>839</v>
       </c>
     </row>
     <row r="27">
@@ -6719,10 +6851,10 @@
         <v>19</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>818</v>
+        <v>840</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>819</v>
+        <v>841</v>
       </c>
     </row>
     <row r="28">
@@ -6730,10 +6862,10 @@
         <v>19</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>820</v>
+        <v>842</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>821</v>
+        <v>843</v>
       </c>
     </row>
     <row r="29">
@@ -6741,10 +6873,10 @@
         <v>19</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>822</v>
+        <v>844</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>823</v>
+        <v>845</v>
       </c>
     </row>
     <row r="30">
@@ -6752,10 +6884,10 @@
         <v>19</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>824</v>
+        <v>846</v>
       </c>
     </row>
     <row r="31">
@@ -6771,7 +6903,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>825</v>
+        <v>847</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>19</v>
@@ -6785,10 +6917,10 @@
         <v>19</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>826</v>
+        <v>848</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>827</v>
+        <v>849</v>
       </c>
     </row>
     <row r="34">
@@ -6796,10 +6928,10 @@
         <v>19</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>828</v>
+        <v>850</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>829</v>
+        <v>851</v>
       </c>
     </row>
     <row r="35">
@@ -6807,10 +6939,10 @@
         <v>19</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>830</v>
+        <v>852</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>831</v>
+        <v>853</v>
       </c>
     </row>
     <row r="36">
@@ -6818,10 +6950,10 @@
         <v>19</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>832</v>
+        <v>854</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>833</v>
+        <v>855</v>
       </c>
     </row>
     <row r="37">
@@ -6829,10 +6961,10 @@
         <v>19</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>834</v>
+        <v>856</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>835</v>
+        <v>857</v>
       </c>
     </row>
     <row r="38">
@@ -6840,10 +6972,10 @@
         <v>19</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>836</v>
+        <v>858</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>837</v>
+        <v>859</v>
       </c>
     </row>
     <row r="39">
@@ -6851,10 +6983,10 @@
         <v>19</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>838</v>
+        <v>860</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>839</v>
+        <v>861</v>
       </c>
     </row>
     <row r="40">
@@ -6862,10 +6994,10 @@
         <v>19</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>840</v>
+        <v>862</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>841</v>
+        <v>863</v>
       </c>
     </row>
     <row r="41">
@@ -6873,10 +7005,10 @@
         <v>19</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>842</v>
+        <v>864</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>843</v>
+        <v>865</v>
       </c>
     </row>
     <row r="42">
@@ -6884,10 +7016,10 @@
         <v>19</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>844</v>
+        <v>866</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>845</v>
+        <v>867</v>
       </c>
     </row>
     <row r="43">
@@ -6895,10 +7027,10 @@
         <v>19</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>846</v>
+        <v>868</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>847</v>
+        <v>869</v>
       </c>
     </row>
   </sheetData>
@@ -6913,43 +7045,43 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>848</v>
+        <v>870</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>849</v>
+        <v>871</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>850</v>
+        <v>872</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>731</v>
+        <v>752</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>734</v>
+        <v>755</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>851</v>
+        <v>873</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>737</v>
+        <v>758</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>740</v>
+        <v>761</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>852</v>
+        <v>874</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>742</v>
+        <v>763</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>745</v>
+        <v>766</v>
       </c>
     </row>
   </sheetData>
@@ -6973,58 +7105,58 @@
         <v>4</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>853</v>
+        <v>875</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>730</v>
+        <v>751</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>696</v>
+        <v>717</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>732</v>
+        <v>753</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>731</v>
+        <v>752</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>735</v>
+        <v>756</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>736</v>
+        <v>757</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>696</v>
+        <v>717</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>738</v>
+        <v>759</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>737</v>
+        <v>758</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>735</v>
+        <v>756</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>741</v>
+        <v>762</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>696</v>
+        <v>717</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>743</v>
+        <v>764</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>742</v>
+        <v>763</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>746</v>
+        <v>767</v>
       </c>
     </row>
   </sheetData>

--- a/docs/test_plan/I3C_Testplan.xlsx
+++ b/docs/test_plan/I3C_Testplan.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="876">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="900">
   <si>
     <t xml:space="preserve">Category</t>
   </si>
@@ -56,7 +56,7 @@
   </si>
   <si>
     <t xml:space="preserve">Preconditions: Reset applied and released.
-Stimulus / Actions: Read `HC_CONTROL`, `HC_STATUS`, all timing registers, `QUEUE_STATUS`, and DAT[0..15].</t>
+Stimulus / Actions: Read `HC_CONTROL`, `HC_STATUS`, all timing registers, `QUEUE_STATUS`, and DAT[0..31].</t>
   </si>
   <si>
     <t xml:space="preserve">Enable is 0; FSM idle/status reflects idle; queue flags show empty; DAT entries are 0; timing defaults match the CSR/module specification.</t>
@@ -147,7 +147,7 @@
   </si>
   <si>
     <t xml:space="preserve">Preconditions: Controller idle.
-Stimulus / Actions: Write DAT[0..15] with varied static address, dynamic address, and `device` bit; read back.</t>
+Stimulus / Actions: Write DAT[0..31] with varied static address, dynamic address, and `device` bit; read back.</t>
   </si>
   <si>
     <t xml:space="preserve">DAT bit fields match `[31]`, `[22:16]`, and `[6:0]`; no adjacent entry corruption.</t>
@@ -317,7 +317,7 @@
 Stimulus / Actions: Read `HC_CONTROL[3]` after reset; set and clear the bit through `HC_CONTROL`; set only this bit without `HC_CONTROL[0]`; hold it set across several read cycles and a queued command.</t>
   </si>
   <si>
-    <t xml:space="preserve">Reset value is 0; writable set/clear behavior is correct; the bit is never auto-cleared by hardware and holds its written value until software clears it; setting it alone does not enable the controller. The abort effect on an active transfer and its response encoding are covered by `SDRW_009`, `SDRR_009`, and `ERR_012`.</t>
+    <t xml:space="preserve">Reset value is 0; writable set/clear behavior is correct; the bit is never auto-cleared by hardware and holds its written value until software clears it; setting it alone does not enable the controller. The abort effect on an active transfer and its response encoding are covered by `SDRW_009`, `SDRR_009`, and `ERR_007`.</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_hc_abort`, `cp_csr_addr`</t>
@@ -672,6 +672,25 @@
     <t xml:space="preserve">`cp_pad_model`, `cp_sda_oe`, `cp_tb_odpp_visibility`</t>
   </si>
   <si>
+    <t xml:space="preserve">BUS_012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that I2C legacy transfers never activate push-pull mode.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`bus_i2c_od_only_check`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: DAT[0].`device=1` with static address programmed; target ACKs all bytes.
+Stimulus / Actions: Issue I2C read and write commands; observe `sel_od_pp_o` and SDA drive at every phase: START, address, ACK, data bytes, final NACK, STOP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`sel_od_pp_o` remains `0` (open-drain) for the entire I2C transaction — at no point does the controller assert PP. Complements BUS_010, which establishes that I3C SDR data phases do switch to PP; together they give `cp_odpp_phase × cp_device_type` cross-coverage showing OD/PP behavior is correctly conditioned on device type.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_odpp_phase`, `cp_device_type`, `cross_odpp_x_device_type`</t>
+  </si>
+  <si>
     <t xml:space="preserve">I3C SDR Private Write</t>
   </si>
   <si>
@@ -688,7 +707,7 @@
 Stimulus / Actions: Run `i3c_write_vseq` with TX word `DEAD_BEEF`.</t>
   </si>
   <si>
-    <t xml:space="preserve">Bus write starts with `START + 0x08/W + ACK`; no `0x7e` preamble is emitted; data byte order follows the project TX FIFO packing contract; RESP success length 4.</t>
+    <t xml:space="preserve">Bus write starts with `START + 0x08/W + ACK`; no `0x7e` preamble is emitted; **device model observes exactly 4 bytes in little-endian order `[EF, BE, AD, DE]` matching the TX FIFO word** (data integrity check: `sampled_data[i]` == `tx_word[(i*8)+:8]` for i=0..3); RESP success length 4; both private-address modes pass this byte-level check.</t>
   </si>
   <si>
     <t xml:space="preserve">Full DUT, UVM scoreboard</t>
@@ -710,7 +729,7 @@
 Stimulus / Actions: Write lengths 0,1,2,3,4,5,7,8,16,64,256 using patterned TX words in both private-address modes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Exact byte count transmitted; correct byte order and T-bit parity; RESP length equals bytes transferred. Length 0 ACKs address then STOPs with no data/T-bit and success length 0. Length 256 consumes 64 TX DWORDs in order and leaves queues empty. Disabled mode starts directly with `START + 0x08/W`; enabled mode emits `START + 0x7e/W + ACK + Sr + 0x08/W` before data.</t>
+    <t xml:space="preserve">Exact byte count transmitted; **for every length N&gt;0, `sampled_data[i]` matches the TX FIFO byte at position i in little-endian DWORD unpacking order for all i &lt; N** (data integrity check); correct T-bit parity; RESP length equals bytes transferred. Length 0 ACKs address then STOPs with no data/T-bit and success length 0. Length 256 consumes 64 TX DWORDs in order and leaves queues empty. Disabled mode starts directly with `START + 0x08/W`; enabled mode emits `START + 0x7e/W + ACK + Sr + 0x08/W` before data.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `hci_queues`, `bus_tx_flow`, UVM scoreboard</t>
@@ -776,7 +795,7 @@
 Stimulus / Actions: Issue an 8-byte write with only one TX DWORD available; issue 4-byte and 8-byte writes with no TX data; run both `toc=1` and `toc=0` in both private-address modes. Also write a late TX DWORD after an aborted underflow.</t>
   </si>
   <si>
-    <t xml:space="preserve">Controller transfers only available bytes, never transmits garbage, does not enter old `StallWrite`, and generates STOP. For `toc=0`, underflow still terminates with STOP and must not create a Repeated START/continuation. Late refill remains in TX FIFO until SW reset flushes queues. Response descriptor encoding is checked by `ERR_005`.</t>
+    <t xml:space="preserve">**Data integrity boundary (primary intent):** every byte that was actually available in the TX FIFO is transmitted correctly in little-endian order; only the bytes beyond the underflow point are absent, and the controller never fabricates or transmits garbage to fill the gap. The controller does not enter the old `StallWrite` and generates STOP. For `toc=0`, underflow still terminates with STOP and must not create a Repeated START/continuation. A late-arriving TX DWORD is not consumed by the aborted transfer — it remains in the TX FIFO until SW reset flushes queues. Response descriptor encoding for the underflow is verified by `ERR_006`.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `hci_queues`, `scl_generator`</t>
@@ -788,17 +807,17 @@
     <t xml:space="preserve">SDRW_006</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify SDR regular write continuation when `toc=0`, including broadcast-header-enabled private continuation framing and missing-continuation policy.</t>
+    <t xml:space="preserve">Verify SDR regular write continuation when `toc=0`, data integrity across the RSTART boundary, and missing-continuation policy.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_write_toc_zero`</t>
   </si>
   <si>
     <t xml:space="preserve">Preconditions: I3C device ACKs; valid-continuation subcase has a second SDR regular I3C command already queued; run once with `HC_CONTROL[BROADCAST_ADDR_ENABLE]=0` and once with it set.
-Stimulus / Actions: Queue first write with `toc=0` and second write with `toc=1`; separately issue a `toc=0` write with no next supported command.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valid case: first write completes data/T-bit then emits `Sr` instead of STOP; second command starts after `Sr`; final STOP occurs only after the `toc=1` command; both RESPs report success with matching TID/length. With broadcast-header enabled, only the first private transfer emits the `0x7e` preamble. Negative case: the first write data is transmitted, controller emits STOP instead of RSTART, and RESP is `NotSupported` with actual length transmitted.</t>
+Stimulus / Actions: Queue first write (`toc=0`) and second write (`toc=1`) with distinct payloads; separately issue a `toc=0` write with no next supported command.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valid case: first write completes data/T-bit then emits `Sr`; **data integrity check: for each transfer, `sampled_data[i]` matches its own TX FIFO byte slice** — confirming the RSTART boundary does not cause data loss, duplication, or cross-command mixing; second command starts after `Sr`; final STOP occurs only after the `toc=1` command; both RESPs report success with matching TID/length. With broadcast-header enabled, only the first private transfer emits the `0x7e` preamble. Negative case: the first write data is transmitted, controller emits STOP instead of RSTART, and RESP is `NotSupported` with actual length transmitted.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `scl_generator`, UVM scoreboard</t>
@@ -810,17 +829,17 @@
     <t xml:space="preserve">SDRW_007</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify write-to-write sequencing.</t>
+    <t xml:space="preserve">Verify write-to-write sequencing and per-segment data integrity.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_write_back_to_back`</t>
   </si>
   <si>
     <t xml:space="preserve">Preconditions: Multiple TX data words and commands queued.
-Stimulus / Actions: Queue several write commands with unique TIDs and data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commands execute FIFO order; each RESP TID/length matches; no stale TX data.</t>
+Stimulus / Actions: Queue several write commands with unique TIDs and distinct payloads; each command owns a distinct word-aligned slice of the TX FIFO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commands execute in FIFO order; each RESP TID/length matches; **for each command, `sampled_data[i]` matches the TX FIFO byte at the correct offset for that segment** — verifying that the TX FIFO consumption boundary between commands is exact and no byte is shared, dropped, or duplicated across segments; each transfer ends with STOP (no RSTART).</t>
   </si>
   <si>
     <t xml:space="preserve">`hci_queues`, `flow_active`, scoreboard</t>
@@ -832,17 +851,17 @@
     <t xml:space="preserve">SDRW_008</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify SDR private write DAT index selection.</t>
+    <t xml:space="preserve">Verify SDR private write DAT index selection and per-target data integrity.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_write_multi_dat_idx`</t>
   </si>
   <si>
     <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; DAT[1] is I3C dynamic address `0x12`; both targets ACK; `HC_CONTROL[BROADCAST_ADDR_ENABLE]=0`.
-Stimulus / Actions: Queue a write to `dev_idx=0` and a write to `dev_idx=1` with distinct TIDs and payloads.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bus addresses are observed in order as `0x08/W` then `0x12/W`; each payload and generated T-bit sequence matches its TX FIFO data; RESP success TID/length fields match each command; queues empty afterward. Broadcast-header DAT[1] coverage is left as a future extension; broadcast-header framing is covered elsewhere with DAT[0].</t>
+Stimulus / Actions: Queue a write to `dev_idx=0` and a write to `dev_idx=1` with distinct TIDs and payloads; also run a `toc=0` continuation case with each command targeting a different DAT index.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bus addresses are observed in order as `0x08/W` then `0x12/W`; **each target's `sampled_data[i]` matches its own TX FIFO byte slice byte-by-byte** — confirming the TX FIFO is partitioned correctly between targets and no payload crosses the address boundary; RESP success TID/length fields match each command; for the `toc=0` case, exactly one RSTART separates the two targets and each target's data is independently verified; queues empty afterward. Broadcast-header DAT[1] coverage is left as a future extension; broadcast-header framing is covered elsewhere with DAT[0].</t>
   </si>
   <si>
     <t xml:space="preserve">`csr_registers`, `flow_active`, `hci_queues`, UVM scoreboard</t>
@@ -854,17 +873,17 @@
     <t xml:space="preserve">SDRW_009</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify HC abort during the SDR private write data phase.</t>
+    <t xml:space="preserve">Verify HC abort during the SDR private write data phase, including data integrity of bytes sent before abort.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_write_abort`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; device ACKs address and data; a multi-byte write is in progress in the data phase (`abort_stop_required` true); run once with `HC_CONTROL[BROADCAST_ADDR_ENABLE]=0` and once with it set.
+    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; device ACKs address and data; a multi-byte write is in progress in the data phase (`abort_stop_required` true); run once with `HC_CONTROL[BROADCAST_ADDR_ENABLE]=0` and once with it set; run an early case (abort fires at FSM entry before data starts), a deep case (abort fires after at least one TX FIFO word is consumed), and a `toc=0` case (abort must override the continuation request).
 Stimulus / Actions: Assert `HC_CONTROL[3]` (HC abort) while the FSM is in the write data phase.</t>
   </si>
   <si>
-    <t xml:space="preserve">Every byte already committed up to the abort point is transmitted on the bus with the correct T-bit and no garbage or extra byte; the in-flight byte plus its T-bit boundary completes, then STOP is generated and the FSM advances to `WriteResp`. This case checks only byte completeness and STOP-at-correct-state; response status/length correctness and all non-data-phase abort entry states are covered by `ERR_012`.</t>
+    <t xml:space="preserve">**Data integrity check (primary pass condition):** for every byte i that was driven on the bus before abort (`sampled_data[i]`), the value must equal the TX FIFO byte at position i in little-endian DWORD order — no valid pre-abort byte may be dropped or corrupted; the number of bytes sampled is at most the number sent before the abort boundary. The in-flight byte plus its T-bit boundary completes, then STOP is generated. **Error overrides continuation:** when the aborted write was programmed `toc=0`, abort still forces STOP and `HcAborted` — `observed_rstart=0` confirms a write abort ends with STOP, not a continuation RSTART. After abort, SW reset flushes any remaining TX FIFO data and leaves all queues empty. Response status/length correctness and all non-data-phase abort entry states are covered by `ERR_007`.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `scl_generator`, `bus_tx_flow`, UVM scoreboard</t>
@@ -886,16 +905,16 @@
   </si>
   <si>
     <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; target returns four bytes; run once with `HC_CONTROL[BROADCAST_ADDR_ENABLE]=0` and once with it set.
-Stimulus / Actions: Run `i3c_read_vseq`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disabled mode starts with `START + 0x08/R + ACK` and emits no `0x7e` preamble. Enabled mode emits `START + 0x7e/W + ACK + Sr + 0x08/R + ACK` before read data. In both modes, RX FIFO word matches the target bytes packed by the project RX FIFO contract, e.g. `32'hBEBA_FECA` for the existing stimulus; RESP success length 4.</t>
+Stimulus / Actions: Run `i3c_read_vseq` with device stimulus `[CA, FE, BA, BE]`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disabled mode starts with `START + 0x08/R + ACK` and emits no `0x7e` preamble. Enabled mode emits `START + 0x7e/W + ACK + Sr + 0x08/R + ACK` before read data. **Data integrity check (primary pass condition): RX FIFO word equals the device-driven bytes in little-endian DWORD packing, i.e. `32'hBEBAFECA`; `rx_word[(i*8)+:8]` == `read_data[i]` for i=0..3** — confirming no read byte is dropped or corrupted through the RX path; RESP success length 4.</t>
   </si>
   <si>
     <t xml:space="preserve">SDRR_002</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify read lengths and RX packing in both private-address modes.</t>
+    <t xml:space="preserve">Verify read lengths, RX packing, and per-byte data integrity in both private-address modes.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_regular_read_len_sweep`</t>
@@ -905,7 +924,7 @@
 Stimulus / Actions: Run `i3c_read_len_sweep_vseq` with lengths 1,2,3,4,5,7,8,16.</t>
   </si>
   <si>
-    <t xml:space="preserve">Each mode uses the expected private-address prefix; RX FIFO contains all bytes in little-endian DWORD packing; partial final DWORD is preserved; RESP success length matches the requested length.</t>
+    <t xml:space="preserve">Each mode uses the expected private-address prefix; **for every length N, `rx_word[i/4][(i%4*8)+:8]` must equal `read_data[i]` for all i &lt; N** (data integrity check); partial final DWORD is preserved with correct byte ordering; no extra or missing byte; RESP success length matches the requested length.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `hci_queues`, UVM scoreboard</t>
@@ -917,17 +936,17 @@
     <t xml:space="preserve">SDRR_003</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify target early end handling in both private-address modes.</t>
+    <t xml:space="preserve">Verify target early end handling: received bytes are stored correctly and no valid byte is dropped.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_read_short_target_end`</t>
   </si>
   <si>
     <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; target returns T-bit end before requested length.
-Stimulus / Actions: Run `i3c_read_short_target_end_vseq` with requested length N and actual target length M&lt;N.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each mode uses the expected private-address prefix; controller does not read fake data after target early end; RX FIFO contains only transferred bytes; queues are cleaned up after the response is drained. Response descriptor encoding is checked by `ERR_004`.</t>
+Stimulus / Actions: Run `i3c_read_short_target_end_vseq` with requested length N and actual target length M&lt;N, including a `toc=0` subcase with a second command already queued.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each mode uses the expected private-address prefix; **data integrity check (primary pass condition): RX FIFO contains exactly M bytes, and `rx_word[i/4][(i%4*8)+:8]` == `read_data[i]` for all i &lt; M** — verifying that every byte the target sent is stored correctly and no byte is silently dropped before the early-end boundary; the controller reads no fake or garbage bytes beyond M; queues are cleaned up after the response is drained. **Error overrides continuation:** when `toc=0` is programmed, the target-driven early end still forces STOP — the transfer ends in STOP and the next queued command is not chained (no *continuation* Repeated START begins the second command). Response descriptor encoding is checked by `ERR_005`.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `bus_rx_flow`, RESP FIFO, UVM scoreboard</t>
@@ -939,20 +958,20 @@
     <t xml:space="preserve">SDRR_004</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify controller termination at requested length in both private-address modes.</t>
+    <t xml:space="preserve">Verify controller termination at requested length in both private-address modes, including the tightest over-run boundary and that normal over-length completion is not misclassified as an error.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_read_target_more_than_requested`</t>
   </si>
   <si>
     <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; target can provide more bytes than requested.
-Stimulus / Actions: Run `i3c_read_target_more_than_requested_vseq` with target data longer than the command length.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each mode uses the expected private-address prefix; controller takes over after the requested byte count, stores no extra RX bytes, and reports RESP success with the requested length.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_read_end_policy`, `cp_private_start_prefix`</t>
+Stimulus / Actions: Run `i3c_read_target_more_than_requested_vseq` with target data longer than the command length, including the `+1` boundary (target offers exactly requested+1 bytes); also run a `toc=0` over-length case with a second command queued.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each mode uses the expected private-address prefix; controller takes over after the requested byte count, stores no extra RX bytes (the `+1` boundary confirms it stops at exactly N and stores no N+1 byte), and reports RESP success with the requested length. **Continuation contrast:** over-length completion sets no error flag, so a `toc=0` over-length read still continues legitimately with exactly one RSTART into the next queued command — confirming the controller does not misclassify normal over-length termination as an error that would suppress continuation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_read_end_policy`, `cp_toc`, `cp_rstart_continuation`, `cp_private_start_prefix`</t>
   </si>
   <si>
     <t xml:space="preserve">SDRR_005</t>
@@ -965,10 +984,10 @@
   </si>
   <si>
     <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; RX FIFO is prefilled full before read data flush.
-Stimulus / Actions: Run `i3c_read_rx_fifo_full_overflow_vseq`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each mode uses the expected private-address prefix; controller takes over the read before forced STOP, preserves prefilled RX FIFO words, and leaves queues empty after drain. Response descriptor encoding is checked by `ERR_005`.</t>
+Stimulus / Actions: Run `i3c_read_rx_fifo_full_overflow_vseq`, including a `toc=0` subcase (overflow must override the continuation request).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each mode uses the expected private-address prefix; **data integrity boundary (primary intent): every RX word already committed to the FIFO (including the prefill) is preserved unchanged — overflow drops only the bytes that could not be committed, never a byte already accepted**; the controller takes over the read before forced STOP and leaves queues empty after drain. **Error overrides continuation:** when `toc=0` is programmed, overflow still forces STOP and reports `Ovl` regardless of the continuation request — the transfer ends in STOP, not a continuation into a next command; the prefill plus the one accepted word are preserved. Response descriptor encoding for the overflow is verified by `ERR_006`.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `hci_queues`, `scl_generator`, UVM scoreboard</t>
@@ -980,7 +999,7 @@
     <t xml:space="preserve">SDRR_006</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify read data integrity in both private-address modes.</t>
+    <t xml:space="preserve">Verify read data integrity across sensitive bit patterns in both private-address modes.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_read_data_patterns`</t>
@@ -990,7 +1009,7 @@
 Stimulus / Actions: Run `i3c_read_data_patterns_vseq` with all-zero, all-one, walking-one, alternating, and fixed-random patterns.</t>
   </si>
   <si>
-    <t xml:space="preserve">Each mode uses the expected private-address prefix; RX FIFO contents match target data exactly; RESP success length matches pattern length.</t>
+    <t xml:space="preserve">Each mode uses the expected private-address prefix; **for every pattern, `rx_word[i/4][(i%4*8)+:8]` == `read_data[i]` for every byte i** (data integrity check) — patterns like `0x00` and `0xFF` specifically stress the RX shift register for stuck-at faults; RESP success length matches pattern length.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_driver`, `bus_rx_flow`, UVM scoreboard</t>
@@ -1012,7 +1031,7 @@
 Stimulus / Actions: Run `i3c_read_no_parity_error_on_end_tbit_vseq`.</t>
   </si>
   <si>
-    <t xml:space="preserve">Each mode uses the expected private-address prefix; T-bit=0 is treated as end-of-data, no extra RX byte is consumed, and queues drain cleanly. Detailed RESP field classification for this same legal end condition is covered by `ERR_013`.</t>
+    <t xml:space="preserve">Each mode uses the expected private-address prefix; T-bit=0 is treated as end-of-data, no extra RX byte is consumed, and queues drain cleanly. Detailed RESP field classification for this same legal end condition is covered by `ERR_008`.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `bus_rx_flow`, UVM scoreboard</t>
@@ -1024,17 +1043,17 @@
     <t xml:space="preserve">SDRR_008</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify SDR regular read continuation when `toc=0` in both private-address modes.</t>
+    <t xml:space="preserve">Verify SDR regular read continuation when `toc=0`, data integrity of the read and the following write.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_read_toc_zero`</t>
   </si>
   <si>
     <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; I3C device returns requested read data; a second SDR regular I3C write command is already queued.
-Stimulus / Actions: Run `i3c_read_toc_zero_vseq`: queue first read with `toc=0` and second write with `toc=1`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disabled mode starts the first read directly with dynamic address; enabled mode emits the broadcast-header preamble only before the first private read. In both modes, the first read ends with `Sr`, the continuation does not repeat the preamble, final STOP occurs only after the second command, and RX data plus both RESPs match expected length/TID.</t>
+Stimulus / Actions: Run `i3c_read_toc_zero_vseq`: queue first read (`toc=0`) and second write (`toc=1`) with distinct payloads.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disabled mode starts the first read directly with dynamic address; enabled mode emits the broadcast-header preamble only before the first private read. In both modes, **data integrity checks: RX bytes from the read match the device-driven stimulus byte-by-byte; write bytes observed on bus match the TX FIFO bytes byte-by-byte** — the RSTART boundary does not cause loss or corruption in either direction; the first read ends with `Sr`, the continuation does not repeat the preamble, final STOP occurs only after the second command, and both RESPs match expected length/TID.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `scl_generator`, `bus_rx_flow`, UVM scoreboard</t>
@@ -1046,17 +1065,36 @@
     <t xml:space="preserve">SDRR_009</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify HC abort during the SDR private read data phase.</t>
+    <t xml:space="preserve">Verify HC abort during the SDR private read data phase, including data integrity of bytes committed before abort.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_read_abort`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; target returns read data; a multi-byte read is in progress in the data phase (`abort_stop_required` true); run once with `HC_CONTROL[BROADCAST_ADDR_ENABLE]=0` and once with it set.
+    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; target returns read data; a multi-byte read is in progress in the data phase (`abort_stop_required` true); run once with `HC_CONTROL[BROADCAST_ADDR_ENABLE]=0` and once with it set; run an early case (abort fires at FSM entry, before data starts), a deep case (abort fires after at least one RX FIFO word is committed), and a `toc=0` case (abort must override the continuation request).
 Stimulus / Actions: Assert `HC_CONTROL[3]` (HC abort) while the FSM is in the read data phase.</t>
   </si>
   <si>
-    <t xml:space="preserve">Bytes already received up to the abort point are stored in the RX FIFO with correct packing and no fake bytes are read after abort; the controller completes the current byte boundary, then STOP is generated and the FSM advances to `WriteResp`. This case checks only byte completeness and STOP-at-correct-state; response status/length correctness and all non-data-phase abort entry states are covered by `ERR_012`.</t>
+    <t xml:space="preserve">**Data integrity check (primary pass condition for the deep case):** after the FSM reaches idle, read the committed bytes from RX FIFO (length given by `resp[15:0]`) *before* issuing SW reset, and verify `rx_word[i/4][(i%4*8)+:8]` == `read_data[i]` for every committed byte i — confirming no valid pre-abort byte is silently dropped or corrupted. No fake bytes may appear beyond the committed boundary. **Error overrides continuation:** when the aborted read was programmed `toc=0`, abort still forces STOP and `HcAborted` — the controller's takeover Repeated START (SDA retake per MIPI §5.1.2.3.4) is followed by STOP, never a continuation into a next command. After verifying, SW reset flushes any remaining residual bytes, leaving all queues empty. Response status/length correctness and all non-data-phase abort entry states are covered by `ERR_007`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDRR_010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify SDR private read selects the programmed DAT index, per-target data integrity, and preservation across a `toc=0` continuation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_read_multi_dat_idx`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08` and DAT[1] is `0x12`; both targets return read data.
+Stimulus / Actions: Run `i3c_read_multi_dat_idx_vseq`: first issue two independent reads to DAT[0] and DAT[1] (`toc=1` each), then a `toc=0` read on DAT[0] continued into a `toc=1` read on DAT[1].</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each read drives the dynamic address programmed in its selected DAT entry; **data integrity check: for each target, `rx_word[i/4][(i%4*8)+:8]` == `read_data[i]` for every byte i** — RX data from each target is stored in the correct FIFO order without cross-target mixing or silent drops; the `toc=0` case emits exactly one repeated START between the two reads while still switching the DAT-selected address; all queues drain empty.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_dev_idx`, `cp_toc`, `cp_rstart_continuation`, `cp_private_start_prefix`</t>
   </si>
   <si>
     <t xml:space="preserve">Immediate Data Transfer</t>
@@ -1065,108 +1103,86 @@
     <t xml:space="preserve">IMM_001</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify baseline immediate write descriptor flow.</t>
+    <t xml:space="preserve">Verify baseline immediate write descriptor flow, including data integrity of inline bytes.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_immediate_write_smoke_existing`</t>
   </si>
   <si>
     <t xml:space="preserve">Preconditions: DAT[0] I3C device; target ACKs.
-Stimulus / Actions: Run `i3c_imm_vseq`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two inline data bytes are transmitted according to descriptor `dtt` and project packing rules; RESP success.</t>
+Stimulus / Actions: Run `i3c_imm_vseq` with `HC_CONTROL[2]` (`broadcast_header_enable`) = 0 and = 1; `dtt=2`, `def_or_data_byte1=0xAA`, `data_byte2=0xBB`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">With `broadcast_header_enable=0` the bus shows `[S] addr+W [ACK] data...`; with `=1` it shows `[S] 7E+W [ACK] [Sr] addr+W [ACK] data...`. **Data integrity check (primary pass condition): `sampled_data[0]`==`0xAA` and `sampled_data[1]`==`0xBB`** — the inline bytes from the command descriptor are transmitted on the bus in descriptor order with no corruption, drop, or reordering; RESP success with length 2 in both modes.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `bus_tx_flow`, UVM</t>
   </si>
   <si>
-    <t xml:space="preserve">`cp_imm`, `cp_len_2`</t>
+    <t xml:space="preserve">`cp_imm`, `cp_len_2`, `cp_private_start_prefix`</t>
   </si>
   <si>
     <t xml:space="preserve">IMM_002</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify inline data byte count.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_immediate_write_dtt_sweep`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: DAT[0] I3C device.
-Stimulus / Actions: Issue immediate commands with `dtt` values covering 0..4 valid bytes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Correct number of inline bytes are transmitted; no TX FIFO access occurs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, CMD descriptor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_imm_dtt`</t>
+    <t xml:space="preserve">Verify inline data byte count, `dtt &gt; 4` early rejection, and per-dtt data integrity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_imm_dtt_sweep_vseq`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: DAT[0] I3C device; both `broadcast_header_enable` modes; cmd bytes always `[A1, A2, A3, A4]`.
+Stimulus / Actions: Sweep `dtt` 0..7 in both private-address modes (no broadcast header and with broadcast header).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**`dtt` 0..4 (positive):** the correct number of inline bytes is transmitted; **data integrity check: `sampled_data[i]` == cmd byte i for i &lt; dtt** — confirming the cmd dword bytes are sent in descriptor order with no extra, missing, or reordered byte; RESP `Success`; `resp.length == dtt`. **`dtt` 5..7 (negative):** FSM rejects in `WaitDAT` before any bus activity; `not_supported_d` is set; RESP error is `NotSupported` (4'hA); no inline bytes sent, queues remain clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active` (`WaitDAT` early-exit), CMD descriptor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_imm_dtt`, `cp_resp_err`, `cp_private_start_prefix`</t>
   </si>
   <si>
     <t xml:space="preserve">IMM_003</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify immediate `toc` policy.</t>
+    <t xml:space="preserve">Verify that `toc=0` is rejected for immediate transfers and that `toc=1` succeeds; verify data integrity in both cases.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_immediate_write_toc`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: Target ACKs; immediate `toc=0` continuation policy is not specified for the current project descriptor set.
-Stimulus / Actions: Repeat immediate command with `toc=1` and `toc=0`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`toc=1` generates STOP and success. `toc=0` is a clarification/negative case until the project spec defines immediate continuation; acceptable sign-off behavior must be one specified policy such as reject/abort with error or forced STOP, and the bus must not hang without STOP or `Sr`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_toc`, `cp_imm`, `cp_unsupported_policy`</t>
+    <t xml:space="preserve">Preconditions: DAT[0] I3C device; target ACKs address and data; `dtt=2`, bytes `[AA, BB]`.
+Stimulus / Actions: Issue one immediate command with `toc=1` and one with `toc=0`; cover both I3C and I2C immediate paths (`I3CWriteImmediate`, `I2CWriteImmediate`).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`toc=1`: STOP is generated after inline data; **data integrity check: `sampled_data[0]`==`0xAA`, `sampled_data[1]`==`0xBB`**; RESP is `Success` with correct length 2. `toc=0`: all dtt bytes are still transmitted before STOP — **data integrity check: same byte-level check applies**; STOP is generated, `not_supported_d` is set, RESP error is `NotSupported` (4'hA); no `Sr` or continuation occurs. Both toc values must complete all dtt bytes on bus with correct values before STOP. Bus must not hang.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_toc`, `cp_imm`, `cp_resp_err`</t>
   </si>
   <si>
     <t xml:space="preserve">IMM_004</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify immediate path for legacy I2C DAT entry.</t>
+    <t xml:space="preserve">Verify immediate path for legacy I2C DAT entry, including data integrity of inline bytes.</t>
   </si>
   <si>
     <t xml:space="preserve">`i2c_immediate_write_basic`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: DAT[0].`device=1`; static address programmed.
-Stimulus / Actions: Issue I2C immediate write with 1..4 bytes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OD-only static address+W, data ACKs, RESP length equals bytes transferred.</t>
+    <t xml:space="preserve">Preconditions: DAT[0].`device=1`; static address programmed; cmd bytes `[D1, D2, D3, D4]`.
+Stimulus / Actions: Issue I2C immediate write with dtt=1..4 bytes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OD-only static address+W, data ACKs; **data integrity check: for each dtt, `sampled_data[i]` == cmd byte i for i &lt; dtt** — the static-address I2C path transmits the same cmd dword bytes as the I3C path, in descriptor order, with no loss; RESP length equals bytes transferred.</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_i2c`, `cp_imm`</t>
   </si>
   <si>
     <t xml:space="preserve">IMM_005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify address NACK for immediate transfer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`immediate_addr_nack`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Target NACKs the address ACK/NACK slot.
-Stimulus / Actions: Issue I3C and I2C immediate writes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Controller generates STOP immediately after address NACK; no inline data byte is transmitted; RESP error is `AddrHeader` with length 0.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `bus_rx_flow`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_resp_err`, `cross_imm_x_device_type`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMM_006</t>
   </si>
   <si>
     <t xml:space="preserve">Verify I2C immediate data NACK handling.</t>
@@ -1179,13 +1195,32 @@
 Stimulus / Actions: Issue multi-byte I2C immediate write.</t>
   </si>
   <si>
-    <t xml:space="preserve">Controller generates STOP after data NACK; no later inline data byte is transmitted; RESP error is `Nack`.</t>
+    <t xml:space="preserve">**Data integrity boundary (primary intent):** the inline bytes sent before the NACK match the cmd descriptor bytes; after the data NACK the controller generates STOP and transmits no later inline byte — only the bytes beyond the NACKed position are dropped, per I2C policy. RESP error encoding for the data NACK is verified by `ERR_004`.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_data_ack`, `cp_resp_err`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMM_006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify HC abort during immediate data transmission phase, including data integrity of bytes sent before abort.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_imm_abort_vseq`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: DAT[0] I3C dynamic address `0x08`; DAT[0] I2C static address `0x52`; target ACKs address and data.
+Stimulus / Actions: Assert `HC_CONTROL[3]` (HC abort) while FSM is in `I3CWriteImmediate` (4'd5) for I3C device; repeat for `I2CWriteImmediate` (4'd6) with I2C device; cover both `broadcast_header_enable` modes for I3C. Use `dtt=4` (max inline bytes) to widen the abort window.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Data integrity check (primary pass condition): for every byte i that was sent before abort (`sampled_data[i]`), the value must equal the cmd descriptor byte i** — no valid pre-abort inline byte may be dropped or corrupted; the in-flight byte boundary completes before STOP. FSM issues STOP and advances to `WriteResp`; no TX or RX FIFO residual (inline data only, no FIFO involved); recovery SW reset leaves all queues empty. RESP status/length encoding for the abort is verified by `ERR_007`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_hc_abort`, `cp_abort_stop_state`, `cp_imm`, `cross_imm_x_device_type`</t>
   </si>
   <si>
     <t xml:space="preserve">Common Command Codes</t>
@@ -1292,69 +1327,6 @@
     <t xml:space="preserve">`cp_ccc_opcode`, `cp_ccc_direct`</t>
   </si>
   <si>
-    <t xml:space="preserve">CCC_006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify CCC NACK recovery.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`ccc_broadcast_header_nack`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Device NACKs `7'h7E+W`.
-Stimulus / Actions: Issue ENEC/DISEC/ENTDAA command.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Controller reports the specified address/header error, generates legal bus recovery, and does not send CCC payload after broadcast-header NACK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, RESP FIFO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_ccc_nack`, `cp_resp_err`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCC_007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify direct CCC target address NACK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`ccc_direct_target_nack`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Target ACKs broadcast header, observes the direct CCC opcode/T-bit, and NACKs direct address.
-Stimulus / Actions: Issue direct ENEC/DISEC.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No direct data byte is sent after address NACK; RESP and bus recovery match the address/header NACK policy in the project spec.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_ccc_direct`, `cp_addr_ack`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCC_008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Define behavior for unsupported CCC opcodes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`ccc_unsupported_opcode_policy`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Immediate CMD `cp=1`, opcode outside ENEC/DISEC/ENTDAA.
-Stimulus / Actions: Issue representative unsupported broadcast and direct opcodes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This is a clarification/negative test until the project spec defines unsupported CCC handling. Required sign-off behavior should be a specified `NotSupported`/error response or software restriction; the controller must not emit an undefined successful CCC frame, corrupt queues, or lock up.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `i3c_pkg`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_unsupported_cmd`</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dynamic Address Assignment / ENTDAA</t>
   </si>
   <si>
@@ -1449,39 +1421,42 @@
     <t xml:space="preserve">DAA_005</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify assigned address parity.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`entdaa_address_parity_sweep`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Target ACKs assigned addresses.
-Stimulus / Actions: Sweep representative dynamic addresses including low, high, alternating patterns.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sent address parity bit matches odd parity calculation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`entdaa_fsm`, `bus_tx_flow`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_daa_addr`, `cp_daa_parity`</t>
+    <t xml:space="preserve">Verify assigned address parity without a dedicated vseq.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`covered_by_sva_no_vseq`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: ENTDAA SVA and functional coverage enabled; successful ENTDAA rounds are exercised by DAA_001/DAA_004 and regression seeds.
+Stimulus / Actions: No standalone stimulus. Existing randomized ENTDAA vseqs provide low, high, alternating, and other representative dynamic addresses across regression runs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`ap_entdaa_send_addr_value` proves every transmitted byte equals `{dynamic_addr, ~^dynamic_addr}`; the bus-level scoreboard checks the observed parity; functional coverage hits address classes, both parity values, and their cross.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`entdaa_fsm_sva`, `entdaa_fsm`, `bus_tx_flow`, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_daa_addr`, `cp_daa_parity`, `cx_daa_addr_parity`</t>
   </si>
   <si>
     <t xml:space="preserve">DAA_006</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify target NACK of assigned address.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`entdaa_address_rejected`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Target ACKs `7'h7E+R`, drives PID/BCR/DCR, then NACKs address.
-Stimulus / Actions: Issue AddressAssignment.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`addr_valid_o` is not asserted; loop continues or completes according to `dev_count`/no-device behavior.</t>
+    <t xml:space="preserve">Verify target NACK of assigned address and the repeated-rejection error policy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_daa_address_rejected_vseq`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: Target ACKs `7'h7E+R`, drives PID/BCR/DCR, then NACKs address twice.
+Stimulus / Actions: Issue AddressAssignment with `dev_count=1`; repeat the same target identity on the retry.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First NACK causes a repeated START and retries the same DAT index/address without producing RX result data. A second NACK from the same target terminates ENTDAA with STOP and RESP `Nack` (`4'h5`) with length 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`entdaa_fsm`, `entdaa_controller`, `flow_active`, UVM scoreboard</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_daa_addr_ack`</t>
@@ -1490,7 +1465,7 @@
     <t xml:space="preserve">DAA_007</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify identity capture.</t>
+    <t xml:space="preserve">Verify identity capture and project-defined RX FIFO result packing.</t>
   </si>
   <si>
     <t xml:space="preserve">`entdaa_pid_bcr_dcr_capture`</t>
@@ -1500,7 +1475,7 @@
 Stimulus / Actions: Run successful ENTDAA.</t>
   </si>
   <si>
-    <t xml:space="preserve">Captured PID/BCR/DCR match the bits driven by the target in the MIPI ENTDAA order; software-visible RX data is checked only after its project format is specified.</t>
+    <t xml:space="preserve">Captured PID/BCR/DCR match the bits driven by the target in the MIPI ENTDAA order; software-visible RX data uses the documented three-DWORD format: `PID[47:16]`, `{PID[15:0],BCR,DCR}`, `{25'h0,DA[6:0]}`.</t>
   </si>
   <si>
     <t xml:space="preserve">`entdaa_fsm`, `flow_active`, RX FIFO</t>
@@ -1591,7 +1566,7 @@
 Stimulus / Actions: Issue RegularTransfer write of 1 and 4 bytes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Static address+W is used; OD mode throughout; data bytes are ACKed; RESP success.</t>
+    <t xml:space="preserve">Static address+W is used; OD mode throughout; data bytes are ACKed; **data integrity check: each byte observed on the bus matches the TX FIFO byte at that position in little-endian DWORD order — no byte is dropped or corrupted during the transaction**; RESP success length equals the bytes written.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `scl_generator`, `bus_tx_flow`</t>
@@ -1613,7 +1588,7 @@
 Stimulus / Actions: Issue RegularTransfer read of 1 and 4 bytes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Static address+R is used; master ACKs intermediate bytes and NACKs final byte; RX data correct.</t>
+    <t xml:space="preserve">Static address+R is used; master ACKs intermediate bytes and NACKs the final byte; **data integrity check: every RX FIFO byte matches the device-driven byte at that position in little-endian DWORD packing — no read byte is dropped or corrupted**; RESP success length equals the bytes read.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `bus_rx_flow`, `bus_tx_flow`</t>
@@ -1657,7 +1632,7 @@
 Stimulus / Actions: Run I2C writes and reads of 1,2,3,4,5,7,8 bytes.</t>
   </si>
   <si>
-    <t xml:space="preserve">Correct TX/RX packing; partial RX DWORD preserved; RESP length correct.</t>
+    <t xml:space="preserve">**Data integrity check: for every length, TX bytes on the bus match the TX FIFO bytes and RX FIFO bytes match the device-driven bytes, byte-by-byte in little-endian order — no byte dropped**; the partial final RX DWORD is preserved with correct byte ordering; RESP length correct.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `hci_queues`</t>
@@ -1667,25 +1642,6 @@
   </si>
   <si>
     <t xml:space="preserve">I2C_005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify I2C address NACK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i2c_addr_nack`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Target NACKs static address.
-Stimulus / Actions: Issue read and write commands.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No data phase; RESP error is `AddrHeader`; bus returns idle.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_resp_err`, `cp_i2c_addr_ack`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I2C_006</t>
   </si>
   <si>
     <t xml:space="preserve">Verify I2C data-byte NACK.</t>
@@ -1698,48 +1654,45 @@
 Stimulus / Actions: Issue multi-byte write.</t>
   </si>
   <si>
-    <t xml:space="preserve">Transfer stops after the NACKed byte per I2C/project error policy; RESP error is `Nack`; next legal transfer passes.</t>
+    <t xml:space="preserve">**Data integrity boundary (primary intent):** bytes sent before the NACK match the TX FIFO bytes; the transfer stops after the NACKed byte and transmits no later byte — only the bytes beyond the NACKed position are dropped, per I2C policy; next legal transfer passes. RESP error encoding for the data NACK is verified by `ERR_004`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I2C_006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify HC abort during I2C RegularTransfer write and read, including data integrity of bytes sent/committed before abort.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i2c_regular_abort`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: DAT[0].`device=1`; static address programmed; target ACKs address and data; multi-byte transfer in progress in the data phase.
+Stimulus / Actions: Assert `HC_CONTROL[3]` (HC abort) while FSM is in `I2CWrite` state (write path) and `I2CRead` state (read path); cover an early case (abort fires before any FIFO word consumed), a deep case (abort fires after at least one TX/RX FIFO word processed), and a `toc=0` case (abort must override continuation).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Data integrity check (primary pass condition):** for write: every byte i driven on the bus before the abort boundary equals the TX FIFO byte at position i in little-endian DWORD order — no valid pre-abort TX byte may be dropped or corrupted. For read: committed RX FIFO bytes must be read before SW reset and each matches the device-driven byte at that position; the controller does not stop mid-byte, ACKs all committed bytes before the abort-final byte, drives NACK on the abort-final ACK/NACK bit, then generates STOP. OD-only mode is maintained throughout (no PP switching); no T-bit on I2C data bytes. **Error overrides continuation:** when the aborted transfer was programmed `toc=0`, abort still forces STOP, never a Repeated START/continuation, and returns `HcAborted`. After abort, SW reset flushes residual TX/RX FIFO data and leaves all queues empty. RESP status/length encoding for the abort is verified by `ERR_007`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `scl_generator`, `bus_tx_flow`, `bus_rx_flow`, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_hc_abort`, `cp_abort_stop_state`, `cp_i2c_dir`, `cp_i2c_ack_seq`</t>
   </si>
   <si>
     <t xml:space="preserve">I2C_007</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify legacy transfers remain open-drain.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i2c_od_only_check`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: I2C read and write commands.
-Stimulus / Actions: Observe `sel_od_pp_o` and SDA drive during address/data/ACK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`sel_od_pp_o` remains OD for entire I2C transaction.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`controller_active`, `i3c_phy`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_odpp_phase`, `cp_i2c`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I2C_008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify configured I2C timing path.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i2c_timing_400k_equivalent`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Timing registers programmed for I2C FM-equivalent values at TB clock.
-Stimulus / Actions: Run representative I2C read/write.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCL low/high and START/STOP timing match programmed counters.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`csr_registers`, `scl_generator`</t>
+    <t xml:space="preserve">Verify default I2C FM-equivalent timing selection without a dedicated vseq.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: SVA enabled; I2C legacy transfers covered by I2C_001/I2C_002.
+Stimulus / Actions: No standalone stimulus. Existing I2C read/write vseqs exercise the path; SVA covers reset/default timing values and I2C timing selection.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`I2C_T_*` reset defaults provide the 400 kHz-equivalent timing, and I2C transfers select `I2C_T_*` rather than generic `T_*`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`csr_registers_sva`, `flow_active_sva`, `controller_active`, `scl_generator`</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_timing_mode`</t>
@@ -1764,29 +1717,51 @@
     <t xml:space="preserve">RESP `[31:28]=Success`, `[27:24]=TID`, `[15:0]=actual length`.</t>
   </si>
   <si>
+    <t xml:space="preserve">`flow_active`, RESP FIFO</t>
+  </si>
+  <si>
     <t xml:space="preserve">`cp_resp_err`, `cp_tid`, `cp_resp_len`</t>
   </si>
   <si>
     <t xml:space="preserve">ERR_002</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify address/header NACK response encoding.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`resp_addr_header_error`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Device NACKs address.
-Stimulus / Actions: Run `i3c_addr_header_nack_resp_vseq` for I3C write/read address NACK; extend to I2C write/read and direct CCC address phases as those directed tests are added.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESP status is `AddrHeader`, TID matches the command, reserved bits are zero, and length is 0 for every supported command class with address/header NACK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_resp_err`, `cp_addr_ack`, `cp_tid`, `cp_resp_len`</t>
+    <t xml:space="preserve">Verify `AddrHeader` response encoding for every command class that has an address phase.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`resp_addr_nack_all_classes`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: Device NACKs address in an I3C, I2C, immediate, or direct CCC transfer.
+Stimulus / Actions: Run `i3c_addr_header_nack_resp_vseq` for I3C write/read and I2C write/read address NACK. Also cover I3C and I2C immediate writes: controller generates STOP immediately after address NACK, no inline data byte is transmitted. Also cover direct CCC address NACK (previously CCC_006): target ACKs broadcast header and CCC opcode/T-bit but NACKs the direct address after Sr; verify no data byte is sent after the NACK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESP status is `AddrHeader`, TID matches the command, reserved bits are zero, and length is 0 for every supported command class with address NACK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_resp_err`, `cp_addr_ack`, `cp_tid`, `cp_resp_len`, `cross_imm_x_device_type`</t>
   </si>
   <si>
     <t xml:space="preserve">ERR_003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify `AddrHeader` response encoding and CCC payload suppression when the broadcast header is NACKed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`resp_ccc_broadcast_header_nack`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: Device NACKs `7'h7E+W` during a CCC command (ENEC/DISEC/ENTDAA).
+Stimulus / Actions: Issue ENEC/DISEC/ENTDAA command; device NACKs the broadcast header.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESP status is `AddrHeader`, TID matches the command, reserved bits are zero, and length is 0; no CCC opcode or payload byte is emitted after the NACK; bus recovery is legal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_resp_err`, `cp_addr_ack`, `cp_tid`, `cp_resp_len`, `cp_ccc_nack`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERR_004</t>
   </si>
   <si>
     <t xml:space="preserve">Verify data NACK error for I2C write-style phases.</t>
@@ -1802,7 +1777,7 @@
     <t xml:space="preserve">RESP error is `Nack`; transfer recovers.</t>
   </si>
   <si>
-    <t xml:space="preserve">ERR_004</t>
+    <t xml:space="preserve">ERR_005</t>
   </si>
   <si>
     <t xml:space="preserve">Verify short read response encoding.</t>
@@ -1821,7 +1796,7 @@
     <t xml:space="preserve">`cp_short_read`, `cp_resp_err`, `cp_tid`, `cp_resp_len`</t>
   </si>
   <si>
-    <t xml:space="preserve">ERR_005</t>
+    <t xml:space="preserve">ERR_006</t>
   </si>
   <si>
     <t xml:space="preserve">Verify overflow response encoding.</t>
@@ -1840,7 +1815,51 @@
     <t xml:space="preserve">`cp_resp_err_ovl`, `cp_tid`, `cp_resp_len`</t>
   </si>
   <si>
-    <t xml:space="preserve">ERR_006</t>
+    <t xml:space="preserve">ERR_007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify HC abort response encoding, status priority, and non-data-phase abort entry states.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`resp_hc_abort_error`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: Controller can be aborted from selectable FSM states via `HC_CONTROL[3]`; bus-error injection available; `HC_CONTROL[3]` is a level bit that is never auto-cleared by hardware.
+Stimulus / Actions: Assert HC abort (a) during a data-phase transfer that terminates via STOP, (b) in a pre-bus state (`FetchDAT`, or `WaitDAT` with no pending continuation), (c) while idle (`Idle`/`WaitForCmd`), (d) after a bus error has already latched, (e) leave the bit asserted across a following queued command, and (f) during the CCC execution state (after broadcast header ACK, while FSM is sending the CCC opcode or data byte).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(a) RESP status is `HcAborted`, TID matches the command, reserved bits zero, and length equals the bytes processed before abort — this encoding is the single owner for abort RESP fields across regular SDR write/read (`SDRW_009`, `SDRR_009`), immediate-data (`IMM_006`), I2C RegularTransfer (`I2C_006`), and CCC-phase abort (subcase (f)). (b) No STOP and no bus activity occur; the FSM advances directly to `WriteResp` with `HcAborted`. (c) Abort is a no-op; the active/next command proceeds normally. (d) The previously latched bus error wins over `HcAborted` per the response-status priority. (e) Because the bit is not auto-cleared, the next command is also aborted until software clears `HC_CONTROL[3]`. (f) Bus terminates with STOP; `HcAborted` is returned; no CCC opcode or data byte beyond the abort point is emitted; bus cleanup is legal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `csr_registers`, RESP FIFO, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_hc_abort`, `cp_resp_err`, `cp_abort_entry_state`, `cp_resp_err_priority`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERR_008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify response classification for a legal SDR read final T-bit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_read_tbit_no_parity_resp`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; target ends transfer with T-bit=0 at the requested length.
+Stimulus / Actions: Run `i3c_read_tbit_no_parity_resp_vseq`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final T-bit=0 at the requested length is not classified as `Parity`; RESP is `Success`, TID matches the command, reserved bits are zero, and length matches the requested length.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, RESP FIFO, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_read_tbit`, `cp_resp_err`, `cp_tid`, `cp_resp_len`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERR_009</t>
   </si>
   <si>
     <t xml:space="preserve">Verify response write stalls safely.</t>
@@ -1859,7 +1878,51 @@
     <t xml:space="preserve">`cp_resp_full`, `cp_stall_type`</t>
   </si>
   <si>
-    <t xml:space="preserve">ERR_007</t>
+    <t xml:space="preserve">ERR_010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify pre-bus rejection of unsupported or invalid descriptor commands.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`invalid_descriptor_attr`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: CMD descriptors can be written directly; `cp=1` immediate CMD available for CCC opcode injection.
+Stimulus / Actions: (a) Issue `ComboTransfer`, reserved attr, HDR mode values, invalid mode encodings, and an `ImmediateDataTransfer` with `rnw=1`. (b) Issue representative unsupported CCC opcodes (`cp=1`, opcode outside ENEC/DISEC/ENTDAA) for both broadcast and direct forms (previously `ccc_unsupported_opcode_policy`).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**(b) Defined:** FSM rejects unsupported CCC opcode before any bus activity; RESP error is `NotSupported` (0xA); no CCC frame is emitted; queues drain cleanly. **(a) Clarification items:** no unbounded hang or illegal queue corruption; for `rnw=1` immediate the controller must not emit a read frame — it either ignores direction (forces write) or returns a specified error response; remaining subcases require sign-off once their expected behavior is specified.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `i3c_pkg`, CMD descriptor parsing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_invalid_cmd`, `cp_imm`, `cp_unsupported_cmd`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERR_011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document the `wroc` (response-on-completion) design gap.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`immediate_wroc_policy`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: CMD descriptors can be written directly.
+Stimulus / Actions: Issue immediate/regular commands with `wroc=0` and `wroc=1`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Documented design gap — to be discussed / implemented later (not positive sign-off coverage).** RTL currently ignores the `wroc` field: `flow_active.sv` asserts `resp_queue_wvalid` unconditionally in `WriteResp` and `wroc` is never read, so a RESP descriptor is always written regardless of `wroc`. Behavior for `wroc=0` (suppress RESP write) is undefined until the project spec decides whether to implement it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, RESP FIFO, `csr_registers`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_wroc`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERR_012</t>
   </si>
   <si>
     <t xml:space="preserve">Verify reset in idle.</t>
@@ -1881,7 +1944,7 @@
     <t xml:space="preserve">`cp_reset_point`</t>
   </si>
   <si>
-    <t xml:space="preserve">ERR_008</t>
+    <t xml:space="preserve">ERR_013</t>
   </si>
   <si>
     <t xml:space="preserve">Verify reset during active operation.</t>
@@ -1900,7 +1963,7 @@
     <t xml:space="preserve">`cp_reset_point`, `cross_reset_x_phase`</t>
   </si>
   <si>
-    <t xml:space="preserve">ERR_009</t>
+    <t xml:space="preserve">ERR_014</t>
   </si>
   <si>
     <t xml:space="preserve">Clarify SW reset during active transfer.</t>
@@ -1922,7 +1985,7 @@
     <t xml:space="preserve">`cp_sw_reset_busy`</t>
   </si>
   <si>
-    <t xml:space="preserve">ERR_010</t>
+    <t xml:space="preserve">ERR_015</t>
   </si>
   <si>
     <t xml:space="preserve">Identify bus recovery gap.</t>
@@ -1944,70 +2007,48 @@
     <t xml:space="preserve">`cp_bus_stuck`</t>
   </si>
   <si>
-    <t xml:space="preserve">ERR_011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify unsupported descriptor behavior.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`invalid_descriptor_attr`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: CMD descriptors can be written directly.
-Stimulus / Actions: Issue `ComboTransfer`, reserved attr, HDR mode values, and invalid mode encodings.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No unbounded hang or illegal queue corruption; expected protocol behavior must be specified before sign-off.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, CMD descriptor parsing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_invalid_cmd`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERR_012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify HC abort response encoding, status priority, and non-data-phase abort entry states.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`resp_hc_abort_error`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Controller can be aborted from selectable FSM states via `HC_CONTROL[3]`; bus-error injection available; `HC_CONTROL[3]` is a level bit that is never auto-cleared by hardware.
-Stimulus / Actions: Assert HC abort (a) during a data-phase transfer that terminates via STOP, (b) in a pre-bus state (`FetchDAT`, or `WaitDAT` with no pending continuation), (c) while idle (`Idle`/`WaitForCmd`), (d) after a bus error has already latched, and (e) leave the bit asserted across a following queued command.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(a) RESP status is `HcAborted`, TID matches the command, reserved bits zero, and length equals the bytes processed before abort. (b) No STOP and no bus activity occur; the FSM advances directly to `WriteResp` with `HcAborted`. (c) Abort is a no-op; the active/next command proceeds normally. (d) The previously latched bus error wins over `HcAborted` per the response-status priority. (e) Because the bit is not auto-cleared, the next command is also aborted until software clears `HC_CONTROL[3]`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `csr_registers`, RESP FIFO, UVM scoreboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_hc_abort`, `cp_resp_err`, `cp_abort_entry_state`, `cp_resp_err_priority`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERR_013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify response classification for a legal SDR read final T-bit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_read_tbit_no_parity_resp`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; target ends transfer with T-bit=0 at the requested length.
-Stimulus / Actions: Run `i3c_read_tbit_no_parity_resp_vseq`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final T-bit=0 at the requested length is not classified as `Parity`; RESP is `Success`, TID matches the command, reserved bits are zero, and length matches the requested length.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, RESP FIFO, UVM scoreboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_read_tbit`, `cp_resp_err`, `cp_tid`, `cp_resp_len`</t>
+    <t xml:space="preserve">ERR_016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify pre-bus rejection and response encoding for invalid `AddressAssignment`/ENTDAA descriptors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`entdaa_invalid_descriptor_resp`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: CMD descriptors can be written directly; DAT entry exists but should not be used because the command is rejected before ENTDAA starts.
+Stimulus / Actions: Run `i3c_entdaa_invalid_descriptor_resp_vseq` with three subcases: `toc=0,wroc=1,dev_count=1`; `toc=1,wroc=0,dev_count=1`; and `toc=1,wroc=1,dev_count=0`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No START, no `7'h7E+W` broadcast header, no ENTDAA opcode, and no DAA round are emitted. Exactly one RESP is written with status `NotSupported`, matching TID, reserved bits zero, and length 0. Queues drain cleanly and a following legal command can run.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `i3c_pkg`, RESP FIFO, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_addr_assign_desc`, `cp_resp_err`, `cp_tid`, `cp_resp_len`, `cp_no_bus_activity`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERR_017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify ENTDAA result storage overflow response encoding for every DAA result boundary.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`entdaa_rx_fifo_partial_overflow`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: DAT[0] supplies an assigned dynamic address; one target joins ENTDAA and ACKs the assigned address; RX FIFO is prefilled so only 0, 1, or 2 DWORD slots remain for the 3-DWORD DAA result.
+Stimulus / Actions: Run `i3c_entdaa_rx_fifo_partial_overflow_vseq`: issue a valid `AddressAssignment` descriptor with `toc=1,wroc=1,dev_count=1`, have the target return PID/BCR/DCR, then attempt to store the DAA result with 0, 1, and 2 free RX FIFO entries.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controller must not silently drop a DAA result while returning `Success`. RESP status is `Ovl`, TID matches the command, reserved bits are zero, and length equals the number of DAA result bytes actually committed to RX FIFO: 0, 4, or 8 bytes for the three subcases. Prefilled RX FIFO entries remain unchanged, and committed DAA result DWORDs match the documented format before the first dropped result word.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `entdaa_controller`, RX FIFO, RESP FIFO, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_resp_err_ovl`, `cp_daa_result`, `cp_tid`, `cp_resp_len`</t>
   </si>
   <si>
     <t xml:space="preserve">Arbitration and Bus Behavior</t>
@@ -2520,6 +2561,21 @@
     <t xml:space="preserve">Coverpoints</t>
   </si>
   <si>
+    <t xml:space="preserve">`cp_data_integrity_write`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">byte match pass, byte mismatch (failure injection only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_data_integrity_read`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_abort_data_boundary`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 bytes before abort, 1 word before abort, &gt;1 word before abort</t>
+  </si>
+  <si>
     <t xml:space="preserve">`cp_cmd_attr`</t>
   </si>
   <si>
@@ -2568,7 +2624,7 @@
     <t xml:space="preserve">`cp_toc`</t>
   </si>
   <si>
-    <t xml:space="preserve">0, 1</t>
+    <t xml:space="preserve">0 (regular transfers only — generates `Sr` on success or STOP on missing continuation), 1 (all transfer types — generates STOP; only valid option for immediate transfers)</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_resp_err`</t>
@@ -2671,6 +2727,24 @@
   </si>
   <si>
     <t xml:space="preserve">Cross coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`data_integrity x dir x abort_data_boundary`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ensure byte-level correctness is verified for writes, reads, and imm at each abort depth (0, 1 word, &gt;1 word committed).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`data_integrity x short_read_actual_len`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify RX FIFO byte correctness at each short-read actual length.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`error_condition x toc`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify abort, short read, TX underflow, and RX overflow each force STOP and suppress the `toc=0` RSTART continuation (the queued command is not chained), while normal completion and over-length reads still continue with RSTART when `toc=0`.</t>
   </si>
   <si>
     <t xml:space="preserve">`cmd_attr x device_type`</t>
@@ -3771,66 +3845,66 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="B31" t="s" s="2">
+      <c r="C31" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="C31" t="s" s="2">
+      <c r="D31" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="D31" t="s" s="2">
+      <c r="E31" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="F31" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="E31" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="F31" t="s" s="2">
+      <c r="G31" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="G31" t="s" s="2">
+      <c r="H31" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="J31" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>217</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>19</v>
+        <v>216</v>
       </c>
       <c r="B32" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="C32" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="C32" t="s" s="2">
+      <c r="D32" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="D32" t="s" s="2">
+      <c r="E32" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="F32" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="E32" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="F32" t="s" s="2">
+      <c r="G32" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="G32" t="s" s="2">
+      <c r="H32" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I32" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="H32" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I32" t="s" s="2">
+      <c r="J32" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>224</v>
       </c>
     </row>
     <row r="33">
@@ -3838,31 +3912,31 @@
         <v>19</v>
       </c>
       <c r="B33" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="C33" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="C33" t="s" s="2">
+      <c r="D33" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="D33" t="s" s="2">
+      <c r="E33" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="F33" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="E33" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="F33" t="s" s="2">
+      <c r="G33" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="G33" t="s" s="2">
+      <c r="H33" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I33" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="H33" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="I33" t="s" s="2">
+      <c r="J33" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>231</v>
       </c>
     </row>
     <row r="34">
@@ -3870,31 +3944,31 @@
         <v>19</v>
       </c>
       <c r="B34" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="C34" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="C34" t="s" s="2">
+      <c r="D34" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="D34" t="s" s="2">
+      <c r="E34" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="F34" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="E34" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="F34" t="s" s="2">
+      <c r="G34" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="G34" t="s" s="2">
+      <c r="H34" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I34" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="H34" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I34" t="s" s="2">
+      <c r="J34" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>238</v>
       </c>
     </row>
     <row r="35">
@@ -3902,31 +3976,31 @@
         <v>19</v>
       </c>
       <c r="B35" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="C35" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="C35" t="s" s="2">
+      <c r="D35" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="D35" t="s" s="2">
+      <c r="E35" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="F35" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="E35" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="F35" t="s" s="2">
+      <c r="G35" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="G35" t="s" s="2">
+      <c r="H35" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I35" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="H35" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I35" t="s" s="2">
+      <c r="J35" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>245</v>
       </c>
     </row>
     <row r="36">
@@ -3934,31 +4008,31 @@
         <v>19</v>
       </c>
       <c r="B36" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="C36" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="C36" t="s" s="2">
+      <c r="D36" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="D36" t="s" s="2">
+      <c r="E36" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="F36" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="E36" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="F36" t="s" s="2">
+      <c r="G36" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="G36" t="s" s="2">
+      <c r="H36" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I36" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="H36" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="I36" t="s" s="2">
+      <c r="J36" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>252</v>
       </c>
     </row>
     <row r="37">
@@ -3966,31 +4040,31 @@
         <v>19</v>
       </c>
       <c r="B37" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="C37" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="C37" t="s" s="2">
+      <c r="D37" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="D37" t="s" s="2">
+      <c r="E37" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="F37" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="E37" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="F37" t="s" s="2">
+      <c r="G37" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="G37" t="s" s="2">
+      <c r="H37" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I37" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="H37" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I37" t="s" s="2">
+      <c r="J37" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>259</v>
       </c>
     </row>
     <row r="38">
@@ -3998,31 +4072,31 @@
         <v>19</v>
       </c>
       <c r="B38" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="C38" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="C38" t="s" s="2">
+      <c r="D38" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="D38" t="s" s="2">
+      <c r="E38" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="F38" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="E38" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="F38" t="s" s="2">
+      <c r="G38" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="G38" t="s" s="2">
+      <c r="H38" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I38" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="H38" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I38" t="s" s="2">
+      <c r="J38" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>266</v>
       </c>
     </row>
     <row r="39">
@@ -4030,95 +4104,95 @@
         <v>19</v>
       </c>
       <c r="B39" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="C39" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="C39" t="s" s="2">
+      <c r="D39" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="D39" t="s" s="2">
+      <c r="E39" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="F39" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="E39" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="F39" t="s" s="2">
+      <c r="G39" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="G39" t="s" s="2">
+      <c r="H39" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I39" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="H39" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I39" t="s" s="2">
+      <c r="J39" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>273</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="C40" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="B40" t="s" s="2">
+      <c r="D40" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="C40" t="s" s="2">
+      <c r="E40" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="F40" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="D40" t="s" s="2">
+      <c r="G40" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="E40" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="F40" t="s" s="2">
+      <c r="H40" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I40" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="G40" t="s" s="2">
+      <c r="J40" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="H40" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>217</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>19</v>
+        <v>280</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D41" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="E41" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="E41" t="s" s="2">
-        <v>281</v>
-      </c>
       <c r="F41" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>285</v>
+        <v>222</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>286</v>
+        <v>223</v>
       </c>
     </row>
     <row r="42">
@@ -4126,31 +4200,31 @@
         <v>19</v>
       </c>
       <c r="B42" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="C42" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="C42" t="s" s="2">
+      <c r="D42" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="D42" t="s" s="2">
+      <c r="E42" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="F42" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="E42" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="F42" t="s" s="2">
+      <c r="G42" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="G42" t="s" s="2">
+      <c r="H42" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I42" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="H42" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I42" t="s" s="2">
+      <c r="J42" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>293</v>
       </c>
     </row>
     <row r="43">
@@ -4158,28 +4232,28 @@
         <v>19</v>
       </c>
       <c r="B43" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="C43" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="C43" t="s" s="2">
+      <c r="D43" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="D43" t="s" s="2">
+      <c r="E43" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="F43" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="E43" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="F43" t="s" s="2">
+      <c r="G43" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="G43" t="s" s="2">
+      <c r="H43" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I43" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>299</v>
@@ -4211,10 +4285,10 @@
         <v>16</v>
       </c>
       <c r="I44" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="J44" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="45">
@@ -4222,31 +4296,31 @@
         <v>19</v>
       </c>
       <c r="B45" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="C45" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="C45" t="s" s="2">
+      <c r="D45" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="D45" t="s" s="2">
+      <c r="E45" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="F45" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="E45" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="F45" t="s" s="2">
+      <c r="G45" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="G45" t="s" s="2">
+      <c r="H45" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I45" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="H45" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="I45" t="s" s="2">
+      <c r="J45" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="46">
@@ -4254,31 +4328,31 @@
         <v>19</v>
       </c>
       <c r="B46" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="C46" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="C46" t="s" s="2">
+      <c r="D46" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="D46" t="s" s="2">
+      <c r="E46" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="F46" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="E46" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="F46" t="s" s="2">
+      <c r="G46" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="G46" t="s" s="2">
+      <c r="H46" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I46" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="H46" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I46" t="s" s="2">
+      <c r="J46" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>320</v>
       </c>
     </row>
     <row r="47">
@@ -4286,31 +4360,31 @@
         <v>19</v>
       </c>
       <c r="B47" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="C47" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="C47" t="s" s="2">
+      <c r="D47" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="D47" t="s" s="2">
+      <c r="E47" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="F47" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="E47" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="F47" t="s" s="2">
+      <c r="G47" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="G47" t="s" s="2">
+      <c r="H47" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I47" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="H47" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="I47" t="s" s="2">
+      <c r="J47" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>327</v>
       </c>
     </row>
     <row r="48">
@@ -4318,36 +4392,36 @@
         <v>19</v>
       </c>
       <c r="B48" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="C48" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="C48" t="s" s="2">
+      <c r="D48" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="D48" t="s" s="2">
+      <c r="E48" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="F48" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="E48" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="F48" t="s" s="2">
+      <c r="G48" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="G48" t="s" s="2">
+      <c r="H48" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I48" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="H48" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>326</v>
-      </c>
       <c r="J48" t="s" s="2">
-        <v>273</v>
+        <v>333</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>333</v>
+        <v>19</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>334</v>
@@ -4371,10 +4445,10 @@
         <v>16</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>340</v>
+        <v>279</v>
       </c>
     </row>
     <row r="50">
@@ -4382,63 +4456,63 @@
         <v>19</v>
       </c>
       <c r="B50" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="D50" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="C50" t="s" s="2">
+      <c r="E50" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="F50" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="D50" t="s" s="2">
+      <c r="G50" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="E50" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="F50" t="s" s="2">
+      <c r="H50" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="J50" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>347</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>19</v>
+        <v>345</v>
       </c>
       <c r="B51" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="D51" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="C51" t="s" s="2">
+      <c r="E51" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="F51" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="D51" t="s" s="2">
+      <c r="G51" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="E51" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="F51" t="s" s="2">
+      <c r="H51" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I51" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="G51" t="s" s="2">
+      <c r="J51" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>353</v>
       </c>
     </row>
     <row r="52">
@@ -4446,28 +4520,28 @@
         <v>19</v>
       </c>
       <c r="B52" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="C52" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="C52" t="s" s="2">
+      <c r="D52" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="D52" t="s" s="2">
+      <c r="E52" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="F52" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="E52" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="F52" t="s" s="2">
+      <c r="G52" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="G52" t="s" s="2">
+      <c r="H52" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I52" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>359</v>
@@ -4499,10 +4573,10 @@
         <v>16</v>
       </c>
       <c r="I53" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="J53" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>366</v>
       </c>
     </row>
     <row r="54">
@@ -4510,63 +4584,63 @@
         <v>19</v>
       </c>
       <c r="B54" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="C54" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="C54" t="s" s="2">
+      <c r="D54" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="D54" t="s" s="2">
+      <c r="E54" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="F54" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="E54" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="F54" t="s" s="2">
+      <c r="G54" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="G54" t="s" s="2">
+      <c r="H54" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="J54" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>373</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="D55" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="B55" t="s" s="2">
+      <c r="E55" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="F55" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="C55" t="s" s="2">
+      <c r="G55" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="D55" t="s" s="2">
+      <c r="H55" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I55" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="E55" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="F55" t="s" s="2">
+      <c r="J55" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>381</v>
       </c>
     </row>
     <row r="56">
@@ -4574,63 +4648,63 @@
         <v>19</v>
       </c>
       <c r="B56" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="D56" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="E56" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="F56" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="C56" t="s" s="2">
+      <c r="G56" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="D56" t="s" s="2">
+      <c r="H56" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="J56" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="E56" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="F56" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>388</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>19</v>
+        <v>385</v>
       </c>
       <c r="B57" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="D57" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="E57" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="F57" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="C57" t="s" s="2">
+      <c r="G57" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="D57" t="s" s="2">
+      <c r="H57" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I57" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="E57" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="F57" t="s" s="2">
+      <c r="J57" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>394</v>
       </c>
     </row>
     <row r="58">
@@ -4638,31 +4712,31 @@
         <v>19</v>
       </c>
       <c r="B58" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="D58" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="C58" t="s" s="2">
+      <c r="E58" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="F58" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="D58" t="s" s="2">
+      <c r="G58" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="E58" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="F58" t="s" s="2">
+      <c r="H58" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I58" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="G58" t="s" s="2">
+      <c r="J58" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>400</v>
       </c>
     </row>
     <row r="59">
@@ -4670,31 +4744,31 @@
         <v>19</v>
       </c>
       <c r="B59" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="C59" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="C59" t="s" s="2">
+      <c r="D59" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="D59" t="s" s="2">
+      <c r="E59" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="F59" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="E59" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="F59" t="s" s="2">
+      <c r="G59" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="G59" t="s" s="2">
+      <c r="H59" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="J59" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>406</v>
       </c>
     </row>
     <row r="60">
@@ -4702,31 +4776,31 @@
         <v>19</v>
       </c>
       <c r="B60" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="C60" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="C60" t="s" s="2">
+      <c r="D60" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="D60" t="s" s="2">
+      <c r="E60" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="F60" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="E60" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="F60" t="s" s="2">
+      <c r="G60" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="G60" t="s" s="2">
+      <c r="H60" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="J60" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>413</v>
       </c>
     </row>
     <row r="61">
@@ -4734,95 +4808,95 @@
         <v>19</v>
       </c>
       <c r="B61" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="D61" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="C61" t="s" s="2">
+      <c r="E61" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="F61" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="D61" t="s" s="2">
+      <c r="G61" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="E61" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="F61" t="s" s="2">
+      <c r="H61" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="J61" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>419</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>19</v>
+        <v>418</v>
       </c>
       <c r="B62" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="C62" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="C62" t="s" s="2">
+      <c r="D62" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="D62" t="s" s="2">
+      <c r="E62" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="F62" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="E62" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="F62" t="s" s="2">
+      <c r="G62" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="G62" t="s" s="2">
+      <c r="H62" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I62" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="H62" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="I62" t="s" s="2">
+      <c r="J62" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>426</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C63" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="B63" t="s" s="2">
+      <c r="D63" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="C63" t="s" s="2">
+      <c r="E63" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="F63" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="D63" t="s" s="2">
+      <c r="G63" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="E63" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="F63" t="s" s="2">
+      <c r="H63" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I63" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="G63" t="s" s="2">
+      <c r="J63" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>434</v>
       </c>
     </row>
     <row r="64">
@@ -4830,31 +4904,31 @@
         <v>19</v>
       </c>
       <c r="B64" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="D64" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="C64" t="s" s="2">
+      <c r="E64" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="F64" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="D64" t="s" s="2">
+      <c r="G64" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="E64" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="F64" t="s" s="2">
+      <c r="H64" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I64" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="G64" t="s" s="2">
+      <c r="J64" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>441</v>
       </c>
     </row>
     <row r="65">
@@ -4862,31 +4936,31 @@
         <v>19</v>
       </c>
       <c r="B65" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="D65" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="C65" t="s" s="2">
+      <c r="E65" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="F65" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="D65" t="s" s="2">
+      <c r="G65" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="E65" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="F65" t="s" s="2">
+      <c r="H65" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I65" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="G65" t="s" s="2">
+      <c r="J65" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>448</v>
       </c>
     </row>
     <row r="66">
@@ -4894,31 +4968,31 @@
         <v>19</v>
       </c>
       <c r="B66" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="D66" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="C66" t="s" s="2">
+      <c r="E66" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="F66" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="D66" t="s" s="2">
+      <c r="G66" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="E66" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="F66" t="s" s="2">
+      <c r="H66" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I66" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="G66" t="s" s="2">
+      <c r="J66" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>455</v>
       </c>
     </row>
     <row r="67">
@@ -4926,31 +5000,31 @@
         <v>19</v>
       </c>
       <c r="B67" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="D67" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="C67" t="s" s="2">
+      <c r="E67" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="F67" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="D67" t="s" s="2">
+      <c r="G67" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="E67" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="F67" t="s" s="2">
+      <c r="H67" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I67" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="G67" t="s" s="2">
+      <c r="J67" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>462</v>
       </c>
     </row>
     <row r="68">
@@ -4958,31 +5032,31 @@
         <v>19</v>
       </c>
       <c r="B68" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="D68" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="C68" t="s" s="2">
+      <c r="E68" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="F68" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="D68" t="s" s="2">
+      <c r="G68" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="E68" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="F68" t="s" s="2">
+      <c r="H68" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I68" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="G68" t="s" s="2">
+      <c r="J68" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>468</v>
       </c>
     </row>
     <row r="69">
@@ -4990,31 +5064,31 @@
         <v>19</v>
       </c>
       <c r="B69" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="C69" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="C69" t="s" s="2">
+      <c r="D69" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="D69" t="s" s="2">
+      <c r="E69" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="F69" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="E69" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="F69" t="s" s="2">
+      <c r="G69" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="G69" t="s" s="2">
+      <c r="H69" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="J69" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>475</v>
       </c>
     </row>
     <row r="70">
@@ -5022,31 +5096,31 @@
         <v>19</v>
       </c>
       <c r="B70" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="D70" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="C70" t="s" s="2">
+      <c r="E70" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="F70" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="D70" t="s" s="2">
+      <c r="G70" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="E70" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="F70" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>59</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="71">
@@ -5054,25 +5128,25 @@
         <v>19</v>
       </c>
       <c r="B71" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C71" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="C71" t="s" s="2">
+      <c r="D71" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="D71" t="s" s="2">
+      <c r="E71" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="F71" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="E71" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="F71" t="s" s="2">
+      <c r="G71" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="G71" t="s" s="2">
+      <c r="H71" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>59</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>487</v>
@@ -5083,28 +5157,28 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>19</v>
+        <v>489</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D72" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="E72" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="E72" t="s" s="2">
-        <v>490</v>
-      </c>
       <c r="F72" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>494</v>
+        <v>16</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>495</v>
@@ -5115,34 +5189,34 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B73" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="B73" t="s" s="2">
+      <c r="C73" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="C73" t="s" s="2">
+      <c r="D73" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="D73" t="s" s="2">
+      <c r="E73" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="F73" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="E73" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="F73" t="s" s="2">
+      <c r="G73" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="G73" t="s" s="2">
+      <c r="H73" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I73" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="H73" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I73" t="s" s="2">
+      <c r="J73" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>504</v>
       </c>
     </row>
     <row r="74">
@@ -5150,31 +5224,31 @@
         <v>19</v>
       </c>
       <c r="B74" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C74" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="C74" t="s" s="2">
+      <c r="D74" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="D74" t="s" s="2">
+      <c r="E74" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="F74" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="E74" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="F74" t="s" s="2">
+      <c r="G74" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="G74" t="s" s="2">
+      <c r="H74" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I74" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="H74" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I74" t="s" s="2">
+      <c r="J74" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>511</v>
       </c>
     </row>
     <row r="75">
@@ -5182,31 +5256,31 @@
         <v>19</v>
       </c>
       <c r="B75" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="C75" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="C75" t="s" s="2">
+      <c r="D75" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="D75" t="s" s="2">
+      <c r="E75" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="F75" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="E75" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="F75" t="s" s="2">
+      <c r="G75" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="G75" t="s" s="2">
+      <c r="H75" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I75" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="H75" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I75" t="s" s="2">
+      <c r="J75" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>518</v>
       </c>
     </row>
     <row r="76">
@@ -5214,31 +5288,31 @@
         <v>19</v>
       </c>
       <c r="B76" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="C76" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="C76" t="s" s="2">
+      <c r="D76" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="D76" t="s" s="2">
+      <c r="E76" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="F76" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="E76" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="F76" t="s" s="2">
+      <c r="G76" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="G76" t="s" s="2">
-        <v>523</v>
-      </c>
       <c r="H76" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>524</v>
+        <v>377</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>525</v>
+        <v>378</v>
       </c>
     </row>
     <row r="77">
@@ -5246,31 +5320,31 @@
         <v>19</v>
       </c>
       <c r="B77" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="D77" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="E77" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="F77" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="C77" t="s" s="2">
+      <c r="G77" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="D77" t="s" s="2">
+      <c r="H77" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I77" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="E77" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="F77" t="s" s="2">
+      <c r="J77" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>531</v>
       </c>
     </row>
     <row r="78">
@@ -5278,36 +5352,36 @@
         <v>19</v>
       </c>
       <c r="B78" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="D78" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="E78" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="F78" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="C78" t="s" s="2">
+      <c r="G78" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="D78" t="s" s="2">
+      <c r="H78" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I78" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="E78" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="F78" t="s" s="2">
+      <c r="J78" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>373</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>19</v>
+        <v>536</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>537</v>
@@ -5360,45 +5434,45 @@
         <v>548</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="I80" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="J80" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>550</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="C81" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="B81" t="s" s="2">
+      <c r="D81" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="C81" t="s" s="2">
+      <c r="E81" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="F81" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="D81" t="s" s="2">
+      <c r="G81" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="E81" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="F81" t="s" s="2">
+      <c r="H81" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="J81" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>557</v>
       </c>
     </row>
     <row r="82">
@@ -5406,31 +5480,31 @@
         <v>19</v>
       </c>
       <c r="B82" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="D82" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="C82" t="s" s="2">
+      <c r="E82" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="F82" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="D82" t="s" s="2">
+      <c r="G82" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="E82" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="F82" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>562</v>
-      </c>
       <c r="H82" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>412</v>
+        <v>377</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>563</v>
+        <v>378</v>
       </c>
     </row>
     <row r="83">
@@ -5438,31 +5512,31 @@
         <v>19</v>
       </c>
       <c r="B83" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="D83" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="E83" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="F83" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="C83" t="s" s="2">
+      <c r="G83" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="D83" t="s" s="2">
+      <c r="H83" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="J83" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="E83" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="F83" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>373</v>
       </c>
     </row>
     <row r="84">
@@ -5470,31 +5544,31 @@
         <v>19</v>
       </c>
       <c r="B84" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="C84" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="D84" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="C84" t="s" s="2">
+      <c r="E84" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="F84" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="D84" t="s" s="2">
+      <c r="G84" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="E84" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="F84" t="s" s="2">
+      <c r="H84" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="J84" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>574</v>
       </c>
     </row>
     <row r="85">
@@ -5502,31 +5576,31 @@
         <v>19</v>
       </c>
       <c r="B85" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="C85" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="D85" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="C85" t="s" s="2">
+      <c r="E85" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="F85" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="D85" t="s" s="2">
+      <c r="G85" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="E85" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="F85" t="s" s="2">
+      <c r="H85" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I85" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="G85" t="s" s="2">
+      <c r="J85" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>580</v>
       </c>
     </row>
     <row r="86">
@@ -5534,28 +5608,28 @@
         <v>19</v>
       </c>
       <c r="B86" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="C86" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="C86" t="s" s="2">
+      <c r="D86" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="D86" t="s" s="2">
+      <c r="E86" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="F86" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="E86" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="F86" t="s" s="2">
+      <c r="G86" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="G86" t="s" s="2">
+      <c r="H86" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I86" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="J86" t="s" s="2">
         <v>586</v>
@@ -5587,10 +5661,10 @@
         <v>16</v>
       </c>
       <c r="I87" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="J87" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>593</v>
       </c>
     </row>
     <row r="88">
@@ -5598,28 +5672,28 @@
         <v>19</v>
       </c>
       <c r="B88" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="C88" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="C88" t="s" s="2">
+      <c r="D88" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="D88" t="s" s="2">
+      <c r="E88" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="F88" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="E88" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="F88" t="s" s="2">
+      <c r="G88" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="G88" t="s" s="2">
+      <c r="H88" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I88" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="J88" t="s" s="2">
         <v>599</v>
@@ -5680,7 +5754,7 @@
         <v>611</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>612</v>
@@ -5712,13 +5786,13 @@
         <v>618</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="I91" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="J91" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>620</v>
       </c>
     </row>
     <row r="92">
@@ -5726,31 +5800,31 @@
         <v>19</v>
       </c>
       <c r="B92" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="C92" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="C92" t="s" s="2">
+      <c r="D92" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="D92" t="s" s="2">
+      <c r="E92" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="F92" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="E92" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="F92" t="s" s="2">
+      <c r="G92" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="G92" t="s" s="2">
+      <c r="H92" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I92" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="H92" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I92" t="s" s="2">
+      <c r="J92" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>627</v>
       </c>
     </row>
     <row r="93">
@@ -5758,63 +5832,63 @@
         <v>19</v>
       </c>
       <c r="B93" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="C93" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="C93" t="s" s="2">
+      <c r="D93" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="D93" t="s" s="2">
+      <c r="E93" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="F93" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="E93" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="F93" t="s" s="2">
+      <c r="G93" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="G93" t="s" s="2">
+      <c r="H93" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I93" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="H93" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I93" t="s" s="2">
+      <c r="J93" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>634</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="C94" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="B94" t="s" s="2">
+      <c r="D94" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="C94" t="s" s="2">
+      <c r="E94" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="F94" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="D94" t="s" s="2">
+      <c r="G94" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="E94" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="F94" t="s" s="2">
+      <c r="H94" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I94" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="G94" t="s" s="2">
+      <c r="J94" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>642</v>
       </c>
     </row>
     <row r="95">
@@ -5822,36 +5896,36 @@
         <v>19</v>
       </c>
       <c r="B95" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="C95" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="D95" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="C95" t="s" s="2">
+      <c r="E95" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="F95" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="D95" t="s" s="2">
+      <c r="G95" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="E95" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="F95" t="s" s="2">
+      <c r="H95" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I95" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="G95" t="s" s="2">
+      <c r="J95" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="I95" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="J95" t="s" s="2">
-        <v>496</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>19</v>
+        <v>648</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>649</v>
@@ -5872,7 +5946,7 @@
         <v>653</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>654</v>
@@ -5904,45 +5978,45 @@
         <v>660</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>59</v>
+        <v>486</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>612</v>
+        <v>661</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>661</v>
+        <v>488</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B98" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="B98" t="s" s="2">
+      <c r="C98" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="C98" t="s" s="2">
+      <c r="D98" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="D98" t="s" s="2">
+      <c r="E98" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="F98" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="E98" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="F98" t="s" s="2">
+      <c r="G98" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="G98" t="s" s="2">
+      <c r="H98" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I98" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="H98" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I98" t="s" s="2">
+      <c r="J98" t="s" s="2">
         <v>668</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>669</v>
       </c>
     </row>
     <row r="99">
@@ -5950,63 +6024,63 @@
         <v>19</v>
       </c>
       <c r="B99" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="C99" t="s" s="2">
         <v>670</v>
       </c>
-      <c r="C99" t="s" s="2">
+      <c r="D99" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="D99" t="s" s="2">
+      <c r="E99" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="F99" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="E99" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="F99" t="s" s="2">
+      <c r="G99" t="s" s="2">
         <v>673</v>
       </c>
-      <c r="G99" t="s" s="2">
+      <c r="H99" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="J99" t="s" s="2">
         <v>674</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>676</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>19</v>
+        <v>675</v>
       </c>
       <c r="B100" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="C100" t="s" s="2">
         <v>677</v>
       </c>
-      <c r="C100" t="s" s="2">
+      <c r="D100" t="s" s="2">
         <v>678</v>
       </c>
-      <c r="D100" t="s" s="2">
+      <c r="E100" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="F100" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="E100" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="F100" t="s" s="2">
+      <c r="G100" t="s" s="2">
         <v>680</v>
       </c>
-      <c r="G100" t="s" s="2">
+      <c r="H100" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I100" t="s" s="2">
         <v>681</v>
       </c>
-      <c r="H100" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I100" t="s" s="2">
+      <c r="J100" t="s" s="2">
         <v>682</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>676</v>
       </c>
     </row>
     <row r="101">
@@ -6064,13 +6138,13 @@
         <v>694</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>695</v>
+        <v>689</v>
       </c>
     </row>
     <row r="103">
@@ -6128,13 +6202,13 @@
         <v>707</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I104" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="J104" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>709</v>
       </c>
     </row>
     <row r="105">
@@ -6142,63 +6216,63 @@
         <v>19</v>
       </c>
       <c r="B105" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="C105" t="s" s="2">
         <v>710</v>
       </c>
-      <c r="C105" t="s" s="2">
+      <c r="D105" t="s" s="2">
         <v>711</v>
       </c>
-      <c r="D105" t="s" s="2">
+      <c r="E105" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="F105" t="s" s="2">
         <v>712</v>
       </c>
-      <c r="E105" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="F105" t="s" s="2">
+      <c r="G105" t="s" s="2">
         <v>713</v>
       </c>
-      <c r="G105" t="s" s="2">
+      <c r="H105" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I105" t="s" s="2">
         <v>714</v>
       </c>
-      <c r="H105" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="I105" t="s" s="2">
+      <c r="J105" t="s" s="2">
         <v>715</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>716</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="C106" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="B106" t="s" s="2">
+      <c r="D106" t="s" s="2">
         <v>718</v>
       </c>
-      <c r="C106" t="s" s="2">
+      <c r="E106" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="F106" t="s" s="2">
         <v>719</v>
       </c>
-      <c r="D106" t="s" s="2">
+      <c r="G106" t="s" s="2">
         <v>720</v>
       </c>
-      <c r="E106" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="F106" t="s" s="2">
+      <c r="H106" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I106" t="s" s="2">
         <v>721</v>
       </c>
-      <c r="G106" t="s" s="2">
+      <c r="J106" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>724</v>
       </c>
     </row>
     <row r="107">
@@ -6206,60 +6280,60 @@
         <v>19</v>
       </c>
       <c r="B107" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="C107" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="D107" t="s" s="2">
         <v>725</v>
       </c>
-      <c r="C107" t="s" s="2">
+      <c r="E107" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="F107" t="s" s="2">
         <v>726</v>
       </c>
-      <c r="D107" t="s" s="2">
+      <c r="G107" t="s" s="2">
         <v>727</v>
       </c>
-      <c r="E107" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="F107" t="s" s="2">
+      <c r="H107" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I107" t="s" s="2">
         <v>728</v>
       </c>
-      <c r="G107" t="s" s="2">
+      <c r="J107" t="s" s="2">
         <v>729</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>731</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>19</v>
+        <v>730</v>
       </c>
       <c r="B108" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="C108" t="s" s="2">
         <v>732</v>
       </c>
-      <c r="C108" t="s" s="2">
+      <c r="D108" t="s" s="2">
         <v>733</v>
       </c>
-      <c r="D108" t="s" s="2">
+      <c r="E108" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="F108" t="s" s="2">
         <v>734</v>
       </c>
-      <c r="E108" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="F108" t="s" s="2">
+      <c r="G108" t="s" s="2">
         <v>735</v>
       </c>
-      <c r="G108" t="s" s="2">
+      <c r="H108" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I108" t="s" s="2">
         <v>736</v>
-      </c>
-      <c r="H108" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>723</v>
       </c>
       <c r="J108" t="s" s="2">
         <v>737</v>
@@ -6320,10 +6394,10 @@
         <v>749</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="I110" t="s" s="2">
-        <v>723</v>
+        <v>736</v>
       </c>
       <c r="J110" t="s" s="2">
         <v>750</v>
@@ -6352,13 +6426,13 @@
         <v>755</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>131</v>
+        <v>16</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>723</v>
+        <v>756</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="112">
@@ -6366,31 +6440,31 @@
         <v>19</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D112" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="E112" t="s" s="2">
         <v>759</v>
       </c>
-      <c r="E112" t="s" s="2">
-        <v>758</v>
-      </c>
       <c r="F112" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>723</v>
+        <v>736</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>756</v>
+        <v>763</v>
       </c>
     </row>
     <row r="113">
@@ -6398,63 +6472,63 @@
         <v>19</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D113" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="E113" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="F113" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>131</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>173</v>
+        <v>736</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>768</v>
+        <v>19</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D114" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="E114" t="s" s="2">
         <v>771</v>
       </c>
-      <c r="E114" t="s" s="2">
-        <v>770</v>
-      </c>
       <c r="F114" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>131</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>774</v>
+        <v>736</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>775</v>
+        <v>769</v>
       </c>
     </row>
     <row r="115">
@@ -6462,63 +6536,63 @@
         <v>19</v>
       </c>
       <c r="B115" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="C115" t="s" s="2">
         <v>776</v>
       </c>
-      <c r="C115" t="s" s="2">
+      <c r="D115" t="s" s="2">
         <v>777</v>
       </c>
-      <c r="D115" t="s" s="2">
+      <c r="E115" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="F115" t="s" s="2">
         <v>778</v>
       </c>
-      <c r="E115" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="F115" t="s" s="2">
+      <c r="G115" t="s" s="2">
         <v>779</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>780</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>131</v>
       </c>
       <c r="I115" t="s" s="2">
-        <v>774</v>
+        <v>173</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>775</v>
+        <v>780</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>19</v>
+        <v>781</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D116" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="E116" t="s" s="2">
         <v>783</v>
       </c>
-      <c r="E116" t="s" s="2">
-        <v>782</v>
-      </c>
       <c r="F116" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>131</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>775</v>
+        <v>788</v>
       </c>
     </row>
     <row r="117">
@@ -6526,31 +6600,95 @@
         <v>19</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="D117" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="E117" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="F117" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>131</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>775</v>
+        <v>788</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="D118" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="E118" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="F118" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="D119" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="E119" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="F119" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>788</v>
       </c>
     </row>
   </sheetData>
@@ -6562,18 +6700,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>793</v>
+        <v>806</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>794</v>
+        <v>807</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>795</v>
+        <v>808</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>796</v>
+        <v>809</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>19</v>
@@ -6587,10 +6725,10 @@
         <v>19</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>797</v>
+        <v>810</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>798</v>
+        <v>811</v>
       </c>
     </row>
     <row r="4">
@@ -6598,10 +6736,10 @@
         <v>19</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>799</v>
+        <v>812</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>800</v>
+        <v>811</v>
       </c>
     </row>
     <row r="5">
@@ -6609,10 +6747,10 @@
         <v>19</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>801</v>
+        <v>813</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>802</v>
+        <v>814</v>
       </c>
     </row>
     <row r="6">
@@ -6620,10 +6758,10 @@
         <v>19</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>804</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -6631,10 +6769,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>806</v>
+        <v>818</v>
       </c>
     </row>
     <row r="8">
@@ -6642,10 +6780,10 @@
         <v>19</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>808</v>
+        <v>820</v>
       </c>
     </row>
     <row r="9">
@@ -6653,10 +6791,10 @@
         <v>19</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>809</v>
+        <v>821</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>810</v>
+        <v>822</v>
       </c>
     </row>
     <row r="10">
@@ -6664,10 +6802,10 @@
         <v>19</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>231</v>
+        <v>823</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>811</v>
+        <v>824</v>
       </c>
     </row>
     <row r="11">
@@ -6675,10 +6813,10 @@
         <v>19</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>812</v>
+        <v>825</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>813</v>
+        <v>826</v>
       </c>
     </row>
     <row r="12">
@@ -6686,10 +6824,10 @@
         <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>814</v>
+        <v>827</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>815</v>
+        <v>828</v>
       </c>
     </row>
     <row r="13">
@@ -6697,10 +6835,10 @@
         <v>19</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>816</v>
+        <v>237</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>817</v>
+        <v>829</v>
       </c>
     </row>
     <row r="14">
@@ -6708,10 +6846,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>818</v>
+        <v>830</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>819</v>
+        <v>831</v>
       </c>
     </row>
     <row r="15">
@@ -6719,10 +6857,10 @@
         <v>19</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>820</v>
+        <v>832</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>821</v>
+        <v>833</v>
       </c>
     </row>
     <row r="16">
@@ -6730,10 +6868,10 @@
         <v>19</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>238</v>
+        <v>834</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>822</v>
+        <v>835</v>
       </c>
     </row>
     <row r="17">
@@ -6741,10 +6879,10 @@
         <v>19</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>823</v>
+        <v>836</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>824</v>
+        <v>837</v>
       </c>
     </row>
     <row r="18">
@@ -6752,10 +6890,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>825</v>
+        <v>838</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>826</v>
+        <v>839</v>
       </c>
     </row>
     <row r="19">
@@ -6763,10 +6901,10 @@
         <v>19</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>827</v>
+        <v>244</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>828</v>
+        <v>840</v>
       </c>
     </row>
     <row r="20">
@@ -6774,10 +6912,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>829</v>
+        <v>841</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>830</v>
+        <v>842</v>
       </c>
     </row>
     <row r="21">
@@ -6785,10 +6923,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>147</v>
+        <v>843</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>831</v>
+        <v>844</v>
       </c>
     </row>
     <row r="22">
@@ -6796,10 +6934,10 @@
         <v>19</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>202</v>
+        <v>845</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>832</v>
+        <v>846</v>
       </c>
     </row>
     <row r="23">
@@ -6807,10 +6945,10 @@
         <v>19</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>550</v>
+        <v>847</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>833</v>
+        <v>848</v>
       </c>
     </row>
     <row r="24">
@@ -6818,10 +6956,10 @@
         <v>19</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>834</v>
+        <v>147</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>835</v>
+        <v>849</v>
       </c>
     </row>
     <row r="25">
@@ -6829,10 +6967,10 @@
         <v>19</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>836</v>
+        <v>202</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>837</v>
+        <v>850</v>
       </c>
     </row>
     <row r="26">
@@ -6840,10 +6978,10 @@
         <v>19</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>838</v>
+        <v>535</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>839</v>
+        <v>851</v>
       </c>
     </row>
     <row r="27">
@@ -6851,10 +6989,10 @@
         <v>19</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>840</v>
+        <v>852</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>841</v>
+        <v>853</v>
       </c>
     </row>
     <row r="28">
@@ -6862,10 +7000,10 @@
         <v>19</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="29">
@@ -6873,10 +7011,10 @@
         <v>19</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>844</v>
+        <v>856</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>845</v>
+        <v>857</v>
       </c>
     </row>
     <row r="30">
@@ -6884,10 +7022,10 @@
         <v>19</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>593</v>
+        <v>858</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>846</v>
+        <v>859</v>
       </c>
     </row>
     <row r="31">
@@ -6895,21 +7033,21 @@
         <v>19</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>19</v>
+        <v>860</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>19</v>
+        <v>861</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>847</v>
+        <v>19</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>19</v>
+        <v>862</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>19</v>
+        <v>863</v>
       </c>
     </row>
     <row r="33">
@@ -6917,10 +7055,10 @@
         <v>19</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>848</v>
+        <v>613</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>849</v>
+        <v>864</v>
       </c>
     </row>
     <row r="34">
@@ -6928,21 +7066,21 @@
         <v>19</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>850</v>
+        <v>19</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>851</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>19</v>
+        <v>865</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>852</v>
+        <v>19</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>853</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36">
@@ -6950,10 +7088,10 @@
         <v>19</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>854</v>
+        <v>866</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>855</v>
+        <v>867</v>
       </c>
     </row>
     <row r="37">
@@ -6961,10 +7099,10 @@
         <v>19</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>856</v>
+        <v>868</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>857</v>
+        <v>869</v>
       </c>
     </row>
     <row r="38">
@@ -6972,10 +7110,10 @@
         <v>19</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>858</v>
+        <v>870</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>859</v>
+        <v>871</v>
       </c>
     </row>
     <row r="39">
@@ -6983,10 +7121,10 @@
         <v>19</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>860</v>
+        <v>872</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>861</v>
+        <v>873</v>
       </c>
     </row>
     <row r="40">
@@ -6994,10 +7132,10 @@
         <v>19</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>863</v>
+        <v>875</v>
       </c>
     </row>
     <row r="41">
@@ -7005,10 +7143,10 @@
         <v>19</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>864</v>
+        <v>876</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>865</v>
+        <v>877</v>
       </c>
     </row>
     <row r="42">
@@ -7016,10 +7154,10 @@
         <v>19</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>866</v>
+        <v>878</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>867</v>
+        <v>879</v>
       </c>
     </row>
     <row r="43">
@@ -7027,10 +7165,76 @@
         <v>19</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>868</v>
+        <v>880</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>869</v>
+        <v>881</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>882</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>884</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>886</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>888</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>890</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>892</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>893</v>
       </c>
     </row>
   </sheetData>
@@ -7045,43 +7249,43 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>870</v>
+        <v>894</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>871</v>
+        <v>895</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>872</v>
+        <v>896</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>752</v>
+        <v>765</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>755</v>
+        <v>768</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>873</v>
+        <v>897</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>758</v>
+        <v>771</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>761</v>
+        <v>774</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>874</v>
+        <v>898</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>763</v>
+        <v>776</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>766</v>
+        <v>779</v>
       </c>
     </row>
   </sheetData>
@@ -7105,58 +7309,58 @@
         <v>4</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>875</v>
+        <v>899</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>751</v>
+        <v>764</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>717</v>
+        <v>730</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>753</v>
+        <v>766</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>752</v>
+        <v>765</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>756</v>
+        <v>769</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>757</v>
+        <v>770</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>717</v>
+        <v>730</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>759</v>
+        <v>772</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>758</v>
+        <v>771</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>756</v>
+        <v>769</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>762</v>
+        <v>775</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>717</v>
+        <v>730</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>764</v>
+        <v>777</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>763</v>
+        <v>776</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>767</v>
+        <v>780</v>
       </c>
     </row>
   </sheetData>

--- a/docs/test_plan/I3C_Testplan.xlsx
+++ b/docs/test_plan/I3C_Testplan.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="900">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="843">
   <si>
     <t xml:space="preserve">Category</t>
   </si>
@@ -84,7 +84,7 @@
   </si>
   <si>
     <t xml:space="preserve">Preconditions: CMD FIFO empty.
-Stimulus / Actions: Toggle `HC_CONTROL[0]`; queue a command while disabled and then enable.</t>
+Stimulus / Actions: Toggle `HC_CONTROL[31]` (BUS_ENABLE); queue a command while disabled and then enable.</t>
   </si>
   <si>
     <t xml:space="preserve">No bus transaction before enable; command starts after enable; status returns idle after completion.</t>
@@ -106,7 +106,7 @@
   </si>
   <si>
     <t xml:space="preserve">Preconditions: Controller idle and CMD FIFO empty; DAT[0] is I3C dynamic address `0x08`; device ACKs target address and, when enabled, broadcast header.
-Stimulus / Actions: Read `HC_CONTROL[BROADCAST_ADDR_ENABLE]` after reset; set and clear the bit through `HC_CONTROL`; set only this bit without `HC_CONTROL[0]`; then issue one 4-byte SDR private write with `BROADCAST_ADDR_ENABLE=0` and one with `BROADCAST_ADDR_ENABLE=1`.</t>
+Stimulus / Actions: Read `HC_CONTROL[BROADCAST_ADDR_ENABLE]` after reset; set and clear the bit through `HC_CONTROL`; set only this bit without `HC_CONTROL[31]` (BUS_ENABLE); then issue one 4-byte SDR private write with `BROADCAST_ADDR_ENABLE=0` and one with `BROADCAST_ADDR_ENABLE=1`.</t>
   </si>
   <si>
     <t xml:space="preserve">Reset value is 0; writable set/clear behavior is correct; setting `BROADCAST_ADDR_ENABLE` alone does not enable the controller and does not start a bus transaction; disabled write starts directly with `START + 0x08/W`; enabled write emits `START + 0x7e/W + ACK + Sr + 0x08/W + ACK + data/T-bit + STOP`; both RESPs report success with matching lengths.</t>
@@ -128,7 +128,7 @@
   </si>
   <si>
     <t xml:space="preserve">Preconditions: Controller idle.
-Stimulus / Actions: Write/read all I3C timing CSRs `T_R` through `T_BUS_FREE` and all I2C timing CSRs `I2C_T_R` through `I2C_T_BUF` using default, zero, minimum nonzero, maximum 20-bit, random legal, and reserved-upper-bit values.</t>
+Stimulus / Actions: Write/read all I3C timing CSRs `T_R` through `T_BUS_FREE` and all I2C timing CSRs `I2C_T_SU_DAT` through `I2C_T_BUF` (I2C shares `T_R`/`T_F`/`T_HD_DAT` with I3C) using default, zero, minimum nonzero, maximum 20-bit, random legal, and reserved-upper-bit values.</t>
   </si>
   <si>
     <t xml:space="preserve">Readback matches written `[19:0]` values; reserved upper bits read 0; writes to one timing CSR do not alter other timing CSRs.</t>
@@ -216,10 +216,10 @@
   </si>
   <si>
     <t xml:space="preserve">Preconditions: Queues contain at least one entry where possible.
-Stimulus / Actions: Poll idle, write `HC_CONTROL[1]=1`, then read queue status and ports.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CMD/TX/RX/RESP queues are empty; `SW_RESET` self-clears.</t>
+Stimulus / Actions: Poll idle, write `RESET_CONTROL[0]=1` (SOFT_RST), then read queue status and ports.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMD/TX/RX/RESP queues are empty; `SOFT_RST` self-clears.</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_sw_reset`, `cp_fifo_state`</t>
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t xml:space="preserve">Preconditions: RX/RESP entries exist.
-Stimulus / Actions: Read `RX_DATA_PORT` and `RESP_PORT`; read again after empty.</t>
+Stimulus / Actions: Read `PIO_DATA_PORT` and `RESP_PORT`; read again after empty.</t>
   </si>
   <si>
     <t xml:space="preserve">Valid reads pop one entry; empty reads return 0 and do not underflow.</t>
@@ -307,17 +307,17 @@
     <t xml:space="preserve">CSR_013</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify `HC_CONTROL[3]` (HC abort) read/write and level-bit persistence.</t>
+    <t xml:space="preserve">Verify `HC_CONTROL[29]` (HC abort) read/write and level-bit persistence.</t>
   </si>
   <si>
     <t xml:space="preserve">`csr_hc_abort_control`</t>
   </si>
   <si>
     <t xml:space="preserve">Preconditions: Controller idle and CMD FIFO empty.
-Stimulus / Actions: Read `HC_CONTROL[3]` after reset; set and clear the bit through `HC_CONTROL`; set only this bit without `HC_CONTROL[0]`; hold it set across several read cycles and a queued command.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reset value is 0; writable set/clear behavior is correct; the bit is never auto-cleared by hardware and holds its written value until software clears it; setting it alone does not enable the controller. The abort effect on an active transfer and its response encoding are covered by `SDRW_009`, `SDRR_009`, and `ERR_007`.</t>
+Stimulus / Actions: Read `HC_CONTROL[29]` after reset; set and clear the bit through `HC_CONTROL`; set only this bit without `HC_CONTROL[31]` (BUS_ENABLE); hold it set across several read cycles and a queued command.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reset value is 0; writable set/clear behavior is correct; the bit is never auto-cleared by hardware and holds its written value until software clears it; setting it alone does not enable the controller. Active SDR write/read abort behavior, response encoding, and recovery are owned by `ERR_009`.</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_hc_abort`, `cp_csr_addr`</t>
@@ -411,23 +411,83 @@
     <t xml:space="preserve">FIFO_005</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify documented depth restriction.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`fifo_non_power_of_two_elaboration`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Block-level elaboration.
-Stimulus / Actions: Instantiate `sync_fifo` with non-power-of-two depth in a negative compile test.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elaboration fails with the documented parameter-check fatal/assertion required by the FIFO contract.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_param_illegal`</t>
+    <t xml:space="preserve">Mark documented depth restriction covered by RTL elaboration assertion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`sync_fifo_depth_power_of_two_contract`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: RTL parameterization.
+Stimulus / Actions: No standalone runtime or negative regression target; `sync_fifo` asserts `Depth == (1 &lt;&lt; $clog2(Depth))` during elaboration.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Illegal non-power-of-two depths fail through the RTL parameter contract; legal configured queue depths are covered by normal compile and FIFO regressions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retired</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTL elaboration assertion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIFO_006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify FIFO pointer wrap and reuse after full-depth traffic.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`fifo_pointer_wrap_reuse`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: FIFO reset; run on CMD, TX, RX, and RESP queue instances.
+Stimulus / Actions: Fill FIFO to depth, drain all entries, then push a second distinct sequence and drain again. Include at least one cycle where write/read pointers have wrapped through the extra-MSB boundary.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both generations preserve FIFO order; stale entries from the first generation never reappear; full/empty/depth flags remain correct after wrap and after final drain.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_fifo_wrap`, `cp_fifo_generation`, `cross_fifo_kind_x_wrap`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIFO_007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify simultaneous read/write behavior at exact empty and exact full boundaries.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`fifo_simultaneous_rw_empty_full_edges`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: FIFO can be driven at block-level or through queue-facing handshakes.
+Stimulus / Actions: Case A: from empty, assert `wvalid` and `rready` in the same cycle. Case B: from full, assert `wvalid` and `rready` in the same cycle, then drain and verify contents. Run on all four queues where practical.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empty case performs only the valid write: depth becomes 1 and the written entry is readable. Full case performs only the valid read because `wready` is low: depth becomes `Depth-1`, no overflow entry is accepted, and remaining data order is preserved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_fifo_empty_rw_edge`, `cp_fifo_full_rw_edge`, `cross_fifo_state_x_rw`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIFO_008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify software-visible blocked CMD/TX writes when queues are full.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`fifo_csr_blocked_sw_write_boundaries`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: Controller idle or disabled so hardware does not consume CMD/TX entries during the boundary check.
+Stimulus / Actions: Fill CMD and TX queues through CSR-visible writes. Attempt one extra CMD descriptor and one extra TX DWORD while each queue is full; observe pending/stalled write behavior, then drain or reset and verify queue contents.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra writes do not corrupt FIFO contents or ordering. CMD two-DWORD staging remains coherent when the CMD FIFO is full. TX pending write is either held until space is available or cleared by SW reset according to existing CSR policy; no duplicate or stale entry appears after recovery.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`csr_registers`, `hci_queues`, `sync_fifo`, reg bus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_csr_full_write_block`, `cp_cmd_staging_full`, `cp_tx_pending_full`, `cross_fifo_kind_x_csr_block`</t>
   </si>
   <si>
     <t xml:space="preserve">PHY, Bus Conditions, and Timing</t>
@@ -442,83 +502,124 @@
     <t xml:space="preserve">`phy_reset_and_sync`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: Block-level PHY or top-level observation.
-Stimulus / Actions: Toggle SCL/SDA inputs around reset.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Controller-side sampled inputs settle after synchronizer latency; reset values are high.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_phy`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_phy_sync`</t>
+    <t xml:space="preserve">Preconditions: Focused PHY stimulus at top-level observation.
+Stimulus / Actions: Run `bus_phy_reset_and_sync_vseq`: force SCL/SDA low across hard reset, then drive `00`, `10`, `01`, and `11` input patterns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">During reset, controller-side sampled inputs return to idle high; after reset, stable raw SCL/SDA inputs settle correctly through the 2FF synchronizer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_phy`, `i3c_phy_sva`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_bus001_reset_sets_sync_idle`, `cp_bus001_scl_two_cycle_settle`, `cp_bus001_sda_two_cycle_settle`, `cp_bus001_sync_pattern_00`, `cp_bus001_sync_pattern_10`, `cp_bus001_sync_pattern_01`, `cp_bus001_sync_pattern_11`</t>
   </si>
   <si>
     <t xml:space="preserve">BUS_002</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify START and STOP detection.</t>
+    <t xml:space="preserve">Verify START and STOP detection in the bus monitor.</t>
   </si>
   <si>
     <t xml:space="preserve">`bus_start_stop_detect`</t>
   </si>
   <si>
     <t xml:space="preserve">Preconditions: Bus monitor enabled.
-Stimulus / Actions: Drive SDA falling/rising while SCL high with legal timing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`start_det` and `stop_det` pulse only for legal conditions.</t>
+Stimulus / Actions: Run focused bus-monitor stimulus that drives legal START/STOP conditions with SCL high, then drives SDA transitions while SCL is not stable high.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legal START reports `state_o.start_det`; legal STOP reports `state_o.stop_det`; SDA transitions that were not qualified by stable-high SCL do not latch candidates or create START/STOP triggers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`bus_monitor`, `edge_detector`, `stable_high_detector`, `bus_monitor_sva`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_bus002_valid_start_reports_start`, `cp_bus002_valid_stop_reports_stop`, `cp_bus002_rejected_falling_edge_no_start_trigger`, `cp_bus002_rejected_rising_edge_no_stop_trigger`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUS_003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify repeated START classification in the bus monitor.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`bus_repeated_start_detect`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: Bus monitor enabled; a START has occurred without STOP.
+Stimulus / Actions: Run a focused bus-monitor stimulus that generates START, then Sr before STOP, then STOP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The first START is exposed as `start_det`; the second START before STOP is exposed as `rstart_det`; STOP clears repeated-START tracking so the next START is not misclassified.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_bus003_first_start_classified_as_start`, `cp_bus003_repeated_start_classified_as_rstart`, `cp_bus003_stop_clears_rstart_detection`, `cp_bus003_start_rstart_stop_sequence`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUS_004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify bus monitor rejects short glitches and coincident SCL/SDA transitions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`bus_monitor_glitch_and_simultaneous_edge_filter`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: Bus monitor enabled; `T_R`/`T_F` programmed to nonzero filter delays.
+Stimulus / Actions: Drive SDA glitches shorter than the configured delay while SCL is high; drive SCL and SDA transitions in the same cycle; include both falling and rising SDA cases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No false `start_det`, `stop_det`, or `rstart_det` pulse is generated; pending candidate state clears when the edge is not confirmed; valid later START/STOP detection still works.</t>
   </si>
   <si>
     <t xml:space="preserve">`bus_monitor`, `edge_detector`, `stable_high_detector`</t>
   </si>
   <si>
-    <t xml:space="preserve">`cp_bus_event`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUS_003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify repeated START detection.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`bus_repeated_start_detect`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: A START has occurred without STOP.
-Stimulus / Actions: Generate Sr before STOP.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`rstart_det` pulses; normal `start_det` is not confused with Sr.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`bus_monitor`, `scl_generator`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUS_004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify generated START/STOP timing.</t>
+    <t xml:space="preserve">`cp_bus004_short_sda_low_glitch_rejected`, `cp_bus004_short_sda_high_glitch_rejected`, `cp_bus004_simultaneous_falling_edges_no_start_candidate`, `cp_bus004_simultaneous_rising_edges_no_stop_candidate`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUS_005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify bus-event enable gating and one-cycle edge/event pulse behavior.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`bus_monitor_enable_gating_and_edge_pulses`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: Bus monitor observed at block or top-level HDL paths.
+Stimulus / Actions: With monitor disabled, drive legal START/STOP/Sr candidates; then enable monitor and drive qualified SCL/SDA edges and START/STOP/Sr events.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disabled monitor produces no event pulses and clears pending candidates; after enable, `scl.pos_edge`, `scl.neg_edge`, `sda.pos_edge`, `sda.neg_edge`, `start_det`, `stop_det`, and `rstart_det` pulse for exactly one cycle per qualified event.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_bus_enable_gating`, `cp_bus_edge_pulse_width`, `cp_bus_event_pulse_width`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUS_006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify generated START/STOP timing without a dedicated vseq.</t>
   </si>
   <si>
     <t xml:space="preserve">`scl_start_stop_timing`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: Timing CSRs programmed.
-Stimulus / Actions: Request START and STOP through normal command flow or block-level control.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDA/SCL sequence matches START/STOP definitions and programmed counter delays.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`scl_generator`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_timing`, `cp_bus_event`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUS_005</t>
+    <t xml:space="preserve">Preconditions: SVA enabled; normal SDR/CCC/I2C/DAA transactions generate START and STOP.
+Stimulus / Actions: No standalone stimulus. Existing transaction vseqs naturally exercise START/STOP while `scl_generator_sva` observes the local FSM and counter loads.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`Idle -&gt; GenerateStart -&gt; SdaFall -&gt; HoldStart -&gt; DriveLow` and `GenerateStop -&gt; SclHighForStop -&gt; SdaRise -&gt; BusFree -&gt; Idle` sequences match START/STOP definitions and programmed counter loads.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`scl_generator`, `scl_generator_sva`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_bus006_start_req_loads_setup_start`, `cp_bus006_sda_fall_loads_hold_start`, `cp_bus006_hold_start_expires_to_drivelow`, `cp_bus006_generate_stop_scl_high_loads_setup_stop`, `cp_bus006_sda_rise_drives_stop`, `cp_bus006_bus_free_expires_to_idle`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUS_007</t>
   </si>
   <si>
     <t xml:space="preserve">Verify SCL low/high periods.</t>
@@ -528,41 +629,38 @@
   </si>
   <si>
     <t xml:space="preserve">Preconditions: Timing CSRs programmed to multiple values.
-Stimulus / Actions: Run I3C SDR and I2C legacy transfers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Measured low/high periods track `t_low`, `t_high`, `t_r`, and `t_f`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`scl_generator`, `csr_registers`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_timing_mode`, `cp_timing_value`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUS_006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify clock stall behavior while waiting for commands or legal backpressure conditions.</t>
+Stimulus / Actions: Run focused `scl_generator` clock stimulus across PP-low, stretched PP-low, OD-low, and I2C-equivalent timing profiles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`scl_generator_sva` checks low-mode timing selection and counter loads: `DriveLow` loads `t_high + t_r`, then `DriveHigh` loads `active_t_low + t_f`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`scl_generator`, `csr_registers`, `scl_generator_sva`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_bus007_drivelow_clock_loads_high_delay`, `cp_bus007_drivehigh_clock_loads_pp_low_delay`, `cp_bus007_drivehigh_clock_loads_od_low_delay`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUS_008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify `scl_generator` parks SCL low in `WaitCmd` when no next command is available, then resumes normal clocking when requested.</t>
   </si>
   <si>
     <t xml:space="preserve">`scl_waitcmd_stall_resume`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: Controller is idle or in a supported wait condition.
-Stimulus / Actions: Hold the relevant wait condition, then release it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCL behavior remains legal and traffic resumes or terminates without data corruption.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `scl_generator`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_wait_state`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUS_007</t>
+    <t xml:space="preserve">Preconditions: Focused `scl_generator` stimulus with timing CSRs programmed.
+Stimulus / Actions: Generate START, withhold `gen_clock_i` so the generator enters `WaitCmd`, then assert `gen_clock_i` to resume.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`scl_generator_sva` checks `WaitCmd` holds state with SCL low and SDA released, then `gen_clock_i` resumes through `DriveLow` with the expected low/fall delay.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_bus008_waitcmd_no_cmd_stays_waitcmd`, `cp_bus008_waitcmd_clock_resume_enters_drivelow`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUS_009</t>
   </si>
   <si>
     <t xml:space="preserve">Verify repeated START while clock is held low.</t>
@@ -571,64 +669,64 @@
     <t xml:space="preserve">`scl_repeated_start_from_waitcmd`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: ENTDAA or directed CCC flow active.
+    <t xml:space="preserve">Preconditions: ENTDAA or directed CCC flow active, or focused `scl_generator` stimulus.
 Stimulus / Actions: Request repeated START while generator is in low/wait state.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sr is generated with legal timing; no bus hang.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`scl_generator`, `controller_active`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_rstart_state`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUS_008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify TX serialization.</t>
+    <t xml:space="preserve">Sr is generated with legal timing; no bus hang. `scl_generator_sva` checks `WaitCmd -&gt; GenerateRstart`, low-delay loading, SCL release before Sr, and SDA falling while SCL is high.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`scl_generator`, `controller_active`, `scl_generator_sva`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_bus009_waitcmd_to_rstart`, `cp_rstart_state_sequence`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUS_010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify TX serialization as a bus-level primitive.</t>
   </si>
   <si>
     <t xml:space="preserve">`bus_tx_byte_and_bit_order`</t>
   </si>
   <si>
     <t xml:space="preserve">Preconditions: Block-level or top-level bus observation.
-Stimulus / Actions: Send byte patterns `00`, `FF`, `A5`, `5A` and single-bit requests.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bits are MSB-first; `bus_tx_done_o` pulses once per request; SDA setup/hold is respected.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`bus_tx`, `bus_tx_flow`</t>
+Stimulus / Actions: Send byte patterns `00`, `FF`, `A5`, `96` through a focused write stimulus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bits are serialized MSB-first; byte order observed by the device model matches the TX FIFO payload; `bus_tx_done_o` pulses once per request.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`bus_tx`, `bus_tx_flow`, UVM scoreboard</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_tx_pattern`, `cp_tx_req_type`</t>
   </si>
   <si>
-    <t xml:space="preserve">BUS_009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify RX deserialization.</t>
+    <t xml:space="preserve">BUS_011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify RX deserialization as a bus-level primitive.</t>
   </si>
   <si>
     <t xml:space="preserve">`bus_rx_byte_and_bit_order`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: Block-level or device model drives SDA.
-Stimulus / Actions: Receive byte patterns and ACK/NACK bits.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data is reconstructed MSB-first; single-bit reads use bit[0]; mutual exclusion SVA passes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`bus_rx_flow`</t>
+    <t xml:space="preserve">Preconditions: Device model drives SDA.
+Stimulus / Actions: Receive byte patterns `00`, `FF`, `A5`, `96` through a focused read stimulus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data is reconstructed MSB-first into RX FIFO byte lanes; single-bit reads use bit[0]; mutual exclusion SVA passes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`bus_rx_flow`, UVM scoreboard</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_rx_pattern`, `cp_rx_req_type`</t>
   </si>
   <si>
-    <t xml:space="preserve">BUS_010</t>
+    <t xml:space="preserve">BUS_012</t>
   </si>
   <si>
     <t xml:space="preserve">Verify OD/PP select by phase.</t>
@@ -637,8 +735,8 @@
     <t xml:space="preserve">`od_pp_phase_switch`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: I3C write/read transfer.
-Stimulus / Actions: Observe `sel_od_pp_o` through address, ACK, data, T-bit, START/STOP.</t>
+    <t xml:space="preserve">Preconditions: Existing SDRW/SDRR/I2C/CCC/ENTDAA stimulus; no BUS_012-specific vseq is required.
+Stimulus / Actions: SVA observes `sel_od_pp_o` through address, ACK, data, T-bit, START/STOP, and applicable ENTDAA phases.</t>
   </si>
   <si>
     <t xml:space="preserve">OD is used for START/address/ACK/STOP and ENTDAA; PP is used only for in-scope MIPI I3C SDR data phases.</t>
@@ -650,7 +748,7 @@
     <t xml:space="preserve">`cp_odpp_phase`</t>
   </si>
   <si>
-    <t xml:space="preserve">BUS_011</t>
+    <t xml:space="preserve">BUS_013</t>
   </si>
   <si>
     <t xml:space="preserve">Verify enhanced TB pad-model wiring for SDA drive/release and OD/PP visibility.</t>
@@ -672,7 +770,7 @@
     <t xml:space="preserve">`cp_pad_model`, `cp_sda_oe`, `cp_tb_odpp_visibility`</t>
   </si>
   <si>
-    <t xml:space="preserve">BUS_012</t>
+    <t xml:space="preserve">BUS_014</t>
   </si>
   <si>
     <t xml:space="preserve">Verify that I2C legacy transfers never activate push-pull mode.</t>
@@ -685,7 +783,7 @@
 Stimulus / Actions: Issue I2C read and write commands; observe `sel_od_pp_o` and SDA drive at every phase: START, address, ACK, data bytes, final NACK, STOP.</t>
   </si>
   <si>
-    <t xml:space="preserve">`sel_od_pp_o` remains `0` (open-drain) for the entire I2C transaction — at no point does the controller assert PP. Complements BUS_010, which establishes that I3C SDR data phases do switch to PP; together they give `cp_odpp_phase × cp_device_type` cross-coverage showing OD/PP behavior is correctly conditioned on device type.</t>
+    <t xml:space="preserve">`sel_od_pp_o` remains `0` (open-drain) for the entire I2C transaction — at no point does the controller assert PP. Complements BUS_012, which establishes that I3C SDR data phases do switch to PP; together they give `cp_odpp_phase × cp_device_type` cross-coverage showing OD/PP behavior is correctly conditioned on device type.</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_odpp_phase`, `cp_device_type`, `cross_odpp_x_device_type`</t>
@@ -741,72 +839,6 @@
     <t xml:space="preserve">SDRW_003</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify data integrity over patterns.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_regular_write_data_patterns`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Device ACKs all phases.
-Stimulus / Actions: Send all-zero, all-one, walking-one, alternating, and random data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Device monitor/scoreboard observes exact expected bytes and generated T-bits.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`bus_tx_flow`, `i3c_monitor`, scoreboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_data_pattern`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDRW_004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify SDR write T-bit generation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_write_tbit_parity_generation`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: I3C device target; bus monitor can sample T-bit.
-Stimulus / Actions: Send data bytes with even and odd parity.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T-bit makes the 8-bit data byte plus T-bit odd parity, equivalent to `~^data_byte`, for every write byte.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `bus_tx_flow`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_tbit_write_parity`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDRW_005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify TX underflow flow handling.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_write_tx_fifo_underflow_ovl`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Write length exceeds available TX FIFO data or TX FIFO is empty at transfer start.
-Stimulus / Actions: Issue an 8-byte write with only one TX DWORD available; issue 4-byte and 8-byte writes with no TX data; run both `toc=1` and `toc=0` in both private-address modes. Also write a late TX DWORD after an aborted underflow.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**Data integrity boundary (primary intent):** every byte that was actually available in the TX FIFO is transmitted correctly in little-endian order; only the bytes beyond the underflow point are absent, and the controller never fabricates or transmits garbage to fill the gap. The controller does not enter the old `StallWrite` and generates STOP. For `toc=0`, underflow still terminates with STOP and must not create a Repeated START/continuation. A late-arriving TX DWORD is not consumed by the aborted transfer — it remains in the TX FIFO until SW reset flushes queues. Response descriptor encoding for the underflow is verified by `ERR_006`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `hci_queues`, `scl_generator`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_tx_empty`, `cp_tx_late_refill`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDRW_006</t>
-  </si>
-  <si>
     <t xml:space="preserve">Verify SDR regular write continuation when `toc=0`, data integrity across the RSTART boundary, and missing-continuation policy.</t>
   </si>
   <si>
@@ -817,7 +849,7 @@
 Stimulus / Actions: Queue first write (`toc=0`) and second write (`toc=1`) with distinct payloads; separately issue a `toc=0` write with no next supported command.</t>
   </si>
   <si>
-    <t xml:space="preserve">Valid case: first write completes data/T-bit then emits `Sr`; **data integrity check: for each transfer, `sampled_data[i]` matches its own TX FIFO byte slice** — confirming the RSTART boundary does not cause data loss, duplication, or cross-command mixing; second command starts after `Sr`; final STOP occurs only after the `toc=1` command; both RESPs report success with matching TID/length. With broadcast-header enabled, only the first private transfer emits the `0x7e` preamble. Negative case: the first write data is transmitted, controller emits STOP instead of RSTART, and RESP is `NotSupported` with actual length transmitted.</t>
+    <t xml:space="preserve">Valid case: first write completes data/T-bit then emits `Sr`; **data integrity check: for each transfer, `sampled_data[i]` matches its own TX FIFO byte slice** — confirming the RSTART boundary does not cause data loss, duplication, or cross-command mixing; second command starts after `Sr`; final STOP occurs only after the `toc=1` command; both RESPs report success with matching TID/length. With broadcast-header enabled, only the first private transfer emits the `0x7e` preamble. Negative case: the first write data is transmitted, controller emits STOP instead of RSTART, and RESP is `Success` with actual length transmitted.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `scl_generator`, UVM scoreboard</t>
@@ -826,7 +858,7 @@
     <t xml:space="preserve">`cp_broadcast_addr_enable`, `cp_toc`, `cp_rstart_continuation`, `cp_private_start_prefix`, `cp_unsupported_policy`</t>
   </si>
   <si>
-    <t xml:space="preserve">SDRW_007</t>
+    <t xml:space="preserve">SDRW_004</t>
   </si>
   <si>
     <t xml:space="preserve">Verify write-to-write sequencing and per-segment data integrity.</t>
@@ -848,7 +880,7 @@
     <t xml:space="preserve">`cp_sequence_type`, `cross_tid_x_order`</t>
   </si>
   <si>
-    <t xml:space="preserve">SDRW_008</t>
+    <t xml:space="preserve">SDRW_005</t>
   </si>
   <si>
     <t xml:space="preserve">Verify SDR private write DAT index selection and per-target data integrity.</t>
@@ -870,28 +902,6 @@
     <t xml:space="preserve">`cp_dat_idx`, `cross_dat_idx_x_tid`</t>
   </si>
   <si>
-    <t xml:space="preserve">SDRW_009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify HC abort during the SDR private write data phase, including data integrity of bytes sent before abort.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_write_abort`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; device ACKs address and data; a multi-byte write is in progress in the data phase (`abort_stop_required` true); run once with `HC_CONTROL[BROADCAST_ADDR_ENABLE]=0` and once with it set; run an early case (abort fires at FSM entry before data starts), a deep case (abort fires after at least one TX FIFO word is consumed), and a `toc=0` case (abort must override the continuation request).
-Stimulus / Actions: Assert `HC_CONTROL[3]` (HC abort) while the FSM is in the write data phase.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**Data integrity check (primary pass condition):** for every byte i that was driven on the bus before abort (`sampled_data[i]`), the value must equal the TX FIFO byte at position i in little-endian DWORD order — no valid pre-abort byte may be dropped or corrupted; the number of bytes sampled is at most the number sent before the abort boundary. The in-flight byte plus its T-bit boundary completes, then STOP is generated. **Error overrides continuation:** when the aborted write was programmed `toc=0`, abort still forces STOP and `HcAborted` — `observed_rstart=0` confirms a write abort ends with STOP, not a continuation RSTART. After abort, SW reset flushes any remaining TX FIFO data and leaves all queues empty. Response status/length correctness and all non-data-phase abort entry states are covered by `ERR_007`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `scl_generator`, `bus_tx_flow`, UVM scoreboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_hc_abort`, `cp_abort_stop_state`, `cp_private_start_prefix`</t>
-  </si>
-  <si>
     <t xml:space="preserve">I3C SDR Private Read</t>
   </si>
   <si>
@@ -936,28 +946,6 @@
     <t xml:space="preserve">SDRR_003</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify target early end handling: received bytes are stored correctly and no valid byte is dropped.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_read_short_target_end`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; target returns T-bit end before requested length.
-Stimulus / Actions: Run `i3c_read_short_target_end_vseq` with requested length N and actual target length M&lt;N, including a `toc=0` subcase with a second command already queued.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each mode uses the expected private-address prefix; **data integrity check (primary pass condition): RX FIFO contains exactly M bytes, and `rx_word[i/4][(i%4*8)+:8]` == `read_data[i]` for all i &lt; M** — verifying that every byte the target sent is stored correctly and no byte is silently dropped before the early-end boundary; the controller reads no fake or garbage bytes beyond M; queues are cleaned up after the response is drained. **Error overrides continuation:** when `toc=0` is programmed, the target-driven early end still forces STOP — the transfer ends in STOP and the next queued command is not chained (no *continuation* Repeated START begins the second command). Response descriptor encoding is checked by `ERR_005`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `bus_rx_flow`, RESP FIFO, UVM scoreboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_short_read`, `cp_private_start_prefix`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDRR_004</t>
-  </si>
-  <si>
     <t xml:space="preserve">Verify controller termination at requested length in both private-address modes, including the tightest over-run boundary and that normal over-length completion is not misclassified as an error.</t>
   </si>
   <si>
@@ -968,79 +956,13 @@
 Stimulus / Actions: Run `i3c_read_target_more_than_requested_vseq` with target data longer than the command length, including the `+1` boundary (target offers exactly requested+1 bytes); also run a `toc=0` over-length case with a second command queued.</t>
   </si>
   <si>
-    <t xml:space="preserve">Each mode uses the expected private-address prefix; controller takes over after the requested byte count, stores no extra RX bytes (the `+1` boundary confirms it stops at exactly N and stores no N+1 byte), and reports RESP success with the requested length. **Continuation contrast:** over-length completion sets no error flag, so a `toc=0` over-length read still continues legitimately with exactly one RSTART into the next queued command — confirming the controller does not misclassify normal over-length termination as an error that would suppress continuation.</t>
+    <t xml:space="preserve">Each mode uses the expected private-address prefix; controller takes over after the requested byte count, stores no extra RX bytes (the `+1` boundary confirms it stops at exactly N and stores no N+1 byte), and reports RESP success with the requested length. **Continuation contrast:** over-length completion sets no error flag, so a `toc=0` over-length read still continues legitimately with exactly one RSTART into the next queued command.</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_read_end_policy`, `cp_toc`, `cp_rstart_continuation`, `cp_private_start_prefix`</t>
   </si>
   <si>
-    <t xml:space="preserve">SDRR_005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify RX FIFO full overflow flow handling in both private-address modes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_read_rx_fifo_full_overflow`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; RX FIFO is prefilled full before read data flush.
-Stimulus / Actions: Run `i3c_read_rx_fifo_full_overflow_vseq`, including a `toc=0` subcase (overflow must override the continuation request).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each mode uses the expected private-address prefix; **data integrity boundary (primary intent): every RX word already committed to the FIFO (including the prefill) is preserved unchanged — overflow drops only the bytes that could not be committed, never a byte already accepted**; the controller takes over the read before forced STOP and leaves queues empty after drain. **Error overrides continuation:** when `toc=0` is programmed, overflow still forces STOP and reports `Ovl` regardless of the continuation request — the transfer ends in STOP, not a continuation into a next command; the prefill plus the one accepted word are preserved. Response descriptor encoding for the overflow is verified by `ERR_006`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `hci_queues`, `scl_generator`, UVM scoreboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_rx_full`, `cp_stall_type`, `cp_private_start_prefix`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDRR_006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify read data integrity across sensitive bit patterns in both private-address modes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_read_data_patterns`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; device sequence can drive arbitrary data.
-Stimulus / Actions: Run `i3c_read_data_patterns_vseq` with all-zero, all-one, walking-one, alternating, and fixed-random patterns.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each mode uses the expected private-address prefix; **for every pattern, `rx_word[i/4][(i%4*8)+:8]` == `read_data[i]` for every byte i** (data integrity check) — patterns like `0x00` and `0xFF` specifically stress the RX shift register for stuck-at faults; RESP success length matches pattern length.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_driver`, `bus_rx_flow`, UVM scoreboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_data_pattern`, `cp_private_start_prefix`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDRR_007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify read T-bit end semantics in both private-address modes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_read_no_parity_error_on_end_tbit`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; target ends transfer with T-bit=0 at the requested length.
-Stimulus / Actions: Run `i3c_read_no_parity_error_on_end_tbit_vseq`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each mode uses the expected private-address prefix; T-bit=0 is treated as end-of-data, no extra RX byte is consumed, and queues drain cleanly. Detailed RESP field classification for this same legal end condition is covered by `ERR_008`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `bus_rx_flow`, UVM scoreboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_read_tbit`, `cp_private_start_prefix`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDRR_008</t>
+    <t xml:space="preserve">SDRR_004</t>
   </si>
   <si>
     <t xml:space="preserve">Verify SDR regular read continuation when `toc=0`, data integrity of the read and the following write.</t>
@@ -1053,7 +975,7 @@
 Stimulus / Actions: Run `i3c_read_toc_zero_vseq`: queue first read (`toc=0`) and second write (`toc=1`) with distinct payloads.</t>
   </si>
   <si>
-    <t xml:space="preserve">Disabled mode starts the first read directly with dynamic address; enabled mode emits the broadcast-header preamble only before the first private read. In both modes, **data integrity checks: RX bytes from the read match the device-driven stimulus byte-by-byte; write bytes observed on bus match the TX FIFO bytes byte-by-byte** — the RSTART boundary does not cause loss or corruption in either direction; the first read ends with `Sr`, the continuation does not repeat the preamble, final STOP occurs only after the second command, and both RESPs match expected length/TID.</t>
+    <t xml:space="preserve">Disabled mode starts the first read directly with dynamic address; enabled mode emits the broadcast-header preamble only before the first private read. RX and TX data remain intact; the first read ends with `Sr`, the continuation does not repeat the preamble, final STOP occurs only after the second command, and both RESPs match expected length/TID.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `scl_generator`, `bus_rx_flow`, UVM scoreboard</t>
@@ -1062,23 +984,29 @@
     <t xml:space="preserve">`cp_broadcast_addr_enable`, `cp_toc`, `cp_rstart_continuation`, `cp_dir_read_to_write`, `cp_private_start_prefix`</t>
   </si>
   <si>
-    <t xml:space="preserve">SDRR_009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify HC abort during the SDR private read data phase, including data integrity of bytes committed before abort.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_read_abort`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; target returns read data; a multi-byte read is in progress in the data phase (`abort_stop_required` true); run once with `HC_CONTROL[BROADCAST_ADDR_ENABLE]=0` and once with it set; run an early case (abort fires at FSM entry, before data starts), a deep case (abort fires after at least one RX FIFO word is committed), and a `toc=0` case (abort must override the continuation request).
-Stimulus / Actions: Assert `HC_CONTROL[3]` (HC abort) while the FSM is in the read data phase.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**Data integrity check (primary pass condition for the deep case):** after the FSM reaches idle, read the committed bytes from RX FIFO (length given by `resp[15:0]`) *before* issuing SW reset, and verify `rx_word[i/4][(i%4*8)+:8]` == `read_data[i]` for every committed byte i — confirming no valid pre-abort byte is silently dropped or corrupted. No fake bytes may appear beyond the committed boundary. **Error overrides continuation:** when the aborted read was programmed `toc=0`, abort still forces STOP and `HcAborted` — the controller's takeover Repeated START (SDA retake per MIPI §5.1.2.3.4) is followed by STOP, never a continuation into a next command. After verifying, SW reset flushes any remaining residual bytes, leaving all queues empty. Response status/length correctness and all non-data-phase abort entry states are covered by `ERR_007`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDRR_010</t>
+    <t xml:space="preserve">SDRR_005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify queued SDR private read commands execute back-to-back without RX FIFO data mixing or command/response reordering.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_read_back_to_back`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: DAT[0] is one I3C dynamic address; three read commands target the same DAT entry; target returns distinct payloads for each command; run in both private-address modes.
+Stimulus / Actions: Run `i3c_read_back_to_back_vseq`: queue three read commands with lengths 3, 5, and 4 bytes and distinct TIDs before enabling the controller.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commands complete in FIFO order; each transfer ends with STOP because all commands use `toc=1`; no repeated START is observed between independent reads; RX FIFO data drains in the same command boundaries as queued (`3/5/4` byte payloads) with no byte crossing between transfers; RESP TID/length metadata matches each queued command; queues empty afterward.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `hci_queues`, `bus_rx_flow`, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_cmd_queue_order`, `cp_rx_fifo_order`, `cp_private_start_prefix`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDRR_006</t>
   </si>
   <si>
     <t xml:space="preserve">Verify SDR private read selects the programmed DAT index, per-target data integrity, and preservation across a `toc=0` continuation.</t>
@@ -1091,7 +1019,7 @@
 Stimulus / Actions: Run `i3c_read_multi_dat_idx_vseq`: first issue two independent reads to DAT[0] and DAT[1] (`toc=1` each), then a `toc=0` read on DAT[0] continued into a `toc=1` read on DAT[1].</t>
   </si>
   <si>
-    <t xml:space="preserve">Each read drives the dynamic address programmed in its selected DAT entry; **data integrity check: for each target, `rx_word[i/4][(i%4*8)+:8]` == `read_data[i]` for every byte i** — RX data from each target is stored in the correct FIFO order without cross-target mixing or silent drops; the `toc=0` case emits exactly one repeated START between the two reads while still switching the DAT-selected address; all queues drain empty.</t>
+    <t xml:space="preserve">Each read drives the dynamic address programmed in its selected DAT entry; RX data remains ordered without cross-target mixing; the `toc=0` case emits exactly one repeated START while switching the DAT-selected address; all queues drain empty.</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_dev_idx`, `cp_toc`, `cp_rstart_continuation`, `cp_private_start_prefix`</t>
@@ -1110,7 +1038,7 @@
   </si>
   <si>
     <t xml:space="preserve">Preconditions: DAT[0] I3C device; target ACKs.
-Stimulus / Actions: Run `i3c_imm_vseq` with `HC_CONTROL[2]` (`broadcast_header_enable`) = 0 and = 1; `dtt=2`, `def_or_data_byte1=0xAA`, `data_byte2=0xBB`.</t>
+Stimulus / Actions: Run `i3c_imm_vseq` with `HC_CONTROL[0]` (`broadcast_header_enable`/IBA_INCLUDE) = 0 and = 1; `dtt=2`, `def_or_data_byte1=0xAA`, `data_byte2=0xBB`.</t>
   </si>
   <si>
     <t xml:space="preserve">With `broadcast_header_enable=0` the bus shows `[S] addr+W [ACK] data...`; with `=1` it shows `[S] 7E+W [ACK] [Sr] addr+W [ACK] data...`. **Data integrity check (primary pass condition): `sampled_data[0]`==`0xAA` and `sampled_data[1]`==`0xBB`** — the inline bytes from the command descriptor are transmitted on the bus in descriptor order with no corruption, drop, or reordering; RESP success with length 2 in both modes.</t>
@@ -1160,6 +1088,9 @@
     <t xml:space="preserve">`toc=1`: STOP is generated after inline data; **data integrity check: `sampled_data[0]`==`0xAA`, `sampled_data[1]`==`0xBB`**; RESP is `Success` with correct length 2. `toc=0`: all dtt bytes are still transmitted before STOP — **data integrity check: same byte-level check applies**; STOP is generated, `not_supported_d` is set, RESP error is `NotSupported` (4'hA); no `Sr` or continuation occurs. Both toc values must complete all dtt bytes on bus with correct values before STOP. Bus must not hang.</t>
   </si>
   <si>
+    <t xml:space="preserve">`flow_active`, `scl_generator`</t>
+  </si>
+  <si>
     <t xml:space="preserve">`cp_toc`, `cp_imm`, `cp_resp_err`</t>
   </si>
   <si>
@@ -1179,48 +1110,10 @@
     <t xml:space="preserve">OD-only static address+W, data ACKs; **data integrity check: for each dtt, `sampled_data[i]` == cmd byte i for i &lt; dtt** — the static-address I2C path transmits the same cmd dword bytes as the I3C path, in descriptor order, with no loss; RESP length equals bytes transferred.</t>
   </si>
   <si>
+    <t xml:space="preserve">`flow_active`, `bus_tx_flow`</t>
+  </si>
+  <si>
     <t xml:space="preserve">`cp_i2c`, `cp_imm`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMM_005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify I2C immediate data NACK handling.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`immediate_data_nack_i2c`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: I2C target ACKs address and NACKs one data byte.
-Stimulus / Actions: Issue multi-byte I2C immediate write.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**Data integrity boundary (primary intent):** the inline bytes sent before the NACK match the cmd descriptor bytes; after the data NACK the controller generates STOP and transmits no later inline byte — only the bytes beyond the NACKed position are dropped, per I2C policy. RESP error encoding for the data NACK is verified by `ERR_004`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_data_ack`, `cp_resp_err`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMM_006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify HC abort during immediate data transmission phase, including data integrity of bytes sent before abort.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_imm_abort_vseq`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: DAT[0] I3C dynamic address `0x08`; DAT[0] I2C static address `0x52`; target ACKs address and data.
-Stimulus / Actions: Assert `HC_CONTROL[3]` (HC abort) while FSM is in `I3CWriteImmediate` (4'd5) for I3C device; repeat for `I2CWriteImmediate` (4'd6) with I2C device; cover both `broadcast_header_enable` modes for I3C. Use `dtt=4` (max inline bytes) to widen the abort window.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**Data integrity check (primary pass condition): for every byte i that was sent before abort (`sampled_data[i]`), the value must equal the cmd descriptor byte i** — no valid pre-abort inline byte may be dropped or corrupted; the in-flight byte boundary completes before STOP. FSM issues STOP and advances to `WriteResp`; no TX or RX FIFO residual (inline data only, no FIFO involved); recovery SW reset leaves all queues empty. RESP status/length encoding for the abort is verified by `ERR_007`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_hc_abort`, `cp_abort_stop_state`, `cp_imm`, `cross_imm_x_device_type`</t>
   </si>
   <si>
     <t xml:space="preserve">Common Command Codes</t>
@@ -1286,6 +1179,9 @@
     <t xml:space="preserve">Bus frame follows the MIPI broadcast DISEC format: START, `7'h7E+W`, broadcast-header ACK, DISEC opcode `8'h01` with T-bit, Target Events byte with T-bit, then STOP; ENTDAA controller is not activated.</t>
   </si>
   <si>
+    <t xml:space="preserve">`flow_active`</t>
+  </si>
+  <si>
     <t xml:space="preserve">`cp_ccc_opcode`, `cp_ccc_broadcast`</t>
   </si>
   <si>
@@ -1333,23 +1229,23 @@
     <t xml:space="preserve">DAA_001</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify one successful ENTDAA round.</t>
+    <t xml:space="preserve">Verify one successful ENTDAA round, including target identity capture and RX FIFO result packing.</t>
   </si>
   <si>
     <t xml:space="preserve">`entdaa_single_device_success`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: DAT[0] contains dynamic address; target can drive PID/BCR/DCR and ACK address.
-Stimulus / Actions: Issue AddressAssignment with `dev_idx=0`, `dev_count=1`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENTDAA frame completes per MIPI sequence; assigned address byte uses correct parity; target ACKs the assignment; RESP success; any software-visible DAA result follows the documented project format.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `entdaa_controller`, `entdaa_fsm`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_daa_count`, `cp_daa_result`</t>
+    <t xml:space="preserve">Preconditions: DAT[0] contains a dynamic address; target drives known PID/BCR/DCR values and ACKs the assigned address.
+Stimulus / Actions: Issue AddressAssignment with `dev_idx=0`, `dev_count=1`; compare the captured identity and RX FIFO result against the PID/BCR/DCR driven by the target.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENTDAA frame completes per MIPI sequence; captured PID/BCR/DCR preserve the transmitted byte order; assigned address and odd-parity bit are correct; target ACKs the assignment; RESP reports `Success` with length 12; RX FIFO contains `PID[47:16]`, `{PID[15:0],BCR,DCR}`, and `{25'h0,DA[6:0]}`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `entdaa_controller`, `entdaa_fsm`, `entdaa_fsm_sva`, RX FIFO, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_daa_count`, `cp_daa_result`, `cp_daa_pid`, `cp_daa_bcr`, `cp_daa_dcr`</t>
   </si>
   <si>
     <t xml:space="preserve">DAA_002</t>
@@ -1465,89 +1361,23 @@
     <t xml:space="preserve">DAA_007</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify identity capture and project-defined RX FIFO result packing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`entdaa_pid_bcr_dcr_capture`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Target drives known PID/BCR/DCR values.
-Stimulus / Actions: Run successful ENTDAA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Captured PID/BCR/DCR match the bits driven by the target in the MIPI ENTDAA order; software-visible RX data uses the documented three-DWORD format: `PID[47:16]`, `{PID[15:0],BCR,DCR}`, `{25'h0,DA[6:0]}`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`entdaa_fsm`, `flow_active`, RX FIFO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_daa_pid`, `cp_daa_bcr`, `cp_daa_dcr`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DAA_008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify DAT boundary behavior.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`entdaa_dat_boundary`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Program `dev_idx` near last DAT entry.
-Stimulus / Actions: Run `dev_idx=15`, `dev_count=1`, then `dev_idx=15`, `dev_count&gt;1`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single entry works; out-of-range `dev_idx+dev_count` is a clarification/negative case that must either produce a specified error or be forbidden by a documented software precondition.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_dat_boundary`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DAA_009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify STOP/abort handling during DAA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`entdaa_stop_mid_round`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: External/device model can force STOP-like bus condition or reset.
-Stimulus / Actions: Interrupt during PID/BCR/DCR reception.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ENTDAA exits through a specified abort/recovery policy and controller returns to a legal idle/recoverable state; if no policy exists, this is a spec gap and not positive sign-off coverage.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`entdaa_fsm`, `entdaa_controller`, `bus_monitor`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_daa_abort_point`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DAA_010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify wired-AND arbitration across multiple targets.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`entdaa_two_target_arbitration`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: UVM bus model supports simultaneous target driving.
-Stimulus / Actions: Two unaddressed targets drive different PID bits; losing target stops participating.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Master assigns arbitration winner first, then remaining target in later round.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Future</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVM I3C agent, bus, `entdaa_fsm`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_daa_arbitration`</t>
+    <t xml:space="preserve">Verify DAT boundary behavior and pre-bus rejection of an out-of-range assignment span.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_daa_dat_boundary_vseq`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: DAT[31] contains a valid dynamic address.
+Stimulus / Actions: Run `dev_idx=31`, `dev_count=1`, then `dev_idx=31`, `dev_count=2`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The single-entry case completes successfully using DAT[31]. The out-of-range case is rejected before DAT access or bus activity with RESP `NotSupported`, matching TID, reserved bits zero, and length 0; DAT index must not wrap to 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `entdaa_controller`, `csr_registers`, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_dat_boundary`, `cp_no_bus_activity`, `cp_resp_err`</t>
   </si>
   <si>
     <t xml:space="preserve">I2C Legacy Compatibility</t>
@@ -1600,28 +1430,6 @@
     <t xml:space="preserve">I2C_003</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify legacy I2C transfers ignore private-transfer broadcast-header control.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i2c_broadcast_addr_enable_ignored`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: `HC_CONTROL[BROADCAST_ADDR_ENABLE]=1`; DAT[0].`device=1` with static address programmed; target ACKs.
-Stimulus / Actions: Run representative I2C read and write commands.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First address remains the DAT static address for both directions; no `0x7e` preamble is emitted; OD-only behavior and I2C ACK/NACK sequencing are unchanged.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `scl_generator`, `bus_tx_flow`, `bus_rx_flow`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_broadcast_addr_enable`, `cp_first_address`, `cp_i2c_dir`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I2C_004</t>
-  </si>
-  <si>
     <t xml:space="preserve">Verify I2C read/write length behavior.</t>
   </si>
   <si>
@@ -1641,45 +1449,7 @@
     <t xml:space="preserve">`cp_data_len`, `cp_rx_partial_dword`</t>
   </si>
   <si>
-    <t xml:space="preserve">I2C_005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify I2C data-byte NACK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i2c_data_nack_write`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Target ACKs address and NACKs byte M.
-Stimulus / Actions: Issue multi-byte write.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**Data integrity boundary (primary intent):** bytes sent before the NACK match the TX FIFO bytes; the transfer stops after the NACKed byte and transmits no later byte — only the bytes beyond the NACKed position are dropped, per I2C policy; next legal transfer passes. RESP error encoding for the data NACK is verified by `ERR_004`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I2C_006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify HC abort during I2C RegularTransfer write and read, including data integrity of bytes sent/committed before abort.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i2c_regular_abort`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: DAT[0].`device=1`; static address programmed; target ACKs address and data; multi-byte transfer in progress in the data phase.
-Stimulus / Actions: Assert `HC_CONTROL[3]` (HC abort) while FSM is in `I2CWrite` state (write path) and `I2CRead` state (read path); cover an early case (abort fires before any FIFO word consumed), a deep case (abort fires after at least one TX/RX FIFO word processed), and a `toc=0` case (abort must override continuation).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**Data integrity check (primary pass condition):** for write: every byte i driven on the bus before the abort boundary equals the TX FIFO byte at position i in little-endian DWORD order — no valid pre-abort TX byte may be dropped or corrupted. For read: committed RX FIFO bytes must be read before SW reset and each matches the device-driven byte at that position; the controller does not stop mid-byte, ACKs all committed bytes before the abort-final byte, drives NACK on the abort-final ACK/NACK bit, then generates STOP. OD-only mode is maintained throughout (no PP switching); no T-bit on I2C data bytes. **Error overrides continuation:** when the aborted transfer was programmed `toc=0`, abort still forces STOP, never a Repeated START/continuation, and returns `HcAborted`. After abort, SW reset flushes residual TX/RX FIFO data and leaves all queues empty. RESP status/length encoding for the abort is verified by `ERR_007`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `scl_generator`, `bus_tx_flow`, `bus_rx_flow`, UVM scoreboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_hc_abort`, `cp_abort_stop_state`, `cp_i2c_dir`, `cp_i2c_ack_seq`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I2C_007</t>
+    <t xml:space="preserve">I2C_004</t>
   </si>
   <si>
     <t xml:space="preserve">Verify default I2C FM-equivalent timing selection without a dedicated vseq.</t>
@@ -1726,17 +1496,17 @@
     <t xml:space="preserve">ERR_002</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify `AddrHeader` response encoding for every command class that has an address phase.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`resp_addr_nack_all_classes`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Device NACKs address in an I3C, I2C, immediate, or direct CCC transfer.
-Stimulus / Actions: Run `i3c_addr_header_nack_resp_vseq` for I3C write/read and I2C write/read address NACK. Also cover I3C and I2C immediate writes: controller generates STOP immediately after address NACK, no inline data byte is transmitted. Also cover direct CCC address NACK (previously CCC_006): target ACKs broadcast header and CCC opcode/T-bit but NACKs the direct address after Sr; verify no data byte is sent after the NACK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESP status is `AddrHeader`, TID matches the command, reserved bits are zero, and length is 0 for every supported command class with address NACK.</t>
+    <t xml:space="preserve">Verify `AddrHeader` response encoding for private/target address NACK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`resp_private_addr_nack`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: Device NACKs the private or target address in an I3C, I2C, immediate, or direct CCC transfer.
+Stimulus / Actions: Run `i3c_private_addr_nack_resp_vseq` for I3C write/read, I2C write/read, I3C/I2C immediate write, and direct CCC target-address NACK. In direct CCC, target ACKs broadcast header and CCC opcode/T-bit but NACKs the direct address after Sr; verify no target data byte is sent after the NACK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESP status is `AddrHeader`, TID matches the command, reserved bits are zero, and length is 0 for every supported command class with private/target address NACK. No regular data, read data, immediate inline data, or direct CCC target data is transferred after the NACK.</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_resp_err`, `cp_addr_ack`, `cp_tid`, `cp_resp_len`, `cross_imm_x_device_type`</t>
@@ -1745,17 +1515,17 @@
     <t xml:space="preserve">ERR_003</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify `AddrHeader` response encoding and CCC payload suppression when the broadcast header is NACKed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`resp_ccc_broadcast_header_nack`</t>
+    <t xml:space="preserve">Verify `AddrHeader` response encoding and payload suppression when broadcast header `7'h7E+W` is NACKed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`resp_broadcast_header_nack`</t>
   </si>
   <si>
     <t xml:space="preserve">Preconditions: Device NACKs `7'h7E+W` during a CCC command (ENEC/DISEC/ENTDAA).
-Stimulus / Actions: Issue ENEC/DISEC/ENTDAA command; device NACKs the broadcast header.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESP status is `AddrHeader`, TID matches the command, reserved bits are zero, and length is 0; no CCC opcode or payload byte is emitted after the NACK; bus recovery is legal.</t>
+Stimulus / Actions: Run `i3c_broadcast_header_nack_resp_vseq`: issue ENEC, DISEC, and ENTDAA commands while the device NACKs the broadcast header.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESP status is `AddrHeader`, TID matches the command, reserved bits are zero, and length is 0. No CCC opcode, CCC payload byte, or ENTDAA `7'h7E+R` round is emitted after the NACK; bus recovery is legal.</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_resp_err`, `cp_addr_ack`, `cp_tid`, `cp_resp_len`, `cp_ccc_nack`</t>
@@ -1764,102 +1534,89 @@
     <t xml:space="preserve">ERR_004</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify data NACK error for I2C write-style phases.</t>
+    <t xml:space="preserve">Verify data NACK error, transmitted-data boundary, response encoding, and recovery for regular and immediate I2C writes.</t>
   </si>
   <si>
     <t xml:space="preserve">`resp_data_nack_error`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: Target NACKs data byte.
-Stimulus / Actions: Run I2C write/immediate write with data NACK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESP error is `Nack`; transfer recovers.</t>
+    <t xml:space="preserve">Preconditions: Target ACKs the address and NACKs a data byte.
+Stimulus / Actions: Run `i2c_data_nack_write_vseq` with a multi-DWORD payload and `i3c_imm_data_nack_i2c_vseq` with `dtt=2..4`. Follow each error path with a successful transfer using the recovery policy appropriate to its data source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The NACKed byte is fully clocked, but no later regular or inline byte is transmitted. Pre-NACK data matches the programmed TX FIFO or descriptor bytes. RESP is `Nack` with matching TID, zero reserved bits, and actual length through the NACKed byte. Regular write can preserve unfetched TX FIFO words, so recovery waits for idle and uses SW reset before the next FIFO-backed write. Immediate data is descriptor-resident, so its next transfer succeeds without SW reset.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `hci_queues`, `bus_tx_flow`, RESP FIFO, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_data_ack`, `cp_resp_err`, `cp_tid`, `cp_resp_len`, `cross_imm_x_device_type`</t>
   </si>
   <si>
     <t xml:space="preserve">ERR_005</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify short read response encoding.</t>
+    <t xml:space="preserve">Verify short-read termination, committed data integrity, response encoding, continuation suppression, and recovery.</t>
   </si>
   <si>
     <t xml:space="preserve">`resp_short_read_error`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: Target ends I3C read early.
-Stimulus / Actions: Run `i3c_short_read_resp_vseq`: request N bytes, target ends after M&lt;N.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESP status is `I3cShortReadErr`, TID matches the command, reserved bits are zero, and length reflects actual received bytes M.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_short_read`, `cp_resp_err`, `cp_tid`, `cp_resp_len`</t>
+    <t xml:space="preserve">Preconditions: Target ends an I3C read after M bytes where M&lt;N requested bytes.
+Stimulus / Actions: Run `i3c_read_short_target_end_vseq` across multiple partial-DWORD boundaries and both private-address modes, including a `toc=0` command with a following command queued.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RX FIFO contains exactly the M valid bytes with correct packing; no fabricated byte is stored. Short read forces STOP and suppresses a requested continuation. RESP is `I3cShortReadErr` with matching TID, zero reserved bits, and actual length M. Draining RX and RESP data leaves queues ready for the next command; SW reset is not required.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `bus_rx_flow`, RESP FIFO, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_short_read`, `cp_resp_err`, `cp_tid`, `cp_resp_len`, `cp_private_start_prefix`</t>
   </si>
   <si>
     <t xml:space="preserve">ERR_006</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify overflow response encoding.</t>
+    <t xml:space="preserve">Verify response classification and end-of-data handling for a legal SDR read final T-bit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_read_tbit_no_parity_resp`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; target ends transfer with T-bit=0 at the requested length.
+Stimulus / Actions: Run `i3c_read_tbit_no_parity_resp_vseq` in both private-address modes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each mode uses the expected private-address prefix. Final T-bit=0 at the requested length is treated as legal end-of-data, no extra RX byte is consumed, queues drain cleanly, and the condition is not classified as `Parity`. RESP is `Success`, TID matches the command, reserved bits are zero, and length matches the requested length.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_read_tbit`, `cp_private_start_prefix`, `cp_resp_err`, `cp_tid`, `cp_resp_len`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERR_007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify TX underflow/RX overflow termination, data boundary, response encoding, and recovery policy, including ENTDAA result storage overflow.</t>
   </si>
   <si>
     <t xml:space="preserve">`resp_ovl_error`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: TX FIFO underflow or RX FIFO full overflow condition.
-Stimulus / Actions: Run `i3c_ovl_resp_vseq` for TX underflow with partial/empty TX FIFO and RX FIFO full during read.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESP status is `Ovl`, TID matches the command, reserved bits are zero, and length equals the number of bytes actually processed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_resp_err_ovl`, `cp_tid`, `cp_resp_len`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERR_007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify HC abort response encoding, status priority, and non-data-phase abort entry states.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`resp_hc_abort_error`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Controller can be aborted from selectable FSM states via `HC_CONTROL[3]`; bus-error injection available; `HC_CONTROL[3]` is a level bit that is never auto-cleared by hardware.
-Stimulus / Actions: Assert HC abort (a) during a data-phase transfer that terminates via STOP, (b) in a pre-bus state (`FetchDAT`, or `WaitDAT` with no pending continuation), (c) while idle (`Idle`/`WaitForCmd`), (d) after a bus error has already latched, (e) leave the bit asserted across a following queued command, and (f) during the CCC execution state (after broadcast header ACK, while FSM is sending the CCC opcode or data byte).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(a) RESP status is `HcAborted`, TID matches the command, reserved bits zero, and length equals the bytes processed before abort — this encoding is the single owner for abort RESP fields across regular SDR write/read (`SDRW_009`, `SDRR_009`), immediate-data (`IMM_006`), I2C RegularTransfer (`I2C_006`), and CCC-phase abort (subcase (f)). (b) No STOP and no bus activity occur; the FSM advances directly to `WriteResp` with `HcAborted`. (c) Abort is a no-op; the active/next command proceeds normally. (d) The previously latched bus error wins over `HcAborted` per the response-status priority. (e) Because the bit is not auto-cleared, the next command is also aborted until software clears `HC_CONTROL[3]`. (f) Bus terminates with STOP; `HcAborted` is returned; no CCC opcode or data byte beyond the abort point is emitted; bus cleanup is legal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `csr_registers`, RESP FIFO, UVM scoreboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_hc_abort`, `cp_resp_err`, `cp_abort_entry_state`, `cp_resp_err_priority`</t>
+    <t xml:space="preserve">Preconditions: TX FIFO underflow, regular-read RX FIFO overflow, or ENTDAA result RX FIFO overflow condition.
+Stimulus / Actions: Run `i3c_ovl_resp_vseq`, `i3c_write_tx_fifo_underflow_vseq`, `i3c_read_rx_fifo_full_overflow_vseq`, and `i3c_entdaa_rx_fifo_partial_overflow_vseq`, including full/partial RX prefill, `toc=0/1`, both private-address modes, late TX refill, and ENTDAA result storage with only 0, 1, or 2 free RX FIFO entries for the 3-DWORD DAA result.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Committed TX/RX/DAA-result data remains correct and no garbage is emitted or stored. Overflow/underflow forces STOP and suppresses continuation. RESP is `Ovl` with matching TID, zero reserved bits, and the processed/committed boundary length. Regular-read RX overflow recovery drains preserved RX FIFO contents and RESP; no SW reset is required. ENTDAA result overflow drains the prefilled RX words plus any committed DAA result DWORDs and RESP; no SW reset is required. Residual/late TX data requires waiting for idle and issuing SW reset before a clean FIFO-backed recovery transfer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `hci_queues`, `scl_generator`, `entdaa_controller`, RX FIFO, RESP FIFO, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_resp_err_ovl`, `cp_daa_result`, `cp_tid`, `cp_resp_len`, `cp_tx_empty`, `cp_tx_late_refill`, `cp_rx_full`, `cp_stall_type`</t>
   </si>
   <si>
     <t xml:space="preserve">ERR_008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify response classification for a legal SDR read final T-bit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_read_tbit_no_parity_resp`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; target ends transfer with T-bit=0 at the requested length.
-Stimulus / Actions: Run `i3c_read_tbit_no_parity_resp_vseq`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final T-bit=0 at the requested length is not classified as `Parity`; RESP is `Success`, TID matches the command, reserved bits are zero, and length matches the requested length.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, RESP FIFO, UVM scoreboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_read_tbit`, `cp_resp_err`, `cp_tid`, `cp_resp_len`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERR_009</t>
   </si>
   <si>
     <t xml:space="preserve">Verify response write stalls safely.</t>
@@ -1878,6 +1635,28 @@
     <t xml:space="preserve">`cp_resp_full`, `cp_stall_type`</t>
   </si>
   <si>
+    <t xml:space="preserve">ERR_009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify HC abort termination for I3C SDR, I2C regular, immediate, and ENTDAA transfers, including data integrity, response encoding, termination, and recovery policy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`resp_hc_abort_error`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: Controller can be aborted from selectable FSM states via persistent level bit `HC_CONTROL[29]` (ABORT).
+Stimulus / Actions: Run `i3c_write_abort_vseq`, `i3c_read_abort_vseq`, and `i2c_regular_abort_vseq` for early/deep/`toc=0` write and read transfers. Run `i3c_imm_abort_vseq` in I3C immediate mode with and without the broadcast-header preamble and in I2C immediate mode. Run `i3c_daa_hc_abort_vseq` during ENTDAA identity receive, assigned-address phase, and after one completed ENTDAA round. Also cover pre-bus, idle, priority, persistent-level, and CCC execution cases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abort completes the defined byte boundary, forces STOP, suppresses continuation, preserves transmitted or committed data, and returns `HcAborted` with matching TID, zero reserved bits, and actual length. I3C/I2C regular writes can retain unfetched TX FIFO data and require clear-abort, idle, then SW reset for clean FIFO-backed recovery. I3C/I2C reads drain and verify committed RX data plus RESP; a following read succeeds without SW reset, which is needed only to discard residual state. Immediate data is descriptor-resident and similarly recovers without SW reset after clearing abort and draining RESP. ENTDAA abort drains any committed DAA result plus RESP, clears abort, and runs a following ENTDAA successfully without SW reset. I2C remains OD-only and uses controller NACK then STOP for read abort.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `csr_registers`, `hci_queues`, `scl_generator`, `bus_tx_flow`, `bus_rx_flow`, `entdaa_controller`, `entdaa_fsm`, RX FIFO, RESP FIFO, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_hc_abort`, `cp_resp_err`, `cp_abort_entry_state`, `cp_resp_err_priority`, `cp_abort_stop_state`, `cp_private_start_prefix`, `cp_i2c_dir`, `cp_i2c_ack_seq`, `cp_daa_abort_point`, `cross_imm_x_device_type`</t>
+  </si>
+  <si>
     <t xml:space="preserve">ERR_010</t>
   </si>
   <si>
@@ -1903,6 +1682,28 @@
     <t xml:space="preserve">ERR_011</t>
   </si>
   <si>
+    <t xml:space="preserve">Verify pre-bus rejection and response encoding for invalid `AddressAssignment`/ENTDAA descriptors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`entdaa_invalid_descriptor_resp`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: CMD descriptors can be written directly; DAT entry exists but should not be used because the command is rejected before ENTDAA starts.
+Stimulus / Actions: Run `i3c_entdaa_invalid_descriptor_resp_vseq` with three subcases: `toc=0,wroc=1,dev_count=1`; `toc=1,wroc=0,dev_count=1`; and `toc=1,wroc=1,dev_count=0`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No START, no `7'h7E+W` broadcast header, no ENTDAA opcode, and no DAA round are emitted. Exactly one RESP is written with status `NotSupported`, matching TID, reserved bits zero, and length 0. Queues drain cleanly and a following legal command can run.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active`, `i3c_pkg`, RESP FIFO, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_addr_assign_desc`, `cp_resp_err`, `cp_tid`, `cp_resp_len`, `cp_no_bus_activity`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERR_012</t>
+  </si>
+  <si>
     <t xml:space="preserve">Document the `wroc` (response-on-completion) design gap.</t>
   </si>
   <si>
@@ -1922,7 +1723,7 @@
     <t xml:space="preserve">`cp_wroc`</t>
   </si>
   <si>
-    <t xml:space="preserve">ERR_012</t>
+    <t xml:space="preserve">ERR_013</t>
   </si>
   <si>
     <t xml:space="preserve">Verify reset in idle.</t>
@@ -1944,7 +1745,7 @@
     <t xml:space="preserve">`cp_reset_point`</t>
   </si>
   <si>
-    <t xml:space="preserve">ERR_013</t>
+    <t xml:space="preserve">ERR_014</t>
   </si>
   <si>
     <t xml:space="preserve">Verify reset during active operation.</t>
@@ -1963,7 +1764,7 @@
     <t xml:space="preserve">`cp_reset_point`, `cross_reset_x_phase`</t>
   </si>
   <si>
-    <t xml:space="preserve">ERR_014</t>
+    <t xml:space="preserve">ERR_015</t>
   </si>
   <si>
     <t xml:space="preserve">Clarify SW reset during active transfer.</t>
@@ -1973,7 +1774,7 @@
   </si>
   <si>
     <t xml:space="preserve">Preconditions: Transfer in progress.
-Stimulus / Actions: Assert `HC_CONTROL[1]` while not idle.</t>
+Stimulus / Actions: Assert `RESET_CONTROL[0]` (SOFT_RST) while not idle.</t>
   </si>
   <si>
     <t xml:space="preserve">If the spec leaves this undefined, the test records a spec gap and recommends SW only reset when `FSM_IDLE=1`; it is not positive sign-off coverage until a busy-reset policy is specified.</t>
@@ -1985,7 +1786,7 @@
     <t xml:space="preserve">`cp_sw_reset_busy`</t>
   </si>
   <si>
-    <t xml:space="preserve">ERR_015</t>
+    <t xml:space="preserve">ERR_016</t>
   </si>
   <si>
     <t xml:space="preserve">Identify bus recovery gap.</t>
@@ -2007,50 +1808,6 @@
     <t xml:space="preserve">`cp_bus_stuck`</t>
   </si>
   <si>
-    <t xml:space="preserve">ERR_016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify pre-bus rejection and response encoding for invalid `AddressAssignment`/ENTDAA descriptors.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`entdaa_invalid_descriptor_resp`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: CMD descriptors can be written directly; DAT entry exists but should not be used because the command is rejected before ENTDAA starts.
-Stimulus / Actions: Run `i3c_entdaa_invalid_descriptor_resp_vseq` with three subcases: `toc=0,wroc=1,dev_count=1`; `toc=1,wroc=0,dev_count=1`; and `toc=1,wroc=1,dev_count=0`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No START, no `7'h7E+W` broadcast header, no ENTDAA opcode, and no DAA round are emitted. Exactly one RESP is written with status `NotSupported`, matching TID, reserved bits zero, and length 0. Queues drain cleanly and a following legal command can run.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `i3c_pkg`, RESP FIFO, UVM scoreboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_addr_assign_desc`, `cp_resp_err`, `cp_tid`, `cp_resp_len`, `cp_no_bus_activity`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERR_017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify ENTDAA result storage overflow response encoding for every DAA result boundary.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`entdaa_rx_fifo_partial_overflow`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: DAT[0] supplies an assigned dynamic address; one target joins ENTDAA and ACKs the assigned address; RX FIFO is prefilled so only 0, 1, or 2 DWORD slots remain for the 3-DWORD DAA result.
-Stimulus / Actions: Run `i3c_entdaa_rx_fifo_partial_overflow_vseq`: issue a valid `AddressAssignment` descriptor with `toc=1,wroc=1,dev_count=1`, have the target return PID/BCR/DCR, then attempt to store the DAA result with 0, 1, and 2 free RX FIFO entries.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Controller must not silently drop a DAA result while returning `Success`. RESP status is `Ovl`, TID matches the command, reserved bits are zero, and length equals the number of DAA result bytes actually committed to RX FIFO: 0, 4, or 8 bytes for the three subcases. Prefilled RX FIFO entries remain unchanged, and committed DAA result DWORDs match the documented format before the first dropped result word.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `entdaa_controller`, RX FIFO, RESP FIFO, UVM scoreboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_resp_err_ovl`, `cp_daa_result`, `cp_tid`, `cp_resp_len`</t>
-  </si>
-  <si>
     <t xml:space="preserve">Arbitration and Bus Behavior</t>
   </si>
   <si>
@@ -2079,20 +1836,26 @@
     <t xml:space="preserve">ARB_002</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify true multi-target DAA arbitration.</t>
+    <t xml:space="preserve">Verify true multi-target ENTDAA arbitration.</t>
   </si>
   <si>
     <t xml:space="preserve">`entdaa_multi_target_arbitration_future`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: Multi-target simultaneous drive model added.
-Stimulus / Actions: Two or more targets participate with different PIDs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wired-AND arbitration winner is assigned first; losing target retries later.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UVM bus model, `entdaa_fsm`</t>
+    <t xml:space="preserve">Preconditions: UVM bus model supports simultaneous target driving.
+Stimulus / Actions: Two or more unaddressed targets participate with different PIDs; losing targets stop participating.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Master assigns the arbitration winner first; losing targets are not assigned in that round and retry in later rounds. The two-target case is the minimum subcase of this multi-target coverage item, not a separate testcase.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Future</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UVM I3C agent, bus, `entdaa_fsm`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_daa_arbitration`</t>
   </si>
   <si>
     <t xml:space="preserve">ARB_003</t>
@@ -2432,6 +2195,9 @@
     <t xml:space="preserve">Report min/avg/max latency and throughput; no functional pass/fail except timeout.</t>
   </si>
   <si>
+    <t xml:space="preserve">Low</t>
+  </si>
+  <si>
     <t xml:space="preserve">Latency metric</t>
   </si>
   <si>
@@ -2514,7 +2280,7 @@
     <t xml:space="preserve">NA_003</t>
   </si>
   <si>
-    <t xml:space="preserve">Document interrupt absence.</t>
+    <t xml:space="preserve">Document IRQ-output absence.</t>
   </si>
   <si>
     <t xml:space="preserve">`na_irq_no_positive_test`</t>
@@ -2524,7 +2290,7 @@
 Stimulus / Actions: Inspect top-level ports and CSR map.</t>
   </si>
   <si>
-    <t xml:space="preserve">No IRQ output or interrupt enable/status registers exist; status verification is through `HC_STATUS`, `QUEUE_STATUS`, and RESP.</t>
+    <t xml:space="preserve">No IRQ output, interrupt enable register, or interrupt-status CSR exists. Software-visible completion/error status is available through `HC_STATUS`, `QUEUE_STATUS`, and RESP.</t>
   </si>
   <si>
     <t xml:space="preserve">`i3c_controller_top`, `csr_registers`</t>
@@ -2618,6 +2384,9 @@
     <t xml:space="preserve">0, 1, 2, 3, 4, 5-7, 8-15, 16+</t>
   </si>
   <si>
+    <t xml:space="preserve">`cp_data_pattern`</t>
+  </si>
+  <si>
     <t xml:space="preserve">zero, all-one, alternating A/5, walking-one, random</t>
   </si>
   <si>
@@ -2651,7 +2420,10 @@
     <t xml:space="preserve">continue, end at expected length, early end</t>
   </si>
   <si>
-    <t xml:space="preserve">even data parity, odd data parity</t>
+    <t xml:space="preserve">`cp_sdr_write_tbit_parity`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">generated T-bit equals `~^data_byte`; companion SVA covers hit T-bit 0 and T-bit 1</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_fifo_kind`</t>
@@ -2678,7 +2450,52 @@
     <t xml:space="preserve">0, 1, 2-14, 15</t>
   </si>
   <si>
-    <t xml:space="preserve">START, STOP, repeated START, unexpected STOP</t>
+    <t xml:space="preserve">`cp_bus001_reset_sets_sync_idle`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reset forces the PHY synchronized controller-side SCL/SDA view to the idle reset value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_bus001_scl_two_cycle_settle`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stable raw SCL input settles to the controller-side PHY output through the 2FF path.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_bus001_sda_two_cycle_settle`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stable raw SDA input settles to the controller-side PHY output through the 2FF path.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_bus001_sync_pattern_00/10/01/11`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Focused PHY stimulus covers the main SCL/SDA sampled input combinations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_bus002_valid_start_reports_start`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legal START condition is detected by `bus_monitor`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_bus002_valid_stop_reports_stop`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legal STOP condition is detected by `bus_monitor`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_bus002_rejected_falling_edge_no_start_trigger`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDA falling edge without a valid START candidate does not trigger START.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_bus002_rejected_rising_edge_no_stop_trigger`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDA rising edge without a valid STOP candidate does not trigger STOP.</t>
   </si>
   <si>
     <t xml:space="preserve">START, address, ACK, I3C data, I3C T-bit, STOP, ENTDAA</t>
@@ -2804,7 +2621,7 @@
     <t xml:space="preserve">`broadcast_addr_enable x transaction_type x first_address`</t>
   </si>
   <si>
-    <t xml:space="preserve">Ensure the control bit changes only private I3C first-address behavior while I2C, CCC, and ENTDAA retain their protocol-required address flows.</t>
+    <t xml:space="preserve">Ensure the control bit changes only private I3C first-address behavior while CCC and ENTDAA retain their protocol-required address flows.</t>
   </si>
   <si>
     <t xml:space="preserve">`prev_cmd_attr x next_cmd_attr`</t>
@@ -3493,34 +3310,34 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="B20" t="s" s="2">
+      <c r="C20" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="C20" t="s" s="2">
+      <c r="D20" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="D20" t="s" s="2">
+      <c r="E20" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="F20" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="E20" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="F20" t="s" s="2">
+      <c r="G20" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="G20" t="s" s="2">
+      <c r="H20" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="H20" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>140</v>
       </c>
     </row>
     <row r="21">
@@ -3528,31 +3345,31 @@
         <v>19</v>
       </c>
       <c r="B21" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="D21" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="C21" t="s" s="2">
+      <c r="E21" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="F21" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="D21" t="s" s="2">
+      <c r="G21" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="E21" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="F21" t="s" s="2">
+      <c r="H21" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="G21" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="H21" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>147</v>
       </c>
     </row>
     <row r="22">
@@ -3560,63 +3377,63 @@
         <v>19</v>
       </c>
       <c r="B22" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="F22" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="C22" t="s" s="2">
+      <c r="G22" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="D22" t="s" s="2">
+      <c r="H22" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I22" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="E22" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="F22" t="s" s="2">
+      <c r="J22" t="s" s="2">
         <v>151</v>
-      </c>
-      <c r="G22" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="H22" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>147</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="B23" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="C23" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="C23" t="s" s="2">
+      <c r="D23" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="D23" t="s" s="2">
+      <c r="E23" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="F23" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="E23" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="F23" t="s" s="2">
+      <c r="G23" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="G23" t="s" s="2">
+      <c r="H23" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I23" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="H23" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I23" t="s" s="2">
+      <c r="J23" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>160</v>
       </c>
     </row>
     <row r="24">
@@ -3624,31 +3441,31 @@
         <v>19</v>
       </c>
       <c r="B24" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="C24" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="C24" t="s" s="2">
+      <c r="D24" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="D24" t="s" s="2">
+      <c r="E24" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="F24" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="E24" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="F24" t="s" s="2">
+      <c r="G24" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="G24" t="s" s="2">
+      <c r="H24" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I24" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I24" t="s" s="2">
+      <c r="J24" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>167</v>
       </c>
     </row>
     <row r="25">
@@ -3656,31 +3473,31 @@
         <v>19</v>
       </c>
       <c r="B25" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="C25" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="C25" t="s" s="2">
+      <c r="D25" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="D25" t="s" s="2">
+      <c r="E25" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="F25" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="E25" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="F25" t="s" s="2">
+      <c r="G25" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="G25" t="s" s="2">
+      <c r="H25" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="H25" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>174</v>
       </c>
     </row>
     <row r="26">
@@ -3688,31 +3505,31 @@
         <v>19</v>
       </c>
       <c r="B26" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="D26" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="C26" t="s" s="2">
+      <c r="E26" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="F26" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="D26" t="s" s="2">
+      <c r="G26" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="E26" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="F26" t="s" s="2">
+      <c r="H26" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I26" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="G26" t="s" s="2">
+      <c r="J26" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="H26" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>181</v>
       </c>
     </row>
     <row r="27">
@@ -3720,31 +3537,31 @@
         <v>19</v>
       </c>
       <c r="B27" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="D27" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="C27" t="s" s="2">
+      <c r="E27" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="F27" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="D27" t="s" s="2">
+      <c r="G27" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="E27" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="F27" t="s" s="2">
+      <c r="H27" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="G27" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>188</v>
       </c>
     </row>
     <row r="28">
@@ -3752,31 +3569,31 @@
         <v>19</v>
       </c>
       <c r="B28" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="F28" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="C28" t="s" s="2">
+      <c r="G28" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="D28" t="s" s="2">
+      <c r="H28" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I28" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="E28" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="F28" t="s" s="2">
+      <c r="J28" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="G28" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="H28" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>195</v>
       </c>
     </row>
     <row r="29">
@@ -3784,31 +3601,31 @@
         <v>19</v>
       </c>
       <c r="B29" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="F29" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="C29" t="s" s="2">
+      <c r="G29" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="D29" t="s" s="2">
+      <c r="H29" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I29" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="E29" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="F29" t="s" s="2">
+      <c r="J29" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="G29" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>202</v>
       </c>
     </row>
     <row r="30">
@@ -3816,31 +3633,31 @@
         <v>19</v>
       </c>
       <c r="B30" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="F30" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="C30" t="s" s="2">
+      <c r="G30" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="D30" t="s" s="2">
+      <c r="H30" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="J30" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="E30" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="F30" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="G30" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>209</v>
       </c>
     </row>
     <row r="31">
@@ -3848,63 +3665,63 @@
         <v>19</v>
       </c>
       <c r="B31" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="D31" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="F31" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="G31" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="C31" t="s" s="2">
+      <c r="H31" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I31" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="D31" t="s" s="2">
+      <c r="J31" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="E31" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="F31" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="G31" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>215</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="D32" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="F32" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="B32" t="s" s="2">
+      <c r="G32" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="C32" t="s" s="2">
+      <c r="H32" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I32" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="D32" t="s" s="2">
+      <c r="J32" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="E32" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="F32" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="G32" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="H32" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>223</v>
       </c>
     </row>
     <row r="33">
@@ -3912,31 +3729,31 @@
         <v>19</v>
       </c>
       <c r="B33" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="E33" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="F33" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="G33" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="C33" t="s" s="2">
+      <c r="H33" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I33" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="D33" t="s" s="2">
+      <c r="J33" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="E33" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="F33" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="G33" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="H33" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>230</v>
       </c>
     </row>
     <row r="34">
@@ -3944,31 +3761,31 @@
         <v>19</v>
       </c>
       <c r="B34" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="E34" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="F34" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="G34" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="C34" t="s" s="2">
+      <c r="H34" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I34" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="D34" t="s" s="2">
+      <c r="J34" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="E34" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="F34" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="G34" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>237</v>
       </c>
     </row>
     <row r="35">
@@ -3976,31 +3793,31 @@
         <v>19</v>
       </c>
       <c r="B35" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="D35" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="E35" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="F35" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="G35" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="C35" t="s" s="2">
+      <c r="H35" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I35" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="D35" t="s" s="2">
+      <c r="J35" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="E35" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="F35" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="G35" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>244</v>
       </c>
     </row>
     <row r="36">
@@ -4008,63 +3825,63 @@
         <v>19</v>
       </c>
       <c r="B36" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="E36" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="F36" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="G36" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="C36" t="s" s="2">
+      <c r="H36" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="J36" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="D36" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="E36" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="F36" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="G36" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>251</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>19</v>
+        <v>247</v>
       </c>
       <c r="B37" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="D37" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="E37" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="G37" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="C37" t="s" s="2">
+      <c r="H37" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I37" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="D37" t="s" s="2">
+      <c r="J37" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="E37" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="F37" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="G37" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>258</v>
       </c>
     </row>
     <row r="38">
@@ -4072,31 +3889,31 @@
         <v>19</v>
       </c>
       <c r="B38" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="E38" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="F38" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="G38" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="C38" t="s" s="2">
+      <c r="H38" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I38" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="D38" t="s" s="2">
+      <c r="J38" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="E38" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="F38" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="G38" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="H38" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I38" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>265</v>
       </c>
     </row>
     <row r="39">
@@ -4104,31 +3921,31 @@
         <v>19</v>
       </c>
       <c r="B39" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="E39" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="F39" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="G39" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="C39" t="s" s="2">
+      <c r="H39" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I39" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="D39" t="s" s="2">
+      <c r="J39" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="E39" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="F39" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="G39" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="H39" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>272</v>
       </c>
     </row>
     <row r="40">
@@ -4136,95 +3953,95 @@
         <v>19</v>
       </c>
       <c r="B40" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="D40" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="E40" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="F40" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="G40" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="C40" t="s" s="2">
+      <c r="H40" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I40" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="D40" t="s" s="2">
+      <c r="J40" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="E40" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="F40" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="G40" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="H40" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>279</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="D41" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="E41" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="F41" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="G41" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="B41" t="s" s="2">
+      <c r="H41" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I41" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="C41" t="s" s="2">
+      <c r="J41" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="D41" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="E41" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="F41" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>223</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>19</v>
+        <v>283</v>
       </c>
       <c r="B42" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="D42" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="C42" t="s" s="2">
+      <c r="E42" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="F42" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="D42" t="s" s="2">
+      <c r="G42" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="E42" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="F42" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>290</v>
-      </c>
       <c r="H42" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>291</v>
+        <v>253</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>292</v>
+        <v>254</v>
       </c>
     </row>
     <row r="43">
@@ -4232,31 +4049,31 @@
         <v>19</v>
       </c>
       <c r="B43" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="D43" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="E43" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="F43" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="G43" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="C43" t="s" s="2">
+      <c r="H43" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I43" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="D43" t="s" s="2">
+      <c r="J43" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="E43" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="F43" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>299</v>
       </c>
     </row>
     <row r="44">
@@ -4264,31 +4081,31 @@
         <v>19</v>
       </c>
       <c r="B44" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="D44" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="E44" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="G44" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="C44" t="s" s="2">
+      <c r="H44" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="J44" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="D44" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="E44" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="F44" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>305</v>
       </c>
     </row>
     <row r="45">
@@ -4296,31 +4113,31 @@
         <v>19</v>
       </c>
       <c r="B45" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="D45" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="E45" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="G45" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="C45" t="s" s="2">
+      <c r="H45" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I45" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="D45" t="s" s="2">
+      <c r="J45" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="E45" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="F45" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>312</v>
       </c>
     </row>
     <row r="46">
@@ -4328,31 +4145,31 @@
         <v>19</v>
       </c>
       <c r="B46" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="D46" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="E46" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="F46" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="G46" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="D46" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="E46" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="F46" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>59</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="47">
@@ -4360,63 +4177,63 @@
         <v>19</v>
       </c>
       <c r="B47" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="D47" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="E47" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="F47" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="G47" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="C47" t="s" s="2">
+      <c r="H47" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="J47" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="D47" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="E47" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="F47" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>326</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>19</v>
+        <v>322</v>
       </c>
       <c r="B48" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="D48" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="E48" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="F48" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="G48" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="C48" t="s" s="2">
+      <c r="H48" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I48" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="D48" t="s" s="2">
+      <c r="J48" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="E48" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="F48" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="G48" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="H48" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="I48" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>333</v>
       </c>
     </row>
     <row r="49">
@@ -4424,31 +4241,31 @@
         <v>19</v>
       </c>
       <c r="B49" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="D49" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="E49" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="F49" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="G49" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="C49" t="s" s="2">
+      <c r="H49" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I49" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="D49" t="s" s="2">
+      <c r="J49" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="E49" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="F49" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>279</v>
       </c>
     </row>
     <row r="50">
@@ -4456,95 +4273,95 @@
         <v>19</v>
       </c>
       <c r="B50" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="D50" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="C50" t="s" s="2">
+      <c r="E50" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="F50" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="D50" t="s" s="2">
+      <c r="G50" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="E50" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="F50" t="s" s="2">
+      <c r="H50" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I50" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="G50" t="s" s="2">
+      <c r="J50" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>344</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="C51" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="B51" t="s" s="2">
+      <c r="D51" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="C51" t="s" s="2">
+      <c r="E51" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="F51" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="D51" t="s" s="2">
+      <c r="G51" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="E51" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="F51" t="s" s="2">
+      <c r="H51" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I51" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="G51" t="s" s="2">
+      <c r="J51" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>352</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>19</v>
+        <v>351</v>
       </c>
       <c r="B52" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="C52" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="C52" t="s" s="2">
+      <c r="D52" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="D52" t="s" s="2">
+      <c r="E52" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="F52" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="E52" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="F52" t="s" s="2">
+      <c r="G52" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="G52" t="s" s="2">
+      <c r="H52" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I52" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="H52" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I52" t="s" s="2">
+      <c r="J52" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>359</v>
       </c>
     </row>
     <row r="53">
@@ -4552,28 +4369,28 @@
         <v>19</v>
       </c>
       <c r="B53" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="C53" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="C53" t="s" s="2">
+      <c r="D53" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="D53" t="s" s="2">
+      <c r="E53" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="F53" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="E53" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="F53" t="s" s="2">
+      <c r="G53" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="G53" t="s" s="2">
+      <c r="H53" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I53" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>173</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>365</v>
@@ -4605,10 +4422,10 @@
         <v>16</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>243</v>
+        <v>371</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="55">
@@ -4616,28 +4433,28 @@
         <v>19</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D55" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="E55" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="E55" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="F55" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>377</v>
+        <v>342</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>378</v>
@@ -4669,7 +4486,7 @@
         <v>16</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>278</v>
+        <v>371</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>384</v>
@@ -4765,10 +4582,10 @@
         <v>16</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>377</v>
+        <v>405</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="60">
@@ -4776,31 +4593,31 @@
         <v>19</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D60" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="E60" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="E60" t="s" s="2">
-        <v>407</v>
-      </c>
       <c r="F60" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>173</v>
+        <v>412</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="61">
@@ -4808,63 +4625,63 @@
         <v>19</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="F61" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>377</v>
+        <v>419</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>418</v>
+        <v>19</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F62" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="63">
@@ -4872,63 +4689,63 @@
         <v>19</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F63" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>19</v>
+        <v>435</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F64" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="65">
@@ -4936,31 +4753,31 @@
         <v>19</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F65" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="66">
@@ -4968,31 +4785,31 @@
         <v>19</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F66" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="67">
@@ -5000,63 +4817,63 @@
         <v>19</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>456</v>
+        <v>416</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F67" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>19</v>
+        <v>463</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="69">
@@ -5064,31 +4881,31 @@
         <v>19</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C69" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="D69" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="E69" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="F69" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I69" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="D69" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="E69" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="F69" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>445</v>
-      </c>
       <c r="J69" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="70">
@@ -5096,31 +4913,31 @@
         <v>19</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="E70" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="F70" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="71">
@@ -5128,36 +4945,36 @@
         <v>19</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F71" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>486</v>
+        <v>16</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>489</v>
+        <v>19</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>490</v>
@@ -5213,10 +5030,10 @@
         <v>16</v>
       </c>
       <c r="I73" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="J73" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>503</v>
       </c>
     </row>
     <row r="74">
@@ -5224,31 +5041,31 @@
         <v>19</v>
       </c>
       <c r="B74" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="C74" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="C74" t="s" s="2">
+      <c r="D74" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="D74" t="s" s="2">
+      <c r="E74" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="F74" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="E74" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="F74" t="s" s="2">
+      <c r="G74" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="G74" t="s" s="2">
+      <c r="H74" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I74" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="H74" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I74" t="s" s="2">
+      <c r="J74" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>510</v>
       </c>
     </row>
     <row r="75">
@@ -5256,31 +5073,31 @@
         <v>19</v>
       </c>
       <c r="B75" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="C75" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="C75" t="s" s="2">
+      <c r="D75" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="D75" t="s" s="2">
+      <c r="E75" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="F75" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="E75" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="F75" t="s" s="2">
+      <c r="G75" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="G75" t="s" s="2">
+      <c r="H75" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="J75" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>517</v>
       </c>
     </row>
     <row r="76">
@@ -5288,31 +5105,31 @@
         <v>19</v>
       </c>
       <c r="B76" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="C76" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="D76" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="C76" t="s" s="2">
+      <c r="E76" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="F76" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="D76" t="s" s="2">
+      <c r="G76" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="E76" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="F76" t="s" s="2">
+      <c r="H76" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I76" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="G76" t="s" s="2">
+      <c r="J76" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>378</v>
       </c>
     </row>
     <row r="77">
@@ -5338,7 +5155,7 @@
         <v>527</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>528</v>
@@ -5358,30 +5175,30 @@
         <v>531</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>449</v>
+        <v>532</v>
       </c>
       <c r="E78" t="s" s="2">
         <v>531</v>
       </c>
       <c r="F78" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>536</v>
+        <v>19</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>537</v>
@@ -5402,7 +5219,7 @@
         <v>541</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>542</v>
@@ -5437,10 +5254,10 @@
         <v>16</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="81">
@@ -5448,31 +5265,31 @@
         <v>19</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D81" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="E81" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="E81" t="s" s="2">
-        <v>551</v>
-      </c>
       <c r="F81" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="82">
@@ -5480,31 +5297,31 @@
         <v>19</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D82" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="E82" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="E82" t="s" s="2">
-        <v>557</v>
-      </c>
       <c r="F82" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>377</v>
+        <v>562</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>378</v>
+        <v>563</v>
       </c>
     </row>
     <row r="83">
@@ -5512,63 +5329,63 @@
         <v>19</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="F83" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>542</v>
+        <v>569</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>19</v>
+        <v>571</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="E84" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="F84" t="s" s="2">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>542</v>
+        <v>577</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>572</v>
+        <v>578</v>
       </c>
     </row>
     <row r="85">
@@ -5576,31 +5393,31 @@
         <v>19</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="F85" t="s" s="2">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>16</v>
+        <v>584</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>579</v>
+        <v>586</v>
       </c>
     </row>
     <row r="86">
@@ -5608,31 +5425,31 @@
         <v>19</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="E86" t="s" s="2">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="F86" t="s" s="2">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>586</v>
+        <v>593</v>
       </c>
     </row>
     <row r="87">
@@ -5640,63 +5457,63 @@
         <v>19</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="E87" t="s" s="2">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="F87" t="s" s="2">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>516</v>
+        <v>569</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>592</v>
+        <v>599</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>19</v>
+        <v>600</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="F88" t="s" s="2">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>599</v>
+        <v>607</v>
       </c>
     </row>
     <row r="89">
@@ -5704,31 +5521,31 @@
         <v>19</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="E89" t="s" s="2">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F89" t="s" s="2">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>606</v>
+        <v>614</v>
       </c>
     </row>
     <row r="90">
@@ -5736,31 +5553,31 @@
         <v>19</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="E90" t="s" s="2">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="F90" t="s" s="2">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="91">
@@ -5768,31 +5585,31 @@
         <v>19</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="F91" t="s" s="2">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>612</v>
+        <v>626</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>619</v>
+        <v>627</v>
       </c>
     </row>
     <row r="92">
@@ -5800,31 +5617,31 @@
         <v>19</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="E92" t="s" s="2">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="F92" t="s" s="2">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>59</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>626</v>
+        <v>633</v>
       </c>
     </row>
     <row r="93">
@@ -5832,31 +5649,31 @@
         <v>19</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="F93" t="s" s="2">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>633</v>
+        <v>640</v>
       </c>
     </row>
     <row r="94">
@@ -5864,31 +5681,31 @@
         <v>19</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="D94" t="s" s="2">
-        <v>636</v>
+        <v>643</v>
       </c>
       <c r="E94" t="s" s="2">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="F94" t="s" s="2">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>640</v>
+        <v>647</v>
       </c>
     </row>
     <row r="95">
@@ -5896,63 +5713,63 @@
         <v>19</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="D95" t="s" s="2">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="E95" t="s" s="2">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="F95" t="s" s="2">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I95" t="s" s="2">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>647</v>
+        <v>654</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="E96" t="s" s="2">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="F96" t="s" s="2">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>16</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>655</v>
+        <v>662</v>
       </c>
     </row>
     <row r="97">
@@ -5960,31 +5777,31 @@
         <v>19</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="F97" t="s" s="2">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>486</v>
+        <v>16</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>488</v>
+        <v>669</v>
       </c>
     </row>
     <row r="98">
@@ -5992,31 +5809,31 @@
         <v>19</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="D98" t="s" s="2">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="E98" t="s" s="2">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="F98" t="s" s="2">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>668</v>
+        <v>675</v>
       </c>
     </row>
     <row r="99">
@@ -6024,63 +5841,63 @@
         <v>19</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="D99" t="s" s="2">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="E99" t="s" s="2">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="F99" t="s" s="2">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>632</v>
+        <v>681</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>674</v>
+        <v>682</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>675</v>
+        <v>19</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D100" t="s" s="2">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="E100" t="s" s="2">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="F100" t="s" s="2">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>681</v>
+        <v>661</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>682</v>
+        <v>688</v>
       </c>
     </row>
     <row r="101">
@@ -6088,31 +5905,31 @@
         <v>19</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="D101" t="s" s="2">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="F101" t="s" s="2">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>16</v>
+        <v>694</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>688</v>
+        <v>661</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>689</v>
+        <v>695</v>
       </c>
     </row>
     <row r="102">
@@ -6120,31 +5937,31 @@
         <v>19</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="D102" t="s" s="2">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="E102" t="s" s="2">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="F102" t="s" s="2">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="G102" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="H102" t="s" s="2">
         <v>694</v>
       </c>
-      <c r="H102" t="s" s="2">
-        <v>16</v>
-      </c>
       <c r="I102" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="J102" t="s" s="2">
         <v>695</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>689</v>
       </c>
     </row>
     <row r="103">
@@ -6152,63 +5969,63 @@
         <v>19</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="D103" t="s" s="2">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="F103" t="s" s="2">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>16</v>
+        <v>694</v>
       </c>
       <c r="I103" t="s" s="2">
-        <v>701</v>
+        <v>342</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>19</v>
+        <v>707</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="D104" t="s" s="2">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="F104" t="s" s="2">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>59</v>
+        <v>694</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>708</v>
+        <v>714</v>
       </c>
     </row>
     <row r="105">
@@ -6216,31 +6033,31 @@
         <v>19</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="D105" t="s" s="2">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="E105" t="s" s="2">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="F105" t="s" s="2">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="G105" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="I105" t="s" s="2">
         <v>713</v>
       </c>
-      <c r="H105" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I105" t="s" s="2">
+      <c r="J105" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>715</v>
       </c>
     </row>
     <row r="106">
@@ -6248,31 +6065,31 @@
         <v>19</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="D106" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="E106" t="s" s="2">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="F106" t="s" s="2">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>16</v>
+        <v>694</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>722</v>
+        <v>714</v>
       </c>
     </row>
     <row r="107">
@@ -6280,415 +6097,31 @@
         <v>19</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="D107" t="s" s="2">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="E107" t="s" s="2">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="F107" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>59</v>
+        <v>694</v>
       </c>
       <c r="I107" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="D108" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="E108" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="F108" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="G108" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="H108" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="C109" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="D109" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="E109" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="F109" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="G109" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="H109" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="C110" t="s" s="2">
-        <v>746</v>
-      </c>
-      <c r="D110" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="E110" t="s" s="2">
-        <v>746</v>
-      </c>
-      <c r="F110" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="G110" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="H110" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I110" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="C111" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="D111" t="s" s="2">
-        <v>753</v>
-      </c>
-      <c r="E111" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="F111" t="s" s="2">
-        <v>754</v>
-      </c>
-      <c r="G111" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="H111" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>756</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="C112" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="D112" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="E112" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="F112" t="s" s="2">
-        <v>761</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>762</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="C113" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="D113" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="E113" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="F113" t="s" s="2">
-        <v>767</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>768</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>770</v>
-      </c>
-      <c r="C114" t="s" s="2">
-        <v>771</v>
-      </c>
-      <c r="D114" t="s" s="2">
-        <v>772</v>
-      </c>
-      <c r="E114" t="s" s="2">
-        <v>771</v>
-      </c>
-      <c r="F114" t="s" s="2">
-        <v>773</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>775</v>
-      </c>
-      <c r="C115" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="D115" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="E115" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="F115" t="s" s="2">
-        <v>778</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="C116" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="D116" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="E116" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="F116" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>786</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>789</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>790</v>
-      </c>
-      <c r="D117" t="s" s="2">
-        <v>791</v>
-      </c>
-      <c r="E117" t="s" s="2">
-        <v>790</v>
-      </c>
-      <c r="F117" t="s" s="2">
-        <v>792</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>793</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>794</v>
-      </c>
-      <c r="C118" t="s" s="2">
-        <v>795</v>
-      </c>
-      <c r="D118" t="s" s="2">
-        <v>796</v>
-      </c>
-      <c r="E118" t="s" s="2">
-        <v>795</v>
-      </c>
-      <c r="F118" t="s" s="2">
-        <v>797</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>798</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>799</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>800</v>
-      </c>
-      <c r="C119" t="s" s="2">
-        <v>801</v>
-      </c>
-      <c r="D119" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="E119" t="s" s="2">
-        <v>801</v>
-      </c>
-      <c r="F119" t="s" s="2">
-        <v>803</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>788</v>
+        <v>714</v>
       </c>
     </row>
   </sheetData>
@@ -6700,18 +6133,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>806</v>
+        <v>732</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>807</v>
+        <v>733</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>808</v>
+        <v>734</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>809</v>
+        <v>735</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>19</v>
@@ -6725,10 +6158,10 @@
         <v>19</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>810</v>
+        <v>736</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>811</v>
+        <v>737</v>
       </c>
     </row>
     <row r="4">
@@ -6736,10 +6169,10 @@
         <v>19</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>812</v>
+        <v>738</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>811</v>
+        <v>737</v>
       </c>
     </row>
     <row r="5">
@@ -6747,10 +6180,10 @@
         <v>19</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>813</v>
+        <v>739</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>814</v>
+        <v>740</v>
       </c>
     </row>
     <row r="6">
@@ -6758,10 +6191,10 @@
         <v>19</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>815</v>
+        <v>741</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>816</v>
+        <v>742</v>
       </c>
     </row>
     <row r="7">
@@ -6769,10 +6202,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>817</v>
+        <v>743</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>818</v>
+        <v>744</v>
       </c>
     </row>
     <row r="8">
@@ -6780,10 +6213,10 @@
         <v>19</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>819</v>
+        <v>745</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>820</v>
+        <v>746</v>
       </c>
     </row>
     <row r="9">
@@ -6791,10 +6224,10 @@
         <v>19</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>821</v>
+        <v>747</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>822</v>
+        <v>748</v>
       </c>
     </row>
     <row r="10">
@@ -6802,10 +6235,10 @@
         <v>19</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>823</v>
+        <v>749</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>824</v>
+        <v>750</v>
       </c>
     </row>
     <row r="11">
@@ -6813,10 +6246,10 @@
         <v>19</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>825</v>
+        <v>751</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>826</v>
+        <v>752</v>
       </c>
     </row>
     <row r="12">
@@ -6824,10 +6257,10 @@
         <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>827</v>
+        <v>753</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>828</v>
+        <v>754</v>
       </c>
     </row>
     <row r="13">
@@ -6835,10 +6268,10 @@
         <v>19</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>237</v>
+        <v>755</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>829</v>
+        <v>756</v>
       </c>
     </row>
     <row r="14">
@@ -6846,10 +6279,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>830</v>
+        <v>757</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>831</v>
+        <v>758</v>
       </c>
     </row>
     <row r="15">
@@ -6857,10 +6290,10 @@
         <v>19</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>832</v>
+        <v>759</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>833</v>
+        <v>760</v>
       </c>
     </row>
     <row r="16">
@@ -6868,10 +6301,10 @@
         <v>19</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>834</v>
+        <v>761</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>835</v>
+        <v>762</v>
       </c>
     </row>
     <row r="17">
@@ -6879,10 +6312,10 @@
         <v>19</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>836</v>
+        <v>763</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>837</v>
+        <v>764</v>
       </c>
     </row>
     <row r="18">
@@ -6890,10 +6323,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>838</v>
+        <v>765</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>839</v>
+        <v>766</v>
       </c>
     </row>
     <row r="19">
@@ -6901,10 +6334,10 @@
         <v>19</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>244</v>
+        <v>767</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>840</v>
+        <v>768</v>
       </c>
     </row>
     <row r="20">
@@ -6912,10 +6345,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>841</v>
+        <v>769</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>842</v>
+        <v>770</v>
       </c>
     </row>
     <row r="21">
@@ -6923,10 +6356,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>843</v>
+        <v>771</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>844</v>
+        <v>772</v>
       </c>
     </row>
     <row r="22">
@@ -6934,10 +6367,10 @@
         <v>19</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>845</v>
+        <v>773</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>846</v>
+        <v>774</v>
       </c>
     </row>
     <row r="23">
@@ -6945,10 +6378,10 @@
         <v>19</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>847</v>
+        <v>775</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>848</v>
+        <v>776</v>
       </c>
     </row>
     <row r="24">
@@ -6956,10 +6389,10 @@
         <v>19</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>147</v>
+        <v>777</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>849</v>
+        <v>778</v>
       </c>
     </row>
     <row r="25">
@@ -6967,10 +6400,10 @@
         <v>19</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>202</v>
+        <v>779</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>850</v>
+        <v>780</v>
       </c>
     </row>
     <row r="26">
@@ -6978,10 +6411,10 @@
         <v>19</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>535</v>
+        <v>781</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>851</v>
+        <v>782</v>
       </c>
     </row>
     <row r="27">
@@ -6989,10 +6422,10 @@
         <v>19</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>852</v>
+        <v>783</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>853</v>
+        <v>784</v>
       </c>
     </row>
     <row r="28">
@@ -7000,10 +6433,10 @@
         <v>19</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>854</v>
+        <v>785</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>855</v>
+        <v>786</v>
       </c>
     </row>
     <row r="29">
@@ -7011,10 +6444,10 @@
         <v>19</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>856</v>
+        <v>787</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>857</v>
+        <v>788</v>
       </c>
     </row>
     <row r="30">
@@ -7022,10 +6455,10 @@
         <v>19</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>858</v>
+        <v>789</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>859</v>
+        <v>790</v>
       </c>
     </row>
     <row r="31">
@@ -7033,10 +6466,10 @@
         <v>19</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>860</v>
+        <v>791</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>861</v>
+        <v>792</v>
       </c>
     </row>
     <row r="32">
@@ -7044,10 +6477,10 @@
         <v>19</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>862</v>
+        <v>233</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>863</v>
+        <v>793</v>
       </c>
     </row>
     <row r="33">
@@ -7055,10 +6488,10 @@
         <v>19</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>613</v>
+        <v>462</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>864</v>
+        <v>794</v>
       </c>
     </row>
     <row r="34">
@@ -7066,21 +6499,21 @@
         <v>19</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>19</v>
+        <v>795</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>19</v>
+        <v>796</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>865</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>19</v>
+        <v>797</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>19</v>
+        <v>798</v>
       </c>
     </row>
     <row r="36">
@@ -7088,10 +6521,10 @@
         <v>19</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>866</v>
+        <v>799</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>867</v>
+        <v>800</v>
       </c>
     </row>
     <row r="37">
@@ -7099,10 +6532,10 @@
         <v>19</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>868</v>
+        <v>801</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>869</v>
+        <v>802</v>
       </c>
     </row>
     <row r="38">
@@ -7110,10 +6543,10 @@
         <v>19</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>870</v>
+        <v>803</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>871</v>
+        <v>804</v>
       </c>
     </row>
     <row r="39">
@@ -7121,10 +6554,10 @@
         <v>19</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>872</v>
+        <v>805</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>873</v>
+        <v>806</v>
       </c>
     </row>
     <row r="40">
@@ -7132,10 +6565,10 @@
         <v>19</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>874</v>
+        <v>550</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>875</v>
+        <v>807</v>
       </c>
     </row>
     <row r="41">
@@ -7143,21 +6576,21 @@
         <v>19</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>876</v>
+        <v>19</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>877</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>19</v>
+        <v>808</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>878</v>
+        <v>19</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>879</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43">
@@ -7165,10 +6598,10 @@
         <v>19</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>880</v>
+        <v>809</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>881</v>
+        <v>810</v>
       </c>
     </row>
     <row r="44">
@@ -7176,10 +6609,10 @@
         <v>19</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>882</v>
+        <v>811</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>883</v>
+        <v>812</v>
       </c>
     </row>
     <row r="45">
@@ -7187,10 +6620,10 @@
         <v>19</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>884</v>
+        <v>813</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>885</v>
+        <v>814</v>
       </c>
     </row>
     <row r="46">
@@ -7198,10 +6631,10 @@
         <v>19</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>886</v>
+        <v>815</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>887</v>
+        <v>816</v>
       </c>
     </row>
     <row r="47">
@@ -7209,10 +6642,10 @@
         <v>19</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>888</v>
+        <v>817</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>889</v>
+        <v>818</v>
       </c>
     </row>
     <row r="48">
@@ -7220,10 +6653,10 @@
         <v>19</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>890</v>
+        <v>819</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>891</v>
+        <v>820</v>
       </c>
     </row>
     <row r="49">
@@ -7231,10 +6664,87 @@
         <v>19</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>892</v>
+        <v>821</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>893</v>
+        <v>822</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="C51" t="s" s="2">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>831</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>835</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>836</v>
       </c>
     </row>
   </sheetData>
@@ -7249,43 +6759,43 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>894</v>
+        <v>837</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>895</v>
+        <v>838</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>896</v>
+        <v>839</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>765</v>
+        <v>690</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>768</v>
+        <v>693</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>897</v>
+        <v>840</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>771</v>
+        <v>697</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>774</v>
+        <v>700</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>898</v>
+        <v>841</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>776</v>
+        <v>702</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>779</v>
+        <v>705</v>
       </c>
     </row>
   </sheetData>
@@ -7309,58 +6819,58 @@
         <v>4</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>899</v>
+        <v>842</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>764</v>
+        <v>689</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>730</v>
+        <v>655</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>766</v>
+        <v>691</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>765</v>
+        <v>690</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>769</v>
+        <v>695</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>770</v>
+        <v>696</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>730</v>
+        <v>655</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>772</v>
+        <v>698</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>771</v>
+        <v>697</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>769</v>
+        <v>695</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>775</v>
+        <v>701</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>730</v>
+        <v>655</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>777</v>
+        <v>703</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>776</v>
+        <v>702</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>780</v>
+        <v>706</v>
       </c>
     </row>
   </sheetData>

--- a/docs/test_plan/I3C_Testplan.xlsx
+++ b/docs/test_plan/I3C_Testplan.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="891">
   <si>
     <t xml:space="preserve">Category</t>
   </si>
@@ -849,7 +849,7 @@
 Stimulus / Actions: Queue first write (`toc=0`) and second write (`toc=1`) with distinct payloads; separately issue a `toc=0` write with no next supported command.</t>
   </si>
   <si>
-    <t xml:space="preserve">Valid case: first write completes data/T-bit then emits `Sr`; **data integrity check: for each transfer, `sampled_data[i]` matches its own TX FIFO byte slice** — confirming the RSTART boundary does not cause data loss, duplication, or cross-command mixing; second command starts after `Sr`; final STOP occurs only after the `toc=1` command; both RESPs report success with matching TID/length. With broadcast-header enabled, only the first private transfer emits the `0x7e` preamble. Negative case: the first write data is transmitted, controller emits STOP instead of RSTART, and RESP is `Success` with actual length transmitted.</t>
+    <t xml:space="preserve">Valid case: first write completes data/T-bit then emits `Sr`; **data integrity check: for each transfer, `sampled_data[i]` matches its own TX FIFO byte slice** — confirming the RSTART boundary does not cause data loss, duplication, or cross-command mixing; second command starts after `Sr`; final STOP occurs only after the `toc=1` command; each `wroc=1` command reports success with matching TID/length. With broadcast-header enabled, only the first private transfer emits the `0x7e` preamble. Negative case: the first write data is transmitted, controller emits STOP instead of RSTART, and RESP is `NotSupported` with actual length transmitted regardless of WROC.</t>
   </si>
   <si>
     <t xml:space="preserve">`flow_active`, `scl_generator`, UVM scoreboard</t>
@@ -1063,10 +1063,10 @@
 Stimulus / Actions: Sweep `dtt` 0..7 in both private-address modes (no broadcast header and with broadcast header).</t>
   </si>
   <si>
-    <t xml:space="preserve">**`dtt` 0..4 (positive):** the correct number of inline bytes is transmitted; **data integrity check: `sampled_data[i]` == cmd byte i for i &lt; dtt** — confirming the cmd dword bytes are sent in descriptor order with no extra, missing, or reordered byte; RESP `Success`; `resp.length == dtt`. **`dtt` 5..7 (negative):** FSM rejects in `WaitDAT` before any bus activity; `not_supported_d` is set; RESP error is `NotSupported` (4'hA); no inline bytes sent, queues remain clean.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active` (`WaitDAT` early-exit), CMD descriptor</t>
+    <t xml:space="preserve">**`dtt` 0..4 (positive):** the correct number of inline bytes is transmitted; **data integrity check: `sampled_data[i]` == cmd byte i for i &lt; dtt** — confirming the cmd dword bytes are sent in descriptor order with no extra, missing, or reordered byte; RESP `Success`; `resp.length == dtt`. **`dtt` 5..7 (negative):** FSM rejects in `FetchDAT` before DAT or bus activity; `not_supported_d` is set; RESP error is `NotSupported` (4'hA); no inline bytes sent, queues remain clean.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active` (`FetchDAT` validation), CMD descriptor</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_imm_dtt`, `cp_resp_err`, `cp_private_start_prefix`</t>
@@ -1082,7 +1082,7 @@
   </si>
   <si>
     <t xml:space="preserve">Preconditions: DAT[0] I3C device; target ACKs address and data; `dtt=2`, bytes `[AA, BB]`.
-Stimulus / Actions: Issue one immediate command with `toc=1` and one with `toc=0`; cover both I3C and I2C immediate paths (`I3CWriteImmediate`, `I2CWriteImmediate`).</t>
+Stimulus / Actions: Issue one immediate command with `toc=1` and one with `toc=0`; cover both private I3C and I2C immediate paths through `InitI3CWrite`/`InitI2CWrite` and `IssueCmd`.</t>
   </si>
   <si>
     <t xml:space="preserve">`toc=1`: STOP is generated after inline data; **data integrity check: `sampled_data[0]`==`0xAA`, `sampled_data[1]`==`0xBB`**; RESP is `Success` with correct length 2. `toc=0`: all dtt bytes are still transmitted before STOP — **data integrity check: same byte-level check applies**; STOP is generated, `not_supported_d` is set, RESP error is `NotSupported` (4'hA); no `Sr` or continuation occurs. Both toc values must complete all dtt bytes on bus with correct values before STOP. Bus must not hang.</t>
@@ -1474,23 +1474,20 @@
     <t xml:space="preserve">ERR_001</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify successful RESP descriptor fields.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`resp_success_tid_length`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: Valid transactions with unique TIDs.
-Stimulus / Actions: Run immediate, regular write, regular read, and ENTDAA success paths.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESP `[31:28]=Success`, `[27:24]=TID`, `[15:0]=actual length`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, RESP FIFO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_resp_err`, `cp_tid`, `cp_resp_len`</t>
+    <t xml:space="preserve">Verify successful RESP descriptor fields without a dedicated vseq.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: SVA enabled; immediate, regular write/read, I2C, CCC, and ENTDAA success paths are exercised by existing functional vseqs.
+Stimulus / Actions: No standalone stimulus. Existing success-path vseqs naturally produce successful responses; `flow_active_sva` checks the common Success/TID/reserved/length encoding at RESP write time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESP `[31:28]=Success`, `[27:24]=TID`, `[23:16]=0`, and `[15:0]=actual length` for every covered successful command class.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active_sva`, `flow_active`, RESP FIFO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_sdr_write_toc1_success_resp`, `cp_sdr_read_success_resp_len`, `cp_i2c_write_success_resp`, `cp_i2c_read_success_resp`, `cp_imm_success_resp`, `cp_daa_success_resp`, CCC success RESP covers</t>
   </si>
   <si>
     <t xml:space="preserve">ERR_002</t>
@@ -1509,26 +1506,26 @@
     <t xml:space="preserve">RESP status is `AddrHeader`, TID matches the command, reserved bits are zero, and length is 0 for every supported command class with private/target address NACK. No regular data, read data, immediate inline data, or direct CCC target data is transferred after the NACK.</t>
   </si>
   <si>
-    <t xml:space="preserve">`cp_resp_err`, `cp_addr_ack`, `cp_tid`, `cp_resp_len`, `cross_imm_x_device_type`</t>
+    <t xml:space="preserve">`cp_sdr_write_addr_nack_resp`, `cp_sdr_read_addr_nack_resp`, `cp_i2c_write_addr_nack_resp`, `cp_i2c_read_addr_nack_resp`, `cp_i3c_imm_addr_nack_resp`, `cp_i2c_imm_addr_nack_resp`, `cp_direct_ccc_target_addr_nack_resp`, `cp_addr_ack`, `cross_imm_x_device_type`</t>
   </si>
   <si>
     <t xml:space="preserve">ERR_003</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify `AddrHeader` response encoding and payload suppression when broadcast header `7'h7E+W` is NACKed.</t>
+    <t xml:space="preserve">Verify command-agnostic `AddrHeader` response encoding and follow-up suppression when the shared broadcast header `7'h7E+W` is NACKed.</t>
   </si>
   <si>
     <t xml:space="preserve">`resp_broadcast_header_nack`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: Device NACKs `7'h7E+W` during a CCC command (ENEC/DISEC/ENTDAA).
-Stimulus / Actions: Run `i3c_broadcast_header_nack_resp_vseq`: issue ENEC, DISEC, and ENTDAA commands while the device NACKs the broadcast header.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESP status is `AddrHeader`, TID matches the command, reserved bits are zero, and length is 0. No CCC opcode, CCC payload byte, or ENTDAA `7'h7E+R` round is emitted after the NACK; bus recovery is legal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_resp_err`, `cp_addr_ack`, `cp_tid`, `cp_resp_len`, `cp_ccc_nack`</t>
+    <t xml:space="preserve">Preconditions: Device NACKs `7'h7E+W` while the controller is in the common broadcast-header frame.
+Stimulus / Actions: Run `i3c_broadcast_header_nack_resp_vseq` to exercise a representative broadcast-header NACK; `flow_active_sva` checks the common `I3CBcastHeader` NACK path independent of whether the pending command is CCC, ENTDAA, or a private I3C transfer using the broadcast-header preamble.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESP status is `AddrHeader`, TID matches the command, reserved bits are zero, and length is 0. No command-specific follow-up is emitted after the NACK: no CCC opcode/payload, no ENTDAA `7'h7E+R` round, no private target-address phase, and no transfer data. Bus recovery is legal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_bcast_header_nack_sample_no_followup`, `cp_bcast_header_nack_stops_no_followup`, `cp_bcast_header_nack_resp`, `cp_addr_nack_resp`</t>
   </si>
   <si>
     <t xml:space="preserve">ERR_004</t>
@@ -1541,16 +1538,16 @@
   </si>
   <si>
     <t xml:space="preserve">Preconditions: Target ACKs the address and NACKs a data byte.
-Stimulus / Actions: Run `i2c_data_nack_write_vseq` with a multi-DWORD payload and `i3c_imm_data_nack_i2c_vseq` with `dtt=2..4`. Follow each error path with a successful transfer using the recovery policy appropriate to its data source.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The NACKed byte is fully clocked, but no later regular or inline byte is transmitted. Pre-NACK data matches the programmed TX FIFO or descriptor bytes. RESP is `Nack` with matching TID, zero reserved bits, and actual length through the NACKed byte. Regular write can preserve unfetched TX FIFO words, so recovery waits for idle and uses SW reset before the next FIFO-backed write. Immediate data is descriptor-resident, so its next transfer succeeds without SW reset.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `hci_queues`, `bus_tx_flow`, RESP FIFO, UVM scoreboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_data_ack`, `cp_resp_err`, `cp_tid`, `cp_resp_len`, `cross_imm_x_device_type`</t>
+Stimulus / Actions: Run `i2c_data_nack_write_vseq` with a multi-DWORD payload and first/middle/final data-byte NACK positions. Run `i3c_imm_data_nack_i2c_vseq` with `dtt=2..4`, covering first, middle, and final inline-byte NACK positions. Follow each error path with the recovery policy appropriate to its data source.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The NACKed byte is fully clocked, but no later regular or inline byte is transmitted. Pre-NACK data matches the programmed TX FIFO or descriptor bytes. RESP is `I2cDataNackOrI3cBusAborted` with matching TID, zero reserved bits, and actual length through the NACKed byte. Regular write can preserve unfetched TX FIFO words, so recovery waits for idle and uses SW reset before the next FIFO-backed write. Immediate data is descriptor-resident, so its next transfer succeeds without SW reset.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active_sva`, `flow_active`, `hci_queues`, `bus_tx_flow`, RESP FIFO, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_i2c_write_data_nack_latches`, `cp_i2c_write_data_nack_stops_no_more_data`, `cp_i2c_imm_data_nack_latches`, `cp_i2c_imm_data_nack_stops_no_more_data`, `cp_data_nack_resp`, `cp_i2c_write_data_nack_resp`, `cp_i2c_imm_data_nack_resp`, `cross_imm_x_device_type`</t>
   </si>
   <si>
     <t xml:space="preserve">ERR_005</t>
@@ -1563,120 +1560,123 @@
   </si>
   <si>
     <t xml:space="preserve">Preconditions: Target ends an I3C read after M bytes where M&lt;N requested bytes.
-Stimulus / Actions: Run `i3c_read_short_target_end_vseq` across multiple partial-DWORD boundaries and both private-address modes, including a `toc=0` command with a following command queued.</t>
+Stimulus / Actions: Run `i3c_read_short_target_end_vseq` across all partial-DWORD packing positions and both private-address modes, explicitly including the off-by-one boundary M=N-1 and a `toc=0` command with a following command queued.</t>
   </si>
   <si>
     <t xml:space="preserve">RX FIFO contains exactly the M valid bytes with correct packing; no fabricated byte is stored. Short read forces STOP and suppresses a requested continuation. RESP is `I3cShortReadErr` with matching TID, zero reserved bits, and actual length M. Draining RX and RESP data leaves queues ready for the next command; SW reset is not required.</t>
   </si>
   <si>
-    <t xml:space="preserve">`flow_active`, `bus_rx_flow`, RESP FIFO, UVM scoreboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_short_read`, `cp_resp_err`, `cp_tid`, `cp_resp_len`, `cp_private_start_prefix`</t>
+    <t xml:space="preserve">`flow_active_sva`, `flow_active`, `bus_rx_flow`, RESP FIFO, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_sdr_read_target_tbit_end_sets_short`, `cp_sdr_read_one_byte_short`, `cp_sdr_read_short_dword_boundary`, `cp_sdr_read_short_commits_received_word_and_stops`, `cp_sdr_read_short_blocks_more_data_and_continuation`, `cp_sdr_read_short_resp_len`, `cp_private_start_prefix`</t>
   </si>
   <si>
     <t xml:space="preserve">ERR_006</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify response classification and end-of-data handling for a legal SDR read final T-bit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`i3c_read_tbit_no_parity_resp`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: DAT[0] is I3C dynamic address `0x08`; target ends transfer with T-bit=0 at the requested length.
-Stimulus / Actions: Run `i3c_read_tbit_no_parity_resp_vseq` in both private-address modes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each mode uses the expected private-address prefix. Final T-bit=0 at the requested length is treated as legal end-of-data, no extra RX byte is consumed, queues drain cleanly, and the condition is not classified as `Parity`. RESP is `Success`, TID matches the command, reserved bits are zero, and length matches the requested length.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_read_tbit`, `cp_private_start_prefix`, `cp_resp_err`, `cp_tid`, `cp_resp_len`</t>
+    <t xml:space="preserve">Verify response classification and end-of-data handling for a legal SDR read final T-bit without a dedicated vseq.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: SVA enabled; existing SDR read vseqs drive final T-bit=0 at the requested length in both private-address modes.
+Stimulus / Actions: No standalone stimulus. `i3c_read_vseq` and `i3c_read_len_sweep_vseq` naturally exercise this condition; `flow_active_sva` checks the final T-bit transition and the resulting response.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final T-bit=0 at the requested length clears the remaining count without setting short-read state or consuming an extra RX byte. RESP is `Success`, TID matches the command, reserved bits are zero, and length matches the requested length, so the condition cannot be classified as `Parity`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active_sva`, `flow_active`, `bus_rx_flow`, RESP FIFO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_sdr_read_target_end_at_requested_len`, `cp_sdr_read_final_tbit_end_policy`, `cp_sdr_read_success_resp_len`, `cp_private_start_prefix`</t>
   </si>
   <si>
     <t xml:space="preserve">ERR_007</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify TX underflow/RX overflow termination, data boundary, response encoding, and recovery policy, including ENTDAA result storage overflow.</t>
+    <t xml:space="preserve">Verify I3C/I2C TX underflow and RX overflow termination, data boundary, response encoding, continuation suppression, and recovery, including ENTDAA result overflow.</t>
   </si>
   <si>
     <t xml:space="preserve">`resp_ovl_error`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: TX FIFO underflow, regular-read RX FIFO overflow, or ENTDAA result RX FIFO overflow condition.
-Stimulus / Actions: Run `i3c_ovl_resp_vseq`, `i3c_write_tx_fifo_underflow_vseq`, `i3c_read_rx_fifo_full_overflow_vseq`, and `i3c_entdaa_rx_fifo_partial_overflow_vseq`, including full/partial RX prefill, `toc=0/1`, both private-address modes, late TX refill, and ENTDAA result storage with only 0, 1, or 2 free RX FIFO entries for the 3-DWORD DAA result.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Committed TX/RX/DAA-result data remains correct and no garbage is emitted or stored. Overflow/underflow forces STOP and suppresses continuation. RESP is `Ovl` with matching TID, zero reserved bits, and the processed/committed boundary length. Regular-read RX overflow recovery drains preserved RX FIFO contents and RESP; no SW reset is required. ENTDAA result overflow drains the prefilled RX words plus any committed DAA result DWORDs and RESP; no SW reset is required. Residual/late TX data requires waiting for idle and issuing SW reset before a clean FIFO-backed recovery transfer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `hci_queues`, `scl_generator`, `entdaa_controller`, RX FIFO, RESP FIFO, UVM scoreboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_resp_err_ovl`, `cp_daa_result`, `cp_tid`, `cp_resp_len`, `cp_tx_empty`, `cp_tx_late_refill`, `cp_rx_full`, `cp_stall_type`</t>
+    <t xml:space="preserve">Preconditions: A regular I3C/I2C write exhausts TX FIFO, a regular I3C/I2C read cannot commit a full or partial DWORD to RX FIFO, or ENTDAA cannot store its complete result.
+Stimulus / Actions: Run `i3c_write_tx_fifo_underflow_vseq`, `i3c_read_rx_fifo_full_overflow_vseq`, and `i3c_entdaa_rx_fifo_partial_overflow_vseq`. Cover I3C and I2C, both I3C private-address modes, `toc=0/1`, TX FIFO empty/one-DWORD/late-refill cases, RX FIFO full/one-free-slot cases, partial-DWORD read lengths 1/2/3, a queued command after `toc=0`, and ENTDAA with 0/1/2 free entries for its 3-DWORD result. Run a successful transfer after each recovery policy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No garbage is transmitted or committed. Underflow/overflow forces STOP and suppresses continuation; at an I2C full-DWORD commit rejection the controller NACKs that byte before STOP. RESP is `Ovl` with matching TID, zero reserved bits, and actual length: bytes transmitted for TX underflow, bytes received through the rejected regular-read commit, or DAA-result bytes successfully committed (0/4/8). RX and ENTDAA paths recover after draining RX/RESP without SW reset. TX residual or late-refill data is cleared by waiting for idle and applying SW reset before the successful FIFO-backed recovery write.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active_sva`, `flow_active`, `hci_queues`, `scl_generator`, `entdaa_controller`, RX FIFO, RESP FIFO, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_i3c_tx_underflow_resp_ovl`, `cp_i2c_tx_underflow_resp_ovl`, `cp_rx_commit_reject_latches_overflow`, `cp_rx_partial_dword_commit_overflow`, `cp_read_rx_overflow_blocks_data_and_continuation`, `cp_read_rx_overflow_requests_stop`, `cp_i2c_read_full_commit_boundary_nacks`, `cp_ovl_resp_matches_current_len`, `cp_i3c_read_rx_overflow_resp_ovl`, `cp_i2c_read_rx_overflow_resp_ovl`, `cp_entdaa_commit_reject_latches_overflow_and_stops`, `cp_entdaa_overflow_blocks_result_write`, `cp_entdaa_rx_overflow_resp_ovl`</t>
   </si>
   <si>
     <t xml:space="preserve">ERR_008</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify response write stalls safely.</t>
+    <t xml:space="preserve">Verify success and error response writes stall safely without loss, overwrite, or duplication.</t>
   </si>
   <si>
     <t xml:space="preserve">`resp_fifo_full_backpressure`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: RESP FIFO full before transaction completes.
-Stimulus / Actions: Complete a transfer while RESP full, then drain RESP.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FSM waits in response write phase; exactly one response is eventually written.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_resp_full`, `cp_stall_type`</t>
+    <t xml:space="preserve">Preconditions: RESP FIFO can be backdoor-filled before a response-producing command completes.
+Stimulus / Actions: Run `i3c_resp_fifo_full_backpressure_vseq`. First complete a successful regular write with `wroc=1` while RESP is full. Then repeat with a `wroc=0` immediate command that receives an address NACK. In each case, hold the FIFO full for multiple cycles, pop one prefilled entry, and drain the remaining entries plus the released response.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FSM remains in `WriteResp`; response valid and descriptor data remain stable; FIFO pointers, depth, and all prefilled entries remain unchanged while blocked. One software pop releases exactly one pending response write. The prefilled entries retain FIFO order, the command response is appended once with the expected status/TID/length, and the final FIFO is empty. Successful `wroc=0` independence remains covered separately by ERR_012.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active_sva`, `flow_active`, `hci_queues`, RESP FIFO, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_resp_full_success_holds_pending_write`, `cp_resp_full_error_holds_pending_write`, `cp_resp_full_keeps_descriptor_stable`, `cp_resp_backpressure_release_writes_once`</t>
   </si>
   <si>
     <t xml:space="preserve">ERR_009</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify HC abort termination for I3C SDR, I2C regular, immediate, and ENTDAA transfers, including data integrity, response encoding, termination, and recovery policy.</t>
+    <t xml:space="preserve">Verify HC abort termination for I3C SDR, I2C regular, immediate, normal CCC, and ENTDAA transfers, including data integrity, response encoding, termination, priority, holdoff, and recovery policy.</t>
   </si>
   <si>
     <t xml:space="preserve">`resp_hc_abort_error`</t>
   </si>
   <si>
     <t xml:space="preserve">Preconditions: Controller can be aborted from selectable FSM states via persistent level bit `HC_CONTROL[29]` (ABORT).
-Stimulus / Actions: Run `i3c_write_abort_vseq`, `i3c_read_abort_vseq`, and `i2c_regular_abort_vseq` for early/deep/`toc=0` write and read transfers. Run `i3c_imm_abort_vseq` in I3C immediate mode with and without the broadcast-header preamble and in I2C immediate mode. Run `i3c_daa_hc_abort_vseq` during ENTDAA identity receive, assigned-address phase, and after one completed ENTDAA round. Also cover pre-bus, idle, priority, persistent-level, and CCC execution cases.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abort completes the defined byte boundary, forces STOP, suppresses continuation, preserves transmitted or committed data, and returns `HcAborted` with matching TID, zero reserved bits, and actual length. I3C/I2C regular writes can retain unfetched TX FIFO data and require clear-abort, idle, then SW reset for clean FIFO-backed recovery. I3C/I2C reads drain and verify committed RX data plus RESP; a following read succeeds without SW reset, which is needed only to discard residual state. Immediate data is descriptor-resident and similarly recovers without SW reset after clearing abort and draining RESP. ENTDAA abort drains any committed DAA result plus RESP, clears abort, and runs a following ENTDAA successfully without SW reset. I2C remains OD-only and uses controller NACK then STOP for read abort.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `csr_registers`, `hci_queues`, `scl_generator`, `bus_tx_flow`, `bus_rx_flow`, `entdaa_controller`, `entdaa_fsm`, RX FIFO, RESP FIFO, UVM scoreboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_hc_abort`, `cp_resp_err`, `cp_abort_entry_state`, `cp_resp_err_priority`, `cp_abort_stop_state`, `cp_private_start_prefix`, `cp_i2c_dir`, `cp_i2c_ack_seq`, `cp_daa_abort_point`, `cross_imm_x_device_type`</t>
+Stimulus / Actions: Run `i3c_write_abort_vseq`, `i3c_read_abort_vseq`, and `i2c_regular_abort_vseq` for early/deep/`toc=0` write and read transfers. Run `i3c_imm_abort_vseq` for private/broadcast-header I3C and I2C immediate transfers. Run `i3c_daa_hc_abort_vseq` during ENTDAA identity receive, assigned-address phase, and after one completed round, with a successful ENTDAA after every abort point. Run `i3c_hc_abort_policy_vseq` to hold abort at idle with a queued command, abort broadcast and direct ENEC at the completed-byte boundary, verify recovery without SW reset, and combine broadcast-header NACK with HC abort to verify `AddrHeader` priority.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abort held at idle prevents CMD acceptance, START, and RESP generation until software clears it. Active abort completes the defined byte boundary, forces STOP, suppresses continuation, preserves transmitted or committed data, and returns `HcAborted` with matching TID, zero reserved bits, and actual length. A pre-existing higher-priority error overrides `HcAborted`. I3C/I2C regular writes can retain unfetched TX FIFO data and require clear-abort, idle, then SW reset for clean FIFO-backed recovery. I3C/I2C reads drain and verify committed RX data plus RESP and run a following read without SW reset. Immediate, normal CCC, and ENTDAA cases clear abort, drain committed data/RESP, and run a successful same-class command without SW reset. I2C remains OD-only and uses controller NACK then STOP for read abort.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active_sva`, `entdaa_fsm_sva`, `flow_active`, `csr_registers`, `hci_queues`, `scl_generator`, `bus_tx_flow`, `bus_rx_flow`, `entdaa_controller`, `entdaa_fsm`, RX FIFO, RESP FIFO, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_abort_entry_state`, `cp_abort_stop_state`, `cp_resp_err_priority`, `cp_abort_idle_blocks_command`, `cp_abort_error_priority_resp`, `cp_regular_write_abort_resp`, `cp_sdr_read_abort_resp`, `cp_i2c_read_abort_resp`, `cp_immediate_abort_resp`, `cp_ccc_abort_resp`, `cp_daa_abort_resp`, `cp_daa_abort_point`, `cp_private_start_prefix`, `cp_i2c_dir`, `cross_imm_x_device_type`</t>
   </si>
   <si>
     <t xml:space="preserve">ERR_010</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify pre-bus rejection of unsupported or invalid descriptor commands.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`invalid_descriptor_attr`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: CMD descriptors can be written directly; `cp=1` immediate CMD available for CCC opcode injection.
-Stimulus / Actions: (a) Issue `ComboTransfer`, reserved attr, HDR mode values, invalid mode encodings, and an `ImmediateDataTransfer` with `rnw=1`. (b) Issue representative unsupported CCC opcodes (`cp=1`, opcode outside ENEC/DISEC/ENTDAA) for both broadcast and direct forms (previously `ccc_unsupported_opcode_policy`).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**(b) Defined:** FSM rejects unsupported CCC opcode before any bus activity; RESP error is `NotSupported` (0xA); no CCC frame is emitted; queues drain cleanly. **(a) Clarification items:** no unbounded hang or illegal queue corruption; for `rnw=1` immediate the controller must not emit a read frame — it either ignores direction (forces write) or returns a specified error response; remaining subcases require sign-off once their expected behavior is specified.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `i3c_pkg`, CMD descriptor parsing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_invalid_cmd`, `cp_imm`, `cp_unsupported_cmd`</t>
+    <t xml:space="preserve">Verify deterministic pre-DAT/pre-bus rejection, response encoding, and recovery for every unsupported descriptor class.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`i3c_invalid_descriptor_attr_vseq`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: CMD descriptors can be written directly; DAT[0] contains a valid I3C target for the recovery command.
+Stimulus / Actions: Sweep `ComboTransfer` and raw attrs `100..111`; Regular and Immediate with every mode other than `sdr0`; Immediate `rnw=1` and `dtt&gt;4`; Regular `cp=1`; unsupported broadcast CCC `02` and direct CCC `82`; and AddressAssignment with opcode other than ENTDAA. Include an invalid `wroc=0` descriptor and run a legal Immediate transfer after every rejection without SW reset.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each invalid command is rejected in `FetchDAT` without DAT read, START/RSTART/STOP, or bus TX/RX request. Exactly one RESP is written with `NotSupported` (0xA), matching TID, zero reserved bits, and length 0 regardless of WROC. CMD/RESP queues drain cleanly, TX/RX remain untouched, and every following legal command succeeds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active_sva`, `flow_active`, CMD/RESP FIFO, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_invalid_cmd`, `cp_imm`, `cp_unsupported_cmd`, `cp_invalid_cmd_rejected_before_access`, `cp_invalid_cmd_not_supported_resp`</t>
   </si>
   <si>
     <t xml:space="preserve">ERR_011</t>
@@ -1688,39 +1688,39 @@
     <t xml:space="preserve">`entdaa_invalid_descriptor_resp`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: CMD descriptors can be written directly; DAT entry exists but should not be used because the command is rejected before ENTDAA starts.
-Stimulus / Actions: Run `i3c_entdaa_invalid_descriptor_resp_vseq` with three subcases: `toc=0,wroc=1,dev_count=1`; `toc=1,wroc=0,dev_count=1`; and `toc=1,wroc=1,dev_count=0`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No START, no `7'h7E+W` broadcast header, no ENTDAA opcode, and no DAA round are emitted. Exactly one RESP is written with status `NotSupported`, matching TID, reserved bits zero, and length 0. Queues drain cleanly and a following legal command can run.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, `i3c_pkg`, RESP FIFO, UVM scoreboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_addr_assign_desc`, `cp_resp_err`, `cp_tid`, `cp_resp_len`, `cp_no_bus_activity`</t>
+    <t xml:space="preserve">Preconditions: CMD descriptors can be written directly; DAT entries exist but must not be read because the command is rejected before ENTDAA starts.
+Stimulus / Actions: Run `i3c_entdaa_invalid_descriptor_resp_vseq` with four isolated subcases: `toc=0`; `wroc=0`; `dev_count=0`; and `dev_idx=31,dev_count=2` with `DatDepth=32`. Run a legal immediate transfer after every rejection without SW reset.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No DAT read, START/RSTART/STOP, bus TX/RX request, ENTDAA opcode, or DAA-controller activation occurs. Exactly one RESP is written with status `NotSupported`, matching TID, reserved bits zero, and length 0. Queues drain cleanly and every following legal command succeeds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active_sva`, `flow_active`, `i3c_pkg`, CMD/RESP FIFO, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_addr_assign_desc`, `cp_resp_err`, `cp_tid`, `cp_resp_len`, `cp_no_bus_activity`, `cp_addr_assign_invalid_rejected_before_access`, `cp_addr_assign_invalid_not_supported_resp`</t>
   </si>
   <si>
     <t xml:space="preserve">ERR_012</t>
   </si>
   <si>
-    <t xml:space="preserve">Document the `wroc` (response-on-completion) design gap.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`immediate_wroc_policy`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: CMD descriptors can be written directly.
-Stimulus / Actions: Issue immediate/regular commands with `wroc=0` and `wroc=1`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**Documented design gap — to be discussed / implemented later (not positive sign-off coverage).** RTL currently ignores the `wroc` field: `flow_active.sv` asserts `resp_queue_wvalid` unconditionally in `WriteResp` and `wroc` is never read, so a RESP descriptor is always written regardless of `wroc`. Behavior for `wroc=0` (suppress RESP write) is undefined until the project spec decides whether to implement it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`flow_active`, RESP FIFO, `csr_registers`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_wroc`</t>
+    <t xml:space="preserve">Verify response-on-completion suppression and error override for every supported command class.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`wroc_policy`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preconditions: DAT[0] is a responsive I3C target; CMD descriptors can set `wroc`; RESP FIFO can be backdoor-filled for the independence case.
+Stimulus / Actions: Run `i3c_wroc_policy_vseq`: issue successful regular, immediate, and immediate-CCC commands with `wroc=0/1`; run mixed-WROC commands; run a supported `toc=0,wroc=0` continuation while RESP is full; and NACK the address of a `wroc=0` immediate command.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Successful `wroc=1` commands write exactly one Success RESP. Successful `wroc=0` commands write no RESP and do not depend on RESP FIFO readiness. A supported `toc=0,wroc=0` command accepts its queued continuation without writing RESP, including while RESP is full; `wroc=1` continuation acceptance waits for RESP readiness. Address NACK and all other errors write a response regardless of WROC. Missing/unsupported continuation writes `NotSupported`. `AddressAssignment.wroc=0` remains invalid under ERR_011.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`flow_active_sva`, `flow_active`, RESP FIFO, UVM scoreboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_wroc0_success_suppresses_resp`, `cp_wroc1_success_enters_write_resp`, `cp_wroc0_error_override_writes_resp`, `cp_wroc0_continuation_ignores_resp_ready`, `cp_wroc1_continuation_waits_for_resp_ready`</t>
   </si>
   <si>
     <t xml:space="preserve">ERR_013</t>
@@ -2342,12 +2342,102 @@
     <t xml:space="preserve">0 bytes before abort, 1 word before abort, &gt;1 word before abort</t>
   </si>
   <si>
+    <t xml:space="preserve">`cp_abort_entry_state`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">idle/WaitForCmd holdoff; active preamble, CCC, transfer, and data states</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_abort_stop_state`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preamble, normal CCC, and transfer data states that request STOP after HC abort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_resp_err_priority`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`AddrHeader`, data NACK, DAA NACK, overflow, short read, and not-supported overriding `HcAborted`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_daa_abort_point`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">identity receive, assigned-address phase, completed-round boundary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_abort_idle_blocks_command`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abort held in WaitForCmd with a command queued and no command pop/START</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_abort_error_priority_resp`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HC abort coexists with a higher-priority error and the prioritized response is emitted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_regular_write_abort_resp`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regular write emits exact `HcAborted` TID/reserved/actual-length fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_immediate_abort_resp`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">immediate transfer emits exact `HcAborted` fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_ccc_abort_resp`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">broadcast/direct normal CCC emits exact `HcAborted` fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_daa_abort_resp`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENTDAA emits exact `HcAborted` fields</t>
+  </si>
+  <si>
     <t xml:space="preserve">`cp_cmd_attr`</t>
   </si>
   <si>
     <t xml:space="preserve">`ImmediateDataTransfer`, `RegularTransfer`, `AddressAssignment`, `ComboTransfer/unsupported`, reserved</t>
   </si>
   <si>
+    <t xml:space="preserve">`cp_invalid_cmd`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">invalid Regular, Immediate, AddressAssignment, Combo, and unsupported direct/internal attributes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_imm`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">invalid Immediate combinations across `cp`, `rnw`, and mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_unsupported_cmd`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unsupported broadcast and direct immediate CCC opcode ranges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_invalid_cmd_rejected_before_access`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">invalid descriptor reaches `FetchDAT` with all DAT and bus request outputs inactive, then enters `WriteResp`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_invalid_cmd_not_supported_resp`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">invalid descriptor emits exact length-zero `NotSupported` response fields</t>
+  </si>
+  <si>
     <t xml:space="preserve">`cp_device_type`</t>
   </si>
   <si>
@@ -2396,10 +2486,40 @@
     <t xml:space="preserve">0 (regular transfers only — generates `Sr` on success or STOP on missing continuation), 1 (all transfer types — generates STOP; only valid option for immediate transfers)</t>
   </si>
   <si>
+    <t xml:space="preserve">`cp_wroc0_success_suppresses_resp`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">successful regular, immediate, and immediate-CCC completion with no RESP write</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_wroc1_success_enters_write_resp`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">successful response-producing completion enters `WriteResp` and asserts RESP valid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_wroc0_error_override_writes_resp`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">error with `wroc=0` still enters `WriteResp` and asserts RESP valid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_wroc0_continuation_ignores_resp_ready`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supported `toc=0,wroc=0` continuation accepted while RESP is not ready</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_wroc1_continuation_waits_for_resp_ready`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supported `toc=0,wroc=1` continuation held until RESP becomes ready</t>
+  </si>
+  <si>
     <t xml:space="preserve">`cp_resp_err`</t>
   </si>
   <si>
-    <t xml:space="preserve">Success, AddrHeader, Nack, Ovl, I3cShortReadErr, unreachable-defined-codes</t>
+    <t xml:space="preserve">Success, AddrHeader, Nack, Ovl, I3cShortReadErr, I2cDataNackOrI3cBusAborted, unreachable-defined-codes</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_addr_ack`</t>
@@ -2508,6 +2628,30 @@
   </si>
   <si>
     <t xml:space="preserve">TX empty, RX full, RESP full, none</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_resp_full_success_holds_pending_write`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A successful `wroc=1` response remains valid in `WriteResp` while RESP is full.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_resp_full_error_holds_pending_write`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An error response remains valid in `WriteResp` while RESP is full, including when the command has `wroc=0`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_resp_full_keeps_descriptor_stable`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response status, TID, reserved bits, and length remain stable across a blocked cycle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">`cp_resp_backpressure_release_writes_once`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A previously blocked response handshakes when space appears and exits `WriteResp` on the following cycle.</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_ccc_opcode`</t>
@@ -4855,25 +4999,25 @@
         <v>465</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>466</v>
+        <v>416</v>
       </c>
       <c r="E68" t="s" s="2">
         <v>465</v>
       </c>
       <c r="F68" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="G68" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="G68" t="s" s="2">
+      <c r="H68" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I68" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="H68" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I68" t="s" s="2">
+      <c r="J68" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>470</v>
       </c>
     </row>
     <row r="69">
@@ -4881,31 +5025,31 @@
         <v>19</v>
       </c>
       <c r="B69" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C69" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="C69" t="s" s="2">
+      <c r="D69" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="D69" t="s" s="2">
+      <c r="E69" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="F69" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="E69" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="F69" t="s" s="2">
+      <c r="G69" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="G69" t="s" s="2">
+      <c r="H69" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="J69" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>476</v>
       </c>
     </row>
     <row r="70">
@@ -4913,31 +5057,31 @@
         <v>19</v>
       </c>
       <c r="B70" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C70" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="C70" t="s" s="2">
+      <c r="D70" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="D70" t="s" s="2">
+      <c r="E70" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="F70" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="E70" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="F70" t="s" s="2">
+      <c r="G70" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="G70" t="s" s="2">
+      <c r="H70" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="J70" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>482</v>
       </c>
     </row>
     <row r="71">
@@ -4945,31 +5089,31 @@
         <v>19</v>
       </c>
       <c r="B71" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C71" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="C71" t="s" s="2">
+      <c r="D71" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="D71" t="s" s="2">
+      <c r="E71" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="F71" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="E71" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="F71" t="s" s="2">
+      <c r="G71" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="G71" t="s" s="2">
+      <c r="H71" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I71" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="H71" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I71" t="s" s="2">
+      <c r="J71" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>489</v>
       </c>
     </row>
     <row r="72">
@@ -4977,31 +5121,31 @@
         <v>19</v>
       </c>
       <c r="B72" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C72" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="C72" t="s" s="2">
+      <c r="D72" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="D72" t="s" s="2">
+      <c r="E72" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="F72" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="E72" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="F72" t="s" s="2">
+      <c r="G72" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="G72" t="s" s="2">
+      <c r="H72" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I72" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="H72" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I72" t="s" s="2">
+      <c r="J72" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>496</v>
       </c>
     </row>
     <row r="73">
@@ -5009,31 +5153,31 @@
         <v>19</v>
       </c>
       <c r="B73" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="C73" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="C73" t="s" s="2">
+      <c r="D73" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="E73" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="F73" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="D73" t="s" s="2">
+      <c r="G73" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="E73" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="F73" t="s" s="2">
+      <c r="H73" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I73" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="G73" t="s" s="2">
+      <c r="J73" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>502</v>
       </c>
     </row>
     <row r="74">
@@ -5041,31 +5185,31 @@
         <v>19</v>
       </c>
       <c r="B74" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C74" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="C74" t="s" s="2">
+      <c r="D74" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="D74" t="s" s="2">
+      <c r="E74" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="F74" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="E74" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="F74" t="s" s="2">
+      <c r="G74" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="G74" t="s" s="2">
+      <c r="H74" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I74" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="H74" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I74" t="s" s="2">
+      <c r="J74" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>509</v>
       </c>
     </row>
     <row r="75">
@@ -5073,28 +5217,28 @@
         <v>19</v>
       </c>
       <c r="B75" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="C75" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="C75" t="s" s="2">
+      <c r="D75" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="D75" t="s" s="2">
+      <c r="E75" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="F75" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="E75" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="F75" t="s" s="2">
+      <c r="G75" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="G75" t="s" s="2">
+      <c r="H75" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I75" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="J75" t="s" s="2">
         <v>515</v>
@@ -5155,7 +5299,7 @@
         <v>527</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>528</v>
@@ -5219,7 +5363,7 @@
         <v>541</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>542</v>
@@ -6477,10 +6621,10 @@
         <v>19</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>233</v>
+        <v>793</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="33">
@@ -6488,10 +6632,10 @@
         <v>19</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>462</v>
+        <v>795</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="34">
@@ -6499,10 +6643,10 @@
         <v>19</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="35">
@@ -6510,10 +6654,10 @@
         <v>19</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="36">
@@ -6521,10 +6665,10 @@
         <v>19</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
     </row>
     <row r="37">
@@ -6532,10 +6676,10 @@
         <v>19</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="38">
@@ -6543,10 +6687,10 @@
         <v>19</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
     </row>
     <row r="39">
@@ -6554,10 +6698,10 @@
         <v>19</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="40">
@@ -6565,10 +6709,10 @@
         <v>19</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>550</v>
+        <v>809</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>807</v>
+        <v>810</v>
       </c>
     </row>
     <row r="41">
@@ -6576,21 +6720,21 @@
         <v>19</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>19</v>
+        <v>811</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>19</v>
+        <v>812</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>808</v>
+        <v>19</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>19</v>
+        <v>813</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>19</v>
+        <v>814</v>
       </c>
     </row>
     <row r="43">
@@ -6598,10 +6742,10 @@
         <v>19</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>810</v>
+        <v>816</v>
       </c>
     </row>
     <row r="44">
@@ -6609,10 +6753,10 @@
         <v>19</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>812</v>
+        <v>818</v>
       </c>
     </row>
     <row r="45">
@@ -6620,10 +6764,10 @@
         <v>19</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>814</v>
+        <v>820</v>
       </c>
     </row>
     <row r="46">
@@ -6631,10 +6775,10 @@
         <v>19</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>816</v>
+        <v>822</v>
       </c>
     </row>
     <row r="47">
@@ -6642,10 +6786,10 @@
         <v>19</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>818</v>
+        <v>824</v>
       </c>
     </row>
     <row r="48">
@@ -6653,10 +6797,10 @@
         <v>19</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>820</v>
+        <v>826</v>
       </c>
     </row>
     <row r="49">
@@ -6664,10 +6808,10 @@
         <v>19</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>822</v>
+        <v>828</v>
       </c>
     </row>
     <row r="50">
@@ -6675,10 +6819,10 @@
         <v>19</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>824</v>
+        <v>830</v>
       </c>
     </row>
     <row r="51">
@@ -6686,10 +6830,10 @@
         <v>19</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>826</v>
+        <v>832</v>
       </c>
     </row>
     <row r="52">
@@ -6697,10 +6841,10 @@
         <v>19</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>827</v>
+        <v>233</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>828</v>
+        <v>833</v>
       </c>
     </row>
     <row r="53">
@@ -6708,10 +6852,10 @@
         <v>19</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>829</v>
+        <v>462</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>830</v>
+        <v>834</v>
       </c>
     </row>
     <row r="54">
@@ -6719,10 +6863,10 @@
         <v>19</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>832</v>
+        <v>836</v>
       </c>
     </row>
     <row r="55">
@@ -6730,10 +6874,10 @@
         <v>19</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>834</v>
+        <v>838</v>
       </c>
     </row>
     <row r="56">
@@ -6741,10 +6885,274 @@
         <v>19</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>836</v>
+        <v>840</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>841</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>843</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>845</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>847</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>849</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>851</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>853</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>856</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>857</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>859</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>863</v>
+      </c>
+      <c r="C70" t="s" s="2">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>865</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>867</v>
+      </c>
+      <c r="C72" t="s" s="2">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>869</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>871</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>873</v>
+      </c>
+      <c r="C75" t="s" s="2">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>875</v>
+      </c>
+      <c r="C76" t="s" s="2">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>877</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>879</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>881</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>883</v>
+      </c>
+      <c r="C80" t="s" s="2">
+        <v>884</v>
       </c>
     </row>
   </sheetData>
@@ -6759,15 +7167,15 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>837</v>
+        <v>885</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>838</v>
+        <v>886</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>839</v>
+        <v>887</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>690</v>
@@ -6778,7 +7186,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>840</v>
+        <v>888</v>
       </c>
       <c r="B3" t="s" s="2">
         <v>697</v>
@@ -6789,7 +7197,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>841</v>
+        <v>889</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>702</v>
@@ -6819,7 +7227,7 @@
         <v>4</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>842</v>
+        <v>890</v>
       </c>
     </row>
     <row r="2">

--- a/docs/test_plan/I3C_Testplan.xlsx
+++ b/docs/test_plan/I3C_Testplan.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="883">
   <si>
     <t xml:space="preserve">Category</t>
   </si>
@@ -1767,17 +1767,17 @@
     <t xml:space="preserve">ERR_015</t>
   </si>
   <si>
-    <t xml:space="preserve">Clarify SW reset during active transfer.</t>
+    <t xml:space="preserve">Verify deterministic SW reset behavior during active transfer.</t>
   </si>
   <si>
     <t xml:space="preserve">`sw_reset_while_busy_policy`</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions: Transfer in progress.
-Stimulus / Actions: Assert `RESET_CONTROL[0]` (SOFT_RST) while not idle.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If the spec leaves this undefined, the test records a spec gap and recommends SW only reset when `FSM_IDLE=1`; it is not positive sign-off coverage until a busy-reset policy is specified.</t>
+    <t xml:space="preserve">Preconditions: Transfer in progress with queued continuation work.
+Stimulus / Actions: Assert `RESET_CONTROL[0]` (SOFT_RST) while `HC_STATUS[FSM_IDLE]=0`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Busy SOFT_RST is accepted as a no-op: no `sw_reset` pulse, no queue flush, no CSR staging clear, no protocol FSM reset, and the active plus queued transfers complete normally. Idle SOFT_RST behavior remains covered by CSR_008/CSR_009.</t>
   </si>
   <si>
     <t xml:space="preserve">`csr_registers`, `hci_queues`, `flow_active`</t>
@@ -1814,32 +1814,10 @@
     <t xml:space="preserve">ARB_001</t>
   </si>
   <si>
-    <t xml:space="preserve">Verify ENTDAA bit-level receiver samples wired bus.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`entdaa_single_bit_arbitration_observe`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preconditions: DAA target drives known PID bits.
-Stimulus / Actions: During ENTDAA, observe each PID/BCR/DCR bit sampled by `bus_rx_flow`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Captured 64-bit identity matches bus data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`entdaa_fsm`, `bus_rx_flow`, bus model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">`cp_daa_bit_pos`</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARB_002</t>
-  </si>
-  <si>
     <t xml:space="preserve">Verify true multi-target ENTDAA arbitration.</t>
   </si>
   <si>
-    <t xml:space="preserve">`entdaa_multi_target_arbitration_future`</t>
+    <t xml:space="preserve">`i3c_entdaa_multi_target_arbitration_vseq`</t>
   </si>
   <si>
     <t xml:space="preserve">Preconditions: UVM bus model supports simultaneous target driving.
@@ -1849,16 +1827,13 @@
     <t xml:space="preserve">Master assigns the arbitration winner first; losing targets are not assigned in that round and retry in later rounds. The two-target case is the minimum subcase of this multi-target coverage item, not a separate testcase.</t>
   </si>
   <si>
-    <t xml:space="preserve">Future</t>
-  </si>
-  <si>
     <t xml:space="preserve">UVM I3C agent, bus, `entdaa_fsm`</t>
   </si>
   <si>
     <t xml:space="preserve">`cp_daa_arbitration`</t>
   </si>
   <si>
-    <t xml:space="preserve">ARB_003</t>
+    <t xml:space="preserve">ARB_002</t>
   </si>
   <si>
     <t xml:space="preserve">Verify STOP detection during active command.</t>
@@ -1880,7 +1855,7 @@
     <t xml:space="preserve">`cp_unexpected_bus_event`</t>
   </si>
   <si>
-    <t xml:space="preserve">ARB_004</t>
+    <t xml:space="preserve">ARB_003</t>
   </si>
   <si>
     <t xml:space="preserve">Verify controller behavior if command starts on busy bus.</t>
@@ -5555,13 +5530,13 @@
         <v>583</v>
       </c>
       <c r="H85" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I85" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="I85" t="s" s="2">
+      <c r="J85" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>586</v>
       </c>
     </row>
     <row r="86">
@@ -5569,60 +5544,60 @@
         <v>19</v>
       </c>
       <c r="B86" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="C86" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="C86" t="s" s="2">
+      <c r="D86" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="D86" t="s" s="2">
+      <c r="E86" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="F86" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="E86" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="F86" t="s" s="2">
+      <c r="G86" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>591</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>59</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>592</v>
+        <v>569</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>19</v>
+        <v>592</v>
       </c>
       <c r="B87" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="C87" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="C87" t="s" s="2">
+      <c r="D87" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="D87" t="s" s="2">
+      <c r="E87" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="F87" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="E87" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="F87" t="s" s="2">
+      <c r="G87" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="G87" t="s" s="2">
+      <c r="H87" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I87" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="J87" t="s" s="2">
         <v>599</v>
@@ -5630,34 +5605,34 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B88" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="B88" t="s" s="2">
+      <c r="C88" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="C88" t="s" s="2">
+      <c r="D88" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="D88" t="s" s="2">
+      <c r="E88" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="F88" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="E88" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="F88" t="s" s="2">
+      <c r="G88" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="G88" t="s" s="2">
+      <c r="H88" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I88" t="s" s="2">
         <v>605</v>
       </c>
-      <c r="H88" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I88" t="s" s="2">
+      <c r="J88" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>607</v>
       </c>
     </row>
     <row r="89">
@@ -5665,31 +5640,31 @@
         <v>19</v>
       </c>
       <c r="B89" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="C89" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="C89" t="s" s="2">
+      <c r="D89" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="D89" t="s" s="2">
+      <c r="E89" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="F89" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="E89" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="F89" t="s" s="2">
+      <c r="G89" t="s" s="2">
         <v>611</v>
       </c>
-      <c r="G89" t="s" s="2">
+      <c r="H89" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I89" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="H89" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>613</v>
-      </c>
       <c r="J89" t="s" s="2">
-        <v>614</v>
+        <v>606</v>
       </c>
     </row>
     <row r="90">
@@ -5697,31 +5672,31 @@
         <v>19</v>
       </c>
       <c r="B90" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="C90" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="D90" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="C90" t="s" s="2">
+      <c r="E90" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="F90" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="D90" t="s" s="2">
+      <c r="G90" t="s" s="2">
         <v>617</v>
       </c>
-      <c r="E90" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="F90" t="s" s="2">
+      <c r="H90" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I90" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="G90" t="s" s="2">
+      <c r="J90" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>614</v>
       </c>
     </row>
     <row r="91">
@@ -5729,31 +5704,31 @@
         <v>19</v>
       </c>
       <c r="B91" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="C91" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="C91" t="s" s="2">
+      <c r="D91" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="D91" t="s" s="2">
+      <c r="E91" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="F91" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="E91" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="F91" t="s" s="2">
+      <c r="G91" t="s" s="2">
         <v>624</v>
       </c>
-      <c r="G91" t="s" s="2">
+      <c r="H91" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="J91" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>627</v>
       </c>
     </row>
     <row r="92">
@@ -5761,31 +5736,31 @@
         <v>19</v>
       </c>
       <c r="B92" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C92" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="D92" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="C92" t="s" s="2">
+      <c r="E92" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="F92" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="D92" t="s" s="2">
+      <c r="G92" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="E92" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="F92" t="s" s="2">
+      <c r="H92" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I92" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="G92" t="s" s="2">
+      <c r="J92" t="s" s="2">
         <v>632</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>633</v>
       </c>
     </row>
     <row r="93">
@@ -5793,31 +5768,31 @@
         <v>19</v>
       </c>
       <c r="B93" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="C93" t="s" s="2">
         <v>634</v>
       </c>
-      <c r="C93" t="s" s="2">
+      <c r="D93" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="D93" t="s" s="2">
+      <c r="E93" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="F93" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="E93" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="F93" t="s" s="2">
+      <c r="G93" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="G93" t="s" s="2">
+      <c r="H93" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I93" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="H93" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I93" t="s" s="2">
+      <c r="J93" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>640</v>
       </c>
     </row>
     <row r="94">
@@ -5825,36 +5800,36 @@
         <v>19</v>
       </c>
       <c r="B94" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="C94" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="C94" t="s" s="2">
+      <c r="D94" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="D94" t="s" s="2">
+      <c r="E94" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="F94" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="E94" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="F94" t="s" s="2">
+      <c r="G94" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="G94" t="s" s="2">
+      <c r="H94" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I94" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="H94" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I94" t="s" s="2">
+      <c r="J94" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>647</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>19</v>
+        <v>647</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>648</v>
@@ -5875,7 +5850,7 @@
         <v>652</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>653</v>
@@ -5886,34 +5861,34 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="B96" t="s" s="2">
+      <c r="C96" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="C96" t="s" s="2">
+      <c r="D96" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="D96" t="s" s="2">
+      <c r="E96" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="F96" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="E96" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="F96" t="s" s="2">
+      <c r="G96" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="G96" t="s" s="2">
+      <c r="H96" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I96" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="H96" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I96" t="s" s="2">
+      <c r="J96" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>662</v>
       </c>
     </row>
     <row r="97">
@@ -5921,31 +5896,31 @@
         <v>19</v>
       </c>
       <c r="B97" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="C97" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="C97" t="s" s="2">
+      <c r="D97" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="D97" t="s" s="2">
+      <c r="E97" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="F97" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="E97" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="F97" t="s" s="2">
+      <c r="G97" t="s" s="2">
         <v>666</v>
       </c>
-      <c r="G97" t="s" s="2">
+      <c r="H97" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="J97" t="s" s="2">
         <v>667</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>669</v>
       </c>
     </row>
     <row r="98">
@@ -5953,31 +5928,31 @@
         <v>19</v>
       </c>
       <c r="B98" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="C98" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="D98" t="s" s="2">
         <v>670</v>
       </c>
-      <c r="C98" t="s" s="2">
+      <c r="E98" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="F98" t="s" s="2">
         <v>671</v>
       </c>
-      <c r="D98" t="s" s="2">
+      <c r="G98" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="E98" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="F98" t="s" s="2">
+      <c r="H98" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="I98" t="s" s="2">
         <v>673</v>
       </c>
-      <c r="G98" t="s" s="2">
+      <c r="J98" t="s" s="2">
         <v>674</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>675</v>
       </c>
     </row>
     <row r="99">
@@ -5985,31 +5960,31 @@
         <v>19</v>
       </c>
       <c r="B99" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="C99" t="s" s="2">
         <v>676</v>
       </c>
-      <c r="C99" t="s" s="2">
+      <c r="D99" t="s" s="2">
         <v>677</v>
       </c>
-      <c r="D99" t="s" s="2">
+      <c r="E99" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="F99" t="s" s="2">
         <v>678</v>
       </c>
-      <c r="E99" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="F99" t="s" s="2">
+      <c r="G99" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="G99" t="s" s="2">
+      <c r="H99" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="J99" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>682</v>
       </c>
     </row>
     <row r="100">
@@ -6017,31 +5992,31 @@
         <v>19</v>
       </c>
       <c r="B100" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="C100" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="D100" t="s" s="2">
         <v>683</v>
       </c>
-      <c r="C100" t="s" s="2">
+      <c r="E100" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="F100" t="s" s="2">
         <v>684</v>
       </c>
-      <c r="D100" t="s" s="2">
+      <c r="G100" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="E100" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="F100" t="s" s="2">
+      <c r="H100" t="s" s="2">
         <v>686</v>
       </c>
-      <c r="G100" t="s" s="2">
+      <c r="I100" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="J100" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>688</v>
       </c>
     </row>
     <row r="101">
@@ -6049,31 +6024,31 @@
         <v>19</v>
       </c>
       <c r="B101" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="C101" t="s" s="2">
         <v>689</v>
       </c>
-      <c r="C101" t="s" s="2">
+      <c r="D101" t="s" s="2">
         <v>690</v>
       </c>
-      <c r="D101" t="s" s="2">
+      <c r="E101" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="F101" t="s" s="2">
         <v>691</v>
       </c>
-      <c r="E101" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="F101" t="s" s="2">
+      <c r="G101" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="G101" t="s" s="2">
-        <v>693</v>
-      </c>
       <c r="H101" t="s" s="2">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>695</v>
+        <v>687</v>
       </c>
     </row>
     <row r="102">
@@ -6081,60 +6056,60 @@
         <v>19</v>
       </c>
       <c r="B102" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="C102" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="D102" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="E102" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="F102" t="s" s="2">
         <v>696</v>
       </c>
-      <c r="C102" t="s" s="2">
+      <c r="G102" t="s" s="2">
         <v>697</v>
       </c>
-      <c r="D102" t="s" s="2">
+      <c r="H102" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="J102" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="E102" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="F102" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>695</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>19</v>
+        <v>699</v>
       </c>
       <c r="B103" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="C103" t="s" s="2">
         <v>701</v>
       </c>
-      <c r="C103" t="s" s="2">
+      <c r="D103" t="s" s="2">
         <v>702</v>
       </c>
-      <c r="D103" t="s" s="2">
+      <c r="E103" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="F103" t="s" s="2">
         <v>703</v>
       </c>
-      <c r="E103" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="F103" t="s" s="2">
+      <c r="G103" t="s" s="2">
         <v>704</v>
       </c>
-      <c r="G103" t="s" s="2">
+      <c r="H103" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="I103" t="s" s="2">
         <v>705</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="J103" t="s" s="2">
         <v>706</v>
@@ -6142,34 +6117,34 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B104" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="B104" t="s" s="2">
+      <c r="C104" t="s" s="2">
         <v>708</v>
       </c>
-      <c r="C104" t="s" s="2">
+      <c r="D104" t="s" s="2">
         <v>709</v>
       </c>
-      <c r="D104" t="s" s="2">
+      <c r="E104" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="F104" t="s" s="2">
         <v>710</v>
       </c>
-      <c r="E104" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="F104" t="s" s="2">
+      <c r="G104" t="s" s="2">
         <v>711</v>
       </c>
-      <c r="G104" t="s" s="2">
-        <v>712</v>
-      </c>
       <c r="H104" t="s" s="2">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>714</v>
+        <v>706</v>
       </c>
     </row>
     <row r="105">
@@ -6177,31 +6152,31 @@
         <v>19</v>
       </c>
       <c r="B105" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="C105" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="D105" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="E105" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="F105" t="s" s="2">
         <v>715</v>
       </c>
-      <c r="C105" t="s" s="2">
+      <c r="G105" t="s" s="2">
         <v>716</v>
       </c>
-      <c r="D105" t="s" s="2">
+      <c r="H105" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="I105" t="s" s="2">
         <v>717</v>
       </c>
-      <c r="E105" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="F105" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>713</v>
-      </c>
       <c r="J105" t="s" s="2">
-        <v>714</v>
+        <v>706</v>
       </c>
     </row>
     <row r="106">
@@ -6209,63 +6184,31 @@
         <v>19</v>
       </c>
       <c r="B106" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="C106" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="D106" t="s" s="2">
         <v>720</v>
       </c>
-      <c r="C106" t="s" s="2">
+      <c r="E106" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="F106" t="s" s="2">
         <v>721</v>
       </c>
-      <c r="D106" t="s" s="2">
+      <c r="G106" t="s" s="2">
         <v>722</v>
       </c>
-      <c r="E106" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="F106" t="s" s="2">
+      <c r="H106" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="I106" t="s" s="2">
         <v>723</v>
       </c>
-      <c r="G106" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>725</v>
-      </c>
       <c r="J106" t="s" s="2">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="C107" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="D107" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="E107" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="F107" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="G107" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>714</v>
+        <v>706</v>
       </c>
     </row>
   </sheetData>
@@ -6277,18 +6220,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>734</v>
+        <v>726</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>19</v>
@@ -6302,10 +6245,10 @@
         <v>19</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>737</v>
+        <v>729</v>
       </c>
     </row>
     <row r="4">
@@ -6313,10 +6256,10 @@
         <v>19</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>737</v>
+        <v>729</v>
       </c>
     </row>
     <row r="5">
@@ -6324,10 +6267,10 @@
         <v>19</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>739</v>
+        <v>731</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>740</v>
+        <v>732</v>
       </c>
     </row>
     <row r="6">
@@ -6335,10 +6278,10 @@
         <v>19</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>742</v>
+        <v>734</v>
       </c>
     </row>
     <row r="7">
@@ -6346,10 +6289,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>744</v>
+        <v>736</v>
       </c>
     </row>
     <row r="8">
@@ -6357,10 +6300,10 @@
         <v>19</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>746</v>
+        <v>738</v>
       </c>
     </row>
     <row r="9">
@@ -6368,10 +6311,10 @@
         <v>19</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>748</v>
+        <v>740</v>
       </c>
     </row>
     <row r="10">
@@ -6379,10 +6322,10 @@
         <v>19</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>750</v>
+        <v>742</v>
       </c>
     </row>
     <row r="11">
@@ -6390,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>752</v>
+        <v>744</v>
       </c>
     </row>
     <row r="12">
@@ -6401,10 +6344,10 @@
         <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>754</v>
+        <v>746</v>
       </c>
     </row>
     <row r="13">
@@ -6412,10 +6355,10 @@
         <v>19</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>756</v>
+        <v>748</v>
       </c>
     </row>
     <row r="14">
@@ -6423,10 +6366,10 @@
         <v>19</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>758</v>
+        <v>750</v>
       </c>
     </row>
     <row r="15">
@@ -6434,10 +6377,10 @@
         <v>19</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>760</v>
+        <v>752</v>
       </c>
     </row>
     <row r="16">
@@ -6445,10 +6388,10 @@
         <v>19</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>762</v>
+        <v>754</v>
       </c>
     </row>
     <row r="17">
@@ -6456,10 +6399,10 @@
         <v>19</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>764</v>
+        <v>756</v>
       </c>
     </row>
     <row r="18">
@@ -6467,10 +6410,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>766</v>
+        <v>758</v>
       </c>
     </row>
     <row r="19">
@@ -6478,10 +6421,10 @@
         <v>19</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>768</v>
+        <v>760</v>
       </c>
     </row>
     <row r="20">
@@ -6489,10 +6432,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>770</v>
+        <v>762</v>
       </c>
     </row>
     <row r="21">
@@ -6500,10 +6443,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>772</v>
+        <v>764</v>
       </c>
     </row>
     <row r="22">
@@ -6511,10 +6454,10 @@
         <v>19</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>773</v>
+        <v>765</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>774</v>
+        <v>766</v>
       </c>
     </row>
     <row r="23">
@@ -6522,10 +6465,10 @@
         <v>19</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>776</v>
+        <v>768</v>
       </c>
     </row>
     <row r="24">
@@ -6533,10 +6476,10 @@
         <v>19</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>778</v>
+        <v>770</v>
       </c>
     </row>
     <row r="25">
@@ -6544,10 +6487,10 @@
         <v>19</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>780</v>
+        <v>772</v>
       </c>
     </row>
     <row r="26">
@@ -6555,10 +6498,10 @@
         <v>19</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>782</v>
+        <v>774</v>
       </c>
     </row>
     <row r="27">
@@ -6566,10 +6509,10 @@
         <v>19</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>784</v>
+        <v>776</v>
       </c>
     </row>
     <row r="28">
@@ -6577,10 +6520,10 @@
         <v>19</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>786</v>
+        <v>778</v>
       </c>
     </row>
     <row r="29">
@@ -6588,10 +6531,10 @@
         <v>19</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>788</v>
+        <v>780</v>
       </c>
     </row>
     <row r="30">
@@ -6599,10 +6542,10 @@
         <v>19</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>790</v>
+        <v>782</v>
       </c>
     </row>
     <row r="31">
@@ -6610,10 +6553,10 @@
         <v>19</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>791</v>
+        <v>783</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>792</v>
+        <v>784</v>
       </c>
     </row>
     <row r="32">
@@ -6621,10 +6564,10 @@
         <v>19</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>794</v>
+        <v>786</v>
       </c>
     </row>
     <row r="33">
@@ -6632,10 +6575,10 @@
         <v>19</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>796</v>
+        <v>788</v>
       </c>
     </row>
     <row r="34">
@@ -6643,10 +6586,10 @@
         <v>19</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>798</v>
+        <v>790</v>
       </c>
     </row>
     <row r="35">
@@ -6654,10 +6597,10 @@
         <v>19</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>800</v>
+        <v>792</v>
       </c>
     </row>
     <row r="36">
@@ -6665,10 +6608,10 @@
         <v>19</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>802</v>
+        <v>794</v>
       </c>
     </row>
     <row r="37">
@@ -6676,10 +6619,10 @@
         <v>19</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>804</v>
+        <v>796</v>
       </c>
     </row>
     <row r="38">
@@ -6687,10 +6630,10 @@
         <v>19</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>805</v>
+        <v>797</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>806</v>
+        <v>798</v>
       </c>
     </row>
     <row r="39">
@@ -6698,10 +6641,10 @@
         <v>19</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>808</v>
+        <v>800</v>
       </c>
     </row>
     <row r="40">
@@ -6709,10 +6652,10 @@
         <v>19</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>810</v>
+        <v>802</v>
       </c>
     </row>
     <row r="41">
@@ -6720,10 +6663,10 @@
         <v>19</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>812</v>
+        <v>804</v>
       </c>
     </row>
     <row r="42">
@@ -6731,10 +6674,10 @@
         <v>19</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>814</v>
+        <v>806</v>
       </c>
     </row>
     <row r="43">
@@ -6742,10 +6685,10 @@
         <v>19</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="44">
@@ -6753,10 +6696,10 @@
         <v>19</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>818</v>
+        <v>810</v>
       </c>
     </row>
     <row r="45">
@@ -6764,10 +6707,10 @@
         <v>19</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>820</v>
+        <v>812</v>
       </c>
     </row>
     <row r="46">
@@ -6775,10 +6718,10 @@
         <v>19</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>822</v>
+        <v>814</v>
       </c>
     </row>
     <row r="47">
@@ -6786,10 +6729,10 @@
         <v>19</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>824</v>
+        <v>816</v>
       </c>
     </row>
     <row r="48">
@@ -6797,10 +6740,10 @@
         <v>19</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>826</v>
+        <v>818</v>
       </c>
     </row>
     <row r="49">
@@ -6808,10 +6751,10 @@
         <v>19</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>828</v>
+        <v>820</v>
       </c>
     </row>
     <row r="50">
@@ -6819,10 +6762,10 @@
         <v>19</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>830</v>
+        <v>822</v>
       </c>
     </row>
     <row r="51">
@@ -6830,10 +6773,10 @@
         <v>19</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>832</v>
+        <v>824</v>
       </c>
     </row>
     <row r="52">
@@ -6844,7 +6787,7 @@
         <v>233</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>833</v>
+        <v>825</v>
       </c>
     </row>
     <row r="53">
@@ -6855,7 +6798,7 @@
         <v>462</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>834</v>
+        <v>826</v>
       </c>
     </row>
     <row r="54">
@@ -6863,10 +6806,10 @@
         <v>19</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>836</v>
+        <v>828</v>
       </c>
     </row>
     <row r="55">
@@ -6874,10 +6817,10 @@
         <v>19</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>838</v>
+        <v>830</v>
       </c>
     </row>
     <row r="56">
@@ -6885,10 +6828,10 @@
         <v>19</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>840</v>
+        <v>832</v>
       </c>
     </row>
     <row r="57">
@@ -6896,10 +6839,10 @@
         <v>19</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>842</v>
+        <v>834</v>
       </c>
     </row>
     <row r="58">
@@ -6907,10 +6850,10 @@
         <v>19</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="59">
@@ -6918,10 +6861,10 @@
         <v>19</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>845</v>
+        <v>837</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>846</v>
+        <v>838</v>
       </c>
     </row>
     <row r="60">
@@ -6929,10 +6872,10 @@
         <v>19</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>848</v>
+        <v>840</v>
       </c>
     </row>
     <row r="61">
@@ -6940,10 +6883,10 @@
         <v>19</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>850</v>
+        <v>842</v>
       </c>
     </row>
     <row r="62">
@@ -6951,10 +6894,10 @@
         <v>19</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>851</v>
+        <v>843</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>852</v>
+        <v>844</v>
       </c>
     </row>
     <row r="63">
@@ -6962,10 +6905,10 @@
         <v>19</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>853</v>
+        <v>845</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>854</v>
+        <v>846</v>
       </c>
     </row>
     <row r="64">
@@ -6976,7 +6919,7 @@
         <v>550</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>855</v>
+        <v>847</v>
       </c>
     </row>
     <row r="65">
@@ -6992,7 +6935,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>856</v>
+        <v>848</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>19</v>
@@ -7006,10 +6949,10 @@
         <v>19</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>857</v>
+        <v>849</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>858</v>
+        <v>850</v>
       </c>
     </row>
     <row r="68">
@@ -7017,10 +6960,10 @@
         <v>19</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>859</v>
+        <v>851</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>860</v>
+        <v>852</v>
       </c>
     </row>
     <row r="69">
@@ -7028,10 +6971,10 @@
         <v>19</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>862</v>
+        <v>854</v>
       </c>
     </row>
     <row r="70">
@@ -7039,10 +6982,10 @@
         <v>19</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>864</v>
+        <v>856</v>
       </c>
     </row>
     <row r="71">
@@ -7050,10 +6993,10 @@
         <v>19</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>865</v>
+        <v>857</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>866</v>
+        <v>858</v>
       </c>
     </row>
     <row r="72">
@@ -7061,10 +7004,10 @@
         <v>19</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>868</v>
+        <v>860</v>
       </c>
     </row>
     <row r="73">
@@ -7072,10 +7015,10 @@
         <v>19</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>870</v>
+        <v>862</v>
       </c>
     </row>
     <row r="74">
@@ -7083,10 +7026,10 @@
         <v>19</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>871</v>
+        <v>863</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>872</v>
+        <v>864</v>
       </c>
     </row>
     <row r="75">
@@ -7094,10 +7037,10 @@
         <v>19</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>874</v>
+        <v>866</v>
       </c>
     </row>
     <row r="76">
@@ -7105,10 +7048,10 @@
         <v>19</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>876</v>
+        <v>868</v>
       </c>
     </row>
     <row r="77">
@@ -7116,10 +7059,10 @@
         <v>19</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>878</v>
+        <v>870</v>
       </c>
     </row>
     <row r="78">
@@ -7127,10 +7070,10 @@
         <v>19</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>879</v>
+        <v>871</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>880</v>
+        <v>872</v>
       </c>
     </row>
     <row r="79">
@@ -7138,10 +7081,10 @@
         <v>19</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>882</v>
+        <v>874</v>
       </c>
     </row>
     <row r="80">
@@ -7149,10 +7092,10 @@
         <v>19</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>884</v>
+        <v>876</v>
       </c>
     </row>
   </sheetData>
@@ -7167,43 +7110,43 @@
         <v>0</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>885</v>
+        <v>877</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>886</v>
+        <v>878</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>693</v>
+        <v>685</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>888</v>
+        <v>880</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>700</v>
+        <v>692</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>705</v>
+        <v>697</v>
       </c>
     </row>
   </sheetData>
@@ -7227,58 +7170,58 @@
         <v>4</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>890</v>
+        <v>882</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>695</v>
+        <v>687</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>695</v>
+        <v>687</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>706</v>
+        <v>698</v>
       </c>
     </row>
   </sheetData>
